--- a/products_snapshot.xlsx
+++ b/products_snapshot.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K181"/>
+  <dimension ref="A1:K195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -705,7 +705,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PLK-COLOR-RADIANCE-PRD-NA-C000</t>
+          <t>PLK-COLOR-RADIANCE-PRD-NA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PLK-COLOR-RADIANCE-PRD-NA</t>
+          <t>PLK-COLOR-RADIANCE-PRD-NA-4FA4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1883,7 +1883,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1936,7 +1936,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -7627,22 +7627,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>KAD-PROFESSI-DEEP-CON-250ML</t>
+          <t>DAV-APSAUGIN-SKYSTIS-PRD-NA</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE LEAVE-IN purÅ¡kiamas kondicionierius, 250 ml</t>
+          <t>DAVINES APSAUGINIS SKYSTIS PLAUKAMS PH: 4 | MELU</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Kadus</t>
+          <t>Davines</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-moisture-leave-in-purskiamas-kondicionierius-250-ml</t>
+          <t>https://plaukuosena.lt/apsauginis-skystis-plaukams-ph-4-or-melu</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/812ff0d8-83cf-4ae5-b03e-7ae58b54d4b3.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/958d66cb-6795-4885-88d2-e4748c0b2e4f.webp</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7670,11 +7670,7 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7684,22 +7680,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>KAD-PROFESSI-DEEP-CON-NA</t>
+          <t>DAV-BLIZGESY-APSAUGA-PRD-NA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE kondicionierius</t>
+          <t>DAVINES Blizgesys ir apsauga Å¡viesiems plaukams | Heart of Glass</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Kadus</t>
+          <t>Davines</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -7709,12 +7705,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-moisture-kondicionierius</t>
+          <t>https://plaukuosena.lt/blizgesys-ir-apsauga-sviesiems-plaukams-or-heart-of-glass</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/11e9244b-f1b4-4fd1-a829-d04264f37221.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/75106ebc-f23c-459b-aebd-1f78c58b78e0.png</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7737,22 +7733,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>KAD-PROFESSI-DEEP-PRD-NA</t>
+          <t>DAV-GEROS-SAVIJAUT-PRD-NA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE Å¡ampÅ«nas</t>
+          <t>DAVINES GEROS SAVIJAUTOS Å AMPÅªNAS PH: 5.5 | WELLâBEING</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Kadus</t>
+          <t>Davines</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>17.90</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7762,12 +7758,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-moisture-sampunas</t>
+          <t>https://plaukuosena.lt/geros-savijautos-sampunas-ph-55-or-well-being</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0f57fac1-e330-41e0-aa79-c1ef82ad3610.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7510575f-99a2-4412-9ed4-4950f2f034fc.webp</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -7790,33 +7786,37 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>KAD-PROFESSI-PLAUKA3-PRD-NA</t>
+          <t>DAV-GREITAI-PLAUKUS-PRD-NA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Kadus Professional plaukÅ³ priemonÄs | Kadus kosmetika â plaukuosena.lt</t>
+          <t>DAVINES GREITAI PLAUKUS ATKURIANTI KAUKÄ | THE QUICK FIX CIRCLE</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Kadus</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
+          <t>Davines</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/kadus-professional-plauku-priemones</t>
+          <t>https://plaukuosena.lt/greitai-plaukus-atkurianti-kauke-or-the-quick-fix-circle</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/333ee115-9451-4bf1-b2b6-62c9b9b773df.png</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -7832,29 +7832,29 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MSK-NO-FRIZZ-PRD-NA</t>
+          <t>DAV-DAA1-2YT-PH-CON-NA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING LIGHT MILK blizgesio ir glotnumo suteikiantis pienelis ploniems plaukams</t>
+          <t>DAVINES KONDICIONIERIUS DAÅ½YTIEMS PLAUKAMS PH: 4 | MINU</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Milk Shake</t>
+          <t>Davines</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>21.60</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-light-milk-blizgesio-ir-glotnumo-suteikiantis-pienelis-ploniems-plaukams</t>
+          <t>https://plaukuosena.lt/kondicionierius-dazytiems-plaukams-ph-4-or-minu</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/05f9a283-0d68-4cbc-8b2b-a9319726c645.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7ec299ab-4d5e-4428-8acb-1d7b2e351dc6.webp</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -7892,22 +7892,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MSK-NO-FRIZZ-SER-NA</t>
+          <t>DAV-PAA1-2EI-PH-CON-NA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING RICH SERUM blizgesio ir glotnumo suteikiantis serumas storiems plaukams</t>
+          <t>DAVINES KONDICIONIERIUS PAÅ½EISTIEMS PLAUKAMS PH: 4 | MELU</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Milk Shake</t>
+          <t>Davines</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-rich-serum-blizgesio-ir-glotnumo-suteikiantis-serumas-storiems-plaukams</t>
+          <t>https://plaukuosena.lt/kondicionierius-pazeistiems-plaukams-ph-4-or-melu</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ffc04fa-0925-48a2-86df-62a08a127ee1.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/27c868d9-4d9f-41dd-b2d1-57259b7ee377.webp</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7945,22 +7945,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MSK-NO-FRIZZ-SPR-NA</t>
+          <t>DAV-TIESINAN-A-PRD-NA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MILK SHAKE NO FRIZZ AMAZING ANTI-HUMIDITY SPRAY apsauginis purÅ¡kiklis garbanotiems plaukams</t>
+          <t>DAVINES TIESINANTIS Å AMPÅªNAS PH: 5.3 | LOVE</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Milk Shake</t>
+          <t>Davines</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/amazing-anti-humidity-spray-apsauginis-purskiklis-garbanotiems-plaukams</t>
+          <t>https://plaukuosena.lt/tiesinantis-sampunas-ph-53-or-love</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ce022c83-2021-4842-9c57-7e44d680edec.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7691e5f8-be0d-4245-88b7-bade815e0174.webp</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7998,33 +7998,37 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MSK-PLAUKA3-PRIEA3-4-PRD-NA</t>
+          <t>DAV-VALANTIS-A-PRD-NA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Milk Shake plaukÅ³ prieÅ¾iÅ«ros priemonÄs | Milk Shake kosmetika â plaukuosena.lt</t>
+          <t>DAVINES VALANTIS Å AMPÅªNAS NUO PLEISKANÅ² PH: 4.9 | PURIFYING</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Milk Shake</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>Davines</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/milk-shake-plauku-prieziuros-priemones</t>
+          <t>https://plaukuosena.lt/valantis-sampunas-nuo-pleiskanu-ph-49-or-purifying</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d4d74325-9146-4a5a-9026-794f20ec97be.webp</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -8040,29 +8044,29 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>OLX-NO-3-PRD-NA</t>
+          <t>DAV-A-AMPAANAS-PRD-NA-E1B3</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 3 HAIR PERFECTOR</t>
+          <t>DAVINES Å AMPÅªNAS DAÅ½YTIEMS PLAUKAMS PH: 5.3 | MINU</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Olaplex</t>
+          <t>Davines</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8072,12 +8076,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-3-hair-perfector</t>
+          <t>https://plaukuosena.lt/sampunas-dazytiems-plaukams-ph-53-or-minu</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1832e17d-37c2-4f27-9dbf-03c1c80d368a.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6a542969-9c0b-4be9-8aba-c7a8bd9ade42.webp</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -8100,22 +8104,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>OLX-NO-4-SHA-NA</t>
+          <t>DAV-A-AMPAANAS-PRD-NA-5E04</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 4 BOND MAINTENANCE SHAMPOO</t>
+          <t>DAVINES Å AMPÅªNAS GARBANUOTIEMS PLAUKAMS PH: 5.3 | LOVE CURL</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Olaplex</t>
+          <t>Davines</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8125,12 +8129,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-4-bond-maintenance-shampoo</t>
+          <t>https://plaukuosena.lt/davines-sampunas-garbanuotiems-plaukams-ph-53-or-love-curl</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2f17f7df-64a9-44b0-8d0d-7beb0d421ee2.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/abd9f475-8e18-4122-854e-e9807ba878f6.webp</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -8153,22 +8157,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OLX-NO-4D-SHA-NA</t>
+          <t>DAV-A-AMPAANAS-PRD-NA-2479</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 4D Dry Shampoo</t>
+          <t>DAVINES Å AMPÅªNAS PAÅ½EISTIEMS PLAUKAMS PH: 5.3 | MELU</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Olaplex</t>
+          <t>Davines</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8178,12 +8182,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-4d-dry-shampoo</t>
+          <t>https://plaukuosena.lt/sampunas-pazeistiems-plaukams-ph-53-or-melu</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4b16b116-5392-4248-beaf-e788b5b65f8c.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9e665e1f-46f0-43ad-a545-d89ee5dbd7d5.webp</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -8206,22 +8210,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>OLX-NO-5-CON-NA</t>
+          <t>DAV-A-AMPAANAS-PRD-NA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 5 BOND MAINTENANCE CONDITIONER</t>
+          <t>DAVINES Å AMPÅªNAS PLAUKÅ² GAUSINIMUI PH: 5.3 | VOLU</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Olaplex</t>
+          <t>Davines</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8231,12 +8235,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-5-bond-maintenance-conditioner</t>
+          <t>https://plaukuosena.lt/sampunas-plauku-gausinimui-ph-53-or-volu</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/17784e89-7411-4bd4-8b97-58350ae502d8.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a13b2f02-8b1b-4288-9602-b6b3af8b7c0a.webp</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8259,22 +8263,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OLX-NO-6-PRD-NA</t>
+          <t>DAV-A-VIESIUS-CON-100ML</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 6 BOND SMOOTHER</t>
+          <t>DAVINES Å viesius plaukus maitinantis kondicionierius | Heart of Glass</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Olaplex</t>
+          <t>Davines</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8284,12 +8288,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-6-bond-smoother</t>
+          <t>https://plaukuosena.lt/hand-soap-giguos</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39301ecc-75fd-4fca-9e6a-0af9debc2e46.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/729b8d37-dea5-416e-a920-52cc0231c3bb.png</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -8302,7 +8306,11 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8312,22 +8320,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>OLX-NO-0-INTENSIV-PRD-NA</t>
+          <t>DAV-A-VIESIUS-PRD-NA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>OLAPLEX No.0 INTENSIVE BOND BUILDING HAIR TREATMENT</t>
+          <t>DAVINES Å viesius plaukus stiprinanti kaukÄ | Heart of Glass</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Olaplex</t>
+          <t>Davines</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8337,12 +8345,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no0-intensive-bond-building-hair-treatment</t>
+          <t>https://plaukuosena.lt/sviesius-plaukus-stiprinanti-kauke-or-heart-of-glass</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d72c34ad-0dbf-4c23-af6a-9e6dbc63c38e.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7062fec7-9648-4348-95e4-b6109a41426c.webp</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -8365,22 +8373,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OLX-NO-3-PLUS-PRD-NA</t>
+          <t>KAD-PROFESSI-DEEP-CON-250ML</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>OLAPLEX No.3 PLUS Ultimate Repair Treatment</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE LEAVE-IN purÅ¡kiamas kondicionierius, 250 ml</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Olaplex</t>
+          <t>Kadus</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8390,12 +8398,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no3-plus-ultimate-repair-treatment</t>
+          <t>https://plaukuosena.lt/deep-moisture-leave-in-purskiamas-kondicionierius-250-ml</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39908a67-c29d-4092-ad0e-d3b12c4c285f.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/812ff0d8-83cf-4ae5-b03e-7ae58b54d4b3.jpg</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -8408,7 +8416,11 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8418,22 +8430,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>OLX-NO-4C-BOND-SHA-NA</t>
+          <t>KAD-PROFESSI-DEEP-CON-NA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>OLAPLEX No.4C BOND MAINTENANCE CLARIFYING SHAMPOO</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE kondicionierius</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Olaplex</t>
+          <t>Kadus</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -8443,12 +8455,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no4c-bond-maintenance-clarifying-shampoo</t>
+          <t>https://plaukuosena.lt/deep-moisture-kondicionierius</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/15aa41ad-b5ee-455b-82fe-67dd4515079d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/11e9244b-f1b4-4fd1-a829-d04264f37221.jpg</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8471,22 +8483,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OLX-NO-5-LEAVE-IN-PRD-NA</t>
+          <t>KAD-PROFESSI-DEEP-PRD-NA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>OLAPLEX No.5 LEAVE-IN Moisturize</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE Å¡ampÅ«nas</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Olaplex</t>
+          <t>Kadus</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>17.90</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -8496,12 +8508,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no5-leave-in-moisturize</t>
+          <t>https://plaukuosena.lt/deep-moisture-sampunas</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e18890ee-ba6f-43ff-a518-fce468bdc091.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0f57fac1-e330-41e0-aa79-c1ef82ad3610.jpg</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -8524,37 +8536,33 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OLX-NO-5P-BLOND-CON-NA</t>
+          <t>KAD-PROFESSI-PLAUKA3-PRD-NA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>OLAPLEX No.5P BLOND ENHANCER TONING CONDITIONER</t>
+          <t>Kadus Professional plaukÅ³ priemonÄs | Kadus kosmetika â plaukuosena.lt</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Olaplex</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>34.00</t>
-        </is>
-      </c>
+          <t>Kadus</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no5p-blond-enhancer-toning-conditioner</t>
+          <t>https://plaukuosena.lt/kadus-professional-plauku-priemones</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/35185d43-ba29-4be4-bd01-153f53e9628a.jpg</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -8570,29 +8578,29 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OLX-NO-7-BONDING-OIL-NA</t>
+          <t>MSK-NO-FRIZZ-PRD-NA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>OLAPLEX No.7 BONDING OIL</t>
+          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING LIGHT MILK blizgesio ir glotnumo suteikiantis pienelis ploniems plaukams</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Olaplex</t>
+          <t>Milk Shake</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>21.60</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -8602,12 +8610,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no7-bonding-oil</t>
+          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-light-milk-blizgesio-ir-glotnumo-suteikiantis-pienelis-ploniems-plaukams</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8f444685-5686-42dd-b4a9-73afbcfb889f.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/05f9a283-0d68-4cbc-8b2b-a9319726c645.png</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -8630,22 +8638,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OLX-NO-8-BOND-MSK-NA</t>
+          <t>MSK-NO-FRIZZ-SER-NA</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>OLAPLEX No.8 BOND INTENSE MOISTURE MASK</t>
+          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING RICH SERUM blizgesio ir glotnumo suteikiantis serumas storiems plaukams</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Olaplex</t>
+          <t>Milk Shake</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -8655,12 +8663,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no8-bond-intense-moisture-mask</t>
+          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-rich-serum-blizgesio-ir-glotnumo-suteikiantis-serumas-storiems-plaukams</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/552d57ab-d055-4c8c-9603-b292e1a25e64.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ffc04fa-0925-48a2-86df-62a08a127ee1.png</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -8683,22 +8691,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>OLX-NO-9-BOND-SER-NA</t>
+          <t>MSK-NO-FRIZZ-SPR-NA</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>OLAPLEX No.9 BOND PROTECTOR NOURISHING HAIR SERUM</t>
+          <t>MILK SHAKE NO FRIZZ AMAZING ANTI-HUMIDITY SPRAY apsauginis purÅ¡kiklis garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Olaplex</t>
+          <t>Milk Shake</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -8708,12 +8716,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no9-bond-protector-nourishing-hair-serum</t>
+          <t>https://plaukuosena.lt/amazing-anti-humidity-spray-apsauginis-purskiklis-garbanotiems-plaukams</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e7ab9fdc-43dc-45c3-914c-fa13f791dc3d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ce022c83-2021-4842-9c57-7e44d680edec.png</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -8736,37 +8744,33 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>OLX-VOLUMIZI-BLOW-PRD-NA</t>
+          <t>MSK-PLAUKA3-PRIEA3-4-PRD-NA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>OLAPLEX Volumizing Blow Dry Mist</t>
+          <t>Milk Shake plaukÅ³ prieÅ¾iÅ«ros priemonÄs | Milk Shake kosmetika â plaukuosena.lt</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Olaplex</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>32.00</t>
-        </is>
-      </c>
+          <t>Milk Shake</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-volumizing-blow-dry-mist</t>
+          <t>https://plaukuosena.lt/milk-shake-plauku-prieziuros-priemones</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/87bf6622-3275-425b-8a73-1bb008b61716.jpg</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8782,19 +8786,19 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>OLX-PLAUKA3-PRIEA3-4-PRD-NA</t>
+          <t>OLX-NO-3-PRD-NA</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Olaplex plaukÅ³ prieÅ¾iÅ«ros priemonÄs | Olaplex produktai â plaukuosena.lt</t>
+          <t>OLAPLEX No. 3 HAIR PERFECTOR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8802,20 +8806,24 @@
           <t>Olaplex</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>34.00</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-plauku-prieziuros-priemones</t>
+          <t>https://plaukuosena.lt/olaplex-no-3-hair-perfector</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1832e17d-37c2-4f27-9dbf-03c1c80d368a.png</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8831,29 +8839,29 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>QIQ-BARE-REPAIR-OIL-NA</t>
+          <t>OLX-NO-4-SHA-NA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>QIQI Bare Repair Oil PlaukÅ³ aliejus</t>
+          <t>OLAPLEX No. 4 BOND MAINTENANCE SHAMPOO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Qiqi</t>
+          <t>Olaplex</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>54.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8863,12 +8871,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-bare-repair-oil-plauku-aliejus</t>
+          <t>https://plaukuosena.lt/olaplex-no-4-bond-maintenance-shampoo</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/85f599b6-1ab5-4fe0-9330-8b393efc56d2.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2f17f7df-64a9-44b0-8d0d-7beb0d421ee2.png</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -8891,22 +8899,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>QIQ-GLOTNINA-A-AMPA-N-PRD-NA</t>
+          <t>OLX-NO-4D-SHA-NA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>QIQI Glotninantis Å¡ampÅ«nas</t>
+          <t>OLAPLEX No. 4D Dry Shampoo</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Qiqi</t>
+          <t>Olaplex</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8916,12 +8924,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-glotninantis-sampunas</t>
+          <t>https://plaukuosena.lt/olaplex-no-4d-dry-shampoo</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9ad34b38-7896-457c-8d2e-598db9e7336d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4b16b116-5392-4248-beaf-e788b5b65f8c.png</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -8944,22 +8952,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>QIQ-POROSITY-PLAY-SPR-NA</t>
+          <t>OLX-NO-5-CON-NA</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>QIQI Porosity Play Spray PlaukÅ³ purÅ¡kiklis</t>
+          <t>OLAPLEX No. 5 BOND MAINTENANCE CONDITIONER</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Qiqi</t>
+          <t>Olaplex</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>54.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8969,12 +8977,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-porosity-play-spray-plauku-purskiklis</t>
+          <t>https://plaukuosena.lt/olaplex-no-5-bond-maintenance-conditioner</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c272a239-cd7a-422f-a950-d80d709d9259.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/17784e89-7411-4bd4-8b97-58350ae502d8.png</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -8997,22 +9005,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>QIQ-POROSITY-VOLUME-PRD-NA</t>
+          <t>OLX-NO-6-PRD-NA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>QIQI Porosity Volume Code Mist Gausos apimties suteikianti dulksna</t>
+          <t>OLAPLEX No. 6 BOND SMOOTHER</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Qiqi</t>
+          <t>Olaplex</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>54.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9022,12 +9030,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-porosity-volume-code-mist-gausos-apimties-suteikianti-dulksna</t>
+          <t>https://plaukuosena.lt/olaplex-no-6-bond-smoother</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40938472-383c-4c92-9b8b-040403000e9d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39301ecc-75fd-4fca-9e6a-0af9debc2e46.png</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -9050,22 +9058,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>QIQ-SUPER-SOAKER-PRD-NA</t>
+          <t>OLX-NO-0-INTENSIV-PRD-NA</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>QIQI Super Soaker Smoothing Masque Glotninanti plaukÅ³ kaukÄ</t>
+          <t>OLAPLEX No.0 INTENSIVE BOND BUILDING HAIR TREATMENT</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Qiqi</t>
+          <t>Olaplex</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9075,12 +9083,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-super-soaker-smoothing-masque-glotninanti-plauku-kauke</t>
+          <t>https://plaukuosena.lt/olaplex-no0-intensive-bond-building-hair-treatment</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c207ccff-61fd-499a-9db4-0ed63a8c34c7.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d72c34ad-0dbf-4c23-af6a-9e6dbc63c38e.png</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -9103,22 +9111,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>QIQ-DRA-KINA-CON-NA</t>
+          <t>OLX-NO-3-PLUS-PRD-NA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>QIQI drÄkinamasis kondicionierius</t>
+          <t>OLAPLEX No.3 PLUS Ultimate Repair Treatment</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Qiqi</t>
+          <t>Olaplex</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9128,12 +9136,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-drekinamasis-kondicionierius</t>
+          <t>https://plaukuosena.lt/olaplex-no3-plus-ultimate-repair-treatment</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e9113e8b-f95c-4cb6-ab03-9977a03ffcd1.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39908a67-c29d-4092-ad0e-d3b12c4c285f.png</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -9156,22 +9164,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>QIQ-ALL-OUT-CRM-NA</t>
+          <t>OLX-NO-4C-BOND-SHA-NA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Qiqi All Out Blowout uÅ¾baigimo kremas</t>
+          <t>OLAPLEX No.4C BOND MAINTENANCE CLARIFYING SHAMPOO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Qiqi</t>
+          <t>Olaplex</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>54.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9181,12 +9189,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-all-out-blowout-uzbaigimo-kremas</t>
+          <t>https://plaukuosena.lt/olaplex-no4c-bond-maintenance-clarifying-shampoo</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ed4db76-21f3-4ce0-a884-2230c7418f53.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/15aa41ad-b5ee-455b-82fe-67dd4515079d.png</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -9209,33 +9217,37 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>QIQ-PLAUKA3-PRIEA3-4-PRD-NA</t>
+          <t>OLX-NO-5-LEAVE-IN-PRD-NA</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Qiqi plaukÅ³ prieÅ¾iÅ«ros priemonÄs | Qiqi kosmetika â plaukuosena.lt</t>
+          <t>OLAPLEX No.5 LEAVE-IN Moisturize</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Qiqi</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
+          <t>Olaplex</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>34.00</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-plauku-prieziuros-priemones</t>
+          <t>https://plaukuosena.lt/olaplex-no5-leave-in-moisturize</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e18890ee-ba6f-43ff-a518-fce468bdc091.png</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -9251,29 +9263,29 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>WEL-FUSION-INTENSE-PRD-NA</t>
+          <t>OLX-NO-5P-BLOND-CON-NA</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS FUSION Intense Repair atkurianti kaukÄ</t>
+          <t>OLAPLEX No.5P BLOND ENHANCER TONING CONDITIONER</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wella Professionals</t>
+          <t>Olaplex</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -9283,12 +9295,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/fusion-intense-repair-atkurianti-kauke</t>
+          <t>https://plaukuosena.lt/olaplex-no5p-blond-enhancer-toning-conditioner</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/49ba0f2c-4336-4e46-8e4e-5997a332dd4b.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/35185d43-ba29-4be4-bd01-153f53e9628a.jpg</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -9311,22 +9323,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>WEL-INVIGO-SCALP-PRD-150ML</t>
+          <t>OLX-NO-7-BONDING-OIL-NA</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminanti bekvapÄ kaukÄ jautriai galvos odai, 150 ml</t>
+          <t>OLAPLEX No.7 BONDING OIL</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Wella Professionals</t>
+          <t>Olaplex</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -9336,12 +9348,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-scalp-balance-raminanti-bekvape-kauke-jautriai-galvos-odai-150-ml</t>
+          <t>https://plaukuosena.lt/olaplex-no7-bonding-oil</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c54a7db1-876d-428e-bb1c-2163064b83e8.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8f444685-5686-42dd-b4a9-73afbcfb889f.png</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -9354,11 +9366,7 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>150ml</t>
-        </is>
-      </c>
+      <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9368,22 +9376,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>WEL-INVIGO-SCALP-PRD-300ML</t>
+          <t>OLX-NO-8-BOND-MSK-NA</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminantis bekvapis Å¡ampÅ«nas jautriai galvos odai, 300 ml</t>
+          <t>OLAPLEX No.8 BOND INTENSE MOISTURE MASK</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Wella Professionals</t>
+          <t>Olaplex</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -9393,12 +9401,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-scalp-balance-raminantis-bekvapis-sampunas-jautriai-galvos-odai-300-ml</t>
+          <t>https://plaukuosena.lt/olaplex-no8-bond-intense-moisture-mask</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1cb4e319-989b-4b53-97f4-6c8d6f9956f4.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/552d57ab-d055-4c8c-9603-b292e1a25e64.png</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -9411,11 +9419,7 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>300ml</t>
-        </is>
-      </c>
+      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9425,22 +9429,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>WEL-INVIGO-SCALP-PRD-300ML-496F</t>
+          <t>OLX-NO-9-BOND-SER-NA</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE Å¡ampÅ«nas nuo pleiskanÅ³, 300 ml</t>
+          <t>OLAPLEX No.9 BOND PROTECTOR NOURISHING HAIR SERUM</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wella Professionals</t>
+          <t>Olaplex</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -9450,12 +9454,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-scalp-balance-sampunas-nuo-pleiskanu-300-ml</t>
+          <t>https://plaukuosena.lt/olaplex-no9-bond-protector-nourishing-hair-serum</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a577bacb-27b2-4dca-bf06-bf92b1ae30c6.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e7ab9fdc-43dc-45c3-914c-fa13f791dc3d.png</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -9468,11 +9472,7 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>300ml</t>
-        </is>
-      </c>
+      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9482,17 +9482,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>WEL-ULTIMATE-COLOR-CON-NA</t>
+          <t>OLX-VOLUMIZI-BLOW-PRD-NA</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE COLOR Conditioner â DrÄkinantis daÅ¾ytÅ³ plaukÅ³ kondicionierius STEP 2</t>
+          <t>OLAPLEX Volumizing Blow Dry Mist</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Wella Professionals</t>
+          <t>Olaplex</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-color-conditioner-drekinantis-dazytu-plauku-kondicionierius-step-2</t>
+          <t>https://plaukuosena.lt/olaplex-volumizing-blow-dry-mist</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bfeffc09-2cb6-4be4-aeec-026917a81c39.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/87bf6622-3275-425b-8a73-1bb008b61716.jpg</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -9535,37 +9535,33 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>WEL-ULTIMATE-COLOR-SHA-NA</t>
+          <t>OLX-PLAUKA3-PRIEA3-4-PRD-NA</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE COLOR Shampoo â DaÅ¾ytÅ³ plaukÅ³ Å¡ampÅ«nas be sulfatÅ³ STEP 1</t>
+          <t>Olaplex plaukÅ³ prieÅ¾iÅ«ros priemonÄs | Olaplex produktai â plaukuosena.lt</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Wella Professionals</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
-      </c>
+          <t>Olaplex</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-color-shampoo-dazytu-plauku-sampunas-be-sulfatu-step-1</t>
+          <t>https://plaukuosena.lt/olaplex-plauku-prieziuros-priemones</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/09df21fa-1581-431d-aba4-e172187f1cff.jpg</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -9581,29 +9577,29 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>WEL-ULTIMATE-SMOOTH-CON-NA</t>
+          <t>QIQ-BARE-REPAIR-OIL-NA</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE SMOOTH maitinantis kondicionierius su skvalanu ir omega-9</t>
+          <t>QIQI Bare Repair Oil PlaukÅ³ aliejus</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Wella Professionals</t>
+          <t>Qiqi</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>54.00</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -9613,12 +9609,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-smooth-maitinantis-kondicionierius-su-skvalanu-ir-omega-9</t>
+          <t>https://plaukuosena.lt/qiqi-bare-repair-oil-plauku-aliejus</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/485269d4-f20c-4f8d-a9be-437f4b0aa81e.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/85f599b6-1ab5-4fe0-9330-8b393efc56d2.png</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -9641,22 +9637,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>WEL-ULTIMATE-SMOOTH-SER-NA</t>
+          <t>QIQ-GLOTNINA-A-AMPA-N-PRD-NA</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE SMOOTH miracle aliejinis serumas skvalanu ir omega-9</t>
+          <t>QIQI Glotninantis Å¡ampÅ«nas</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Wella Professionals</t>
+          <t>Qiqi</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -9666,12 +9662,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-smooth-miracle-aliejinis-serumas-skvalanu-ir-omega-9</t>
+          <t>https://plaukuosena.lt/qiqi-glotninantis-sampunas</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/518f9af2-8fc1-4590-932e-eaa87cdb3ac6.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9ad34b38-7896-457c-8d2e-598db9e7336d.png</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -9694,22 +9690,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>WEL-FUSION-ATSTATOM-PRD-NA</t>
+          <t>QIQ-POROSITY-PLAY-SPR-NA</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Wella Professionals FUSION atstatomasis Å¡ampÅ«nas</t>
+          <t>QIQI Porosity Play Spray PlaukÅ³ purÅ¡kiklis</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Wella Professionals</t>
+          <t>Qiqi</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>54.00</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -9719,12 +9715,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/loreal-professionnel-metal-detox-sampunas</t>
+          <t>https://plaukuosena.lt/qiqi-porosity-play-spray-plauku-purskiklis</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ed6894bd-b132-4cb6-9a8a-0a4f96b07eac.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c272a239-cd7a-422f-a950-d80d709d9259.png</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -9747,22 +9743,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>WEL-ULTIMATE-SMOOTH-PRD-NA</t>
+          <t>QIQ-POROSITY-VOLUME-PRD-NA</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Wella Professionals Ultimate Smooth intensyviai maitinantis Å¡ampÅ«nas</t>
+          <t>QIQI Porosity Volume Code Mist Gausos apimties suteikianti dulksna</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Wella Professionals</t>
+          <t>Qiqi</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>27.00</t>
+          <t>54.00</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -9772,12 +9768,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/wella-professionals-ultimate-smooth-intensyviai-maitinantis-sampunas</t>
+          <t>https://plaukuosena.lt/qiqi-porosity-volume-code-mist-gausos-apimties-suteikianti-dulksna</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/90552437-c3c8-46c1-ad07-2d1cbaa18300.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40938472-383c-4c92-9b8b-040403000e9d.png</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -9800,33 +9796,37 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>WEL-PLAUKA3-PRIEA3-4-PRD-NA</t>
+          <t>QIQ-SUPER-SOAKER-PRD-NA</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Wella Professionals plaukÅ³ prieÅ¾iÅ«ros priemonÄs â plaukuosena.lt</t>
+          <t>QIQI Super Soaker Smoothing Masque Glotninanti plaukÅ³ kaukÄ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Wella Professionals</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>Qiqi</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/wella-professionals-plauku-prieziuros-priemones</t>
+          <t>https://plaukuosena.lt/qiqi-super-soaker-smoothing-masque-glotninanti-plauku-kauke</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c207ccff-61fd-499a-9db4-0ed63a8c34c7.png</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -9841,6 +9841,752 @@
       </c>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>QIQ-DRA-KINA-CON-NA</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>QIQI drÄkinamasis kondicionierius</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Qiqi</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/qiqi-drekinamasis-kondicionierius</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e9113e8b-f95c-4cb6-ab03-9977a03ffcd1.png</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>American Crew</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>QIQ-ALL-OUT-CRM-NA</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Qiqi All Out Blowout uÅ¾baigimo kremas</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Qiqi</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>54.00</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/qiqi-all-out-blowout-uzbaigimo-kremas</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ed4db76-21f3-4ce0-a884-2230c7418f53.png</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>American Crew</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>QIQ-PLAUKA3-PRIEA3-4-PRD-NA</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Qiqi plaukÅ³ prieÅ¾iÅ«ros priemonÄs | Qiqi kosmetika â plaukuosena.lt</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Qiqi</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/qiqi-plauku-prieziuros-priemones</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>American Crew</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>CHECK_PRICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>WEL-FUSION-INTENSE-PRD-NA</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>WELLA PROFESSIONALS FUSION Intense Repair atkurianti kaukÄ</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Wella Professionals</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/fusion-intense-repair-atkurianti-kauke</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/49ba0f2c-4336-4e46-8e4e-5997a332dd4b.jpg</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>American Crew</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>WEL-INVIGO-SCALP-PRD-150ML</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminanti bekvapÄ kaukÄ jautriai galvos odai, 150 ml</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Wella Professionals</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/invigo-scalp-balance-raminanti-bekvape-kauke-jautriai-galvos-odai-150-ml</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2afb2854-6bd1-40cf-8cdc-974055d4e6d7.jpg</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>American Crew</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>WEL-INVIGO-SCALP-PRD-300ML</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminantis bekvapis Å¡ampÅ«nas jautriai galvos odai, 300 ml |1000 ml</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Wella Professionals</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/invigo-scalp-balance-raminantis-bekvapis-sampunas-jautriai-galvos-odai-300-ml</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d760b01d-97b7-44c5-a495-8a1f29726f57.jpg</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>American Crew</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>WEL-INVIGO-SCALP-PRD-300ML-496F</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE Å¡ampÅ«nas nuo pleiskanÅ³, 300 ml</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Wella Professionals</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/invigo-scalp-balance-sampunas-nuo-pleiskanu-300-ml</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8da87958-5134-4d18-936e-4df20ffc120b.jpg</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>American Crew</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>WEL-ULTIMATE-COLOR-CON-NA</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>WELLA PROFESSIONALS ULTIMATE COLOR Conditioner â DrÄkinantis daÅ¾ytÅ³ plaukÅ³ kondicionierius STEP 2</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Wella Professionals</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/ultimate-color-conditioner-drekinantis-dazytu-plauku-kondicionierius-step-2</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bfeffc09-2cb6-4be4-aeec-026917a81c39.jpg</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>American Crew</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>WEL-ULTIMATE-COLOR-SHA-NA</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>WELLA PROFESSIONALS ULTIMATE COLOR Shampoo â DaÅ¾ytÅ³ plaukÅ³ Å¡ampÅ«nas be sulfatÅ³ STEP 1</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Wella Professionals</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/ultimate-color-shampoo-dazytu-plauku-sampunas-be-sulfatu-step-1</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/09df21fa-1581-431d-aba4-e172187f1cff.jpg</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>American Crew</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>WEL-ULTIMATE-SMOOTH-CON-NA</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>WELLA PROFESSIONALS ULTIMATE SMOOTH maitinantis kondicionierius su skvalanu ir omega-9</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Wella Professionals</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>29.00</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/ultimate-smooth-maitinantis-kondicionierius-su-skvalanu-ir-omega-9</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/485269d4-f20c-4f8d-a9be-437f4b0aa81e.jpg</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>American Crew</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>WEL-ULTIMATE-SMOOTH-SER-NA</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>WELLA PROFESSIONALS ULTIMATE SMOOTH miracle aliejinis serumas skvalanu ir omega-9</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Wella Professionals</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/ultimate-smooth-miracle-aliejinis-serumas-skvalanu-ir-omega-9</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/518f9af2-8fc1-4590-932e-eaa87cdb3ac6.jpg</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>American Crew</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>WEL-FUSION-ATSTATOM-PRD-NA</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Wella Professionals FUSION atstatomasis Å¡ampÅ«nas</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Wella Professionals</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/loreal-professionnel-metal-detox-sampunas</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ed6894bd-b132-4cb6-9a8a-0a4f96b07eac.jpg</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>American Crew</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>WEL-ULTIMATE-SMOOTH-PRD-NA</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Wella Professionals Ultimate Smooth intensyviai maitinantis Å¡ampÅ«nas</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Wella Professionals</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>27.00</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/wella-professionals-ultimate-smooth-intensyviai-maitinantis-sampunas</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/90552437-c3c8-46c1-ad07-2d1cbaa18300.jpg</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>American Crew</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>WEL-PLAUKA3-PRIEA3-4-PRD-NA</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Wella Professionals plaukÅ³ prieÅ¾iÅ«ros priemonÄs â plaukuosena.lt</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Wella Professionals</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/wella-professionals-plauku-prieziuros-priemones</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>American Crew</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
         <is>
           <t>CHECK_PRICE</t>
         </is>

--- a/products_snapshot.xlsx
+++ b/products_snapshot.xlsx
@@ -501,12 +501,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PLK-ARGAN-DEEP-PRD-NA</t>
+          <t>PLK-ARGAN-DEEP-MSK-NA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARGAN DEEP TREATMENT kaukÄ su arganÅ³ aliejumi</t>
+          <t>ARGAN DEEP TREATMENT kaukė su arganų aliejumi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -550,12 +550,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLK-ARGAN-A-AMPA-N-SHA-NA</t>
+          <t>PLK-ARGAN-ARGANU-SHA-NA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ARGAN SHAMPOO Å¡ampÅ«nas su arganÅ³ aliejumi</t>
+          <t>ARGAN SHAMPOO šampūnas su arganų aliejumi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -599,12 +599,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLK-COLOR-FRESH-PRD-150ML</t>
+          <t>PLK-COLOR-FRESH-MSK-150ML</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>COLOR FRESH daÅ¾anti kaukÄ, 150 ml</t>
+          <t>COLOR FRESH dažanti kaukė, 150 ml</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -657,7 +657,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>COLOR RADIANCE LEAVE-IN SPRAY purÅ¡kiamas kondicionierius, 250 ml</t>
+          <t>COLOR RADIANCE LEAVE-IN SPRAY purškiamas kondicionierius, 250 ml</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -705,12 +705,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PLK-COLOR-RADIANCE-PRD-NA</t>
+          <t>PLK-COLOR-RADIANCE-MSK-NA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COLOR RADIANCE kaukÄ</t>
+          <t>COLOR RADIANCE kaukė</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -803,12 +803,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PLK-COLOR-RADIANCE-PRD-NA-4FA4</t>
+          <t>PLK-COLOR-RADIANCE-SHA-NA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>COLOR RADIANCE Å¡ampÅ«nas</t>
+          <t>COLOR RADIANCE šampūnas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -857,7 +857,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>COLOUR MAINTAINER FLOWER FRAGRANCE CONDITIONER kondicionierius daÅ¾ytiems plaukams</t>
+          <t>COLOUR MAINTAINER FLOWER FRAGRANCE CONDITIONER kondicionierius dažytiems plaukams</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COLOUR MAINTAINER FLOWER FRAGRANCE SHAMPOO Å¡ampÅ«nas daÅ¾ytiems plaukams</t>
+          <t>COLOUR MAINTAINER FLOWER FRAGRANCE SHAMPOO šampūnas dažytiems plaukams</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CURL PASSION MASK kaukÄ garbanotiems plaukams</t>
+          <t>CURL PASSION MASK kaukė garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CURL PASSION PERFECTIONIST garbanÅ³ formavimo kremas</t>
+          <t>CURL PASSION PERFECTIONIST garbanų formavimo kremas</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CURL PASSION SHAMPOO Å¡ampÅ«nas garbanotiems plaukams</t>
+          <t>CURL PASSION SHAMPOO šampūnas garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CURL PASSION SHAPER garbanotÅ³ plaukÅ³ formavimo priemonÄ</t>
+          <t>CURL PASSION SHAPER garbanotų plaukų formavimo priemonė</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEEP CONDITIONING MASK intensyvaus poveikio kaukÄ daÅ¾ytiems plaukams</t>
+          <t>DEEP CONDITIONING MASK intensyvaus poveikio kaukė dažytiems plaukams</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -1293,12 +1293,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PLK-DEEP-MOISTURE-PRD-NA</t>
+          <t>PLK-DEEP-MOISTURE-MSK-NA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEEP MOISTURE kaukÄ</t>
+          <t>DEEP MOISTURE kaukė</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1395,12 +1395,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PLK-EIMI-DRY-PRD-180ML</t>
+          <t>PLK-EIMI-DRY-SHA-180ML</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIMI Dry Me Dry sausas Å¡ampÅ«nas #1, 180 ml</t>
+          <t>EIMI Dry Me Dry sausas šampūnas #1, 180 ml</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EIMI NUTRICURLS BOOST BOUNCE 72h Å¡velnios putos garbanoms #2, 300 ml</t>
+          <t>EIMI NUTRICURLS BOOST BOUNCE 72h švelnios putos garbanoms #2, 300 ml</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EIMI Nutricurls Fresh Up purÅ¡kalas #1, 150 ml</t>
+          <t>EIMI Nutricurls Fresh Up purškalas #1, 150 ml</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EIMI Ocean Spritz purÅ¡kalas su druska #2, 150 ml</t>
+          <t>EIMI Ocean Spritz purškalas su druska #2, 150 ml</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EIMI Perfect Setting purÅ¡kiamas plaukÅ³ losjonas #2, 150 ml</t>
+          <t>EIMI Perfect Setting purškiamas plaukų losjonas #2, 150 ml</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EIMI Root Shoot purÅ¡kiamos putos #2, 200 ml</t>
+          <t>EIMI Root Shoot purškiamos putos #2, 200 ml</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EIMI SHAPE ME 48 val plaukÅ³ formÄ iÅ¡laikantis gelis #2, 150 ml</t>
+          <t>EIMI SHAPE ME 48 val plaukų formą išlaikantis gelis #2, 150 ml</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EIMI Sugar Lift purÅ¡kalas apimÄiai #3, 150 ml</t>
+          <t>EIMI Sugar Lift purškalas apimčiai #3, 150 ml</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EIMI Thermal Image purÅ¡kalas nuo karÅ¡Äio #2, 150 ml</t>
+          <t>EIMI Thermal Image purškalas nuo karščio #2, 150 ml</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GLISTENING ARGAN OIL arganÅ³ aliejus</t>
+          <t>GLISTENING ARGAN OIL arganų aliejus</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Garbanoti plaukai | PrieÅ¾iÅ«ros priemonÄs garbanotiems plaukams â plaukuosena.lt</t>
+          <t>Garbanoti plaukai | Priežiūros priemonės garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ICY BLOND CONDITIONER kondicionierius Å¡viesiems plaukams</t>
+          <t>ICY BLOND CONDITIONER kondicionierius šviesiems plaukams</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ICY BLOND SHAMPOO Å¡ampÅ«nas Å¡viesiems plaukams</t>
+          <t>ICY BLOND SHAMPOO šampūnas šviesiems plaukams</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>INSTALIGHT SHAMPOO stiprinamasis Å¡ampÅ«nas plaukams</t>
+          <t>INSTALIGHT SHAMPOO stiprinamasis šampūnas plaukams</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -2900,12 +2900,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PLK-INSTALOT-SKYSTA-PRD-NA</t>
+          <t>PLK-INSTALOT-SKYSTA-MSK-NA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INSTALOTION skysta kaukÄ plaukams</t>
+          <t>INSTALOTION skysta kaukė plaukams</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -2998,12 +2998,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PLK-INTEGRIT-LEAVE-PRD-NA</t>
+          <t>PLK-INTEGRIT-LEAVE-SPR-NA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>INTEGRITY LEAVE IN purÅ¡kiklis paÅ¾eistiems plaukams</t>
+          <t>INTEGRITY LEAVE IN purškiklis pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -3047,12 +3047,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PLK-INTEGRIT-INTENSIV-PRD-NA</t>
+          <t>PLK-INTEGRIT-INTENSIV-MSK-NA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH INTENSIVE TREATMENT stipriai maitinanti kaukÄ paÅ¾eistiems plaukams</t>
+          <t>INTEGRITY&amp;STRENGTH INTENSIVE TREATMENT stipriai maitinanti kaukė pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH NOURISHING SHAMPOO maitinantis Å¡ampÅ«nas paÅ¾eistiems plaukams</t>
+          <t>INTEGRITY&amp;STRENGTH NOURISHING SHAMPOO maitinantis šampūnas pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH REPAIRING HAIR LOTION stiprus proteinÅ³ koncentratas plaukams</t>
+          <t>INTEGRITY&amp;STRENGTH REPAIRING HAIR LOTION stiprus proteinų koncentratas plaukams</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -3243,12 +3243,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PLK-INTEGRIT-SPLIT-PRD-NA</t>
+          <t>PLK-INTEGRIT-SPLIT-SPR-NA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH SPLIT ENDS SAVIOR purÅ¡kiklis paÅ¾eistiems plaukams</t>
+          <t>INTEGRITY&amp;STRENGTH SPLIT ENDS SAVIOR purškiklis pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -3292,12 +3292,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PLK-INVIGO-BLONDE-GEL-NA</t>
+          <t>PLK-INVIGO-BLONDE-SHA-NA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>INVIGO BLONDE RECHARGE geltonÄ atspalvÄ¯ neutralizuojantis Å¡ampÅ«nas</t>
+          <t>INVIGO BLONDE RECHARGE geltoną atspalvį neutralizuojantis šampūnas</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>INVIGO BLONDE RECHARGE Å¡altÄ atspalvÄ¯ suteikiantis kondicionierius, 200 ml</t>
+          <t>INVIGO BLONDE RECHARGE šaltą atspalvį suteikiantis kondicionierius, 200 ml</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>INVIGO SCALP BALANCE serumas nuo plaukÅ³ slinkimo, 8x6ml</t>
+          <t>INVIGO SCALP BALANCE serumas nuo plaukų slinkimo, 8x6ml</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>INVIGO SUN CARE UV purÅ¡kalas apsaugantis nuo UV spinduliÅ³ su provitaminu B5, 150 ml</t>
+          <t>INVIGO SUN CARE UV purškalas apsaugantis nuo UV spindulių su provitaminu B5, 150 ml</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -3500,12 +3500,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PLK-KARA-A-I-APSAUGA-PRD-NA</t>
+          <t>PLK-KARSCIO-APSAUGA-PRD-NA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KarÅ¡Äio apsauga plaukams | Apsauga nuo karÅ¡Äio â plaukuosena.lt</t>
+          <t>Karščio apsauga plaukams | Apsauga nuo karščio</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MOISTURE &amp; MORE CONDITIONER drÄkinamasis kondicionierius sausiems plaukams</t>
+          <t>MOISTURE &amp; MORE CONDITIONER drėkinamasis kondicionierius sausiems plaukams</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MOISTURE PLUS WHIPPED CREAM drÄkinamosios putos sausiems plaukams</t>
+          <t>MOISTURE PLUS WHIPPED CREAM drėkinamosios putos sausiems plaukams</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE HYDRATING LOTION drÄkinamasis losjonas sausiems plaukams</t>
+          <t>MOISTURE&amp;MORE HYDRATING LOTION drėkinamasis losjonas sausiems plaukams</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -3741,12 +3741,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PLK-MOISTURE-DRA-KINA-SHA-NA</t>
+          <t>PLK-MOISTURE-DREKINAM-SHA-NA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE SHAMPOO drÄkinamasis Å¡ampÅ«nas sausiems plaukams</t>
+          <t>MOISTURE&amp;MORE SHAMPOO drėkinamasis šampūnas sausiems plaukams</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE SIERO ILLUMINANTE drÄkinamasis spindesio suteikiantis serumas</t>
+          <t>MOISTURE&amp;MORE SIERO ILLUMINANTE drėkinamasis spindesio suteikiantis serumas</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NO FRIZZ ALLOWED PERFECTING CONDITIONER kondicionierius Å¡iauÅ¡tis linkusiems plaukams</t>
+          <t>NO FRIZZ ALLOWED PERFECTING CONDITIONER kondicionierius šiauštis linkusiems plaukams</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NO FRIZZ ALLOWED PERFECTING SHAMPOO Å¡ampÅ«nas Å¡iauÅ¡tis linkusiems plaukams</t>
+          <t>NO FRIZZ ALLOWED PERFECTING SHAMPOO šampūnas šiauštis linkusiems plaukams</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>No.10 BOND SHAPERâ¢ CURL DEFINING GEL</t>
+          <t>No.10 BOND SHAPER™ CURL DEFINING GEL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -4133,12 +4133,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PLK-PINIGA3-GRA-PRD-NA</t>
+          <t>PLK-PINIGU-GRAZINIM-PRD-NA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PinigÅ³ grÄ Å¾inimo politika â grÄ Å¾inimo sÄ lygos</t>
+          <t>Pinigų grąžinimo politika – grąžinimo sąlygos</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -4178,12 +4178,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PLK-PLAUKA3-GELIAI-SER-NA</t>
+          <t>PLK-GELIAI-SERUMAI-SER-NA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PlaukÅ³ geliai ir serumai | Profesionalios formavimo priemonÄs â plaukuosena.lt</t>
+          <t>Plaukų geliai ir serumai | Profesionalios formavimo priemonės</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -4223,12 +4223,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PLK-PLAUKA3-KAUKA-S-PRD-NA</t>
+          <t>PLK-KAUKES-PROFESIO-MSK-NA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PlaukÅ³ kaukÄs | Profesionalios plaukÅ³ kaukÄs internetu â plaukuosena.lt</t>
+          <t>Plaukų kaukės | Profesionalios plaukų kaukės internetu</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SILVER SHINE CONDITIONER kondicionierius Å¾iliems / Å¡viesintiems plaukams</t>
+          <t>SILVER SHINE CONDITIONER kondicionierius žiliems / šviesintiems plaukams</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SILVER SHINE LIGHT SHAMPOO Å¡ampÅ«nas Å¾iliems / Å¡viesintiems plaukams</t>
+          <t>SILVER SHINE LIGHT SHAMPOO šampūnas žiliems / šviesintiems plaukams</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -4415,12 +4415,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PLK-SMOOTHIN-MIRACLE-PRD-NA</t>
+          <t>PLK-SMOOTHIN-MIRACLE-SPR-NA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SMOOTHING MIRACLE SHIELD nuo karÅ¡Äio ir drÄgmÄs apsaugantis purÅ¡kiklis</t>
+          <t>SMOOTHING MIRACLE SHIELD nuo karščio ir drėgmės apsaugantis purškiklis</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -4517,12 +4517,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PLK-SAULA-S-APSAUGA-PRD-NA</t>
+          <t>PLK-SAULES-APSAUGA-PRD-NA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SaulÄs apsauga plaukams | Apsauga nuo UV â plaukuosena.lt</t>
+          <t>Saulės apsauga plaukams | Apsauga nuo UV</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -4562,12 +4562,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PLK-TONEPLEX-PEARL-PRD-NA</t>
+          <t>PLK-TONEPLEX-PEARL-SHA-NA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TONEPLEX Pearl Blonde atspalvÄ¯ suteikiantis Å¡ampÅ«nas</t>
+          <t>TONEPLEX Pearl Blonde atspalvį suteikiantis šampūnas</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -4611,12 +4611,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PLK-TONEPLEX-DAA3-4AN-PRD-200ML</t>
+          <t>PLK-TONEPLEX-DAZANTI-MSK-200ML</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TONEPLEX daÅ¾anti kaukÄ, 200 ml</t>
+          <t>TONEPLEX dažanti kaukė, 200 ml</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ULTIMATE COLOR Miracle Leaveâin Mask â Miracle nenuplaunama kaukÄ STEP 2</t>
+          <t>ULTIMATE COLOR Miracle Leave–in Mask – Miracle nenuplaunama kaukė STEP 2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ULTIMATE COLOR Shine Spray â Blizgesio suteikiantis purÅ¡kiklis STEP 3, 95 ml</t>
+          <t>ULTIMATE COLOR Shine Spray – Blizgesio suteikiantis purškiklis STEP 3, 95 ml</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -4766,12 +4766,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PLK-ULTIMATE-REPAIR-PRD-NA-A224</t>
+          <t>PLK-ULTIMATE-REPAIR-MSK-NA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR intensyvaus poveikio kaukÄ paÅ¾eistiems plaukams STEP 2</t>
+          <t>ULTIMATE REPAIR intensyvaus poveikio kaukė pažeistiems plaukams STEP 2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR intensyvaus poveikio kondicionierius paÅ¾eistiems plaukams STEP 2</t>
+          <t>ULTIMATE REPAIR intensyvaus poveikio kondicionierius pažeistiems plaukams STEP 2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -4864,12 +4864,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PLK-ULTIMATE-REPAIR-PRD-NA</t>
+          <t>PLK-ULTIMATE-REPAIR-SHA-NA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR intensyvaus poveikio Å¡ampÅ«nas paÅ¾eistiems plaukams STEP 1</t>
+          <t>ULTIMATE REPAIR intensyvaus poveikio šampūnas pažeistiems plaukams STEP 1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR naktinis plaukÅ³ serumas STEP 5</t>
+          <t>ULTIMATE REPAIR naktinis plaukų serumas STEP 5</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -4962,12 +4962,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PLK-ULTIMATE-SMOOTH-PRD-NA</t>
+          <t>PLK-ULTIMATE-SMOOTH-MSK-NA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ULTIMATE SMOOTH maitinanti kaukÄ su skvalanu ir omega-9</t>
+          <t>ULTIMATE SMOOTH maitinanti kaukė su skvalanu ir omega-9</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -5064,12 +5064,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PLK-VISIBLE-REPAIR-PRD-NA</t>
+          <t>PLK-VISIBLE-REPAIR-MSK-NA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VISIBLE REPAIR kaukÄ</t>
+          <t>VISIBLE REPAIR kaukė</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -5162,12 +5162,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PLK-VISIBLE-REPAIR-PRD-NA-93B3</t>
+          <t>PLK-VISIBLE-REPAIR-SHA-NA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VISIBLE REPAIR Å¡ampÅ«nas</t>
+          <t>VISIBLE REPAIR šampūnas</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -5260,12 +5260,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AMC-A-2-CON-100ML</t>
+          <t>AMC-TM-2-CON-100ML</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ 2 IN 1 SKIN MOISTURIZER AND BEARD CONDITIONER odos ir barzdos drÄkinimo priemonÄ</t>
+          <t>AMERICAN CREW™ 2 IN 1 SKIN MOISTURIZER AND BEARD CONDITIONER odos ir barzdos drėkinimo priemonė</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5317,12 +5317,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AMC-A-24-PRD-450ML</t>
+          <t>AMC-TM-24-PRD-450ML</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ 24 HOUR DEODORANT BODY WASH 24 valandas gaivos pojÅ«tÄ¯ suteikiantis kÅ«no prausiklis</t>
+          <t>AMERICAN CREW™ 24 HOUR DEODORANT BODY WASH 24 valandas gaivos pojūtį suteikiantis kūno prausiklis</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5374,12 +5374,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AMC-A-3-IN-1-CON-250ML</t>
+          <t>AMC-TM-3-IN-1-SHA-250ML</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ 3-IN-1 CHAMOMILE + PINE Å¡ampÅ«nas, kondicionierius ir duÅ¡o Å¾elÄ viename</t>
+          <t>AMERICAN CREW™ 3-IN-1 CHAMOMILE + PINE šampūnas, kondicionierius ir dušo želė viename</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5431,12 +5431,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AMC-A-3-IN-1-CON-250ML-93DE</t>
+          <t>AMC-TM-3-IN-1-SHA-250ML-93DE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ 3-IN-1 GINGER + TEA Å¡ampÅ«nas, kondicionierius ir duÅ¡o Å¾elÄ viename</t>
+          <t>AMERICAN CREW™ 3-IN-1 GINGER + TEA šampūnas, kondicionierius ir dušo želė viename</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5488,12 +5488,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AMC-A-3-IN-1-CON-250ML-2D63</t>
+          <t>AMC-TM-3-IN-1-SHA-250ML-2D63</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ 3-IN-1 TEA TREE Å¡ampÅ«nas, kondicionierius ir duÅ¡o Å¾elÄ viename</t>
+          <t>AMERICAN CREW™ 3-IN-1 TEA TREE šampūnas, kondicionierius ir dušo želė viename</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5545,12 +5545,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AMC-A-3-IN-1-CON-250ML-5A9C</t>
+          <t>AMC-TM-3-IN-1-SHA-250ML-5A9C</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ 3-IN-1 Å¡ampÅ«nas, kondicionierius ir duÅ¡o Å¾elÄ viename</t>
+          <t>AMERICAN CREW™ 3-IN-1 šampūnas, kondicionierius ir dušo želė viename</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5602,12 +5602,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AMC-A-ALTERNAT-PRD-100ML</t>
+          <t>AMC-TM-ALTERNAT-PRD-100ML</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ ALTERNATOR purÅ¡kiama plaukÅ³ formavimo priemonÄ</t>
+          <t>AMERICAN CREW™ ALTERNATOR purškiama plaukų formavimo priemonė</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5659,12 +5659,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AMC-A-ANTI-DAN-SHA-250ML</t>
+          <t>AMC-TM-ANTI-DAN-SHA-250ML</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ ANTI-DANDRUFF + DRY SCALP SHAMPOO Å¡ampÅ«nas nuo pleiskanÅ³ ir sausos galvos odos</t>
+          <t>AMERICAN CREW™ ANTI-DANDRUFF + DRY SCALP SHAMPOO šampūnas nuo pleiskanų ir sausos galvos odos</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5716,12 +5716,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AMC-A-BEARD-CON-60G</t>
+          <t>AMC-TM-BEARD-CON-60G</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ BEARD BALM barzdos kondicionierius ir formuotojas</t>
+          <t>AMERICAN CREW™ BEARD BALM barzdos kondicionierius ir formuotojas</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5773,12 +5773,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AMC-A-BEARD-SER-NA</t>
+          <t>AMC-TM-BEARD-SER-NA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ BEARD SERUM serumas barzdai</t>
+          <t>AMERICAN CREW™ BEARD SERUM serumas barzdai</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5826,12 +5826,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AMC-A-BOOST-PRD-10G</t>
+          <t>AMC-TM-BOOST-PRD-10G</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ BOOST POWDER apimties suteikianti plaukÅ³ formavimo pudra</t>
+          <t>AMERICAN CREW™ BOOST POWDER apimties suteikianti plaukų formavimo pudra</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5883,12 +5883,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AMC-A-BOOST-SHA-NA</t>
+          <t>AMC-TM-BOOST-SHA-NA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ BOOST PRE-STYLING SHAMPOO</t>
+          <t>AMERICAN CREW™ BOOST PRE-STYLING SHAMPOO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5936,12 +5936,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AMC-A-CLASSIC-PRD-450ML</t>
+          <t>AMC-TM-CLASSIC-PRD-450ML</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ CLASSIC BODY WASH klasikinio aromato kÅ«no prausiklis</t>
+          <t>AMERICAN CREW™ CLASSIC BODY WASH klasikinio aromato kūno prausiklis</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5993,12 +5993,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AMC-A-POMADE-CRM-85G</t>
+          <t>AMC-TM-POMADE-CRM-85G</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ CREAM POMADE silpnos, vidutinÄs fiksacijos plaukÅ³ formavimo kreminÄ pomada</t>
+          <t>AMERICAN CREW™ CREAM POMADE silpnos, vidutinės fiksacijos plaukų formavimo kreminė pomada</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6050,12 +6050,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AMC-A-DAILY-SHA-NA-6DA8</t>
+          <t>AMC-TM-DAILY-SHA-NA-6DA8</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ DAILY CLEANSING SHAMPOO Å¡ampÅ«nas kasdienei galvos odos ir plaukÅ³ prieÅ¾iÅ«rai</t>
+          <t>AMERICAN CREW™ DAILY CLEANSING SHAMPOO šampūnas kasdienei galvos odos ir plaukų priežiūrai</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6103,12 +6103,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AMC-A-DAILY-SHA-NA</t>
+          <t>AMC-TM-DAILY-SHA-NA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ DAILY DEEP MOISTURIZING SHAMPOO drÄkinantis Å¡ampÅ«nas kasdienei galvos odos ir plaukÅ³ prieÅ¾iÅ«rai</t>
+          <t>AMERICAN CREW™ DAILY DEEP MOISTURIZING SHAMPOO drėkinantis šampūnas kasdienei galvos odos ir plaukų priežiūrai</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6156,12 +6156,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AMC-A-DAILY-CON-NA</t>
+          <t>AMC-TM-DAILY-CON-NA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ DAILY MOISTURIZING CONDITIONER kasdienis kondicionierius plaukams</t>
+          <t>AMERICAN CREW™ DAILY MOISTURIZING CONDITIONER kasdienis kondicionierius plaukams</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6209,12 +6209,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AMC-A-DAILY-SHA-NA-9FF9</t>
+          <t>AMC-TM-DAILY-SHA-NA-9FF9</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ DAILY SILVER SHAMPOO kasdienis Å¡ampÅ«nas Å¾iliems plaukams</t>
+          <t>AMERICAN CREW™ DAILY SILVER SHAMPOO kasdienis šampūnas žiliems plaukams</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6262,12 +6262,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AMC-A-DEFINING-PAS-NA</t>
+          <t>AMC-TM-DEFINING-PAS-NA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ DEFINING PASTE vidutinÄs fiksacijos matinÄ plaukÅ³ formavimo pasta</t>
+          <t>AMERICAN CREW™ DEFINING PASTE vidutinės fiksacijos matinė plaukų formavimo pasta</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6315,12 +6315,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AMC-A-DETOX-SHA-NA</t>
+          <t>AMC-TM-DETOX-SHA-NA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ DETOX SHAMPOO giliai valantis Å¡ampÅ«nas</t>
+          <t>AMERICAN CREW™ DETOX SHAMPOO giliai valantis šampūnas</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6368,12 +6368,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AMC-A-FIBER-CRM-100ML</t>
+          <t>AMC-TM-FIBER-CRM-100ML</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ FIBER CREAM vidutinÄs fiksacijos formavimo kremas</t>
+          <t>AMERICAN CREW™ FIBER CREAM vidutinės fiksacijos formavimo kremas</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6425,12 +6425,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AMC-A-FIBER-FOA-200ML</t>
+          <t>AMC-TM-FIBER-FOA-200ML</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ FIBER GROOMING FOAM vidutinÄs fiksacijos putos</t>
+          <t>AMERICAN CREW™ FIBER GROOMING FOAM vidutinės fiksacijos putos</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6482,12 +6482,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AMC-A-FIBER-SHA-NA</t>
+          <t>AMC-TM-FIBER-SHA-NA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ FIBER PRE-STYLING SHAMPOO</t>
+          <t>AMERICAN CREW™ FIBER PRE-STYLING SHAMPOO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6535,12 +6535,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AMC-A-FIBERA-CRM-85G</t>
+          <t>AMC-TM-FIBERTM-CRM-85G</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ FIBERâ¢ stiprios fiksacijos plaukÅ³ formavimo kremas</t>
+          <t>AMERICAN CREW™ FIBER™ stiprios fiksacijos plaukų formavimo kremas</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6592,12 +6592,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AMC-A-FIRM-GEL-NA</t>
+          <t>AMC-TM-FIRM-GEL-NA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ FIRM HOLD STYLING GEL stiprios fiksacijos plaukÅ³ formavimo gelis</t>
+          <t>AMERICAN CREW™ FIRM HOLD STYLING GEL stiprios fiksacijos plaukų formavimo gelis</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6645,12 +6645,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AMC-A-FORMING-CRM-85G</t>
+          <t>AMC-TM-FORMING-CRM-85G</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ FORMING CREAM vidutinÄs fiksacijos plaukÅ³ formavimo kremas</t>
+          <t>AMERICAN CREW™ FORMING CREAM vidutinės fiksacijos plaukų formavimo kremas</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6702,12 +6702,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AMC-A-FORMING-SHA-NA</t>
+          <t>AMC-TM-FORMING-SHA-NA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ FORMING PRE-STYLING SHAMPOO</t>
+          <t>AMERICAN CREW™ FORMING PRE-STYLING SHAMPOO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6755,12 +6755,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AMC-A-GROOMING-CRM-85G</t>
+          <t>AMC-TM-GROOMING-CRM-85G</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ GROOMING CREAM stiprios fiksacijos plaukÅ³ formavimo kremas su alavijo ekstraktu</t>
+          <t>AMERICAN CREW™ GROOMING CREAM stiprios fiksacijos plaukų formavimo kremas su alavijo ekstraktu</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6812,12 +6812,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AMC-A-GROOMING-SPR-NA</t>
+          <t>AMC-TM-GROOMING-SPR-NA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ GROOMING SPRAY stiprios fiksacijos plaukÅ³ formavimo priemonÄ</t>
+          <t>AMERICAN CREW™ GROOMING SPRAY stiprios fiksacijos plaukų formavimo priemonė</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6865,12 +6865,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AMC-A-HEAVY-PRD-85G</t>
+          <t>AMC-TM-HEAVY-PRD-85G</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ HEAVY HOLD POMADE stiprios fiksacijos plaukÅ³ formavimo pomada su Å¾vilgesiu</t>
+          <t>AMERICAN CREW™ HEAVY HOLD POMADE stiprios fiksacijos plaukų formavimo pomada su žvilgesiu</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6922,12 +6922,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AMC-A-MATTE-SPR-150ML</t>
+          <t>AMC-TM-MATTE-SPR-150ML</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ MATTE CLAY SPRAY absorbuojantis aliejaus perteklÄ¯ ir teksturizuojamas purÅ¡kalas plaukams</t>
+          <t>AMERICAN CREW™ MATTE CLAY SPRAY absorbuojantis aliejaus perteklį ir teksturizuojamas purškalas plaukams</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6979,12 +6979,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AMC-A-MATTE-PRD-85G</t>
+          <t>AMC-TM-MATTE-PRD-85G</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ MATTE CLAY vidutinÄs fiksacijos plaukÅ³ formavimo molis</t>
+          <t>AMERICAN CREW™ MATTE CLAY vidutinės fiksacijos plaukų formavimo molis</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7036,12 +7036,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AMC-A-MEDIUM-SPR-NA</t>
+          <t>AMC-TM-MEDIUM-SPR-NA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ MEDIUM HOLD SPRAY GEL vidutinÄs fiksacijos purÅ¡kiamas plaukÅ³ formavimo gelis</t>
+          <t>AMERICAN CREW™ MEDIUM HOLD SPRAY GEL vidutinės fiksacijos purškiamas plaukų formavimo gelis</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7089,12 +7089,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AMC-A-MOISTURI-CRM-NA</t>
+          <t>AMC-TM-MOISTURI-CRM-NA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ MOISTURIZING SHAVE CREAM drÄkinantis skutimo kremas</t>
+          <t>AMERICAN CREW™ MOISTURIZING SHAVE CREAM drėkinantis skutimo kremas</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7142,12 +7142,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AMC-A-MOLDING-PRD-NA</t>
+          <t>AMC-TM-MOLDING-PRD-NA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ MOLDING CLAY stiprios fiksacijos plaukÅ³ formavimo molis su biÄiÅ³ vaÅ¡ku</t>
+          <t>AMERICAN CREW™ MOLDING CLAY stiprios fiksacijos plaukų formavimo molis su bičių vašku</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7195,12 +7195,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AMC-A-POMADE-PRD-NA</t>
+          <t>AMC-TM-POMADE-PRD-NA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ POMADE klasikinÄ pomada plaukÅ³ formavimui</t>
+          <t>AMERICAN CREW™ POMADE klasikinė pomada plaukų formavimui</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7248,12 +7248,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AMC-A-POMADE-PRD-NA-9DF4</t>
+          <t>AMC-TM-POMADE-PRD-NA-9DF4</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ POMADE klasikinÄ pomada plaukÅ³ formavimui</t>
+          <t>AMERICAN CREW™ POMADE klasikinė pomada plaukų formavimui</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7301,12 +7301,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AMC-A-POST-CRM-150ML</t>
+          <t>AMC-TM-POST-CRM-150ML</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ POST SHAVE COOLING LOTION drÄkinamasis kremas po skutimosi</t>
+          <t>AMERICAN CREW™ POST SHAVE COOLING LOTION drėkinamasis kremas po skutimosi</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7358,12 +7358,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AMC-A-PRECISIO-GEL-150ML</t>
+          <t>AMC-TM-PRECISIO-GEL-150ML</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ PRECISION SHAVE GEL skutimo gelis</t>
+          <t>AMERICAN CREW™ PRECISION SHAVE GEL skutimo gelis</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7415,12 +7415,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AMC-A-REVITALI-PRD-150ML</t>
+          <t>AMC-TM-REVITALI-PRD-150ML</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ REVITALIZING TONER atgaivinantis tonikas po skutimo</t>
+          <t>AMERICAN CREW™ REVITALIZING TONER atgaivinantis tonikas po skutimo</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7472,12 +7472,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AMC-A-ULTRA-OIL-NA</t>
+          <t>AMC-TM-ULTRA-OIL-NA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ ULTRA GLIDING SHAVE OIL apsauginis aliejus po arba skutimo metu</t>
+          <t>AMERICAN CREW™ ULTRA GLIDING SHAVE OIL apsauginis aliejus po arba skutimo metu</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7525,12 +7525,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AMC-A-WHIP-CRM-NA</t>
+          <t>AMC-TM-WHIP-CRM-NA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>AMERICAN CREWâ¢ WHIP silpnos fiksacijos plaukÅ³ formavimo kremas</t>
+          <t>AMERICAN CREW™ WHIP silpnos fiksacijos plaukų formavimo kremas</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7578,12 +7578,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AMC-PLAUKA3-PRIEA3-4-PRD-NA</t>
+          <t>AMC-PRIEZIUR-VYRAMS-PRD-NA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>American Crew plaukÅ³ prieÅ¾iÅ«ra vyrams | Pomados, Å¡ampÅ«nai ir formavimo priemonÄs â plaukuosena.lt</t>
+          <t>American Crew plaukų priežiūra vyrams | Pomados, šampūnai ir formavimo priemonės</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DAVINES Blizgesys ir apsauga Å¡viesiems plaukams | Heart of Glass</t>
+          <t>DAVINES Blizgesys ir apsauga šviesiems plaukams | Heart of Glass</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7733,12 +7733,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DAV-GEROS-SAVIJAUT-PRD-NA</t>
+          <t>DAV-GEROS-SAVIJAUT-SHA-NA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DAVINES GEROS SAVIJAUTOS Å AMPÅªNAS PH: 5.5 | WELLâBEING</t>
+          <t>DAVINES GEROS SAVIJAUTOS ŠAMPŪNAS PH: 5.5 | WELL–BEING</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7786,12 +7786,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DAV-GREITAI-PLAUKUS-PRD-NA</t>
+          <t>DAV-GREITAI-PLAUKUS-MSK-NA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DAVINES GREITAI PLAUKUS ATKURIANTI KAUKÄ | THE QUICK FIX CIRCLE</t>
+          <t>DAVINES GREITAI PLAUKUS ATKURIANTI KAUKĖ | THE QUICK FIX CIRCLE</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7839,12 +7839,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DAV-DAA1-2YT-PH-CON-NA</t>
+          <t>DAV-DAZYTIEM-PH-CON-NA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DAVINES KONDICIONIERIUS DAÅ½YTIEMS PLAUKAMS PH: 4 | MINU</t>
+          <t>DAVINES KONDICIONIERIUS DAŽYTIEMS PLAUKAMS PH: 4 | MINU</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7892,12 +7892,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DAV-PAA1-2EI-PH-CON-NA</t>
+          <t>DAV-PAZEISTI-PH-CON-NA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DAVINES KONDICIONIERIUS PAÅ½EISTIEMS PLAUKAMS PH: 4 | MELU</t>
+          <t>DAVINES KONDICIONIERIUS PAŽEISTIEMS PLAUKAMS PH: 4 | MELU</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7945,12 +7945,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DAV-TIESINAN-A-PRD-NA</t>
+          <t>DAV-TIESINAN-PH-SHA-NA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DAVINES TIESINANTIS Å AMPÅªNAS PH: 5.3 | LOVE</t>
+          <t>DAVINES TIESINANTIS ŠAMPŪNAS PH: 5.3 | LOVE</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -7998,12 +7998,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DAV-VALANTIS-A-PRD-NA</t>
+          <t>DAV-VALANTIS-NUO-SHA-NA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DAVINES VALANTIS Å AMPÅªNAS NUO PLEISKANÅ² PH: 4.9 | PURIFYING</t>
+          <t>DAVINES VALANTIS ŠAMPŪNAS NUO PLEISKANŲ PH: 4.9 | PURIFYING</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8051,12 +8051,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DAV-A-AMPAANAS-PRD-NA-E1B3</t>
+          <t>DAV-DAZYTIEM-PH-SHA-NA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DAVINES Å AMPÅªNAS DAÅ½YTIEMS PLAUKAMS PH: 5.3 | MINU</t>
+          <t>DAVINES ŠAMPŪNAS DAŽYTIEMS PLAUKAMS PH: 5.3 | MINU</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8104,12 +8104,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DAV-A-AMPAANAS-PRD-NA-5E04</t>
+          <t>DAV-GARBANUO-PH-SHA-NA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DAVINES Å AMPÅªNAS GARBANUOTIEMS PLAUKAMS PH: 5.3 | LOVE CURL</t>
+          <t>DAVINES ŠAMPŪNAS GARBANUOTIEMS PLAUKAMS PH: 5.3 | LOVE CURL</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8157,12 +8157,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DAV-A-AMPAANAS-PRD-NA-2479</t>
+          <t>DAV-PAZEISTI-PH-SHA-NA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DAVINES Å AMPÅªNAS PAÅ½EISTIEMS PLAUKAMS PH: 5.3 | MELU</t>
+          <t>DAVINES ŠAMPŪNAS PAŽEISTIEMS PLAUKAMS PH: 5.3 | MELU</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8210,12 +8210,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DAV-A-AMPAANAS-PRD-NA</t>
+          <t>DAV-GAUSINIM-PH-SHA-NA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DAVINES Å AMPÅªNAS PLAUKÅ² GAUSINIMUI PH: 5.3 | VOLU</t>
+          <t>DAVINES ŠAMPŪNAS PLAUKŲ GAUSINIMUI PH: 5.3 | VOLU</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8263,12 +8263,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DAV-A-VIESIUS-CON-100ML</t>
+          <t>DAV-SVIESIUS-PLAUKUS-CON-100ML</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DAVINES Å viesius plaukus maitinantis kondicionierius | Heart of Glass</t>
+          <t>DAVINES Šviesius plaukus maitinantis kondicionierius | Heart of Glass</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8320,12 +8320,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>DAV-A-VIESIUS-PRD-NA</t>
+          <t>DAV-SVIESIUS-PLAUKUS-MSK-NA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DAVINES Å viesius plaukus stiprinanti kaukÄ | Heart of Glass</t>
+          <t>DAVINES Šviesius plaukus stiprinanti kaukė | Heart of Glass</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE LEAVE-IN purÅ¡kiamas kondicionierius, 250 ml</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE LEAVE-IN purškiamas kondicionierius, 250 ml</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8483,12 +8483,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>KAD-PROFESSI-DEEP-PRD-NA</t>
+          <t>KAD-PROFESSI-DEEP-SHA-NA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE Å¡ampÅ«nas</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE šampūnas</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8536,12 +8536,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>KAD-PROFESSI-PLAUKA3-PRD-NA</t>
+          <t>KAD-PROFESSI-PRIEMONE-PRD-NA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Kadus Professional plaukÅ³ priemonÄs | Kadus kosmetika â plaukuosena.lt</t>
+          <t>Kadus Professional plaukų priemonės | Kadus kosmetika</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MILK SHAKE NO FRIZZ AMAZING ANTI-HUMIDITY SPRAY apsauginis purÅ¡kiklis garbanotiems plaukams</t>
+          <t>MILK SHAKE NO FRIZZ AMAZING ANTI-HUMIDITY SPRAY apsauginis purškiklis garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -8744,12 +8744,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MSK-PLAUKA3-PRIEA3-4-PRD-NA</t>
+          <t>MSK-PRIEMONE-KOSMETIK-PRD-NA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Milk Shake plaukÅ³ prieÅ¾iÅ«ros priemonÄs | Milk Shake kosmetika â plaukuosena.lt</t>
+          <t>Milk Shake plaukų priežiūros priemonės | Milk Shake kosmetika</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9535,12 +9535,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>OLX-PLAUKA3-PRIEA3-4-PRD-NA</t>
+          <t>OLX-PRIEMONE-PRODUKTA-PRD-NA</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Olaplex plaukÅ³ prieÅ¾iÅ«ros priemonÄs | Olaplex produktai â plaukuosena.lt</t>
+          <t>Olaplex plaukų priežiūros priemonės | Olaplex produktai</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>QIQI Bare Repair Oil PlaukÅ³ aliejus</t>
+          <t>QIQI Bare Repair Oil Plaukų aliejus</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -9637,12 +9637,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>QIQ-GLOTNINA-A-AMPA-N-PRD-NA</t>
+          <t>QIQ-GLOTNINA-SHA-NA</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>QIQI Glotninantis Å¡ampÅ«nas</t>
+          <t>QIQI Glotninantis šampūnas</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>QIQI Porosity Play Spray PlaukÅ³ purÅ¡kiklis</t>
+          <t>QIQI Porosity Play Spray Plaukų purškiklis</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -9796,12 +9796,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>QIQ-SUPER-SOAKER-PRD-NA</t>
+          <t>QIQ-SUPER-SOAKER-MSK-NA</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>QIQI Super Soaker Smoothing Masque Glotninanti plaukÅ³ kaukÄ</t>
+          <t>QIQI Super Soaker Smoothing Masque Glotninanti plaukų kaukė</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -9849,12 +9849,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>QIQ-DRA-KINA-CON-NA</t>
+          <t>QIQ-DREKINAM-CON-NA</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>QIQI drÄkinamasis kondicionierius</t>
+          <t>QIQI drėkinamasis kondicionierius</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Qiqi All Out Blowout uÅ¾baigimo kremas</t>
+          <t>Qiqi All Out Blowout užbaigimo kremas</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -9955,12 +9955,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>QIQ-PLAUKA3-PRIEA3-4-PRD-NA</t>
+          <t>QIQ-PRIEMONE-KOSMETIK-PRD-NA</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Qiqi plaukÅ³ prieÅ¾iÅ«ros priemonÄs | Qiqi kosmetika â plaukuosena.lt</t>
+          <t>Qiqi plaukų priežiūros priemonės | Qiqi kosmetika</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10004,12 +10004,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>WEL-FUSION-INTENSE-PRD-NA</t>
+          <t>WEL-FUSION-INTENSE-MSK-NA</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS FUSION Intense Repair atkurianti kaukÄ</t>
+          <t>WELLA PROFESSIONALS FUSION Intense Repair atkurianti kaukė</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10057,12 +10057,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>WEL-INVIGO-SCALP-PRD-150ML</t>
+          <t>WEL-INVIGO-SCALP-MSK-150ML</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminanti bekvapÄ kaukÄ jautriai galvos odai, 150 ml</t>
+          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminanti bekvapė kaukė jautriai galvos odai, 150 ml</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10114,12 +10114,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>WEL-INVIGO-SCALP-PRD-300ML</t>
+          <t>WEL-INVIGO-SCALP-SHA-300ML</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminantis bekvapis Å¡ampÅ«nas jautriai galvos odai, 300 ml |1000 ml</t>
+          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminantis bekvapis šampūnas jautriai galvos odai, 300 ml |1000 ml</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10171,12 +10171,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>WEL-INVIGO-SCALP-PRD-300ML-496F</t>
+          <t>WEL-INVIGO-SCALP-SHA-300ML-496F</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE Å¡ampÅ«nas nuo pleiskanÅ³, 300 ml</t>
+          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE šampūnas nuo pleiskanų, 300 ml</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE COLOR Conditioner â DrÄkinantis daÅ¾ytÅ³ plaukÅ³ kondicionierius STEP 2</t>
+          <t>WELLA PROFESSIONALS ULTIMATE COLOR Conditioner – Drėkinantis dažytų plaukų kondicionierius STEP 2</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE COLOR Shampoo â DaÅ¾ytÅ³ plaukÅ³ Å¡ampÅ«nas be sulfatÅ³ STEP 1</t>
+          <t>WELLA PROFESSIONALS ULTIMATE COLOR Shampoo – Dažytų plaukų šampūnas be sulfatų STEP 1</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -10440,12 +10440,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>WEL-FUSION-ATSTATOM-PRD-NA</t>
+          <t>WEL-FUSION-ATSTATOM-SHA-NA</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Wella Professionals FUSION atstatomasis Å¡ampÅ«nas</t>
+          <t>Wella Professionals FUSION atstatomasis šampūnas</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -10493,12 +10493,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>WEL-ULTIMATE-SMOOTH-PRD-NA</t>
+          <t>WEL-ULTIMATE-SMOOTH-SHA-NA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Wella Professionals Ultimate Smooth intensyviai maitinantis Å¡ampÅ«nas</t>
+          <t>Wella Professionals Ultimate Smooth intensyviai maitinantis šampūnas</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -10546,12 +10546,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>WEL-PLAUKA3-PRIEA3-4-PRD-NA</t>
+          <t>WEL-PRIEMONE-PRD-NA</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Wella Professionals plaukÅ³ prieÅ¾iÅ«ros priemonÄs â plaukuosena.lt</t>
+          <t>Wella Professionals plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">

--- a/products_snapshot.xlsx
+++ b/products_snapshot.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų geliai</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų geliai</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų geliai</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų geliai</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų geliai</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>American Crew</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">

--- a/products_snapshot.xlsx
+++ b/products_snapshot.xlsx
@@ -553,7 +553,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ 2 IN 1 SKIN MOISTURIZER AND BEARD CONDITIONER odos ir barzdos drėkinimo priemonė</t>
+          <t>AMERICAN CREW™ 2 IN 1 SKIN MOISTURIZER AND BEARD CONDITIONER odos ir barzdos drėkinimo priemonė | 100ML</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>669316457108</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ 24 HOUR DEODORANT BODY WASH 24 valandas gaivos pojūtį suteikiantis kūno prausiklis</t>
+          <t>AMERICAN CREW™ 24 HOUR DEODORANT BODY WASH 24 valandas gaivos pojūtį suteikiantis kūno prausiklis | 450ML</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678248102</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMC-TM-3-IN-1-SHA-250ML</t>
+          <t>AMC-TM-3-IN-1-SHA-250ML-D77C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ 3-IN-1 CHAMOMILE + PINE šampūnas, kondicionierius ir dušo želė viename</t>
+          <t>AMERICAN CREW™ 3-IN-1 CHAMOMILE + PINE šampūnas, kondicionierius ir dušo želė viename | 250 ml / 450 ml</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678003381</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMC-TM-3-IN-1-SHA-250ML-93DE</t>
+          <t>AMC-TM-3-IN-1-SHA-250ML</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ 3-IN-1 GINGER + TEA šampūnas, kondicionierius ir dušo želė viename</t>
+          <t>AMERICAN CREW™ 3-IN-1 GINGER + TEA šampūnas, kondicionierius ir dušo želė viename | 250 ml / 450 ml</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678003398</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ 3-IN-1 TEA TREE šampūnas, kondicionierius ir dušo želė viename</t>
+          <t>AMERICAN CREW™ 3-IN-1 TEA TREE šampūnas, kondicionierius ir dušo želė viename | 250ML/450ML</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678001509</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ 3-IN-1 šampūnas, kondicionierius ir dušo želė viename</t>
+          <t>AMERICAN CREW™ 3-IN-1 šampūnas, kondicionierius ir dušo želė viename | 250 ml / 450 ml</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>669316058220</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ ALTERNATOR purškiama plaukų formavimo priemonė</t>
+          <t>AMERICAN CREW™ ALTERNATOR purškiama plaukų formavimo priemonė | 100ML</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>669316388327</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ ANTI-DANDRUFF + DRY SCALP SHAMPOO šampūnas nuo pleiskanų ir sausos galvos odos</t>
+          <t>AMERICAN CREW™ ANTI-DANDRUFF + DRY SCALP SHAMPOO šampūnas nuo pleiskanų ir sausos galvos odos | 250ML</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8432225131887</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ BEARD BALM barzdos kondicionierius ir formuotojas</t>
+          <t>AMERICAN CREW™ BEARD BALM barzdos kondicionierius ir formuotojas | 60G</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>669316434673</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1181,12 +1181,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMC-TM-BEARD-SER-NA</t>
+          <t>AMC-TM-BEARD-SER-50ML</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ BEARD SERUM serumas barzdai</t>
+          <t>AMERICAN CREW™ BEARD SERUM serumas barzdai | 50ML</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1224,10 +1224,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>50ml</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>669316401699</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1244,7 +1248,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ BOOST POWDER apimties suteikianti plaukų formavimo pudra</t>
+          <t>AMERICAN CREW™ BOOST POWDER apimties suteikianti plaukų formavimo pudra | 10G</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,7 +1258,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1289,7 +1293,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678250013</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1301,12 +1305,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMC-TM-BOOST-SHA-NA</t>
+          <t>AMC-TM-BOOST-SHA-250ML</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ BOOST PRE-STYLING SHAMPOO</t>
+          <t>AMERICAN CREW™ BOOST PRE-STYLING SHAMPOO | 250ML</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1316,7 +1320,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1344,10 +1348,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1364,7 +1372,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ CLASSIC BODY WASH klasikinio aromato kūno prausiklis</t>
+          <t>AMERICAN CREW™ CLASSIC BODY WASH klasikinio aromato kūno prausiklis | 450ML</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1374,7 +1382,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1409,7 +1417,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678240755</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1426,7 +1434,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ CREAM POMADE silpnos, vidutinės fiksacijos plaukų formavimo kreminė pomada</t>
+          <t>AMERICAN CREW™ CREAM POMADE silpnos, vidutinės fiksacijos plaukų formavimo kreminė pomada | 85G</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1436,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1471,7 +1479,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678242513</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1483,12 +1491,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMC-TM-DAILY-SHA-NA-6DA8</t>
+          <t>AMC-TM-DAILY-SHA-250ML-6DA8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ DAILY CLEANSING SHAMPOO šampūnas kasdienei galvos odos ir plaukų priežiūrai</t>
+          <t>AMERICAN CREW™ DAILY CLEANSING SHAMPOO šampūnas kasdienei galvos odos ir plaukų priežiūrai | 250 ml / 450 ml</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,7 +1506,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1526,10 +1534,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678001349</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1541,12 +1553,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMC-TM-DAILY-SHA-NA</t>
+          <t>AMC-TM-DAILY-SHA-250ML-DE4A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ DAILY DEEP MOISTURIZING SHAMPOO drėkinantis šampūnas kasdienei galvos odos ir plaukų priežiūrai</t>
+          <t>AMERICAN CREW™ DAILY DEEP MOISTURIZING SHAMPOO drėkinantis šampūnas kasdienei galvos odos ir plaukų priežiūrai | 250 ml / 450 ml</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1556,7 +1568,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1584,10 +1596,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678001370</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1599,12 +1615,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMC-TM-DAILY-CON-NA</t>
+          <t>AMC-TM-DAILY-CON-250ML</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ DAILY MOISTURIZING CONDITIONER kasdienis kondicionierius plaukams</t>
+          <t>AMERICAN CREW™ DAILY MOISTURIZING CONDITIONER kasdienis kondicionierius plaukams | 250 ml / 450 ml</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1614,7 +1630,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1642,10 +1658,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678001325</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1657,12 +1677,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AMC-TM-DAILY-SHA-NA-9FF9</t>
+          <t>AMC-TM-DAILY-SHA-250ML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ DAILY SILVER SHAMPOO kasdienis šampūnas žiliems plaukams</t>
+          <t>AMERICAN CREW™ DAILY SILVER SHAMPOO kasdienis šampūnas žiliems plaukams | 250ML</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1672,7 +1692,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1700,10 +1720,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678001585</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1715,12 +1739,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AMC-TM-DEFINING-PAS-NA</t>
+          <t>AMC-TM-DEFINING-PAS-85G</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ DEFINING PASTE vidutinės fiksacijos matinė plaukų formavimo pasta</t>
+          <t>AMERICAN CREW™ DEFINING PASTE vidutinės fiksacijos matinė plaukų formavimo pasta | 85G</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1730,7 +1754,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1758,10 +1782,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>85g</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678242520</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1773,12 +1801,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AMC-TM-DETOX-SHA-NA</t>
+          <t>AMC-TM-DETOX-SHA-250ML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ DETOX SHAMPOO giliai valantis šampūnas</t>
+          <t>AMERICAN CREW™ DETOX SHAMPOO giliai valantis šampūnas | 250ML</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1788,7 +1816,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1816,10 +1844,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678001158</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1836,7 +1868,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ FIBER CREAM vidutinės fiksacijos formavimo kremas</t>
+          <t>AMERICAN CREW™ FIBER CREAM vidutinės fiksacijos formavimo kremas | 100ML</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,7 +1878,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,7 +1913,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>669316408063</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1898,7 +1930,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ FIBER GROOMING FOAM vidutinės fiksacijos putos</t>
+          <t>AMERICAN CREW™ FIBER GROOMING FOAM vidutinės fiksacijos putos | 200ML</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1908,7 +1940,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1943,7 +1975,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>0738678003916</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1955,12 +1987,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMC-TM-FIBER-SHA-NA</t>
+          <t>AMC-TM-FIBER-SHA-250ML</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ FIBER PRE-STYLING SHAMPOO</t>
+          <t>AMERICAN CREW™ FIBER PRE-STYLING SHAMPOO | 250ML</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1970,7 +2002,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1998,10 +2030,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678004173</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2018,7 +2054,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ FIBER™ stiprios fiksacijos plaukų formavimo kremas</t>
+          <t>AMERICAN CREW™ FIBER™ stiprios fiksacijos plaukų formavimo kremas | 85G</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2028,7 +2064,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2063,7 +2099,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>0738678002698</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2075,12 +2111,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AMC-TM-FIRM-GEL-NA</t>
+          <t>AMC-TM-FIRM-GEL-250ML</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ FIRM HOLD STYLING GEL stiprios fiksacijos plaukų formavimo gelis</t>
+          <t>AMERICAN CREW™ FIRM HOLD STYLING GEL stiprios fiksacijos plaukų formavimo gelis | 250ML</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,7 +2126,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2118,10 +2154,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>669316060506</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2138,7 +2178,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ FORMING CREAM vidutinės fiksacijos plaukų formavimo kremas</t>
+          <t>AMERICAN CREW™ FORMING CREAM vidutinės fiksacijos plaukų formavimo kremas | 85G</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2148,7 +2188,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2183,7 +2223,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678002711</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2195,12 +2235,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AMC-TM-FORMING-SHA-NA</t>
+          <t>AMC-TM-FORMING-SHA-250ML</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ FORMING PRE-STYLING SHAMPOO</t>
+          <t>AMERICAN CREW™ FORMING PRE-STYLING SHAMPOO | 250ML</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2210,7 +2250,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2238,10 +2278,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678004180</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2258,7 +2302,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ GROOMING CREAM stiprios fiksacijos plaukų formavimo kremas su alavijo ekstraktu</t>
+          <t>AMERICAN CREW™ GROOMING CREAM stiprios fiksacijos plaukų formavimo kremas su alavijo ekstraktu | 85G</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2268,7 +2312,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2303,7 +2347,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678002766</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2315,12 +2359,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AMC-TM-GROOMING-SPR-NA</t>
+          <t>AMC-TM-GROOMING-SPR-250ML</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ GROOMING SPRAY stiprios fiksacijos plaukų formavimo priemonė</t>
+          <t>AMERICAN CREW™ GROOMING SPRAY stiprios fiksacijos plaukų formavimo priemonė | 250ML</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2330,7 +2374,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2358,10 +2402,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>669316080733</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2378,7 +2426,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ HEAVY HOLD POMADE stiprios fiksacijos plaukų formavimo pomada su žvilgesiu</t>
+          <t>AMERICAN CREW™ HEAVY HOLD POMADE stiprios fiksacijos plaukų formavimo pomada su žvilgesiu | 85G</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2388,7 +2436,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2423,7 +2471,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678002742</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2440,7 +2488,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ MATTE CLAY SPRAY absorbuojantis aliejaus perteklį ir teksturizuojamas purškalas plaukams</t>
+          <t>AMERICAN CREW™ MATTE CLAY SPRAY absorbuojantis aliejaus perteklį ir teksturizuojamas purškalas plaukams | 150ML</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2450,7 +2498,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2485,7 +2533,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678001820</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2502,7 +2550,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ MATTE CLAY vidutinės fiksacijos plaukų formavimo molis</t>
+          <t>AMERICAN CREW™ MATTE CLAY vidutinės fiksacijos plaukų formavimo molis | 85G</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2512,7 +2560,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2547,7 +2595,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678002759</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2559,12 +2607,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AMC-TM-MEDIUM-SPR-NA</t>
+          <t>AMC-TM-MEDIUM-SPR-250ML</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ MEDIUM HOLD SPRAY GEL vidutinės fiksacijos purškiamas plaukų formavimo gelis</t>
+          <t>AMERICAN CREW™ MEDIUM HOLD SPRAY GEL vidutinės fiksacijos purškiamas plaukų formavimo gelis | 250ML</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2574,7 +2622,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2602,10 +2650,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678151846</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2617,12 +2669,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMC-TM-MOISTURI-CRM-NA</t>
+          <t>AMC-TM-MOISTURI-CRM-150ML</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ MOISTURIZING SHAVE CREAM drėkinantis skutimo kremas</t>
+          <t>AMERICAN CREW™ MOISTURIZING SHAVE CREAM drėkinantis skutimo kremas | 150ML</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2632,7 +2684,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2660,10 +2712,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>669316434819</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2675,12 +2731,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMC-TM-MOLDING-PRD-NA</t>
+          <t>AMC-TM-MOLDING-PRD-85G</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ MOLDING CLAY stiprios fiksacijos plaukų formavimo molis su bičių vašku</t>
+          <t>AMERICAN CREW™ MOLDING CLAY stiprios fiksacijos plaukų formavimo molis su bičių vašku | 85G</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2690,7 +2746,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2718,10 +2774,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>85g</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678242025</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2733,12 +2793,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AMC-TM-POMADE-PRD-NA</t>
+          <t>AMC-TM-POMADE-PRD-85G</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ POMADE klasikinė pomada plaukų formavimui</t>
+          <t>AMERICAN CREW™ POMADE klasikinė pomada plaukų formavimui | 85G</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2748,7 +2808,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2776,10 +2836,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>85g</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678174470</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2791,12 +2855,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AMC-TM-POMADE-PRD-NA-9DF4</t>
+          <t>AMC-TM-POMADE-PRD-85G-9DF4</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ POMADE klasikinė pomada plaukų formavimui</t>
+          <t>AMERICAN CREW™ POMADE klasikinė pomada plaukų formavimui | 85G</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2806,7 +2870,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2834,10 +2898,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>85g</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678174470</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2854,7 +2922,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ POST SHAVE COOLING LOTION drėkinamasis kremas po skutimosi</t>
+          <t>AMERICAN CREW™ POST SHAVE COOLING LOTION drėkinamasis kremas po skutimosi | 150ML</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2864,7 +2932,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2899,7 +2967,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>669316434802</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2916,7 +2984,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ PRECISION SHAVE GEL skutimo gelis</t>
+          <t>AMERICAN CREW™ PRECISION SHAVE GEL skutimo gelis | 150ML</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2926,7 +2994,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2961,7 +3029,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>669316406168</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2978,7 +3046,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ REVITALIZING TONER atgaivinantis tonikas po skutimo</t>
+          <t>AMERICAN CREW™ REVITALIZING TONER atgaivinantis tonikas po skutimo | 150ML</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2988,7 +3056,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3023,7 +3091,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>669316406151</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3035,12 +3103,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMC-TM-ULTRA-OIL-NA</t>
+          <t>AMC-TM-ULTRA-OIL-50ML</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ ULTRA GLIDING SHAVE OIL apsauginis aliejus po arba skutimo metu</t>
+          <t>AMERICAN CREW™ ULTRA GLIDING SHAVE OIL apsauginis aliejus po arba skutimo metu | 50ML</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3050,7 +3118,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3078,10 +3146,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>50ml</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>669316406175</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3093,12 +3165,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMC-TM-WHIP-CRM-NA</t>
+          <t>AMC-TM-WHIP-CRM-85G</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AMERICAN CREW™ WHIP silpnos fiksacijos plaukų formavimo kremas</t>
+          <t>AMERICAN CREW™ WHIP silpnos fiksacijos plaukų formavimo kremas | 85G</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3108,7 +3180,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3136,10 +3208,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>85g</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>738678003190</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3193,7 +3269,7 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3255,7 +3331,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3267,22 +3343,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>COLO-RADIANCE-LEAVE-IN-CON-250ML</t>
+          <t>COLO-MAINTAIN-FLOWER-CON-NA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>COLOR RADIANCE LEAVE-IN SPRAY purškiamas kondicionierius, 250 ml</t>
+          <t>COLOUR MAINTAINER FLOWER FRAGRANCE CONDITIONER kondicionierius dažytiems plaukams</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>COLOR</t>
+          <t>COLOUR</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3292,12 +3368,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/color-radiance-leave-in-spray-purskiamas-kondicionierius-250-ml</t>
+          <t>https://plaukuosena.lt/colour-maintainer-flower-fragrance-conditioner-kondicionierius-dazytiems-plaukams</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1496fbcb-5032-476b-bcd5-ff6a423b360e.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f12f4ee8-316b-41a7-8d3b-30ea414d5751.png</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3310,14 +3386,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3329,22 +3401,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>COLO-RADIANCE-MSK-NA</t>
+          <t>COLO-MAINTAIN-FLOWER-SHA-NA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COLOR RADIANCE kaukė</t>
+          <t>COLOUR MAINTAINER FLOWER FRAGRANCE SHAMPOO šampūnas dažytiems plaukams</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>COLOR</t>
+          <t>COLOUR</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3354,17 +3426,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/color-radiance-kauke1</t>
+          <t>https://plaukuosena.lt/colour-maintainer-flower-fragrance-shampoo-sampunas-dazytiems-plaukams</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/188953a6-01e0-4821-b09a-418707b8ae5a.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e2ba385c-cd82-46d8-a674-c29c565d4b36.png</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3375,7 +3447,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3387,22 +3459,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>COLO-RADIANCE-CON-NA</t>
+          <t>CURL-PASSION-GARBANOT-CON-NA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>COLOR RADIANCE kondicionierius</t>
+          <t>CURL PASSION CONDITIONER kondicionierius garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>COLOR</t>
+          <t>CURL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3412,12 +3484,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/color-radiance-kauke</t>
+          <t>https://plaukuosena.lt/curl-passion-conditioner-kondicionierius-garbanotiems-plaukams</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b5200496-819e-44d4-9eeb-cfa65fbe0213.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a9008a8a-9ca2-40f4-af88-644753de306f.webp</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3433,7 +3505,7 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3445,22 +3517,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>COLO-RADIANCE-SHA-NA</t>
+          <t>CURL-PASSION-LEAVE-CON-NA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>COLOR RADIANCE šampūnas</t>
+          <t>CURL PASSION LEAVE IN nenuskalaujamas kondicionierius</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>COLOR</t>
+          <t>CURL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>22.30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3470,17 +3542,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/color-radiance-sampunas</t>
+          <t>https://plaukuosena.lt/curl-passion-leave-in-nenuskalaujamas-kondicionierius</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/70c7fad4-d7d0-4326-8b82-3955f89277d7.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/03bbe43d-1d1e-40a3-b7eb-95a6c413e398.png</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3491,7 +3563,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3503,22 +3575,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>COLO-MAINTAIN-FLOWER-CON-NA</t>
+          <t>CURL-PASSION-GARBANOT-MSK-NA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>COLOUR MAINTAINER FLOWER FRAGRANCE CONDITIONER kondicionierius dažytiems plaukams</t>
+          <t>CURL PASSION MASK kaukė garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>COLOUR</t>
+          <t>CURL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3528,17 +3600,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/colour-maintainer-flower-fragrance-conditioner-kondicionierius-dazytiems-plaukams</t>
+          <t>https://plaukuosena.lt/curl-passion-mask-kauke-garbanotiems-plaukams</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f12f4ee8-316b-41a7-8d3b-30ea414d5751.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/fd2c5cb6-c6fa-4919-b1b8-4581b2ab8a84.png</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3549,7 +3621,7 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3561,22 +3633,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>COLO-MAINTAIN-FLOWER-SHA-NA</t>
+          <t>CURL-PASSION-PERFECTI-CRM-NA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>COLOUR MAINTAINER FLOWER FRAGRANCE SHAMPOO šampūnas dažytiems plaukams</t>
+          <t>CURL PASSION PERFECTIONIST garbanų formavimo kremas</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>COLOUR</t>
+          <t>CURL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>22.30</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3586,17 +3658,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/colour-maintainer-flower-fragrance-shampoo-sampunas-dazytiems-plaukams</t>
+          <t>https://plaukuosena.lt/curl-passion-perfectionist-garbanu-formavimo-kremas</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e2ba385c-cd82-46d8-a674-c29c565d4b36.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/92fc1d2f-8e70-43aa-9649-4bf29c9685eb.png</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3607,7 +3679,7 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3619,12 +3691,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CURL-PASSION-GARBANOT-CON-NA</t>
+          <t>CURL-PASSION-GARBANOT-SHA-NA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CURL PASSION CONDITIONER kondicionierius garbanotiems plaukams</t>
+          <t>CURL PASSION SHAMPOO šampūnas garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3634,7 +3706,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3644,17 +3716,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/curl-passion-conditioner-kondicionierius-garbanotiems-plaukams</t>
+          <t>https://plaukuosena.lt/curl-passion-shampoo-sampunas-garbanotiems-plaukams</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a9008a8a-9ca2-40f4-af88-644753de306f.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9abc0fee-56a1-407b-b57b-cc3b8f2b64d8.webp</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3665,7 +3737,7 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3677,12 +3749,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CURL-PASSION-LEAVE-CON-NA</t>
+          <t>CURL-PASSION-SHAPER-PRD-NA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CURL PASSION LEAVE IN nenuskalaujamas kondicionierius</t>
+          <t>CURL PASSION SHAPER garbanotų plaukų formavimo priemonė</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3692,7 +3764,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>22.30</t>
+          <t>29.30</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3702,17 +3774,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/curl-passion-leave-in-nenuskalaujamas-kondicionierius</t>
+          <t>https://plaukuosena.lt/curl-passion-shaper-garbanotu-plauku-formavimo-priemone</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/03bbe43d-1d1e-40a3-b7eb-95a6c413e398.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c0e31067-f847-411e-8829-46d992b004de.png</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3723,7 +3795,7 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3735,22 +3807,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CURL-PASSION-GARBANOT-MSK-NA</t>
+          <t>DAVI-APSAUGIN-SKYSTIS-PRD-250ML</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CURL PASSION MASK kaukė garbanotiems plaukams</t>
+          <t>DAVINES APSAUGINIS SKYSTIS PLAUKAMS PH: 4 | MELU | 250ML</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CURL</t>
+          <t>DAVINES</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3760,17 +3832,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/curl-passion-mask-kauke-garbanotiems-plaukams</t>
+          <t>https://plaukuosena.lt/apsauginis-skystis-plaukams-ph-4-or-melu</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/fd2c5cb6-c6fa-4919-b1b8-4581b2ab8a84.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/958d66cb-6795-4885-88d2-e4748c0b2e4f.webp</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3778,10 +3850,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8004608242505</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3793,22 +3869,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CURL-PASSION-PERFECTI-CRM-NA</t>
+          <t>DAVI-BLIZGESY-APSAUGA-PRD-150ML</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CURL PASSION PERFECTIONIST garbanų formavimo kremas</t>
+          <t>DAVINES Blizgesys ir apsauga šviesiems plaukams | Heart of Glass | 150ML</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CURL</t>
+          <t>DAVINES</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>22.30</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3818,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/curl-passion-perfectionist-garbanu-formavimo-kremas</t>
+          <t>https://plaukuosena.lt/blizgesys-ir-apsauga-sviesiems-plaukams-or-heart-of-glass</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/92fc1d2f-8e70-43aa-9649-4bf29c9685eb.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/75106ebc-f23c-459b-aebd-1f78c58b78e0.png</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3836,10 +3912,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8004608294702</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3851,22 +3931,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CURL-PASSION-GARBANOT-SHA-NA</t>
+          <t>DAVI-GEROS-SAVIJAUT-SHA-250ML</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CURL PASSION SHAMPOO šampūnas garbanotiems plaukams</t>
+          <t>DAVINES GEROS SAVIJAUTOS ŠAMPŪNAS PH: 5.5 | WELL–BEING | 250ML</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CURL</t>
+          <t>DAVINES</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3876,12 +3956,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/curl-passion-shampoo-sampunas-garbanotiems-plaukams</t>
+          <t>https://plaukuosena.lt/geros-savijautos-sampunas-ph-55-or-well-being</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9abc0fee-56a1-407b-b57b-cc3b8f2b64d8.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7510575f-99a2-4412-9ed4-4950f2f034fc.webp</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3894,10 +3974,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8004608256502</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3909,22 +3993,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CURL-PASSION-SHAPER-PRD-NA</t>
+          <t>DAVI-GREITAI-PLAUKUS-MSK-50ML</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CURL PASSION SHAPER garbanotų plaukų formavimo priemonė</t>
+          <t>DAVINES GREITAI PLAUKUS ATKURIANTI KAUKĖ | THE QUICK FIX CIRCLE | 50ML</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CURL</t>
+          <t>DAVINES</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>29.30</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3934,17 +4018,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/curl-passion-shaper-garbanotu-plauku-formavimo-priemone</t>
+          <t>https://plaukuosena.lt/greitai-plaukus-atkurianti-kauke-or-the-quick-fix-circle</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c0e31067-f847-411e-8829-46d992b004de.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/333ee115-9451-4bf1-b2b6-62c9b9b773df.png</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3952,10 +4036,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>50ml</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>58688808</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3967,12 +4055,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DAVI-APSAUGIN-SKYSTIS-PRD-NA</t>
+          <t>DAVI-DAZYTIEM-PH-CON-250ML</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DAVINES APSAUGINIS SKYSTIS PLAUKAMS PH: 4 | MELU</t>
+          <t>DAVINES KONDICIONIERIUS DAŽYTIEMS PLAUKAMS PH: 4 | MINU | 250ML</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3982,7 +4070,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3992,17 +4080,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/apsauginis-skystis-plaukams-ph-4-or-melu</t>
+          <t>https://plaukuosena.lt/kondicionierius-dazytiems-plaukams-ph-4-or-minu</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/958d66cb-6795-4885-88d2-e4748c0b2e4f.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7ec299ab-4d5e-4428-8acb-1d7b2e351dc6.webp</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4010,10 +4098,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8004608275879</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4025,12 +4117,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DAVI-BLIZGESY-APSAUGA-PRD-NA</t>
+          <t>DAVI-PAZEISTI-PH-CON-250ML</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DAVINES Blizgesys ir apsauga šviesiems plaukams | Heart of Glass</t>
+          <t>DAVINES KONDICIONIERIUS PAŽEISTIEMS PLAUKAMS PH: 4 | MELU | 250ML</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4040,7 +4132,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4050,17 +4142,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/blizgesys-ir-apsauga-sviesiems-plaukams-or-heart-of-glass</t>
+          <t>https://plaukuosena.lt/kondicionierius-pazeistiems-plaukams-ph-4-or-melu</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/75106ebc-f23c-459b-aebd-1f78c58b78e0.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/27c868d9-4d9f-41dd-b2d1-57259b7ee377.webp</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4068,10 +4160,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8004608276722</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4083,12 +4179,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DAVI-GEROS-SAVIJAUT-SHA-NA</t>
+          <t>DAVI-REFIL-GARBANUO-SHA-500ML</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DAVINES GEROS SAVIJAUTOS ŠAMPŪNAS PH: 5.5 | WELL–BEING</t>
+          <t>DAVINES REFIL ŠAMPŪNAS GARBANUOTIEMS PLAUKAMS PH: 5.3 | LOVE CURL | 500ML</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4098,7 +4194,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4108,12 +4204,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/geros-savijautos-sampunas-ph-55-or-well-being</t>
+          <t>https://plaukuosena.lt/davines-sampunas-garbanuotiems-plaukams-ph-53-or-love-curl</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7510575f-99a2-4412-9ed4-4950f2f034fc.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/abd9f475-8e18-4122-854e-e9807ba878f6.webp</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4126,10 +4222,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8004608280654</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4141,12 +4241,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DAVI-GREITAI-PLAUKUS-MSK-NA</t>
+          <t>DAVI-TIESINAN-PH-SHA-250ML</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DAVINES GREITAI PLAUKUS ATKURIANTI KAUKĖ | THE QUICK FIX CIRCLE</t>
+          <t>DAVINES TIESINANTIS ŠAMPŪNAS PH: 5.3 | LOVE | 250ML</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4156,7 +4256,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4166,17 +4266,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/greitai-plaukus-atkurianti-kauke-or-the-quick-fix-circle</t>
+          <t>https://plaukuosena.lt/tiesinantis-sampunas-ph-53-or-love</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/333ee115-9451-4bf1-b2b6-62c9b9b773df.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7691e5f8-be0d-4245-88b7-bade815e0174.webp</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4184,10 +4284,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8004608274865</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4199,12 +4303,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DAVI-DAZYTIEM-PH-CON-NA</t>
+          <t>DAVI-VALANTIS-NUO-SHA-250ML</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DAVINES KONDICIONIERIUS DAŽYTIEMS PLAUKAMS PH: 4 | MINU</t>
+          <t>DAVINES VALANTIS ŠAMPŪNAS NUO PLEISKANŲ PH: 4.9 | PURIFYING | 250ML</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4224,17 +4328,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/kondicionierius-dazytiems-plaukams-ph-4-or-minu</t>
+          <t>https://plaukuosena.lt/valantis-sampunas-nuo-pleiskanu-ph-49-or-purifying</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7ec299ab-4d5e-4428-8acb-1d7b2e351dc6.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d4d74325-9146-4a5a-9026-794f20ec97be.webp</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4242,10 +4346,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8004608236580</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4257,12 +4365,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DAVI-PAZEISTI-PH-CON-NA</t>
+          <t>DAVI-DAZYTIEM-PH-SHA-250ML</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DAVINES KONDICIONIERIUS PAŽEISTIEMS PLAUKAMS PH: 4 | MELU</t>
+          <t>DAVINES ŠAMPŪNAS DAŽYTIEMS PLAUKAMS PH: 5.3 | MINU | 250ML</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4282,17 +4390,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/kondicionierius-pazeistiems-plaukams-ph-4-or-melu</t>
+          <t>https://plaukuosena.lt/sampunas-dazytiems-plaukams-ph-53-or-minu</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/27c868d9-4d9f-41dd-b2d1-57259b7ee377.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6a542969-9c0b-4be9-8aba-c7a8bd9ade42.webp</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4300,10 +4408,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8004608242550</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4315,12 +4427,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DAVI-TIESINAN-PH-SHA-NA</t>
+          <t>DAVI-PAZEISTI-PH-SHA-250ML</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DAVINES TIESINANTIS ŠAMPŪNAS PH: 5.3 | LOVE</t>
+          <t>DAVINES ŠAMPŪNAS PAŽEISTIEMS PLAUKAMS PH: 5.3 | MELU | 250ML</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4340,12 +4452,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/tiesinantis-sampunas-ph-53-or-love</t>
+          <t>https://plaukuosena.lt/sampunas-pazeistiems-plaukams-ph-53-or-melu</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7691e5f8-be0d-4245-88b7-bade815e0174.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9e665e1f-46f0-43ad-a545-d89ee5dbd7d5.webp</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4358,10 +4470,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8004608242444</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4373,12 +4489,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DAVI-VALANTIS-NUO-SHA-NA</t>
+          <t>DAVI-GAUSINIM-PH-SHA-250ML</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DAVINES VALANTIS ŠAMPŪNAS NUO PLEISKANŲ PH: 4.9 | PURIFYING</t>
+          <t>DAVINES ŠAMPŪNAS PLAUKŲ GAUSINIMUI PH: 5.3 | VOLU | 250ML</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4398,12 +4514,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/valantis-sampunas-nuo-pleiskanu-ph-49-or-purifying</t>
+          <t>https://plaukuosena.lt/sampunas-plauku-gausinimui-ph-53-or-volu</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d4d74325-9146-4a5a-9026-794f20ec97be.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a13b2f02-8b1b-4288-9602-b6b3af8b7c0a.webp</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4416,10 +4532,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8004608242512</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4431,12 +4551,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DAVI-DAZYTIEM-PH-SHA-NA</t>
+          <t>DAVI-SVIESIUS-PLAUKUS-CON-250ML</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DAVINES ŠAMPŪNAS DAŽYTIEMS PLAUKAMS PH: 5.3 | MINU</t>
+          <t>DAVINES Šviesius plaukus maitinantis kondicionierius | Heart of Glass | 250ML</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4446,7 +4566,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4456,17 +4576,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/sampunas-dazytiems-plaukams-ph-53-or-minu</t>
+          <t>https://plaukuosena.lt/hand-soap-giguos</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6a542969-9c0b-4be9-8aba-c7a8bd9ade42.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/729b8d37-dea5-416e-a920-52cc0231c3bb.png</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4474,10 +4594,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8004608271697</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4489,12 +4613,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DAVI-GARBANUO-PH-SHA-NA</t>
+          <t>DAVI-SVIESIUS-PLAUKUS-MSK-150ML</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DAVINES ŠAMPŪNAS GARBANUOTIEMS PLAUKAMS PH: 5.3 | LOVE CURL</t>
+          <t>DAVINES Šviesius plaukus stiprinanti kaukė | Heart of Glass | 150ml</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4504,7 +4628,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4514,17 +4638,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/davines-sampunas-garbanuotiems-plaukams-ph-53-or-love-curl</t>
+          <t>https://plaukuosena.lt/sviesius-plaukus-stiprinanti-kauke-or-heart-of-glass</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/abd9f475-8e18-4122-854e-e9807ba878f6.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7062fec7-9648-4348-95e4-b6109a41426c.webp</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4532,10 +4656,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8004608272526</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4547,22 +4675,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DAVI-PAZEISTI-PH-SHA-NA</t>
+          <t>DEEP-CONDITIO-INTENSYV-MSK-NA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DAVINES ŠAMPŪNAS PAŽEISTIEMS PLAUKAMS PH: 5.3 | MELU</t>
+          <t>DEEP CONDITIONING MASK intensyvaus poveikio kaukė dažytiems plaukams</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DAVINES</t>
+          <t>DEEP</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4572,17 +4700,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/sampunas-pazeistiems-plaukams-ph-53-or-melu</t>
+          <t>https://plaukuosena.lt/deep-conditioning-mask-intensyvaus-poveikio-kauke-dazytiems-plaukams</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9e665e1f-46f0-43ad-a545-d89ee5dbd7d5.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e6b9db3b-a6bb-4912-b17a-c6d3e9600555.webp</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4593,7 +4721,7 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4605,22 +4733,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DAVI-GAUSINIM-PH-SHA-NA</t>
+          <t>EIMI-ABSOLUTE-SET-PRD-300ML</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DAVINES ŠAMPŪNAS PLAUKŲ GAUSINIMUI PH: 5.3 | VOLU</t>
+          <t>EIMI Absolute Set lakas # 4+, 300 ml</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DAVINES</t>
+          <t>EIMI</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4630,17 +4758,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/sampunas-plauku-gausinimui-ph-53-or-volu</t>
+          <t>https://plaukuosena.lt/eimi-absolute-set-lakas-4-300-ml</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a13b2f02-8b1b-4288-9602-b6b3af8b7c0a.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4609936e-f051-43d0-bf28-23a210169d95.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4648,10 +4776,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4663,22 +4795,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DAVI-SVIESIUS-PLAUKUS-CON-100ML</t>
+          <t>EIMI-DRY-ME-SHA-180ML</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DAVINES Šviesius plaukus maitinantis kondicionierius | Heart of Glass</t>
+          <t>EIMI Dry Me Dry sausas šampūnas #1, 180 ml</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DAVINES</t>
+          <t>EIMI</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4688,17 +4820,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/hand-soap-giguos</t>
+          <t>https://plaukuosena.lt/eimi-dry-me-dry-sausas-sampunas-1-180-ml</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/729b8d37-dea5-416e-a920-52cc0231c3bb.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/685481b5-65b1-4e9e-a0d1-967851f46e02.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4708,12 +4840,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>180ml</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4725,22 +4857,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DAVI-SVIESIUS-PLAUKUS-MSK-NA</t>
+          <t>EIMI-EXTRA-VOLUME-FOA-300ML</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DAVINES Šviesius plaukus stiprinanti kaukė | Heart of Glass</t>
+          <t>EIMI Extra Volume putos #3, 300 ml</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DAVINES</t>
+          <t>EIMI</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4750,17 +4882,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/sviesius-plaukus-stiprinanti-kauke-or-heart-of-glass</t>
+          <t>https://plaukuosena.lt/eimi-extra-volume-putos-3-300-ml</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7062fec7-9648-4348-95e4-b6109a41426c.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4ce5d05e-e0eb-4588-9266-14c75d59b5b2.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4768,10 +4900,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4783,22 +4919,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DEEP-CONDITIO-INTENSYV-MSK-NA</t>
+          <t>EIMI-FLEXIBLE-FINISH-PRD-250ML</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DEEP CONDITIONING MASK intensyvaus poveikio kaukė dažytiems plaukams</t>
+          <t>EIMI Flexible Finish lakas #2, 250 ml</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DEEP</t>
+          <t>EIMI</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4808,17 +4944,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-conditioning-mask-intensyvaus-poveikio-kauke-dazytiems-plaukams</t>
+          <t>https://plaukuosena.lt/eimi-flexible-finish-lakas-2-250-ml</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e6b9db3b-a6bb-4912-b17a-c6d3e9600555.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/690edb16-bb3f-41bc-a6d0-6e1c32ae98d2.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4826,10 +4962,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4841,22 +4981,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DEEP-MOISTURE-MSK-NA</t>
+          <t>EIMI-FLOWING-FORM-PRD-100ML</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DEEP MOISTURE kaukė</t>
+          <t>EIMI Flowing Form balzamas #2, 100 ml</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DEEP</t>
+          <t>EIMI</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>24.90</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4866,17 +5006,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-moisture-kauke</t>
+          <t>https://plaukuosena.lt/eimi-flowing-form-balzamas-2-100-ml</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/02191c64-c0d0-435c-acfd-4abe70c7d286.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1544dbd7-35f9-42b5-92ec-d0cd6f9943ab.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4884,10 +5024,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4899,12 +5043,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EIMI-ABSOLUTE-SET-PRD-300ML</t>
+          <t>EIMI-GLAM-MIST-PRD-200ML</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EIMI Absolute Set lakas # 4+, 300 ml</t>
+          <t>EIMI Glam Mist lakas / blizgis #1, 200 ml</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4914,7 +5058,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>27.00</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4924,12 +5068,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-absolute-set-lakas-4-300-ml</t>
+          <t>https://plaukuosena.lt/eimi-glam-mist-lakas-blizgis-1-200-ml</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4609936e-f051-43d0-bf28-23a210169d95.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/47a0bc9e-6340-462e-a327-ccd1efe76dda.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4944,12 +5088,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4961,12 +5105,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EIMI-DRY-ME-SHA-180ML</t>
+          <t>EIMI-MISTIFY-ME-PRD-300ML</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIMI Dry Me Dry sausas šampūnas #1, 180 ml</t>
+          <t>EIMI Mistify Me Light lakas #2, 300 ml</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4986,17 +5130,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-dry-me-dry-sausas-sampunas-1-180-ml</t>
+          <t>https://plaukuosena.lt/eimi-mistify-me-light-lakas-2-300-ml</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/685481b5-65b1-4e9e-a0d1-967851f46e02.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f44de339-ff78-47c5-bef9-4840e03045b9.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5006,12 +5150,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>180ml</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5023,12 +5167,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EIMI-EXTRA-VOLUME-FOA-300ML</t>
+          <t>EIMI-MISTIFY-ME-PRD-300ML-4AE5</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIMI Extra Volume putos #3, 300 ml</t>
+          <t>EIMI Mistify Me Strong lakas #3, 300 ml</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5038,7 +5182,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5048,12 +5192,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-extra-volume-putos-3-300-ml</t>
+          <t>https://plaukuosena.lt/eimi-mistify-me-strong-lakas-3-300-ml</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4ce5d05e-e0eb-4588-9266-14c75d59b5b2.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/25a65e8a-b11d-4d44-9b95-7db4a88549e5.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5073,7 +5217,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5085,12 +5229,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EIMI-FLEXIBLE-FINISH-PRD-250ML</t>
+          <t>EIMI-NUTRICUR-BOOST-FOA-300ML</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIMI Flexible Finish lakas #2, 250 ml</t>
+          <t>EIMI NUTRICURLS BOOST BOUNCE 72h švelnios putos garbanoms #2, 300 ml</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5100,7 +5244,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>23.50</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5110,12 +5254,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-flexible-finish-lakas-2-250-ml</t>
+          <t>https://plaukuosena.lt/eimi-nutricurls-boost-bounce-72h-svelnios-putos-garbanoms-2-300-ml</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/690edb16-bb3f-41bc-a6d0-6e1c32ae98d2.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e1731c4e-394c-435e-b753-e948d7cfbf89.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5130,12 +5274,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>250ml</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5147,12 +5291,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EIMI-FLOWING-FORM-PRD-100ML</t>
+          <t>EIMI-NATURAL-VOLUME-FOA-300ML</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIMI Flowing Form balzamas #2, 100 ml</t>
+          <t>EIMI Natural Volume putos #2, 300 ml</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5162,7 +5306,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5172,12 +5316,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-flowing-form-balzamas-2-100-ml</t>
+          <t>https://plaukuosena.lt/eimi-natural-volume-putos-2-300-ml</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1544dbd7-35f9-42b5-92ec-d0cd6f9943ab.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9473f762-aafe-44c0-9acb-7e105a4f8d11.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5192,12 +5336,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5209,12 +5353,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EIMI-GLAM-MIST-PRD-200ML</t>
+          <t>EIMI-NUTRICUR-CURL-CRM-150ML</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIMI Glam Mist lakas / blizgis #1, 200 ml</t>
+          <t>EIMI Nutricurls Curl Shaper kremas #2, 150 ml</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5224,7 +5368,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>27.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5234,12 +5378,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-glam-mist-lakas-blizgis-1-200-ml</t>
+          <t>https://plaukuosena.lt/eimi-nutricurls-curl-shaper-kremas-2-150-ml</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/47a0bc9e-6340-462e-a327-ccd1efe76dda.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/05eb6823-d484-4232-a92a-05a825b67fc3.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5254,12 +5398,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5271,12 +5415,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EIMI-MISTIFY-ME-PRD-300ML</t>
+          <t>EIMI-NUTRICUR-FRESH-PRD-150ML</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIMI Mistify Me Light lakas #2, 300 ml</t>
+          <t>EIMI Nutricurls Fresh Up purškalas #1, 150 ml</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5286,7 +5430,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5296,17 +5440,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-mistify-me-light-lakas-2-300-ml</t>
+          <t>https://plaukuosena.lt/eimi-nutricurls-fresh-up-purskalas-1-150-ml</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f44de339-ff78-47c5-bef9-4840e03045b9.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c849de07-4e68-4b6b-b4ed-a59ac843799e.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5316,12 +5460,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5333,12 +5477,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EIMI-MISTIFY-ME-PRD-300ML-4AE5</t>
+          <t>EIMI-NUTRICUR-SOFT-FOA-200ML</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIMI Mistify Me Strong lakas #3, 300 ml</t>
+          <t>EIMI Nutricurls Soft Twirl putos #2, 200 ml</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5348,7 +5492,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>26.50</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5358,12 +5502,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-mistify-me-strong-lakas-3-300-ml</t>
+          <t>https://plaukuosena.lt/eimi-nutricurls-soft-twirl-putos-2-200-ml</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/25a65e8a-b11d-4d44-9b95-7db4a88549e5.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/01c8bbb3-0429-4f4c-9d1e-508b94ae4ba9.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5378,12 +5522,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5395,12 +5539,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EIMI-NUTRICUR-BOOST-FOA-300ML</t>
+          <t>EIMI-OCEAN-SPRITZ-PRD-150ML</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIMI NUTRICURLS BOOST BOUNCE 72h švelnios putos garbanoms #2, 300 ml</t>
+          <t>EIMI Ocean Spritz purškalas su druska #2, 150 ml</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5410,7 +5554,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>23.50</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5420,17 +5564,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-nutricurls-boost-bounce-72h-svelnios-putos-garbanoms-2-300-ml</t>
+          <t>https://plaukuosena.lt/eimi-ocean-spritz-purskalas-su-druska-2-150-ml</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e1731c4e-394c-435e-b753-e948d7cfbf89.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ad6f5336-91da-4ba8-8a8d-12468afe45c7.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5440,12 +5584,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5457,12 +5601,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EIMI-NATURAL-VOLUME-FOA-300ML</t>
+          <t>EIMI-PEARL-STYLER-GEL-100ML</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIMI Natural Volume putos #2, 300 ml</t>
+          <t>EIMI Pearl Styler gelis #3, 100 ml</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5472,7 +5616,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5482,17 +5626,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-natural-volume-putos-2-300-ml</t>
+          <t>https://plaukuosena.lt/eimi-pearl-styler-gelis-3-100-ml</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9473f762-aafe-44c0-9acb-7e105a4f8d11.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/144e8417-a5e5-4fb1-a96d-9ea6632bffa9.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų geliai</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5502,12 +5646,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5519,12 +5663,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EIMI-NUTRICUR-CURL-CRM-150ML</t>
+          <t>EIMI-PERFECT-ME-PRD-100ML</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIMI Nutricurls Curl Shaper kremas #2, 150 ml</t>
+          <t>EIMI Perfect Me losjonas #1, 100 ml</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5534,7 +5678,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5544,12 +5688,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-nutricurls-curl-shaper-kremas-2-150-ml</t>
+          <t>https://plaukuosena.lt/eimi-perfect-me-losjonas-1-100-ml</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/05eb6823-d484-4232-a92a-05a825b67fc3.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c2858f89-5b77-4ca7-9214-22d5758e79fd.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5564,12 +5708,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5581,12 +5725,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EIMI-NUTRICUR-FRESH-PRD-150ML</t>
+          <t>EIMI-PERFECT-SETTING-PRD-150ML</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EIMI Nutricurls Fresh Up purškalas #1, 150 ml</t>
+          <t>EIMI Perfect Setting purškiamas plaukų losjonas #2, 150 ml</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5596,7 +5740,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5606,12 +5750,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-nutricurls-fresh-up-purskalas-1-150-ml</t>
+          <t>https://plaukuosena.lt/eimi-perfect-setting-purskiamas-plauku-losjonas-2-150-ml</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c849de07-4e68-4b6b-b4ed-a59ac843799e.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/831cbe0a-7ea7-4da3-9d64-a7da293455c7.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5631,7 +5775,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5643,12 +5787,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EIMI-NUTRICUR-SOFT-FOA-200ML</t>
+          <t>EIMI-ROOT-SHOOT-FOA-200ML</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EIMI Nutricurls Soft Twirl putos #2, 200 ml</t>
+          <t>EIMI Root Shoot purškiamos putos #2, 200 ml</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5658,7 +5802,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>23.50</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5668,17 +5812,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-nutricurls-soft-twirl-putos-2-200-ml</t>
+          <t>https://plaukuosena.lt/eimi-root-shoot-purskiamos-putos-2-200-ml</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/01c8bbb3-0429-4f4c-9d1e-508b94ae4ba9.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/20d544d5-a43b-420a-8011-c64e7eae68ee.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5693,7 +5837,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5705,12 +5849,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EIMI-OCEAN-SPRITZ-PRD-150ML</t>
+          <t>EIMI-SHAPE-ME-GEL-150ML</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EIMI Ocean Spritz purškalas su druska #2, 150 ml</t>
+          <t>EIMI SHAPE ME 48 val plaukų formą išlaikantis gelis #2, 150 ml</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5720,7 +5864,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5730,17 +5874,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-ocean-spritz-purskalas-su-druska-2-150-ml</t>
+          <t>https://plaukuosena.lt/eimi-shape-me-48-val-plauku-forma-islaikantis-gelis-2-150-ml</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ad6f5336-91da-4ba8-8a8d-12468afe45c7.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cf24ed41-364c-4e1f-8323-ab8095dae01b.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų geliai</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5755,7 +5899,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5767,12 +5911,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EIMI-PEARL-STYLER-GEL-100ML</t>
+          <t>EIMI-SHAPE-CONTROL-FOA-300ML</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EIMI Pearl Styler gelis #3, 100 ml</t>
+          <t>EIMI Shape Control putos #4, 300 ml</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5782,7 +5926,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5792,17 +5936,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-pearl-styler-gelis-3-100-ml</t>
+          <t>https://plaukuosena.lt/eimi-shape-control-putos-4-300-ml</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/144e8417-a5e5-4fb1-a96d-9ea6632bffa9.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bbbd8914-6602-4103-878b-c10b2612242f.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Plaukų geliai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5812,12 +5956,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5829,12 +5973,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EIMI-PERFECT-ME-PRD-100ML</t>
+          <t>EIMI-SUGAR-LIFT-PRD-150ML</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EIMI Perfect Me losjonas #1, 100 ml</t>
+          <t>EIMI Sugar Lift purškalas apimčiai #3, 150 ml</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5844,7 +5988,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5854,17 +5998,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-perfect-me-losjonas-1-100-ml</t>
+          <t>https://plaukuosena.lt/eimi-sugar-lift-purskalas-apimciai-3-150-ml</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c2858f89-5b77-4ca7-9214-22d5758e79fd.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0e33562e-8331-4101-a44a-730c2fbfb1af.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5874,12 +6018,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5891,12 +6035,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EIMI-PERFECT-SETTING-PRD-150ML</t>
+          <t>EIMI-SUPER-SET-PRD-300ML</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EIMI Perfect Setting purškiamas plaukų losjonas #2, 150 ml</t>
+          <t>EIMI Super Set lakas #4, 300 ml</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5906,7 +6050,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5916,17 +6060,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-perfect-setting-purskiamas-plauku-losjonas-2-150-ml</t>
+          <t>https://plaukuosena.lt/eimi-super-set-lakas-4-300-ml</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/831cbe0a-7ea7-4da3-9d64-a7da293455c7.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a4229f5f-7428-44ab-b006-da4faa1587a9.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5936,12 +6080,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5953,12 +6097,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EIMI-ROOT-SHOOT-FOA-200ML</t>
+          <t>EIMI-THERMAL-IMAGE-PRD-150ML</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EIMI Root Shoot purškiamos putos #2, 200 ml</t>
+          <t>EIMI Thermal Image purškalas nuo karščio #2, 150 ml</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5968,7 +6112,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>23.50</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5978,12 +6122,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-root-shoot-purskiamos-putos-2-200-ml</t>
+          <t>https://plaukuosena.lt/eimi-thermal-image-purskalas-nuo-karscio-2-150-ml</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/20d544d5-a43b-420a-8011-c64e7eae68ee.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/27f63de3-6f4d-4932-9873-48b4fbc2f296.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5998,12 +6142,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6015,22 +6159,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EIMI-SHAPE-ME-GEL-150ML</t>
+          <t>FUSI-INTENSYV-PLAUKUS-CON-NA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EIMI SHAPE ME 48 val plaukų formą išlaikantis gelis #2, 150 ml</t>
+          <t>FUSION intensyviai plaukus atkuriantis kondicionierius</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>FUSION</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6040,17 +6184,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-shape-me-48-val-plauku-forma-islaikantis-gelis-2-150-ml</t>
+          <t>https://plaukuosena.lt/fusion-intensyviai-plaukus-atkuriantis-kondicionierius</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cf24ed41-364c-4e1f-8323-ab8095dae01b.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9f9fdb95-485e-476c-b6b2-486e49f19cfe.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Plaukų geliai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6058,14 +6202,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>150ml</t>
-        </is>
-      </c>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6077,22 +6217,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EIMI-SHAPE-CONTROL-FOA-300ML</t>
+          <t>GLIS-ARGAN-ARGANU-OIL-NA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EIMI Shape Control putos #4, 300 ml</t>
+          <t>GLISTENING ARGAN OIL arganų aliejus</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>GLISTENING</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6102,17 +6242,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-shape-control-putos-4-300-ml</t>
+          <t>https://plaukuosena.lt/glistening-argan-oil-arganu-aliejus</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bbbd8914-6602-4103-878b-c10b2612242f.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e8ec0139-6902-4e09-8f7e-92dbc42a0048.png</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6120,14 +6260,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>300ml</t>
-        </is>
-      </c>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6139,42 +6275,38 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EIMI-SUGAR-LIFT-PRD-150ML</t>
+          <t>GARB-PLAUKAI-PRIEMONE-PRD-NA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EIMI Sugar Lift purškalas apimčiai #3, 150 ml</t>
+          <t>Garbanoti plaukai | Priežiūros priemonės garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>EIMI</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>22.00</t>
-        </is>
-      </c>
+          <t>Garbanoti</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-sugar-lift-purskalas-apimciai-3-150-ml</t>
+          <t>https://plaukuosena.lt/garbanoti-plaukai</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0e33562e-8331-4101-a44a-730c2fbfb1af.jpg</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6182,41 +6314,37 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>150ml</t>
-        </is>
-      </c>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EIMI-SUPER-SET-PRD-300ML</t>
+          <t>ICY-BLOND-SVIESIEM-CON-NA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EIMI Super Set lakas #4, 300 ml</t>
+          <t>ICY BLOND CONDITIONER kondicionierius šviesiems plaukams</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6226,17 +6354,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-super-set-lakas-4-300-ml</t>
+          <t>https://plaukuosena.lt/icy-blond-conditioner-kondicionierius-sviesiems-plaukams</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a4229f5f-7428-44ab-b006-da4faa1587a9.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/43ff1e78-0eaf-481b-8b24-b56b697a19c0.png</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6244,14 +6372,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>300ml</t>
-        </is>
-      </c>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6263,22 +6387,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EIMI-THERMAL-IMAGE-PRD-150ML</t>
+          <t>ICY-BLOND-SVIESIEM-SHA-NA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EIMI Thermal Image purškalas nuo karščio #2, 150 ml</t>
+          <t>ICY BLOND SHAMPOO šampūnas šviesiems plaukams</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6288,17 +6412,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-thermal-image-purskalas-nuo-karscio-2-150-ml</t>
+          <t>https://plaukuosena.lt/icy-blond-shampoo-sampunas-sviesiems-plaukams</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/27f63de3-6f4d-4932-9873-48b4fbc2f296.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cac84108-877e-4753-baa2-36d67665c464.png</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6306,14 +6430,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>150ml</t>
-        </is>
-      </c>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6325,22 +6445,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FUSI-INTENSYV-PLAUKUS-CON-NA</t>
+          <t>INCR-MILK-FLOWER-PRD-NA</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FUSION intensyviai plaukus atkuriantis kondicionierius</t>
+          <t>INCREDIBLE MILK FLOWER FRAGRANCE plaukus kondicionuojantis pienelis</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FUSION</t>
+          <t>INCREDIBLE</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>18.90</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6350,17 +6470,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/fusion-intensyviai-plaukus-atkuriantis-kondicionierius</t>
+          <t>https://plaukuosena.lt/incredible-milk-flower-fragrance-plaukus-kondicionuojantis-pienelis</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9f9fdb95-485e-476c-b6b2-486e49f19cfe.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/728171ea-b913-4828-bd2e-5816d611a9a2.png</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6371,7 +6491,7 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6383,22 +6503,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GLIS-ARGAN-ARGANU-OIL-NA</t>
+          <t>INST-STIPRINA-SHA-NA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GLISTENING ARGAN OIL arganų aliejus</t>
+          <t>INSTALIGHT SHAMPOO stiprinamasis šampūnas plaukams</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GLISTENING</t>
+          <t>INSTALIGHT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6408,17 +6528,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/glistening-argan-oil-arganu-aliejus</t>
+          <t>https://plaukuosena.lt/instalight-shampoo-stiprinamasis-sampunas-plaukams</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e8ec0139-6902-4e09-8f7e-92dbc42a0048.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40bb94ca-92af-4d11-9f97-87579e8d0d24.png</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Plaukų aliejai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6429,7 +6549,7 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6441,38 +6561,42 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GARB-PLAUKAI-PRIEMONE-PRD-NA</t>
+          <t>INST-SKYSTA-MSK-NA</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Garbanoti plaukai | Priežiūros priemonės garbanotiems plaukams</t>
+          <t>INSTALOTION skysta kaukė plaukams</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Garbanoti</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>INSTALOTION</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/garbanoti-plaukai</t>
+          <t>https://plaukuosena.lt/instalotion-skysta-kauke-plaukams</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b00458f3-53bf-48dc-a159-d98ece3d546d.webp</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6483,34 +6607,34 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ICY-BLOND-SVIESIEM-CON-NA</t>
+          <t>INTE-INCREDIB-APSAUGIN-OIL-NA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ICY BLOND CONDITIONER kondicionierius šviesiems plaukams</t>
+          <t>INTEGRITY INCREDIBLE OIL apsauginis atkuriamasis aliejus</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>INTEGRITY</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6520,17 +6644,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/icy-blond-conditioner-kondicionierius-sviesiems-plaukams</t>
+          <t>https://plaukuosena.lt/integrity-incredible-oil-apsauginis-atkuriamasis-aliejus</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/43ff1e78-0eaf-481b-8b24-b56b697a19c0.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/80d0d251-f362-4ff0-aa1f-23a517459152.png</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6541,7 +6665,7 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6553,22 +6677,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ICY-BLOND-SVIESIEM-SHA-NA</t>
+          <t>INTE-LEAVE-IN-SPR-NA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ICY BLOND SHAMPOO šampūnas šviesiems plaukams</t>
+          <t>INTEGRITY LEAVE IN purškiklis pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>INTEGRITY</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6578,17 +6702,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/icy-blond-shampoo-sampunas-sviesiems-plaukams</t>
+          <t>https://plaukuosena.lt/integrity-leave-in-purskiklis-pazeistiems-plaukams</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cac84108-877e-4753-baa2-36d67665c464.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f74f788d-213a-40fc-8be9-75aa8e85a177.webp</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6599,7 +6723,7 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6611,22 +6735,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>INCR-MILK-FLOWER-PRD-NA</t>
+          <t>INTE-INTENSIV-TREATMEN-MSK-NA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>INCREDIBLE MILK FLOWER FRAGRANCE plaukus kondicionuojantis pienelis</t>
+          <t>INTEGRITY&amp;STRENGTH INTENSIVE TREATMENT stipriai maitinanti kaukė pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>INCREDIBLE</t>
+          <t>INTEGRITY&amp;STRENGTH</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>18.90</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6636,17 +6760,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/incredible-milk-flower-fragrance-plaukus-kondicionuojantis-pienelis</t>
+          <t>https://plaukuosena.lt/integrityandstrength-intensive-treatment-stipriai-maitinanti-kauke-pazeistiems-plaukams</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/728171ea-b913-4828-bd2e-5816d611a9a2.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9d17895a-b0dc-4293-9fb5-25d4e81c7172.png</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6657,7 +6781,7 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6669,22 +6793,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>INST-STIPRINA-SHA-NA</t>
+          <t>INTE-NOURISHI-MAITINAN-CON-NA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>INSTALIGHT SHAMPOO stiprinamasis šampūnas plaukams</t>
+          <t>INTEGRITY&amp;STRENGTH NOURISHING CONDITIONER maitinantis kondicionierius</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>INSTALIGHT</t>
+          <t>INTEGRITY&amp;STRENGTH</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6694,17 +6818,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/instalight-shampoo-stiprinamasis-sampunas-plaukams</t>
+          <t>https://plaukuosena.lt/integrityandstrength-nourishing-conditioner-maitinantis-kondicionierius</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40bb94ca-92af-4d11-9f97-87579e8d0d24.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d7eb8303-1738-41b2-8aad-585928205249.png</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6715,7 +6839,7 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6727,22 +6851,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>INST-SKYSTA-MSK-NA</t>
+          <t>INTE-NOURISHI-MAITINAN-SHA-NA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>INSTALOTION skysta kaukė plaukams</t>
+          <t>INTEGRITY&amp;STRENGTH NOURISHING SHAMPOO maitinantis šampūnas pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>INSTALOTION</t>
+          <t>INTEGRITY&amp;STRENGTH</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6752,17 +6876,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/instalotion-skysta-kauke-plaukams</t>
+          <t>https://plaukuosena.lt/integrityandstrength-nourishing-shampoo-maitinantis-sampunas-pazeistiems-plaukams</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b00458f3-53bf-48dc-a159-d98ece3d546d.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cf1f1398-28da-45f8-9ea9-a3c1e85c7ff6.png</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6773,7 +6897,7 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6785,22 +6909,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>INTE-INCREDIB-APSAUGIN-OIL-NA</t>
+          <t>INTE-REPAIRIN-HAIR-PRD-NA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>INTEGRITY INCREDIBLE OIL apsauginis atkuriamasis aliejus</t>
+          <t>INTEGRITY&amp;STRENGTH REPAIRING HAIR LOTION stiprus proteinų koncentratas plaukams</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>INTEGRITY</t>
+          <t>INTEGRITY&amp;STRENGTH</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>56.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6810,17 +6934,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrity-incredible-oil-apsauginis-atkuriamasis-aliejus</t>
+          <t>https://plaukuosena.lt/integrityandstrength-repairing-hair-lotion-stiprus-proteinu-koncentratas-plaukams</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/80d0d251-f362-4ff0-aa1f-23a517459152.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b1caa947-5c47-4e89-8b01-59096365bd8d.webp</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Plaukų aliejai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6831,7 +6955,7 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6843,22 +6967,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>INTE-LEAVE-IN-SPR-NA</t>
+          <t>INTE-SPLIT-ENDS-SPR-NA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>INTEGRITY LEAVE IN purškiklis pažeistiems plaukams</t>
+          <t>INTEGRITY&amp;STRENGTH SPLIT ENDS SAVIOR purškiklis pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>INTEGRITY</t>
+          <t>INTEGRITY&amp;STRENGTH</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6868,12 +6992,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrity-leave-in-purskiklis-pazeistiems-plaukams</t>
+          <t>https://plaukuosena.lt/integrityandstrength-split-ends-savior-purskiklis-pazeistiems-plaukams</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f74f788d-213a-40fc-8be9-75aa8e85a177.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/aeb4d580-8f81-4cc3-bdeb-0b966ad13c7e.png</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -6889,7 +7013,7 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6901,22 +7025,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>INTE-INTENSIV-TREATMEN-MSK-NA</t>
+          <t>INVI-BLONDE-RECHARGE-SHA-NA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH INTENSIVE TREATMENT stipriai maitinanti kaukė pažeistiems plaukams</t>
+          <t>INVIGO BLONDE RECHARGE geltoną atspalvį neutralizuojantis šampūnas</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH</t>
+          <t>INVIGO</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6926,17 +7050,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-intensive-treatment-stipriai-maitinanti-kauke-pazeistiems-plaukams</t>
+          <t>https://plaukuosena.lt/invigo-blonde-recharge-geltona-atspalvi-neutralizuojantis-sampunas</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9d17895a-b0dc-4293-9fb5-25d4e81c7172.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/61e0e49f-b917-4955-b58c-1a2dc44b9b47.jpg</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6947,7 +7071,7 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -6959,22 +7083,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>INTE-NOURISHI-MAITINAN-CON-NA</t>
+          <t>INVI-BLONDE-RECHARGE-CON-200ML</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH NOURISHING CONDITIONER maitinantis kondicionierius</t>
+          <t>INVIGO BLONDE RECHARGE šaltą atspalvį suteikiantis kondicionierius, 200 ml</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH</t>
+          <t>INVIGO</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6984,12 +7108,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-nourishing-conditioner-maitinantis-kondicionierius</t>
+          <t>https://plaukuosena.lt/invigo-blonde-recharge-salta-atspalvi-suteikiantis-kondicionierius-200-ml</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d7eb8303-1738-41b2-8aad-585928205249.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3dc901e9-409d-4ffd-808f-292e3328f27b.jpg</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7002,10 +7126,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7017,22 +7145,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>INTE-NOURISHI-MAITINAN-SHA-NA</t>
+          <t>INVI-SCALP-BALANCE-SER-6ML</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH NOURISHING SHAMPOO maitinantis šampūnas pažeistiems plaukams</t>
+          <t>INVIGO SCALP BALANCE serumas nuo plaukų slinkimo, 8x6ml</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH</t>
+          <t>INVIGO</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>44.00</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7042,17 +7170,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-nourishing-shampoo-maitinantis-sampunas-pazeistiems-plaukams</t>
+          <t>https://plaukuosena.lt/invigo-scalp-balance-serumas-nuo-plauku-slinkimo-8x6ml</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cf1f1398-28da-45f8-9ea9-a3c1e85c7ff6.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0ac06d9c-42c4-4ede-b4e6-ff007d17f540.jpg</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7060,10 +7188,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>6ml</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7075,22 +7207,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>INTE-REPAIRIN-HAIR-PRD-NA</t>
+          <t>INVI-SUN-CARE-PRD-150ML</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH REPAIRING HAIR LOTION stiprus proteinų koncentratas plaukams</t>
+          <t>INVIGO SUN CARE UV purškalas apsaugantis nuo UV spindulių su provitaminu B5, 150 ml</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH</t>
+          <t>INVIGO</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7100,17 +7232,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-repairing-hair-lotion-stiprus-proteinu-koncentratas-plaukams</t>
+          <t>https://plaukuosena.lt/invigo-sun-care-uv-purskalas-apsaugantis-nuo-uv-spinduliu-su-provitaminu-b5-150-ml</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b1caa947-5c47-4e89-8b01-59096365bd8d.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bea4f015-42e6-4f80-b369-3c74778fa577.jpg</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7118,10 +7250,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7133,22 +7269,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>INTE-SPLIT-ENDS-SPR-NA</t>
+          <t>KADU-COLOR-RADIANCE-CON-250ML</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH SPLIT ENDS SAVIOR purškiklis pažeistiems plaukams</t>
+          <t>KADUS PROFESSIONAL COLOR RADIANCE LEAVE-IN SPRAY purškiamas kondicionierius | 250 ml</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7158,17 +7294,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-split-ends-savior-purskiklis-pazeistiems-plaukams</t>
+          <t>https://plaukuosena.lt/color-radiance-leave-in-spray-purskiamas-kondicionierius-250-ml</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/aeb4d580-8f81-4cc3-bdeb-0b966ad13c7e.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1496fbcb-5032-476b-bcd5-ff6a423b360e.jpg</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7176,10 +7312,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>4064666318448</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7191,22 +7331,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>INVI-BLONDE-RECHARGE-SHA-NA</t>
+          <t>KADU-COLOR-RADIANCE-MSK-200ML</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>INVIGO BLONDE RECHARGE geltoną atspalvį neutralizuojantis šampūnas</t>
+          <t>KADUS PROFESSIONAL COLOR RADIANCE kaukė | 200ML</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>INVIGO</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7216,17 +7356,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-blonde-recharge-geltona-atspalvi-neutralizuojantis-sampunas</t>
+          <t>https://plaukuosena.lt/color-radiance-kauke1</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/61e0e49f-b917-4955-b58c-1a2dc44b9b47.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/188953a6-01e0-4821-b09a-418707b8ae5a.jpg</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7234,10 +7374,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>4064666318509</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7249,22 +7393,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>INVI-BLONDE-RECHARGE-CON-200ML</t>
+          <t>KADU-COLOR-RADIANCE-CON-250ML-1EC4</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>INVIGO BLONDE RECHARGE šaltą atspalvį suteikiantis kondicionierius, 200 ml</t>
+          <t>KADUS PROFESSIONAL COLOR RADIANCE kondicionierius | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>INVIGO</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7274,12 +7418,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-blonde-recharge-salta-atspalvi-suteikiantis-kondicionierius-200-ml</t>
+          <t>https://plaukuosena.lt/color-radiance-kauke</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3dc901e9-409d-4ffd-808f-292e3328f27b.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b5200496-819e-44d4-9eeb-cfa65fbe0213.jpg</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7294,12 +7438,12 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>4064666318387</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7311,22 +7455,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>INVI-SCALP-BALANCE-SER-6ML</t>
+          <t>KADU-COLOR-RADIANCE-SHA-250ML</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>INVIGO SCALP BALANCE serumas nuo plaukų slinkimo, 8x6ml</t>
+          <t>KADUS PROFESSIONAL COLOR RADIANCE šampūnas | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>INVIGO</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>44.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7336,17 +7480,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-scalp-balance-serumas-nuo-plauku-slinkimo-8x6ml</t>
+          <t>https://plaukuosena.lt/color-radiance-sampunas</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0ac06d9c-42c4-4ede-b4e6-ff007d17f540.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/70c7fad4-d7d0-4326-8b82-3955f89277d7.jpg</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7356,12 +7500,12 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>6ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>4064666318325</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7373,22 +7517,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>INVI-SUN-CARE-PRD-150ML</t>
+          <t>KADU-DEEP-MOISTURE-CON-250ML</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>INVIGO SUN CARE UV purškalas apsaugantis nuo UV spindulių su provitaminu B5, 150 ml</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE LEAVE-IN purškiamas kondicionierius | 250 ml</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>INVIGO</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7398,17 +7542,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-sun-care-uv-purskalas-apsaugantis-nuo-uv-spinduliu-su-provitaminu-b5-150-ml</t>
+          <t>https://plaukuosena.lt/deep-moisture-leave-in-purskiamas-kondicionierius-250-ml</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bea4f015-42e6-4f80-b369-3c74778fa577.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/812ff0d8-83cf-4ae5-b03e-7ae58b54d4b3.jpg</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7418,12 +7562,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8005610571560</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7435,12 +7579,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KADU-DEEP-MOISTURE-CON-250ML</t>
+          <t>KADU-DEEP-MOISTURE-MSK-200ML</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE LEAVE-IN purškiamas kondicionierius, 250 ml</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE kaukė | 200ML</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7450,7 +7594,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7460,17 +7604,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-moisture-leave-in-purskiamas-kondicionierius-250-ml</t>
+          <t>https://plaukuosena.lt/deep-moisture-kauke</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/812ff0d8-83cf-4ae5-b03e-7ae58b54d4b3.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/02191c64-c0d0-435c-acfd-4abe70c7d286.jpg</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7480,12 +7624,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>250ml</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8005610604022</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7497,12 +7641,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KADU-DEEP-MOISTURE-CON-NA</t>
+          <t>KADU-DEEP-MOISTURE-CON-250ML-BB59</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE kondicionierius</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE kondicionierius | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7512,7 +7656,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7540,10 +7684,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8005610555089</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7555,12 +7703,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>KADU-DEEP-MOISTURE-SHA-NA</t>
+          <t>KADU-DEEP-MOISTURE-SHA-250ML</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE šampūnas</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE šampūnas | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7570,7 +7718,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>17.90</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7598,10 +7746,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8005610602509</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7613,12 +7765,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>KADU-PRIEMONE-KADUS-PRD-NA</t>
+          <t>KADU-SUN-SPARK-PRD-250ML</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Kadus Professional plaukų priemonės | Kadus kosmetika</t>
+          <t>KADUS PROFESSIONAL SUN SPARK LEAVE-IN losjonas | 250 ml</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7626,20 +7778,24 @@
           <t>Kadus Professional</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/kadus-professional-plauku-priemones</t>
+          <t>https://plaukuosena.lt/sun-spark-leave-in-losjonas-250-ml</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ed98f39-97be-49f3-9ff0-0d72b6b30996.png</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7652,53 +7808,61 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>8005610573397</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>KARS-APSAUGA-APSAUGA-PRD-NA</t>
+          <t>KADU-TONEPLEX-PEARL-SHA-250ML</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Karščio apsauga plaukams | Apsauga nuo karščio</t>
+          <t>KADUS PROFESSIONAL TONEPLEX Pearl Blonde atspalvį suteikiantis šampūnas | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Karščio</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t>Kadus Professional</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>14.00</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/karscio-apsauga-plaukams</t>
+          <t>https://plaukuosena.lt/toneplex-pearl-blonde-atspalvi-suteikiantis-sampunas</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/078c44d1-6f55-4d97-9171-76689b1e9e61.jpg</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7706,37 +7870,41 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>4064666244150</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LEAV-IN-FLOWER-CON-NA</t>
+          <t>KADU-TONEPLEX-DAZANTI-MSK-200ML</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LEAVE IN CONDITIONER FLOWER FRAGRANCE nenuskalaujamas kondicionierius</t>
+          <t>KADUS PROFESSIONAL TONEPLEX dažanti kaukė | 200 ml</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7746,17 +7914,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/leave-in-conditioner-flower-fragrance-nenuskalaujamas-kondicionierius</t>
+          <t>https://plaukuosena.lt/toneplex-dazanti-kauke-200-ml</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8c38e360-1aa4-40f3-80d1-63fd05fadb48.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/72f4806d-8501-4247-b92b-946b795f3452.jpg</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7764,10 +7932,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>4064666244396</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7779,22 +7951,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MILK-NO-FRIZZ-PRD-NA</t>
+          <t>KADU-VISIBLE-REPAIR-PRD-250ML</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING LIGHT MILK blizgesio ir glotnumo suteikiantis pienelis ploniems plaukams</t>
+          <t>KADUS PROFESSIONAL VISIBLE REPAIR LEAVE-IN balzamas | 250 ml</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MILK SHAKE</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>21.60</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7804,12 +7976,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-light-milk-blizgesio-ir-glotnumo-suteikiantis-pienelis-ploniems-plaukams</t>
+          <t>https://plaukuosena.lt/visible-repair-leave-in-balzamas-250-ml</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/05f9a283-0d68-4cbc-8b2b-a9319726c645.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f58db6be-f708-4260-b0ea-414e86e49877.jpg</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7822,10 +7994,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>4064666318035</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7837,22 +8013,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MILK-NO-FRIZZ-SER-NA</t>
+          <t>KADU-VISIBLE-REPAIR-MSK-200ML</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING RICH SERUM blizgesio ir glotnumo suteikiantis serumas storiems plaukams</t>
+          <t>KADUS PROFESSIONAL VISIBLE REPAIR kaukė | 200ML/750ML</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MILK SHAKE</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7862,17 +8038,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-rich-serum-blizgesio-ir-glotnumo-suteikiantis-serumas-storiems-plaukams</t>
+          <t>https://plaukuosena.lt/visible-repair-kauke</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ffc04fa-0925-48a2-86df-62a08a127ee1.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bb4a55d4-fca2-4714-9e27-863c4396c8c5.jpg</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7880,10 +8056,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>4064666318967</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -7895,22 +8075,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MILK-NO-FRIZZ-SPR-NA</t>
+          <t>KADU-VISIBLE-REPAIR-CON-250ML</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MILK SHAKE NO FRIZZ AMAZING ANTI-HUMIDITY SPRAY apsauginis purškiklis garbanotiems plaukams</t>
+          <t>KADUS PROFESSIONAL VISIBLE REPAIR kondicionierius | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MILK SHAKE</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7920,17 +8100,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/amazing-anti-humidity-spray-apsauginis-purskiklis-garbanotiems-plaukams</t>
+          <t>https://plaukuosena.lt/visible-repair-kondicionierius</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ce022c83-2021-4842-9c57-7e44d680edec.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/01643d0f-9cbd-4081-8652-c7463c2b4580.jpg</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7938,10 +8118,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>4064666317977</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -7953,38 +8137,42 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MILK-PRIEMONE-KOSMETIK-PRD-NA</t>
+          <t>KADU-VISIBLE-REPAIR-SHA-250ML</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Milk Shake plaukų priežiūros priemonės | Milk Shake kosmetika</t>
+          <t>KADUS PROFESSIONAL VISIBLE REPAIR šampūnas | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MILK SHAKE</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
+          <t>Kadus Professional</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/milk-shake-plauku-prieziuros-priemones</t>
+          <t>https://plaukuosena.lt/visible-repair-sampunas</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bc18386f-a0b4-4385-aa76-4494ebab2985.jpg</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7992,57 +8180,57 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>4064666317915</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MOIS-MORE-DREKINAM-CON-NA</t>
+          <t>KADU-PRIEMONE-KADUS-PRD-NA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MOISTURE &amp; MORE CONDITIONER drėkinamasis kondicionierius sausiems plaukams</t>
+          <t>Kadus Professional plaukų priemonės | Kadus kosmetika</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MOISTURE</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
-      </c>
+          <t>Kadus Professional</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moisture-and-more-conditioner-drekinamasis-kondicionierius-sausiems-plaukams</t>
+          <t>https://plaukuosena.lt/kadus-professional-plauku-priemones</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9fd3e0cd-3cd4-4c27-9475-b1bd26bb4e46.png</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8053,49 +8241,45 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MOIS-PLUS-WHIPPED-CRM-NA</t>
+          <t>KARS-APSAUGA-APSAUGA-PRD-NA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MOISTURE PLUS WHIPPED CREAM drėkinamosios putos sausiems plaukams</t>
+          <t>Karščio apsauga plaukams | Apsauga nuo karščio</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MOISTURE</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
+          <t>Karščio</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moisture-plus-whipped-cream-drekinamosios-putos-sausiems-plaukams</t>
+          <t>https://plaukuosena.lt/karscio-apsauga-plaukams</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8af7f7bd-70ae-43f3-b8a7-ca5fa1c0bbc8.webp</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8111,34 +8295,34 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MOIS-HYDRATIN-LOTION-PRD-NA</t>
+          <t>LEAV-IN-FLOWER-CON-NA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE HYDRATING LOTION drėkinamasis losjonas sausiems plaukams</t>
+          <t>LEAVE IN CONDITIONER FLOWER FRAGRANCE nenuskalaujamas kondicionierius</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8148,17 +8332,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moistureandmore-hydrating-lotion-drekinamasis-losjonas-sausiems-plaukams</t>
+          <t>https://plaukuosena.lt/leave-in-conditioner-flower-fragrance-nenuskalaujamas-kondicionierius</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/34e3c3da-7fa7-4bb4-a951-8ff1150e33ac.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8c38e360-1aa4-40f3-80d1-63fd05fadb48.png</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8169,7 +8353,7 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8181,22 +8365,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MOIS-DREKINAM-SAUSIEMS-SHA-NA</t>
+          <t>MILK-NO-FRIZZ-PRD-NA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE SHAMPOO drėkinamasis šampūnas sausiems plaukams</t>
+          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING LIGHT MILK blizgesio ir glotnumo suteikiantis pienelis ploniems plaukams</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE</t>
+          <t>MILK SHAKE</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>21.60</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8206,17 +8390,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moistureandmore-shampoo-drekinamasis-sampunas-sausiems-plaukams</t>
+          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-light-milk-blizgesio-ir-glotnumo-suteikiantis-pienelis-ploniems-plaukams</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3e5f63cf-df47-45e5-88af-e3561a3c7134.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/05f9a283-0d68-4cbc-8b2b-a9319726c645.png</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8227,7 +8411,7 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8239,22 +8423,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MOIS-SIERO-ILLUMINA-SER-NA</t>
+          <t>MILK-NO-FRIZZ-SER-NA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE SIERO ILLUMINANTE drėkinamasis spindesio suteikiantis serumas</t>
+          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING RICH SERUM blizgesio ir glotnumo suteikiantis serumas storiems plaukams</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE</t>
+          <t>MILK SHAKE</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8264,12 +8448,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moistureandmore-siero-illuminante-drekinamasis-spindesio-suteikiantis-serumas</t>
+          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-rich-serum-blizgesio-ir-glotnumo-suteikiantis-serumas-storiems-plaukams</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/07c4138c-6a51-4ae1-b02a-24cdfad63075.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ffc04fa-0925-48a2-86df-62a08a127ee1.png</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8285,7 +8469,7 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8297,22 +8481,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NO-FRIZZ-ALLOWED-CON-NA</t>
+          <t>MILK-NO-FRIZZ-SPR-NA</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>NO FRIZZ ALLOWED PERFECTING CONDITIONER kondicionierius šiauštis linkusiems plaukams</t>
+          <t>MILK SHAKE NO FRIZZ AMAZING ANTI-HUMIDITY SPRAY apsauginis purškiklis garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MILK SHAKE</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8322,17 +8506,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no-frizz-allowed-perfecting-conditioner-kondicionierius-siaustis-linkusiems-plaukams</t>
+          <t>https://plaukuosena.lt/amazing-anti-humidity-spray-apsauginis-purskiklis-garbanotiems-plaukams</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/74260607-8186-41a3-aab0-fa7b9d33cdfa.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ce022c83-2021-4842-9c57-7e44d680edec.png</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8343,7 +8527,7 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8355,42 +8539,38 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NO-FRIZZ-ALLOWED-SHA-NA</t>
+          <t>MILK-PRIEMONE-KOSMETIK-PRD-NA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NO FRIZZ ALLOWED PERFECTING SHAMPOO šampūnas šiauštis linkusiems plaukams</t>
+          <t>Milk Shake plaukų priežiūros priemonės | Milk Shake kosmetika</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
+          <t>MILK SHAKE</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no-frizz-allowed-perfecting-shampoo-sampunas-siaustis-linkusiems-plaukams</t>
+          <t>https://plaukuosena.lt/milk-shake-plauku-prieziuros-priemones</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1b73df2a-a171-4121-a186-d4279faaf31c.png</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8401,34 +8581,34 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NO-4-BOND-ENHANCER-SHA-NA</t>
+          <t>MOIS-MORE-DREKINAM-CON-NA</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>No.4P BOND ENHANCER TONING SHAMPOO</t>
+          <t>MOISTURE &amp; MORE CONDITIONER drėkinamasis kondicionierius sausiems plaukams</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>No.4P</t>
+          <t>MOISTURE</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8438,17 +8618,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no4p-bond-enhancer-toning-shampoo</t>
+          <t>https://plaukuosena.lt/moisture-and-more-conditioner-drekinamasis-kondicionierius-sausiems-plaukams</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/edb6f281-e6cd-4872-bec1-b7478940b7ed.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9fd3e0cd-3cd4-4c27-9475-b1bd26bb4e46.png</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8459,7 +8639,7 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8471,22 +8651,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>OLAP-NO-3-PRD-NA</t>
+          <t>MOIS-PLUS-WHIPPED-CRM-NA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 3 HAIR PERFECTOR</t>
+          <t>MOISTURE PLUS WHIPPED CREAM drėkinamosios putos sausiems plaukams</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>MOISTURE</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8496,12 +8676,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-3-hair-perfector</t>
+          <t>https://plaukuosena.lt/moisture-plus-whipped-cream-drekinamosios-putos-sausiems-plaukams</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1832e17d-37c2-4f27-9dbf-03c1c80d368a.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8af7f7bd-70ae-43f3-b8a7-ca5fa1c0bbc8.webp</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8517,7 +8697,7 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>850018802840</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8529,22 +8709,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>OLAP-NO-4-SHA-NA</t>
+          <t>MOIS-HYDRATIN-LOTION-PRD-NA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 4 BOND MAINTENANCE SHAMPOO</t>
+          <t>MOISTURE&amp;MORE HYDRATING LOTION drėkinamasis losjonas sausiems plaukams</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>MOISTURE&amp;MORE</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8554,17 +8734,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-4-bond-maintenance-shampoo</t>
+          <t>https://plaukuosena.lt/moistureandmore-hydrating-lotion-drekinamasis-losjonas-sausiems-plaukams</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2f17f7df-64a9-44b0-8d0d-7beb0d421ee2.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/34e3c3da-7fa7-4bb4-a951-8ff1150e33ac.webp</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8575,7 +8755,7 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>896364002756</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8587,22 +8767,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>OLAP-NO-4D-SHA-NA</t>
+          <t>MOIS-DREKINAM-SAUSIEMS-SHA-NA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 4D Dry Shampoo</t>
+          <t>MOISTURE&amp;MORE SHAMPOO drėkinamasis šampūnas sausiems plaukams</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>MOISTURE&amp;MORE</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8612,12 +8792,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-4d-dry-shampoo</t>
+          <t>https://plaukuosena.lt/moistureandmore-shampoo-drekinamasis-sampunas-sausiems-plaukams</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4b16b116-5392-4248-beaf-e788b5b65f8c.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3e5f63cf-df47-45e5-88af-e3561a3c7134.webp</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8633,7 +8813,7 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>850018802567</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8645,22 +8825,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>OLAP-NO-5-CON-NA</t>
+          <t>MOIS-SIERO-ILLUMINA-SER-NA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 5 BOND MAINTENANCE CONDITIONER</t>
+          <t>MOISTURE&amp;MORE SIERO ILLUMINANTE drėkinamasis spindesio suteikiantis serumas</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>MOISTURE&amp;MORE</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8670,17 +8850,17 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-5-bond-maintenance-conditioner</t>
+          <t>https://plaukuosena.lt/moistureandmore-siero-illuminante-drekinamasis-spindesio-suteikiantis-serumas</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/17784e89-7411-4bd4-8b97-58350ae502d8.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/07c4138c-6a51-4ae1-b02a-24cdfad63075.webp</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8691,7 +8871,7 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>896364002763</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8703,22 +8883,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>OLAP-NO-6-PRD-NA</t>
+          <t>NO-FRIZZ-ALLOWED-CON-NA</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 6 BOND SMOOTHER</t>
+          <t>NO FRIZZ ALLOWED PERFECTING CONDITIONER kondicionierius šiauštis linkusiems plaukams</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8728,17 +8908,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-6-bond-smoother</t>
+          <t>https://plaukuosena.lt/no-frizz-allowed-perfecting-conditioner-kondicionierius-siaustis-linkusiems-plaukams</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39301ecc-75fd-4fca-9e6a-0af9debc2e46.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/74260607-8186-41a3-aab0-fa7b9d33cdfa.png</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8749,7 +8929,7 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>896364002961</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8761,22 +8941,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>OLAP-NO-0-INTENSIV-PRD-NA</t>
+          <t>NO-FRIZZ-ALLOWED-SHA-NA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>OLAPLEX No.0 INTENSIVE BOND BUILDING HAIR TREATMENT</t>
+          <t>NO FRIZZ ALLOWED PERFECTING SHAMPOO šampūnas šiauštis linkusiems plaukams</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8786,17 +8966,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no0-intensive-bond-building-hair-treatment</t>
+          <t>https://plaukuosena.lt/no-frizz-allowed-perfecting-shampoo-sampunas-siaustis-linkusiems-plaukams</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d72c34ad-0dbf-4c23-af6a-9e6dbc63c38e.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1b73df2a-a171-4121-a186-d4279faaf31c.png</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8807,7 +8987,7 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>850018802833</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8819,22 +8999,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>OLAP-NO-10-BOND-GEL-NA</t>
+          <t>NO-4-BOND-ENHANCER-SHA-NA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>OLAPLEX No.10 BOND SHAPER™ CURL DEFINING GEL</t>
+          <t>No.4P BOND ENHANCER TONING SHAMPOO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>No.4P</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8844,17 +9024,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no10-bond-shapertm-curl-defining-gel</t>
+          <t>https://plaukuosena.lt/no4p-bond-enhancer-toning-shampoo</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6e3ed035-956b-465b-a424-b8b30e2641de.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/edb6f281-e6cd-4872-bec1-b7478940b7ed.png</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Plaukų geliai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8865,7 +9045,7 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>850056933155</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -8877,12 +9057,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>OLAP-NO-3-PLUS-PRD-NA</t>
+          <t>OLAP-NO-3-PRD-NA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>OLAPLEX No.3 PLUS Ultimate Repair Treatment</t>
+          <t>OLAPLEX No. 3 HAIR PERFECTOR</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8892,7 +9072,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8902,12 +9082,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no3-plus-ultimate-repair-treatment</t>
+          <t>https://plaukuosena.lt/olaplex-no-3-hair-perfector</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39908a67-c29d-4092-ad0e-d3b12c4c285f.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1832e17d-37c2-4f27-9dbf-03c1c80d368a.png</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -8923,7 +9103,7 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>810177860273</t>
+          <t>850018802840</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -8935,12 +9115,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>OLAP-NO-4C-BOND-SHA-NA</t>
+          <t>OLAP-NO-4-SHA-NA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>OLAPLEX No.4C BOND MAINTENANCE CLARIFYING SHAMPOO</t>
+          <t>OLAPLEX No. 4 BOND MAINTENANCE SHAMPOO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8950,7 +9130,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8960,12 +9140,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no4c-bond-maintenance-clarifying-shampoo</t>
+          <t>https://plaukuosena.lt/olaplex-no-4-bond-maintenance-shampoo</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/15aa41ad-b5ee-455b-82fe-67dd4515079d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2f17f7df-64a9-44b0-8d0d-7beb0d421ee2.png</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -8981,7 +9161,7 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>850018802581</t>
+          <t>896364002756</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -8993,12 +9173,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>OLAP-NO-4FINE-BOND-SHA-NA</t>
+          <t>OLAP-NO-4D-SHA-NA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>OLAPLEX No.4FINE Bond Maintenance Shampoo</t>
+          <t>OLAPLEX No. 4D Dry Shampoo</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9018,12 +9198,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no4fine-bond-maintenance-shampoo</t>
+          <t>https://plaukuosena.lt/olaplex-no-4d-dry-shampoo</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c99d5b13-2995-490c-b568-67b721c151a7.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4b16b116-5392-4248-beaf-e788b5b65f8c.png</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9039,7 +9219,7 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>850056933575</t>
+          <t>850018802567</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9051,12 +9231,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>OLAP-NO-5-LEAVE-IN-PRD-NA</t>
+          <t>OLAP-NO-5-CON-NA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>OLAPLEX No.5 LEAVE-IN Moisturize</t>
+          <t>OLAPLEX No. 5 BOND MAINTENANCE CONDITIONER</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9066,7 +9246,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9076,17 +9256,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no5-leave-in-moisturize</t>
+          <t>https://plaukuosena.lt/olaplex-no-5-bond-maintenance-conditioner</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e18890ee-ba6f-43ff-a518-fce468bdc091.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/17784e89-7411-4bd4-8b97-58350ae502d8.png</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9097,7 +9277,7 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>850056933285</t>
+          <t>896364002763</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9109,12 +9289,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>OLAP-NO-5FINE-BOND-CON-NA</t>
+          <t>OLAP-NO-6-PRD-NA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>OLAPLEX No.5FINE Bond Maintenance Conditioner</t>
+          <t>OLAPLEX No. 6 BOND SMOOTHER</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9124,7 +9304,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9134,17 +9314,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no5fine-bond-maintenance-conditioner</t>
+          <t>https://plaukuosena.lt/olaplex-no-6-bond-smoother</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ccafd5f1-87db-45ae-af6b-3dad5b5af329.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39301ecc-75fd-4fca-9e6a-0af9debc2e46.png</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9155,7 +9335,7 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>850056933612</t>
+          <t>896364002961</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9167,12 +9347,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>OLAP-NO-5P-BLOND-CON-NA</t>
+          <t>OLAP-NO-0-INTENSIV-PRD-NA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>OLAPLEX No.5P BLOND ENHANCER TONING CONDITIONER</t>
+          <t>OLAPLEX No.0 INTENSIVE BOND BUILDING HAIR TREATMENT</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9192,17 +9372,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no5p-blond-enhancer-toning-conditioner</t>
+          <t>https://plaukuosena.lt/olaplex-no0-intensive-bond-building-hair-treatment</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/35185d43-ba29-4be4-bd01-153f53e9628a.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d72c34ad-0dbf-4c23-af6a-9e6dbc63c38e.png</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9213,7 +9393,7 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>850045076290</t>
+          <t>850018802833</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9225,12 +9405,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>OLAP-NO-7-BONDING-OIL-NA</t>
+          <t>OLAP-NO-10-BOND-GEL-NA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>OLAPLEX No.7 BONDING OIL</t>
+          <t>OLAPLEX No.10 BOND SHAPER™ CURL DEFINING GEL</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9250,17 +9430,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no7-bonding-oil</t>
+          <t>https://plaukuosena.lt/no10-bond-shapertm-curl-defining-gel</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8f444685-5686-42dd-b4a9-73afbcfb889f.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6e3ed035-956b-465b-a424-b8b30e2641de.png</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Plaukų aliejai</t>
+          <t>Plaukų geliai</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9271,7 +9451,7 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>896364002695</t>
+          <t>850056933155</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9283,12 +9463,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OLAP-NO-8-BOND-MSK-NA</t>
+          <t>OLAP-NO-3-PLUS-PRD-NA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>OLAPLEX No.8 BOND INTENSE MOISTURE MASK</t>
+          <t>OLAPLEX No.3 PLUS Ultimate Repair Treatment</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9298,7 +9478,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9308,17 +9488,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no8-bond-intense-moisture-mask</t>
+          <t>https://plaukuosena.lt/olaplex-no3-plus-ultimate-repair-treatment</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/552d57ab-d055-4c8c-9603-b292e1a25e64.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39908a67-c29d-4092-ad0e-d3b12c4c285f.png</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9329,7 +9509,7 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>810177860273</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9341,12 +9521,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>OLAP-NO-9-BOND-SER-NA</t>
+          <t>OLAP-NO-4C-BOND-SHA-NA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>OLAPLEX No.9 BOND PROTECTOR NOURISHING HAIR SERUM</t>
+          <t>OLAPLEX No.4C BOND MAINTENANCE CLARIFYING SHAMPOO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9366,17 +9546,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no9-bond-protector-nourishing-hair-serum</t>
+          <t>https://plaukuosena.lt/olaplex-no4c-bond-maintenance-clarifying-shampoo</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e7ab9fdc-43dc-45c3-914c-fa13f791dc3d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/15aa41ad-b5ee-455b-82fe-67dd4515079d.png</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9387,7 +9567,7 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>850018802826</t>
+          <t>850018802581</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9399,12 +9579,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OLAP-RICH-HYDRATIO-MSK-200ML</t>
+          <t>OLAP-NO-4FINE-BOND-SHA-NA</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>OLAPLEX Rich Hydration Mask 200ML</t>
+          <t>OLAPLEX No.4FINE Bond Maintenance Shampoo</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9414,7 +9594,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>47.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9424,17 +9604,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/rich-hydration-mask</t>
+          <t>https://plaukuosena.lt/no4fine-bond-maintenance-shampoo</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2d89d52d-0761-42dc-a4d6-d3ebe5da60b7.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c99d5b13-2995-490c-b568-67b721c151a7.png</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9442,14 +9622,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>850056933919</t>
+          <t>850056933575</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9461,12 +9637,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>OLAP-VOLUMIZI-BLOW-PRD-NA</t>
+          <t>OLAP-NO-5-LEAVE-IN-PRD-NA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>OLAPLEX Volumizing Blow Dry Mist</t>
+          <t>OLAPLEX No.5 LEAVE-IN Moisturize</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9486,12 +9662,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-volumizing-blow-dry-mist</t>
+          <t>https://plaukuosena.lt/olaplex-no5-leave-in-moisturize</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/87bf6622-3275-425b-8a73-1bb008b61716.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e18890ee-ba6f-43ff-a518-fce468bdc091.png</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9507,7 +9683,7 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>850045076221</t>
+          <t>850056933285</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9519,12 +9695,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OLAP-WEIGHTLE-NOURISHI-MSK-200ML</t>
+          <t>OLAP-NO-5FINE-BOND-CON-NA</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>OLAPLEX Weightless Nourishing Mask 200ML</t>
+          <t>OLAPLEX No.5FINE Bond Maintenance Conditioner</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9534,7 +9710,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>47.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9544,17 +9720,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/weightless-nourishing-mask</t>
+          <t>https://plaukuosena.lt/no5fine-bond-maintenance-conditioner</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/da078417-7753-4c31-95e9-19242f1b1aff.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ccafd5f1-87db-45ae-af6b-3dad5b5af329.png</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9562,14 +9738,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>850056933889</t>
+          <t>850056933612</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -9581,12 +9753,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>OLAP-PRIEMONE-PRODUKTA-PRD-NA</t>
+          <t>OLAP-NO-5P-BLOND-CON-NA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Olaplex plaukų priežiūros priemonės | Olaplex produktai</t>
+          <t>OLAPLEX No.5P BLOND ENHANCER TONING CONDITIONER</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9594,25 +9766,29 @@
           <t>OLAPLEX</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-plauku-prieziuros-priemones</t>
+          <t>https://plaukuosena.lt/olaplex-no5p-blond-enhancer-toning-conditioner</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/35185d43-ba29-4be4-bd01-153f53e9628a.jpg</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9623,50 +9799,54 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>850045076290</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PINI-GRAZINIM-POLITIKA-PRD-NA</t>
+          <t>OLAP-NO-7-BONDING-OIL-NA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Pinigų grąžinimo politika – grąžinimo sąlygos</t>
+          <t>OLAPLEX No.7 BONDING OIL</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Pinigų</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>OLAPLEX</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/pinigu-grazinimo-politika</t>
+          <t>https://plaukuosena.lt/olaplex-no7-bonding-oil</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8f444685-5686-42dd-b4a9-73afbcfb889f.png</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9677,50 +9857,54 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>896364002695</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PLAU-GELIAI-SERUMAI-SER-NA</t>
+          <t>OLAP-NO-8-BOND-MSK-NA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Plaukų geliai ir serumai | Profesionalios formavimo priemonės</t>
+          <t>OLAPLEX No.8 BOND INTENSE MOISTURE MASK</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Plaukų</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>OLAPLEX</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/plauku-geliai-ir-serumai</t>
+          <t>https://plaukuosena.lt/olaplex-no8-bond-intense-moisture-mask</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/552d57ab-d055-4c8c-9603-b292e1a25e64.png</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9731,50 +9915,54 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PLAU-KAUKES-PROFESIO-MSK-NA</t>
+          <t>OLAP-NO-9-BOND-SER-NA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Plaukų kaukės | Profesionalios plaukų kaukės internetu</t>
+          <t>OLAPLEX No.9 BOND PROTECTOR NOURISHING HAIR SERUM</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Plaukų</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>OLAPLEX</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/plauku-kaukes</t>
+          <t>https://plaukuosena.lt/olaplex-no9-bond-protector-nourishing-hair-serum</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e7ab9fdc-43dc-45c3-914c-fa13f791dc3d.png</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9785,34 +9973,34 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>850018802826</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>QIQI-BARE-REPAIR-OIL-NA</t>
+          <t>OLAP-RICH-HYDRATIO-MSK-200ML</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>QIQI Bare Repair Oil Plaukų aliejus</t>
+          <t>OLAPLEX Rich Hydration Mask 200ML</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>QIQI</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>54.00</t>
+          <t>47.00</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9822,17 +10010,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-bare-repair-oil-plauku-aliejus</t>
+          <t>https://plaukuosena.lt/rich-hydration-mask</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/85f599b6-1ab5-4fe0-9330-8b393efc56d2.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2d89d52d-0761-42dc-a4d6-d3ebe5da60b7.png</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Plaukų aliejai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9840,10 +10028,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr"/>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>850056933919</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -9855,22 +10047,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>QIQI-GLOTNINA-SHA-NA</t>
+          <t>OLAP-VOLUMIZI-BLOW-PRD-NA</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>QIQI Glotninantis šampūnas</t>
+          <t>OLAPLEX Volumizing Blow Dry Mist</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>QIQI</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9880,17 +10072,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-glotninantis-sampunas</t>
+          <t>https://plaukuosena.lt/olaplex-volumizing-blow-dry-mist</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9ad34b38-7896-457c-8d2e-598db9e7336d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/87bf6622-3275-425b-8a73-1bb008b61716.jpg</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9901,7 +10093,7 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>850045076221</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -9913,22 +10105,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>QIQI-POROSITY-PLAY-SPR-NA</t>
+          <t>OLAP-WEIGHTLE-NOURISHI-MSK-200ML</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>QIQI Porosity Play Spray Plaukų purškiklis</t>
+          <t>OLAPLEX Weightless Nourishing Mask 200ML</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>QIQI</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>54.00</t>
+          <t>47.00</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9938,17 +10130,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-porosity-play-spray-plauku-purskiklis</t>
+          <t>https://plaukuosena.lt/weightless-nourishing-mask</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c272a239-cd7a-422f-a950-d80d709d9259.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/da078417-7753-4c31-95e9-19242f1b1aff.png</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9956,10 +10148,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr"/>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>850056933889</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -9971,37 +10167,33 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>QIQI-POROSITY-VOLUME-PRD-NA</t>
+          <t>OLAP-PRIEMONE-PRODUKTA-PRD-NA</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>QIQI Porosity Volume Code Mist Gausos apimties suteikianti dulksna</t>
+          <t>Olaplex plaukų priežiūros priemonės | Olaplex produktai</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>QIQI</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>54.00</t>
-        </is>
-      </c>
+          <t>OLAPLEX</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-porosity-volume-code-mist-gausos-apimties-suteikianti-dulksna</t>
+          <t>https://plaukuosena.lt/olaplex-plauku-prieziuros-priemones</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40938472-383c-4c92-9b8b-040403000e9d.png</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10017,54 +10209,50 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>QIQI-SUPER-SOAKER-MSK-NA</t>
+          <t>PINI-GRAZINIM-POLITIKA-PRD-NA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>QIQI Super Soaker Smoothing Masque Glotninanti plaukų kaukė</t>
+          <t>Pinigų grąžinimo politika – grąžinimo sąlygos</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>QIQI</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
+          <t>Pinigų</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-super-soaker-smoothing-masque-glotninanti-plauku-kauke</t>
+          <t>https://plaukuosena.lt/pinigu-grazinimo-politika</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c207ccff-61fd-499a-9db4-0ed63a8c34c7.png</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10075,54 +10263,50 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>QIQI-DREKINAM-CON-NA</t>
+          <t>PLAU-GELIAI-SERUMAI-SER-NA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>QIQI drėkinamasis kondicionierius</t>
+          <t>Plaukų geliai ir serumai | Profesionalios formavimo priemonės</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>QIQI</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
-      </c>
+          <t>Plaukų</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-drekinamasis-kondicionierius</t>
+          <t>https://plaukuosena.lt/plauku-geliai-ir-serumai</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e9113e8b-f95c-4cb6-ab03-9977a03ffcd1.png</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10133,54 +10317,50 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>QIQI-ALL-OUT-CRM-NA</t>
+          <t>PLAU-KAUKES-PROFESIO-MSK-NA</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Qiqi All Out Blowout užbaigimo kremas</t>
+          <t>Plaukų kaukės | Profesionalios plaukų kaukės internetu</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>QIQI</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>54.00</t>
-        </is>
-      </c>
+          <t>Plaukų</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-all-out-blowout-uzbaigimo-kremas</t>
+          <t>https://plaukuosena.lt/plauku-kaukes</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ed4db76-21f3-4ce0-a884-2230c7418f53.png</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10191,24 +10371,24 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>QIQI-PRIEMONE-KOSMETIK-PRD-NA</t>
+          <t>QIQI-BARE-REPAIR-OIL-NA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Qiqi plaukų priežiūros priemonės | Qiqi kosmetika</t>
+          <t>QIQI Bare Repair Oil Plaukų aliejus</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10216,25 +10396,29 @@
           <t>QIQI</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-plauku-prieziuros-priemones</t>
+          <t>https://plaukuosena.lt/qiqi-bare-repair-oil-plauku-aliejus</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/85f599b6-1ab5-4fe0-9330-8b393efc56d2.png</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10245,34 +10429,34 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>7290019116882</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SILV-SHINE-ZILIEMS-CON-NA</t>
+          <t>QIQI-GLOTNINA-SHA-NA</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SILVER SHINE CONDITIONER kondicionierius žiliems / šviesintiems plaukams</t>
+          <t>QIQI Glotninantis šampūnas</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SILVER</t>
+          <t>QIQI</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10282,17 +10466,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/silver-shine-conditioner-kondicionierius-ziliems-sviesintiems-plaukams</t>
+          <t>https://plaukuosena.lt/qiqi-glotninantis-sampunas</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/78ae2b87-aede-4bf6-a3fc-ede2a0e31735.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9ad34b38-7896-457c-8d2e-598db9e7336d.png</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10303,7 +10487,7 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>7290019116042</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10315,22 +10499,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SILV-SHINE-LIGHT-SHA-NA</t>
+          <t>QIQI-POROSITY-PLAY-SPR-NA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SILVER SHINE LIGHT SHAMPOO šampūnas žiliems / šviesintiems plaukams</t>
+          <t>QIQI Porosity Play Spray Plaukų purškiklis</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SILVER</t>
+          <t>QIQI</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10340,17 +10524,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/silver-shine-shampoo-sampunas-ziliems-sviesintiems-plaukams</t>
+          <t>https://plaukuosena.lt/qiqi-porosity-play-spray-plauku-purskiklis</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/33a6ba33-a228-4fc9-8fe9-6b66a129541b.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c272a239-cd7a-422f-a950-d80d709d9259.png</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10361,7 +10545,7 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>7290019116455</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10373,22 +10557,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SMOO-MIRACLE-SHIELD-SPR-NA</t>
+          <t>QIQI-POROSITY-VOLUME-PRD-NA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SMOOTHING MIRACLE SHIELD nuo karščio ir drėgmės apsaugantis purškiklis</t>
+          <t>QIQI Porosity Volume Code Mist Gausos apimties suteikianti dulksna</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>SMOOTHING</t>
+          <t>QIQI</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10398,17 +10582,17 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/smoothing-miracle-shield-nuo-karscio-ir-dregmes-apsaugantis-purskiklis</t>
+          <t>https://plaukuosena.lt/qiqi-porosity-volume-code-mist-gausos-apimties-suteikianti-dulksna</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4f9a2abf-0979-4209-b9ac-a2365f16cfd9.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40938472-383c-4c92-9b8b-040403000e9d.png</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10419,7 +10603,7 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>7290019116899</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -10431,22 +10615,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SUN-SPARK-LEAVE-IN-PRD-250ML</t>
+          <t>QIQI-SUPER-SOAKER-MSK-NA</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SUN SPARK LEAVE-IN losjonas, 250 ml</t>
+          <t>QIQI Super Soaker Smoothing Masque Glotninanti plaukų kaukė</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>QIQI</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10456,17 +10640,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/sun-spark-leave-in-losjonas-250-ml</t>
+          <t>https://plaukuosena.lt/qiqi-super-soaker-smoothing-masque-glotninanti-plauku-kauke</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ed98f39-97be-49f3-9ff0-0d72b6b30996.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c207ccff-61fd-499a-9db4-0ed63a8c34c7.png</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10474,14 +10658,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>7290019116448</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10493,38 +10673,42 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SAUL-APSAUGA-APSAUGA-PRD-NA</t>
+          <t>QIQI-DREKINAM-CON-NA</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Saulės apsauga plaukams | Apsauga nuo UV</t>
+          <t>QIQI drėkinamasis kondicionierius</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Saulės</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>QIQI</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>14.00</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/saules-apsauga-plaukams</t>
+          <t>https://plaukuosena.lt/qiqi-drekinamasis-kondicionierius</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e9113e8b-f95c-4cb6-ab03-9977a03ffcd1.png</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10535,34 +10719,34 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>7290019116240</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>TONE-PEARL-BLONDE-SHA-NA</t>
+          <t>QIQI-ALL-OUT-CRM-NA</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TONEPLEX Pearl Blonde atspalvį suteikiantis šampūnas</t>
+          <t>Qiqi All Out Blowout užbaigimo kremas</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>TONEPLEX</t>
+          <t>QIQI</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>17.90</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10572,17 +10756,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/toneplex-pearl-blonde-atspalvi-suteikiantis-sampunas</t>
+          <t>https://plaukuosena.lt/qiqi-all-out-blowout-uzbaigimo-kremas</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/078c44d1-6f55-4d97-9171-76689b1e9e61.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ed4db76-21f3-4ce0-a884-2230c7418f53.png</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10593,7 +10777,7 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>7290019116264</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10605,42 +10789,38 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TONE-DAZANTI-MSK-200ML</t>
+          <t>QIQI-PRIEMONE-KOSMETIK-PRD-NA</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TONEPLEX dažanti kaukė, 200 ml</t>
+          <t>Qiqi plaukų priežiūros priemonės | Qiqi kosmetika</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>TONEPLEX</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>24.90</t>
-        </is>
-      </c>
+          <t>QIQI</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/toneplex-dazanti-kauke-200-ml</t>
+          <t>https://plaukuosena.lt/qiqi-plauku-prieziuros-priemones</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/72f4806d-8501-4247-b92b-946b795f3452.jpg</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10648,41 +10828,37 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ULTI-COLOR-MIRACLE-MSK-NA</t>
+          <t>SILV-SHINE-ZILIEMS-CON-NA</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ULTIMATE COLOR Miracle Leave–in Mask – Miracle nenuplaunama kaukė STEP 2</t>
+          <t>SILVER SHINE CONDITIONER kondicionierius žiliems / šviesintiems plaukams</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>SILVER</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10692,17 +10868,17 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-color-miracle-leave-in-mask-miracle-nenuplaunama-kauke-step-2</t>
+          <t>https://plaukuosena.lt/silver-shine-conditioner-kondicionierius-ziliems-sviesintiems-plaukams</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6f764996-cf18-4ba3-a94a-1d565d3722ba.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/78ae2b87-aede-4bf6-a3fc-ede2a0e31735.webp</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10713,7 +10889,7 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -10725,22 +10901,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ULTI-COLOR-SHINE-SPR-95ML</t>
+          <t>SILV-SHINE-LIGHT-SHA-NA</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ULTIMATE COLOR Shine Spray – Blizgesio suteikiantis purškiklis STEP 3, 95 ml</t>
+          <t>SILVER SHINE LIGHT SHAMPOO šampūnas žiliems / šviesintiems plaukams</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>SILVER</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10750,17 +10926,17 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-color-shine-spray-blizgesio-suteikiantis-purskiklis-step-3-95-ml</t>
+          <t>https://plaukuosena.lt/silver-shine-shampoo-sampunas-ziliems-sviesintiems-plaukams</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/dde4d1d2-891e-49a2-8f98-89265d9ed025.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/33a6ba33-a228-4fc9-8fe9-6b66a129541b.webp</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10768,14 +10944,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>95ml</t>
-        </is>
-      </c>
+      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10787,22 +10959,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ULTI-REPAIR-INTENSYV-MSK-NA</t>
+          <t>SMOO-MIRACLE-SHIELD-SPR-NA</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR intensyvaus poveikio kaukė pažeistiems plaukams STEP 2</t>
+          <t>SMOOTHING MIRACLE SHIELD nuo karščio ir drėgmės apsaugantis purškiklis</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>SMOOTHING</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10812,17 +10984,17 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-kauke-pazeistiems-plaukams-step-2</t>
+          <t>https://plaukuosena.lt/smoothing-miracle-shield-nuo-karscio-ir-dregmes-apsaugantis-purskiklis</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40b6a8c2-185a-422b-9154-64aa5d5b8555.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4f9a2abf-0979-4209-b9ac-a2365f16cfd9.webp</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10833,7 +11005,7 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10845,42 +11017,38 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ULTI-REPAIR-INTENSYV-CON-NA</t>
+          <t>SAUL-APSAUGA-APSAUGA-PRD-NA</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR intensyvaus poveikio kondicionierius pažeistiems plaukams STEP 2</t>
+          <t>Saulės apsauga plaukams | Apsauga nuo UV</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>29.00</t>
-        </is>
-      </c>
+          <t>Saulės</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-kondicionierius-pazeistiems-plaukams-step-2-</t>
+          <t>https://plaukuosena.lt/saules-apsauga-plaukams</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3634c6f3-03f0-47ee-800b-94c7e7402d89.jpg</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10891,24 +11059,24 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ULTI-REPAIR-INTENSYV-SHA-NA</t>
+          <t>ULTI-COLOR-MIRACLE-MSK-NA</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR intensyvaus poveikio šampūnas pažeistiems plaukams STEP 1</t>
+          <t>ULTIMATE COLOR Miracle Leave–in Mask – Miracle nenuplaunama kaukė STEP 2</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10918,7 +11086,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>27.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10928,17 +11096,17 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-sampunas-pazeistiems-plaukams-step-1</t>
+          <t>https://plaukuosena.lt/ultimate-color-miracle-leave-in-mask-miracle-nenuplaunama-kauke-step-2</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/10b51403-3d69-4efa-8f65-c0c2bf55fa06.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6f764996-cf18-4ba3-a94a-1d565d3722ba.jpg</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -10949,7 +11117,7 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -10961,12 +11129,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ULTI-REPAIR-NAKTINIS-SER-NA</t>
+          <t>ULTI-COLOR-SHINE-SPR-95ML</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR naktinis plaukų serumas STEP 5</t>
+          <t>ULTIMATE COLOR Shine Spray – Blizgesio suteikiantis purškiklis STEP 3, 95 ml</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10976,7 +11144,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10986,17 +11154,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-repair-naktinis-plauku-serumas-step-5</t>
+          <t>https://plaukuosena.lt/ultimate-color-shine-spray-blizgesio-suteikiantis-purskiklis-step-3-95-ml</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0cda5ab2-52cf-4f06-8b6c-0f7b5b4bc2cf.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/dde4d1d2-891e-49a2-8f98-89265d9ed025.jpg</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11004,10 +11172,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr"/>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>95ml</t>
+        </is>
+      </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11019,12 +11191,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ULTI-SMOOTH-MAITINAN-MSK-NA</t>
+          <t>ULTI-REPAIR-INTENSYV-MSK-NA</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ULTIMATE SMOOTH maitinanti kaukė su skvalanu ir omega-9</t>
+          <t>ULTIMATE REPAIR intensyvaus poveikio kaukė pažeistiems plaukams STEP 2</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11044,12 +11216,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-smooth-maitinanti-kauke-su-skvalanu-ir-omega-9</t>
+          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-kauke-pazeistiems-plaukams-step-2</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f7774306-1953-481b-9f15-746af2bac04c.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40b6a8c2-185a-422b-9154-64aa5d5b8555.png</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11065,7 +11237,7 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11077,22 +11249,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>VISI-REPAIR-LEAVE-IN-PRD-250ML</t>
+          <t>ULTI-REPAIR-INTENSYV-CON-NA</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>VISIBLE REPAIR LEAVE-IN balzamas, 250 ml</t>
+          <t>ULTIMATE REPAIR intensyvaus poveikio kondicionierius pažeistiems plaukams STEP 2</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>VISIBLE</t>
+          <t>ULTIMATE</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11102,17 +11274,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/visible-repair-leave-in-balzamas-250-ml</t>
+          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-kondicionierius-pazeistiems-plaukams-step-2-</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f58db6be-f708-4260-b0ea-414e86e49877.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3634c6f3-03f0-47ee-800b-94c7e7402d89.jpg</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11120,14 +11292,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11139,22 +11307,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>VISI-REPAIR-MSK-NA</t>
+          <t>ULTI-REPAIR-INTENSYV-SHA-NA</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>VISIBLE REPAIR kaukė</t>
+          <t>ULTIMATE REPAIR intensyvaus poveikio šampūnas pažeistiems plaukams STEP 1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>VISIBLE</t>
+          <t>ULTIMATE</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>27.00</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11164,17 +11332,17 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/visible-repair-kauke</t>
+          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-sampunas-pazeistiems-plaukams-step-1</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bb4a55d4-fca2-4714-9e27-863c4396c8c5.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/10b51403-3d69-4efa-8f65-c0c2bf55fa06.jpg</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11185,7 +11353,7 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11197,22 +11365,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>VISI-REPAIR-CON-NA</t>
+          <t>ULTI-REPAIR-NAKTINIS-SER-NA</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>VISIBLE REPAIR kondicionierius</t>
+          <t>ULTIMATE REPAIR naktinis plaukų serumas STEP 5</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>VISIBLE</t>
+          <t>ULTIMATE</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11222,17 +11390,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/visible-repair-kondicionierius</t>
+          <t>https://plaukuosena.lt/ultimate-repair-naktinis-plauku-serumas-step-5</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/01643d0f-9cbd-4081-8652-c7463c2b4580.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0cda5ab2-52cf-4f06-8b6c-0f7b5b4bc2cf.jpg</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11243,7 +11411,7 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11255,22 +11423,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>VISI-REPAIR-SHA-NA</t>
+          <t>ULTI-SMOOTH-MAITINAN-MSK-NA</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>VISIBLE REPAIR šampūnas</t>
+          <t>ULTIMATE SMOOTH maitinanti kaukė su skvalanu ir omega-9</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>VISIBLE</t>
+          <t>ULTIMATE</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11280,17 +11448,17 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/visible-repair-sampunas</t>
+          <t>https://plaukuosena.lt/ultimate-smooth-maitinanti-kauke-su-skvalanu-ir-omega-9</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bc18386f-a0b4-4385-aa76-4494ebab2985.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f7774306-1953-481b-9f15-746af2bac04c.jpg</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11301,7 +11469,7 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11359,7 +11527,7 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11421,7 +11589,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11483,7 +11651,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11545,7 +11713,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11603,7 +11771,7 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -11661,7 +11829,7 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11719,7 +11887,7 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11777,7 +11945,7 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11835,7 +12003,7 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -11893,7 +12061,7 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -11947,7 +12115,7 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>1780126063671</t>
+          <t>1780138894900</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">

--- a/products_snapshot.xlsx
+++ b/products_snapshot.xlsx
@@ -553,7 +553,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMC-TM-DAILY-SHA-250ML-DE4A</t>
+          <t>AMC-TM-DAILY-SHA-250ML</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1677,7 +1677,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AMC-TM-DAILY-SHA-250ML</t>
+          <t>AMC-TM-DAILY-SHA-250ML-9FF9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>16.50</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3269,7 +3269,7 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3389,7 +3389,7 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,7 +3447,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3505,7 +3505,7 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3563,7 +3563,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3679,7 +3679,7 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3737,7 +3737,7 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3795,7 +3795,7 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>31.00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>42.00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>31.00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4721,7 +4721,7 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6205,7 +6205,7 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6263,7 +6263,7 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6317,7 +6317,7 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6375,7 +6375,7 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6433,7 +6433,7 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6491,7 +6491,7 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6549,7 +6549,7 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6607,7 +6607,7 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6665,7 +6665,7 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6723,7 +6723,7 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6781,7 +6781,7 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6839,7 +6839,7 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6897,7 +6897,7 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6955,7 +6955,7 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7013,7 +7013,7 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7071,7 +7071,7 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8241,7 +8241,7 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8295,7 +8295,7 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8353,7 +8353,7 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8411,7 +8411,7 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8469,7 +8469,7 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8527,7 +8527,7 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8581,7 +8581,7 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8639,7 +8639,7 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8697,7 +8697,7 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8755,7 +8755,7 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8813,7 +8813,7 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8871,7 +8871,7 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8929,7 +8929,7 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8987,7 +8987,7 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9045,7 +9045,7 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9915,7 +9915,7 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10209,7 +10209,7 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10263,7 +10263,7 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10317,7 +10317,7 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10371,7 +10371,7 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10831,7 +10831,7 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -10889,7 +10889,7 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -10947,7 +10947,7 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11005,7 +11005,7 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11059,7 +11059,7 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11117,7 +11117,7 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11237,7 +11237,7 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11295,7 +11295,7 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11353,7 +11353,7 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11411,7 +11411,7 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11469,7 +11469,7 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11527,7 +11527,7 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11771,7 +11771,7 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -11829,7 +11829,7 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11887,7 +11887,7 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11945,7 +11945,7 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -12003,7 +12003,7 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12061,7 +12061,7 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12115,7 +12115,7 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>1780138894900</t>
+          <t>1780380247042</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">

--- a/products_snapshot.xlsx
+++ b/products_snapshot.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L195"/>
+  <dimension ref="A1:L197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -3269,7 +3269,7 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3389,7 +3389,7 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,7 +3447,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3505,7 +3505,7 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3563,7 +3563,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3679,7 +3679,7 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3737,7 +3737,7 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3795,7 +3795,7 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4721,7 +4721,7 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4733,22 +4733,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EIMI-ABSOLUTE-SET-PRD-300ML</t>
+          <t>FUSI-INTENSYV-PLAUKUS-CON-NA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EIMI Absolute Set lakas # 4+, 300 ml</t>
+          <t>FUSION intensyviai plaukus atkuriantis kondicionierius</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>FUSION</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4758,17 +4758,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-absolute-set-lakas-4-300-ml</t>
+          <t>https://plaukuosena.lt/fusion-intensyviai-plaukus-atkuriantis-kondicionierius</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4609936e-f051-43d0-bf28-23a210169d95.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9f9fdb95-485e-476c-b6b2-486e49f19cfe.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4776,14 +4776,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>300ml</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4795,22 +4791,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EIMI-DRY-ME-SHA-180ML</t>
+          <t>GLIS-ARGAN-ARGANU-OIL-NA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EIMI Dry Me Dry sausas šampūnas #1, 180 ml</t>
+          <t>GLISTENING ARGAN OIL arganų aliejus</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>GLISTENING</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4820,17 +4816,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-dry-me-dry-sausas-sampunas-1-180-ml</t>
+          <t>https://plaukuosena.lt/glistening-argan-oil-arganu-aliejus</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/685481b5-65b1-4e9e-a0d1-967851f46e02.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e8ec0139-6902-4e09-8f7e-92dbc42a0048.png</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4838,14 +4834,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>180ml</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4857,37 +4849,33 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EIMI-EXTRA-VOLUME-FOA-300ML</t>
+          <t>GARB-PLAUKAI-PRIEMONE-PRD-NA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EIMI Extra Volume putos #3, 300 ml</t>
+          <t>Garbanoti plaukai | Priežiūros priemonės garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EIMI</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>23.00</t>
-        </is>
-      </c>
+          <t>Garbanoti</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-extra-volume-putos-3-300-ml</t>
+          <t>https://plaukuosena.lt/garbanoti-plaukai</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4ce5d05e-e0eb-4588-9266-14c75d59b5b2.jpg</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,41 +4888,37 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>300ml</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EIMI-FLEXIBLE-FINISH-PRD-250ML</t>
+          <t>ICY-BLOND-SVIESIEM-CON-NA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EIMI Flexible Finish lakas #2, 250 ml</t>
+          <t>ICY BLOND CONDITIONER kondicionierius šviesiems plaukams</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4944,17 +4928,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-flexible-finish-lakas-2-250-ml</t>
+          <t>https://plaukuosena.lt/icy-blond-conditioner-kondicionierius-sviesiems-plaukams</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/690edb16-bb3f-41bc-a6d0-6e1c32ae98d2.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/43ff1e78-0eaf-481b-8b24-b56b697a19c0.png</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4962,14 +4946,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4981,22 +4961,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EIMI-FLOWING-FORM-PRD-100ML</t>
+          <t>ICY-BLOND-SVIESIEM-SHA-NA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EIMI Flowing Form balzamas #2, 100 ml</t>
+          <t>ICY BLOND SHAMPOO šampūnas šviesiems plaukams</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5006,17 +4986,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-flowing-form-balzamas-2-100-ml</t>
+          <t>https://plaukuosena.lt/icy-blond-shampoo-sampunas-sviesiems-plaukams</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1544dbd7-35f9-42b5-92ec-d0cd6f9943ab.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cac84108-877e-4753-baa2-36d67665c464.png</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5024,14 +5004,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>100ml</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5043,22 +5019,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EIMI-GLAM-MIST-PRD-200ML</t>
+          <t>INCR-MILK-FLOWER-PRD-NA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EIMI Glam Mist lakas / blizgis #1, 200 ml</t>
+          <t>INCREDIBLE MILK FLOWER FRAGRANCE plaukus kondicionuojantis pienelis</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>INCREDIBLE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>27.00</t>
+          <t>18.90</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5068,12 +5044,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-glam-mist-lakas-blizgis-1-200-ml</t>
+          <t>https://plaukuosena.lt/incredible-milk-flower-fragrance-plaukus-kondicionuojantis-pienelis</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/47a0bc9e-6340-462e-a327-ccd1efe76dda.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/728171ea-b913-4828-bd2e-5816d611a9a2.png</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5086,14 +5062,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5105,22 +5077,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EIMI-MISTIFY-ME-PRD-300ML</t>
+          <t>INST-STIPRINA-SHA-NA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIMI Mistify Me Light lakas #2, 300 ml</t>
+          <t>INSTALIGHT SHAMPOO stiprinamasis šampūnas plaukams</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>INSTALIGHT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5130,17 +5102,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-mistify-me-light-lakas-2-300-ml</t>
+          <t>https://plaukuosena.lt/instalight-shampoo-stiprinamasis-sampunas-plaukams</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f44de339-ff78-47c5-bef9-4840e03045b9.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40bb94ca-92af-4d11-9f97-87579e8d0d24.png</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5148,14 +5120,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>300ml</t>
-        </is>
-      </c>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5167,17 +5135,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EIMI-MISTIFY-ME-PRD-300ML-4AE5</t>
+          <t>INST-SKYSTA-MSK-NA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIMI Mistify Me Strong lakas #3, 300 ml</t>
+          <t>INSTALOTION skysta kaukė plaukams</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>INSTALOTION</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5192,17 +5160,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-mistify-me-strong-lakas-3-300-ml</t>
+          <t>https://plaukuosena.lt/instalotion-skysta-kauke-plaukams</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/25a65e8a-b11d-4d44-9b95-7db4a88549e5.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b00458f3-53bf-48dc-a159-d98ece3d546d.webp</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5210,14 +5178,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>300ml</t>
-        </is>
-      </c>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5229,22 +5193,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EIMI-NUTRICUR-BOOST-FOA-300ML</t>
+          <t>INTE-INCREDIB-APSAUGIN-OIL-NA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIMI NUTRICURLS BOOST BOUNCE 72h švelnios putos garbanoms #2, 300 ml</t>
+          <t>INTEGRITY INCREDIBLE OIL apsauginis atkuriamasis aliejus</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>INTEGRITY</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>23.50</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5254,17 +5218,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-nutricurls-boost-bounce-72h-svelnios-putos-garbanoms-2-300-ml</t>
+          <t>https://plaukuosena.lt/integrity-incredible-oil-apsauginis-atkuriamasis-aliejus</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e1731c4e-394c-435e-b753-e948d7cfbf89.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/80d0d251-f362-4ff0-aa1f-23a517459152.png</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5272,14 +5236,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>300ml</t>
-        </is>
-      </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5291,22 +5251,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EIMI-NATURAL-VOLUME-FOA-300ML</t>
+          <t>INTE-LEAVE-IN-SPR-NA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIMI Natural Volume putos #2, 300 ml</t>
+          <t>INTEGRITY LEAVE IN purškiklis pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>INTEGRITY</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5316,17 +5276,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-natural-volume-putos-2-300-ml</t>
+          <t>https://plaukuosena.lt/integrity-leave-in-purskiklis-pazeistiems-plaukams</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9473f762-aafe-44c0-9acb-7e105a4f8d11.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f74f788d-213a-40fc-8be9-75aa8e85a177.webp</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5334,14 +5294,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>300ml</t>
-        </is>
-      </c>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5353,17 +5309,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EIMI-NUTRICUR-CURL-CRM-150ML</t>
+          <t>INTE-INTENSIV-TREATMEN-MSK-NA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIMI Nutricurls Curl Shaper kremas #2, 150 ml</t>
+          <t>INTEGRITY&amp;STRENGTH INTENSIVE TREATMENT stipriai maitinanti kaukė pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>INTEGRITY&amp;STRENGTH</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5378,17 +5334,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-nutricurls-curl-shaper-kremas-2-150-ml</t>
+          <t>https://plaukuosena.lt/integrityandstrength-intensive-treatment-stipriai-maitinanti-kauke-pazeistiems-plaukams</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/05eb6823-d484-4232-a92a-05a825b67fc3.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9d17895a-b0dc-4293-9fb5-25d4e81c7172.png</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5396,14 +5352,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>150ml</t>
-        </is>
-      </c>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5415,22 +5367,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EIMI-NUTRICUR-FRESH-PRD-150ML</t>
+          <t>INTE-NOURISHI-MAITINAN-CON-NA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIMI Nutricurls Fresh Up purškalas #1, 150 ml</t>
+          <t>INTEGRITY&amp;STRENGTH NOURISHING CONDITIONER maitinantis kondicionierius</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>INTEGRITY&amp;STRENGTH</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5440,17 +5392,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-nutricurls-fresh-up-purskalas-1-150-ml</t>
+          <t>https://plaukuosena.lt/integrityandstrength-nourishing-conditioner-maitinantis-kondicionierius</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c849de07-4e68-4b6b-b4ed-a59ac843799e.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d7eb8303-1738-41b2-8aad-585928205249.png</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5458,14 +5410,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>150ml</t>
-        </is>
-      </c>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5477,22 +5425,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EIMI-NUTRICUR-SOFT-FOA-200ML</t>
+          <t>INTE-NOURISHI-MAITINAN-SHA-NA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIMI Nutricurls Soft Twirl putos #2, 200 ml</t>
+          <t>INTEGRITY&amp;STRENGTH NOURISHING SHAMPOO maitinantis šampūnas pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>INTEGRITY&amp;STRENGTH</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5502,17 +5450,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-nutricurls-soft-twirl-putos-2-200-ml</t>
+          <t>https://plaukuosena.lt/integrityandstrength-nourishing-shampoo-maitinantis-sampunas-pazeistiems-plaukams</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/01c8bbb3-0429-4f4c-9d1e-508b94ae4ba9.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cf1f1398-28da-45f8-9ea9-a3c1e85c7ff6.png</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5520,14 +5468,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5539,22 +5483,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EIMI-OCEAN-SPRITZ-PRD-150ML</t>
+          <t>INTE-REPAIRIN-HAIR-PRD-NA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIMI Ocean Spritz purškalas su druska #2, 150 ml</t>
+          <t>INTEGRITY&amp;STRENGTH REPAIRING HAIR LOTION stiprus proteinų koncentratas plaukams</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>INTEGRITY&amp;STRENGTH</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5564,17 +5508,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-ocean-spritz-purskalas-su-druska-2-150-ml</t>
+          <t>https://plaukuosena.lt/integrityandstrength-repairing-hair-lotion-stiprus-proteinu-koncentratas-plaukams</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ad6f5336-91da-4ba8-8a8d-12468afe45c7.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b1caa947-5c47-4e89-8b01-59096365bd8d.webp</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5582,14 +5526,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>150ml</t>
-        </is>
-      </c>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5601,22 +5541,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EIMI-PEARL-STYLER-GEL-100ML</t>
+          <t>INTE-SPLIT-ENDS-SPR-NA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIMI Pearl Styler gelis #3, 100 ml</t>
+          <t>INTEGRITY&amp;STRENGTH SPLIT ENDS SAVIOR purškiklis pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>INTEGRITY&amp;STRENGTH</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5626,17 +5566,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-pearl-styler-gelis-3-100-ml</t>
+          <t>https://plaukuosena.lt/integrityandstrength-split-ends-savior-purskiklis-pazeistiems-plaukams</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/144e8417-a5e5-4fb1-a96d-9ea6632bffa9.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/aeb4d580-8f81-4cc3-bdeb-0b966ad13c7e.png</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Plaukų geliai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5644,14 +5584,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>100ml</t>
-        </is>
-      </c>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5663,22 +5599,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EIMI-PERFECT-ME-PRD-100ML</t>
+          <t>KADU-COLOR-RADIANCE-CON-250ML</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIMI Perfect Me losjonas #1, 100 ml</t>
+          <t>KADUS PROFESSIONAL COLOR RADIANCE LEAVE-IN SPRAY purškiamas kondicionierius | 250 ml</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5688,17 +5624,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-perfect-me-losjonas-1-100-ml</t>
+          <t>https://plaukuosena.lt/color-radiance-leave-in-spray-purskiamas-kondicionierius-250-ml</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c2858f89-5b77-4ca7-9214-22d5758e79fd.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1496fbcb-5032-476b-bcd5-ff6a423b360e.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5708,12 +5644,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666318448</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5725,22 +5661,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EIMI-PERFECT-SETTING-PRD-150ML</t>
+          <t>KADU-COLOR-RADIANCE-MSK-200ML</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EIMI Perfect Setting purškiamas plaukų losjonas #2, 150 ml</t>
+          <t>KADUS PROFESSIONAL COLOR RADIANCE kaukė | 200ML</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5750,17 +5686,17 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-perfect-setting-purskiamas-plauku-losjonas-2-150-ml</t>
+          <t>https://plaukuosena.lt/color-radiance-kauke1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/831cbe0a-7ea7-4da3-9d64-a7da293455c7.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/188953a6-01e0-4821-b09a-418707b8ae5a.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5770,12 +5706,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666318509</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5787,22 +5723,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EIMI-ROOT-SHOOT-FOA-200ML</t>
+          <t>KADU-COLOR-RADIANCE-CON-250ML-1EC4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EIMI Root Shoot purškiamos putos #2, 200 ml</t>
+          <t>KADUS PROFESSIONAL COLOR RADIANCE kondicionierius | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>23.50</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5812,17 +5748,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-root-shoot-purskiamos-putos-2-200-ml</t>
+          <t>https://plaukuosena.lt/color-radiance-kauke</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/20d544d5-a43b-420a-8011-c64e7eae68ee.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b5200496-819e-44d4-9eeb-cfa65fbe0213.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5832,12 +5768,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666318387</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5849,22 +5785,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EIMI-SHAPE-ME-GEL-150ML</t>
+          <t>KADU-COLOR-RADIANCE-SHA-250ML</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EIMI SHAPE ME 48 val plaukų formą išlaikantis gelis #2, 150 ml</t>
+          <t>KADUS PROFESSIONAL COLOR RADIANCE šampūnas | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5874,17 +5810,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-shape-me-48-val-plauku-forma-islaikantis-gelis-2-150-ml</t>
+          <t>https://plaukuosena.lt/color-radiance-sampunas</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cf24ed41-364c-4e1f-8323-ab8095dae01b.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/70c7fad4-d7d0-4326-8b82-3955f89277d7.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Plaukų geliai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5894,12 +5830,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666318325</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5911,22 +5847,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EIMI-SHAPE-CONTROL-FOA-300ML</t>
+          <t>KADU-DEEP-MOISTURE-CON-250ML</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EIMI Shape Control putos #4, 300 ml</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE LEAVE-IN purškiamas kondicionierius | 250 ml</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5936,17 +5872,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-shape-control-putos-4-300-ml</t>
+          <t>https://plaukuosena.lt/deep-moisture-leave-in-purskiamas-kondicionierius-250-ml</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bbbd8914-6602-4103-878b-c10b2612242f.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/812ff0d8-83cf-4ae5-b03e-7ae58b54d4b3.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5956,12 +5892,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>8005610571560</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5973,22 +5909,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EIMI-SUGAR-LIFT-PRD-150ML</t>
+          <t>KADU-DEEP-MOISTURE-MSK-200ML</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EIMI Sugar Lift purškalas apimčiai #3, 150 ml</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE kaukė | 200ML</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5998,17 +5934,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-sugar-lift-purskalas-apimciai-3-150-ml</t>
+          <t>https://plaukuosena.lt/deep-moisture-kauke</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0e33562e-8331-4101-a44a-730c2fbfb1af.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/02191c64-c0d0-435c-acfd-4abe70c7d286.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6018,12 +5954,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>8005610604022</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6035,22 +5971,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EIMI-SUPER-SET-PRD-300ML</t>
+          <t>KADU-DEEP-MOISTURE-CON-250ML-BB59</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EIMI Super Set lakas #4, 300 ml</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE kondicionierius | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6060,17 +5996,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-super-set-lakas-4-300-ml</t>
+          <t>https://plaukuosena.lt/deep-moisture-kondicionierius</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a4229f5f-7428-44ab-b006-da4faa1587a9.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/11e9244b-f1b4-4fd1-a829-d04264f37221.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6080,12 +6016,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>8005610555089</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6097,22 +6033,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EIMI-THERMAL-IMAGE-PRD-150ML</t>
+          <t>KADU-DEEP-MOISTURE-SHA-250ML</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EIMI Thermal Image purškalas nuo karščio #2, 150 ml</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE šampūnas | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>EIMI</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6122,17 +6058,17 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-thermal-image-purskalas-nuo-karscio-2-150-ml</t>
+          <t>https://plaukuosena.lt/deep-moisture-sampunas</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/27f63de3-6f4d-4932-9873-48b4fbc2f296.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0f57fac1-e330-41e0-aa79-c1ef82ad3610.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6142,12 +6078,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>8005610602509</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6159,22 +6095,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FUSI-INTENSYV-PLAUKUS-CON-NA</t>
+          <t>KADU-SUN-SPARK-PRD-250ML</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FUSION intensyviai plaukus atkuriantis kondicionierius</t>
+          <t>KADUS PROFESSIONAL SUN SPARK LEAVE-IN losjonas | 250 ml</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FUSION</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6184,17 +6120,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/fusion-intensyviai-plaukus-atkuriantis-kondicionierius</t>
+          <t>https://plaukuosena.lt/sun-spark-leave-in-losjonas-250-ml</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9f9fdb95-485e-476c-b6b2-486e49f19cfe.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ed98f39-97be-49f3-9ff0-0d72b6b30996.png</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6202,10 +6138,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>8005610573397</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6217,22 +6157,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GLIS-ARGAN-ARGANU-OIL-NA</t>
+          <t>KADU-TONEPLEX-PEARL-SHA-250ML</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GLISTENING ARGAN OIL arganų aliejus</t>
+          <t>KADUS PROFESSIONAL TONEPLEX Pearl Blonde atspalvį suteikiantis šampūnas | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GLISTENING</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6242,17 +6182,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/glistening-argan-oil-arganu-aliejus</t>
+          <t>https://plaukuosena.lt/toneplex-pearl-blonde-atspalvi-suteikiantis-sampunas</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e8ec0139-6902-4e09-8f7e-92dbc42a0048.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/078c44d1-6f55-4d97-9171-76689b1e9e61.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Plaukų aliejai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6260,10 +6200,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666244150</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6275,38 +6219,42 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GARB-PLAUKAI-PRIEMONE-PRD-NA</t>
+          <t>KADU-TONEPLEX-DAZANTI-MSK-200ML</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Garbanoti plaukai | Priežiūros priemonės garbanotiems plaukams</t>
+          <t>KADUS PROFESSIONAL TONEPLEX dažanti kaukė | 200 ml</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Garbanoti</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Kadus Professional</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/garbanoti-plaukai</t>
+          <t>https://plaukuosena.lt/toneplex-dazanti-kauke-200-ml</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/72f4806d-8501-4247-b92b-946b795f3452.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6314,37 +6262,41 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666244396</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ICY-BLOND-SVIESIEM-CON-NA</t>
+          <t>KADU-VISIBLE-REPAIR-PRD-250ML</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ICY BLOND CONDITIONER kondicionierius šviesiems plaukams</t>
+          <t>KADUS PROFESSIONAL VISIBLE REPAIR LEAVE-IN balzamas | 250 ml</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6354,17 +6306,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/icy-blond-conditioner-kondicionierius-sviesiems-plaukams</t>
+          <t>https://plaukuosena.lt/visible-repair-leave-in-balzamas-250-ml</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/43ff1e78-0eaf-481b-8b24-b56b697a19c0.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f58db6be-f708-4260-b0ea-414e86e49877.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6372,10 +6324,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666318035</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6387,22 +6343,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ICY-BLOND-SVIESIEM-SHA-NA</t>
+          <t>KADU-VISIBLE-REPAIR-MSK-200ML</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ICY BLOND SHAMPOO šampūnas šviesiems plaukams</t>
+          <t>KADUS PROFESSIONAL VISIBLE REPAIR kaukė | 200ML/750ML</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6412,17 +6368,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/icy-blond-shampoo-sampunas-sviesiems-plaukams</t>
+          <t>https://plaukuosena.lt/visible-repair-kauke</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cac84108-877e-4753-baa2-36d67665c464.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bb4a55d4-fca2-4714-9e27-863c4396c8c5.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6430,10 +6386,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666318967</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6445,22 +6405,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>INCR-MILK-FLOWER-PRD-NA</t>
+          <t>KADU-VISIBLE-REPAIR-CON-250ML</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>INCREDIBLE MILK FLOWER FRAGRANCE plaukus kondicionuojantis pienelis</t>
+          <t>KADUS PROFESSIONAL VISIBLE REPAIR kondicionierius | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>INCREDIBLE</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>18.90</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6470,17 +6430,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/incredible-milk-flower-fragrance-plaukus-kondicionuojantis-pienelis</t>
+          <t>https://plaukuosena.lt/visible-repair-kondicionierius</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/728171ea-b913-4828-bd2e-5816d611a9a2.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/01643d0f-9cbd-4081-8652-c7463c2b4580.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6488,10 +6448,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666317977</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6503,22 +6467,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>INST-STIPRINA-SHA-NA</t>
+          <t>KADU-VISIBLE-REPAIR-SHA-250ML</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>INSTALIGHT SHAMPOO stiprinamasis šampūnas plaukams</t>
+          <t>KADUS PROFESSIONAL VISIBLE REPAIR šampūnas | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>INSTALIGHT</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6528,12 +6492,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/instalight-shampoo-stiprinamasis-sampunas-plaukams</t>
+          <t>https://plaukuosena.lt/visible-repair-sampunas</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40bb94ca-92af-4d11-9f97-87579e8d0d24.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bc18386f-a0b4-4385-aa76-4494ebab2985.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6546,10 +6510,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666317915</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6561,42 +6529,38 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>INST-SKYSTA-MSK-NA</t>
+          <t>KADU-PRIEMONE-KADUS-PRD-NA</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>INSTALOTION skysta kaukė plaukams</t>
+          <t>Kadus Professional plaukų priemonės | Kadus kosmetika</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>INSTALOTION</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>22.00</t>
-        </is>
-      </c>
+          <t>Kadus Professional</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/instalotion-skysta-kauke-plaukams</t>
+          <t>https://plaukuosena.lt/kadus-professional-plauku-priemones</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b00458f3-53bf-48dc-a159-d98ece3d546d.webp</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6607,54 +6571,50 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>INTE-INCREDIB-APSAUGIN-OIL-NA</t>
+          <t>KARS-APSAUGA-APSAUGA-PRD-NA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>INTEGRITY INCREDIBLE OIL apsauginis atkuriamasis aliejus</t>
+          <t>Karščio apsauga plaukams | Apsauga nuo karščio</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>INTEGRITY</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>56.00</t>
-        </is>
-      </c>
+          <t>Karščio</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrity-incredible-oil-apsauginis-atkuriamasis-aliejus</t>
+          <t>https://plaukuosena.lt/karscio-apsauga-plaukams</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/80d0d251-f362-4ff0-aa1f-23a517459152.png</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Plaukų aliejai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6665,34 +6625,34 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>INTE-LEAVE-IN-SPR-NA</t>
+          <t>LEAV-IN-FLOWER-CON-NA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>INTEGRITY LEAVE IN purškiklis pažeistiems plaukams</t>
+          <t>LEAVE IN CONDITIONER FLOWER FRAGRANCE nenuskalaujamas kondicionierius</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>INTEGRITY</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6702,17 +6662,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrity-leave-in-purskiklis-pazeistiems-plaukams</t>
+          <t>https://plaukuosena.lt/leave-in-conditioner-flower-fragrance-nenuskalaujamas-kondicionierius</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f74f788d-213a-40fc-8be9-75aa8e85a177.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8c38e360-1aa4-40f3-80d1-63fd05fadb48.png</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6723,7 +6683,7 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6735,22 +6695,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>INTE-INTENSIV-TREATMEN-MSK-NA</t>
+          <t>MILK-NO-FRIZZ-PRD-NA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH INTENSIVE TREATMENT stipriai maitinanti kaukė pažeistiems plaukams</t>
+          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING LIGHT MILK blizgesio ir glotnumo suteikiantis pienelis ploniems plaukams</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH</t>
+          <t>MILK SHAKE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>21.60</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6760,17 +6720,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-intensive-treatment-stipriai-maitinanti-kauke-pazeistiems-plaukams</t>
+          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-light-milk-blizgesio-ir-glotnumo-suteikiantis-pienelis-ploniems-plaukams</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9d17895a-b0dc-4293-9fb5-25d4e81c7172.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/05f9a283-0d68-4cbc-8b2b-a9319726c645.png</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6781,7 +6741,7 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6793,22 +6753,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>INTE-NOURISHI-MAITINAN-CON-NA</t>
+          <t>MILK-NO-FRIZZ-SER-NA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH NOURISHING CONDITIONER maitinantis kondicionierius</t>
+          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING RICH SERUM blizgesio ir glotnumo suteikiantis serumas storiems plaukams</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH</t>
+          <t>MILK SHAKE</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6818,17 +6778,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-nourishing-conditioner-maitinantis-kondicionierius</t>
+          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-rich-serum-blizgesio-ir-glotnumo-suteikiantis-serumas-storiems-plaukams</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d7eb8303-1738-41b2-8aad-585928205249.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ffc04fa-0925-48a2-86df-62a08a127ee1.png</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6839,7 +6799,7 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6851,22 +6811,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>INTE-NOURISHI-MAITINAN-SHA-NA</t>
+          <t>MILK-NO-FRIZZ-SPR-NA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH NOURISHING SHAMPOO maitinantis šampūnas pažeistiems plaukams</t>
+          <t>MILK SHAKE NO FRIZZ AMAZING ANTI-HUMIDITY SPRAY apsauginis purškiklis garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH</t>
+          <t>MILK SHAKE</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6876,17 +6836,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-nourishing-shampoo-maitinantis-sampunas-pazeistiems-plaukams</t>
+          <t>https://plaukuosena.lt/amazing-anti-humidity-spray-apsauginis-purskiklis-garbanotiems-plaukams</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cf1f1398-28da-45f8-9ea9-a3c1e85c7ff6.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ce022c83-2021-4842-9c57-7e44d680edec.png</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6897,7 +6857,7 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6909,37 +6869,33 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>INTE-REPAIRIN-HAIR-PRD-NA</t>
+          <t>MILK-PRIEMONE-KOSMETIK-PRD-NA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH REPAIRING HAIR LOTION stiprus proteinų koncentratas plaukams</t>
+          <t>Milk Shake plaukų priežiūros priemonės | Milk Shake kosmetika</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>24.00</t>
-        </is>
-      </c>
+          <t>MILK SHAKE</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-repairing-hair-lotion-stiprus-proteinu-koncentratas-plaukams</t>
+          <t>https://plaukuosena.lt/milk-shake-plauku-prieziuros-priemones</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b1caa947-5c47-4e89-8b01-59096365bd8d.webp</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6955,34 +6911,34 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>INTE-SPLIT-ENDS-SPR-NA</t>
+          <t>MOIS-MORE-DREKINAM-CON-NA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH SPLIT ENDS SAVIOR purškiklis pažeistiems plaukams</t>
+          <t>MOISTURE &amp; MORE CONDITIONER drėkinamasis kondicionierius sausiems plaukams</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH</t>
+          <t>MOISTURE</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6992,17 +6948,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-split-ends-savior-purskiklis-pazeistiems-plaukams</t>
+          <t>https://plaukuosena.lt/moisture-and-more-conditioner-drekinamasis-kondicionierius-sausiems-plaukams</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/aeb4d580-8f81-4cc3-bdeb-0b966ad13c7e.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9fd3e0cd-3cd4-4c27-9475-b1bd26bb4e46.png</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7013,7 +6969,7 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7025,22 +6981,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>INVI-BLONDE-RECHARGE-SHA-NA</t>
+          <t>MOIS-PLUS-WHIPPED-CRM-NA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>INVIGO BLONDE RECHARGE geltoną atspalvį neutralizuojantis šampūnas</t>
+          <t>MOISTURE PLUS WHIPPED CREAM drėkinamosios putos sausiems plaukams</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>INVIGO</t>
+          <t>MOISTURE</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7050,17 +7006,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-blonde-recharge-geltona-atspalvi-neutralizuojantis-sampunas</t>
+          <t>https://plaukuosena.lt/moisture-plus-whipped-cream-drekinamosios-putos-sausiems-plaukams</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/61e0e49f-b917-4955-b58c-1a2dc44b9b47.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8af7f7bd-70ae-43f3-b8a7-ca5fa1c0bbc8.webp</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7071,7 +7027,7 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7083,22 +7039,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>INVI-BLONDE-RECHARGE-CON-200ML</t>
+          <t>MOIS-HYDRATIN-LOTION-PRD-NA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>INVIGO BLONDE RECHARGE šaltą atspalvį suteikiantis kondicionierius, 200 ml</t>
+          <t>MOISTURE&amp;MORE HYDRATING LOTION drėkinamasis losjonas sausiems plaukams</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>INVIGO</t>
+          <t>MOISTURE&amp;MORE</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7108,17 +7064,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-blonde-recharge-salta-atspalvi-suteikiantis-kondicionierius-200-ml</t>
+          <t>https://plaukuosena.lt/moistureandmore-hydrating-lotion-drekinamasis-losjonas-sausiems-plaukams</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3dc901e9-409d-4ffd-808f-292e3328f27b.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/34e3c3da-7fa7-4bb4-a951-8ff1150e33ac.webp</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7126,14 +7082,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7145,22 +7097,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>INVI-SCALP-BALANCE-SER-6ML</t>
+          <t>MOIS-DREKINAM-SAUSIEMS-SHA-NA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>INVIGO SCALP BALANCE serumas nuo plaukų slinkimo, 8x6ml</t>
+          <t>MOISTURE&amp;MORE SHAMPOO drėkinamasis šampūnas sausiems plaukams</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>INVIGO</t>
+          <t>MOISTURE&amp;MORE</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>44.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7170,17 +7122,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-scalp-balance-serumas-nuo-plauku-slinkimo-8x6ml</t>
+          <t>https://plaukuosena.lt/moistureandmore-shampoo-drekinamasis-sampunas-sausiems-plaukams</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0ac06d9c-42c4-4ede-b4e6-ff007d17f540.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3e5f63cf-df47-45e5-88af-e3561a3c7134.webp</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7188,14 +7140,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>6ml</t>
-        </is>
-      </c>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7207,22 +7155,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>INVI-SUN-CARE-PRD-150ML</t>
+          <t>MOIS-SIERO-ILLUMINA-SER-NA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>INVIGO SUN CARE UV purškalas apsaugantis nuo UV spindulių su provitaminu B5, 150 ml</t>
+          <t>MOISTURE&amp;MORE SIERO ILLUMINANTE drėkinamasis spindesio suteikiantis serumas</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>INVIGO</t>
+          <t>MOISTURE&amp;MORE</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7232,17 +7180,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-sun-care-uv-purskalas-apsaugantis-nuo-uv-spinduliu-su-provitaminu-b5-150-ml</t>
+          <t>https://plaukuosena.lt/moistureandmore-siero-illuminante-drekinamasis-spindesio-suteikiantis-serumas</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bea4f015-42e6-4f80-b369-3c74778fa577.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/07c4138c-6a51-4ae1-b02a-24cdfad63075.webp</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7250,14 +7198,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>150ml</t>
-        </is>
-      </c>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7269,22 +7213,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KADU-COLOR-RADIANCE-CON-250ML</t>
+          <t>NO-FRIZZ-ALLOWED-CON-NA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL COLOR RADIANCE LEAVE-IN SPRAY purškiamas kondicionierius | 250 ml</t>
+          <t>NO FRIZZ ALLOWED PERFECTING CONDITIONER kondicionierius šiauštis linkusiems plaukams</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7294,12 +7238,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/color-radiance-leave-in-spray-purskiamas-kondicionierius-250-ml</t>
+          <t>https://plaukuosena.lt/no-frizz-allowed-perfecting-conditioner-kondicionierius-siaustis-linkusiems-plaukams</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1496fbcb-5032-476b-bcd5-ff6a423b360e.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/74260607-8186-41a3-aab0-fa7b9d33cdfa.png</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7312,14 +7256,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>4064666318448</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7331,22 +7271,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KADU-COLOR-RADIANCE-MSK-200ML</t>
+          <t>NO-FRIZZ-ALLOWED-SHA-NA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL COLOR RADIANCE kaukė | 200ML</t>
+          <t>NO FRIZZ ALLOWED PERFECTING SHAMPOO šampūnas šiauštis linkusiems plaukams</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7356,17 +7296,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/color-radiance-kauke1</t>
+          <t>https://plaukuosena.lt/no-frizz-allowed-perfecting-shampoo-sampunas-siaustis-linkusiems-plaukams</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/188953a6-01e0-4821-b09a-418707b8ae5a.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1b73df2a-a171-4121-a186-d4279faaf31c.png</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7374,14 +7314,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>4064666318509</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7393,22 +7329,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KADU-COLOR-RADIANCE-CON-250ML-1EC4</t>
+          <t>NO-4-BOND-ENHANCER-SHA-NA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL COLOR RADIANCE kondicionierius | 250ML/1000ML</t>
+          <t>No.4P BOND ENHANCER TONING SHAMPOO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>No.4P</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7418,17 +7354,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/color-radiance-kauke</t>
+          <t>https://plaukuosena.lt/no4p-bond-enhancer-toning-shampoo</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b5200496-819e-44d4-9eeb-cfa65fbe0213.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/edb6f281-e6cd-4872-bec1-b7478940b7ed.png</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7436,14 +7372,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>4064666318387</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7455,22 +7387,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>KADU-COLOR-RADIANCE-SHA-250ML</t>
+          <t>OLAP-NO-3-PRD-NA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL COLOR RADIANCE šampūnas | 250ML/1000ML</t>
+          <t>OLAPLEX No. 3 HAIR PERFECTOR</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7480,17 +7412,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/color-radiance-sampunas</t>
+          <t>https://plaukuosena.lt/olaplex-no-3-hair-perfector</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/70c7fad4-d7d0-4326-8b82-3955f89277d7.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1832e17d-37c2-4f27-9dbf-03c1c80d368a.png</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7498,14 +7430,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>4064666318325</t>
+          <t>850018802840</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7517,22 +7445,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>KADU-DEEP-MOISTURE-CON-250ML</t>
+          <t>OLAP-NO-4-SHA-NA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE LEAVE-IN purškiamas kondicionierius | 250 ml</t>
+          <t>OLAPLEX No. 4 BOND MAINTENANCE SHAMPOO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7542,17 +7470,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-moisture-leave-in-purskiamas-kondicionierius-250-ml</t>
+          <t>https://plaukuosena.lt/olaplex-no-4-bond-maintenance-shampoo</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/812ff0d8-83cf-4ae5-b03e-7ae58b54d4b3.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2f17f7df-64a9-44b0-8d0d-7beb0d421ee2.png</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7560,14 +7488,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>8005610571560</t>
+          <t>896364002756</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7579,22 +7503,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KADU-DEEP-MOISTURE-MSK-200ML</t>
+          <t>OLAP-NO-4D-SHA-NA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE kaukė | 200ML</t>
+          <t>OLAPLEX No. 4D Dry Shampoo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7604,17 +7528,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-moisture-kauke</t>
+          <t>https://plaukuosena.lt/olaplex-no-4d-dry-shampoo</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/02191c64-c0d0-435c-acfd-4abe70c7d286.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4b16b116-5392-4248-beaf-e788b5b65f8c.png</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7622,14 +7546,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>8005610604022</t>
+          <t>850018802567</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7641,22 +7561,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KADU-DEEP-MOISTURE-CON-250ML-BB59</t>
+          <t>OLAP-NO-5-CON-NA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE kondicionierius | 250ML/1000ML</t>
+          <t>OLAPLEX No. 5 BOND MAINTENANCE CONDITIONER</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7666,12 +7586,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-moisture-kondicionierius</t>
+          <t>https://plaukuosena.lt/olaplex-no-5-bond-maintenance-conditioner</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/11e9244b-f1b4-4fd1-a829-d04264f37221.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/17784e89-7411-4bd4-8b97-58350ae502d8.png</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7684,14 +7604,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>8005610555089</t>
+          <t>896364002763</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7703,22 +7619,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>KADU-DEEP-MOISTURE-SHA-250ML</t>
+          <t>OLAP-NO-6-PRD-NA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE šampūnas | 250ML/1000ML</t>
+          <t>OLAPLEX No. 6 BOND SMOOTHER</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7728,17 +7644,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-moisture-sampunas</t>
+          <t>https://plaukuosena.lt/olaplex-no-6-bond-smoother</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0f57fac1-e330-41e0-aa79-c1ef82ad3610.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39301ecc-75fd-4fca-9e6a-0af9debc2e46.png</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7746,14 +7662,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>8005610602509</t>
+          <t>896364002961</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7765,22 +7677,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>KADU-SUN-SPARK-PRD-250ML</t>
+          <t>OLAP-NO-0-INTENSIV-PRD-NA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL SUN SPARK LEAVE-IN losjonas | 250 ml</t>
+          <t>OLAPLEX No.0 INTENSIVE BOND BUILDING HAIR TREATMENT</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7790,12 +7702,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/sun-spark-leave-in-losjonas-250-ml</t>
+          <t>https://plaukuosena.lt/olaplex-no0-intensive-bond-building-hair-treatment</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ed98f39-97be-49f3-9ff0-0d72b6b30996.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d72c34ad-0dbf-4c23-af6a-9e6dbc63c38e.png</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7808,14 +7720,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>8005610573397</t>
+          <t>850018802833</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7827,22 +7735,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>KADU-TONEPLEX-PEARL-SHA-250ML</t>
+          <t>OLAP-NO-10-BOND-GEL-NA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL TONEPLEX Pearl Blonde atspalvį suteikiantis šampūnas | 250ML/1000ML</t>
+          <t>OLAPLEX No.10 BOND SHAPER™ CURL DEFINING GEL</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7852,17 +7760,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/toneplex-pearl-blonde-atspalvi-suteikiantis-sampunas</t>
+          <t>https://plaukuosena.lt/no10-bond-shapertm-curl-defining-gel</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/078c44d1-6f55-4d97-9171-76689b1e9e61.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6e3ed035-956b-465b-a424-b8b30e2641de.png</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų geliai</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7870,14 +7778,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>4064666244150</t>
+          <t>850056933155</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7889,22 +7793,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>KADU-TONEPLEX-DAZANTI-MSK-200ML</t>
+          <t>OLAP-NO-3-PLUS-PRD-NA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL TONEPLEX dažanti kaukė | 200 ml</t>
+          <t>OLAPLEX No.3 PLUS Ultimate Repair Treatment</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7914,17 +7818,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/toneplex-dazanti-kauke-200-ml</t>
+          <t>https://plaukuosena.lt/olaplex-no3-plus-ultimate-repair-treatment</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/72f4806d-8501-4247-b92b-946b795f3452.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39908a67-c29d-4092-ad0e-d3b12c4c285f.png</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7932,14 +7836,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>4064666244396</t>
+          <t>810177860273</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7951,22 +7851,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>KADU-VISIBLE-REPAIR-PRD-250ML</t>
+          <t>OLAP-NO-4-CURL-SHA-250ML</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL VISIBLE REPAIR LEAVE-IN balzamas | 250 ml</t>
+          <t>OLAPLEX No.4 Curl Hydrating Shampoo | 250ML</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7976,17 +7876,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/visible-repair-leave-in-balzamas-250-ml</t>
+          <t>https://plaukuosena.lt/olaplex-no4-curl-hydrating-shampoo-or-250ml</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f58db6be-f708-4260-b0ea-414e86e49877.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/96c834cd-3879-4555-8051-670ffa93e48b.png</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8001,7 +7901,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>4064666318035</t>
+          <t>810177861041</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8013,22 +7913,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>KADU-VISIBLE-REPAIR-MSK-200ML</t>
+          <t>OLAP-NO-4C-BOND-SHA-NA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL VISIBLE REPAIR kaukė | 200ML/750ML</t>
+          <t>OLAPLEX No.4C BOND MAINTENANCE CLARIFYING SHAMPOO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8038,17 +7938,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/visible-repair-kauke</t>
+          <t>https://plaukuosena.lt/olaplex-no4c-bond-maintenance-clarifying-shampoo</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bb4a55d4-fca2-4714-9e27-863c4396c8c5.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/15aa41ad-b5ee-455b-82fe-67dd4515079d.png</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8056,14 +7956,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>4064666318967</t>
+          <t>850018802581</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8075,22 +7971,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>KADU-VISIBLE-REPAIR-CON-250ML</t>
+          <t>OLAP-NO-4FINE-BOND-SHA-NA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL VISIBLE REPAIR kondicionierius | 250ML/1000ML</t>
+          <t>OLAPLEX No.4FINE Bond Maintenance Shampoo</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8100,17 +7996,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/visible-repair-kondicionierius</t>
+          <t>https://plaukuosena.lt/no4fine-bond-maintenance-shampoo</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/01643d0f-9cbd-4081-8652-c7463c2b4580.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c99d5b13-2995-490c-b568-67b721c151a7.png</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8118,14 +8014,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>4064666317977</t>
+          <t>850056933575</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8137,22 +8029,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>KADU-VISIBLE-REPAIR-SHA-250ML</t>
+          <t>OLAP-NO-5-CURL-CON-250ML</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL VISIBLE REPAIR šampūnas | 250ML/1000ML</t>
+          <t>OLAPLEX No.5 Curl Hydrating Conditioner | 250ml</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8162,17 +8054,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/visible-repair-sampunas</t>
+          <t>https://plaukuosena.lt/olaplex-no5-curl-hydrating-conditioner-or-250ml</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bc18386f-a0b4-4385-aa76-4494ebab2985.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/73d73934-cc28-4c05-aa81-056ef03db222.webp</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8187,7 +8079,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>4064666317915</t>
+          <t>810177861010</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8199,33 +8091,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>KADU-PRIEMONE-KADUS-PRD-NA</t>
+          <t>OLAP-NO-5-LEAVE-IN-PRD-NA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Kadus Professional plaukų priemonės | Kadus kosmetika</t>
+          <t>OLAPLEX No.5 LEAVE-IN Moisturize</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>OLAPLEX</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/kadus-professional-plauku-priemones</t>
+          <t>https://plaukuosena.lt/olaplex-no5-leave-in-moisturize</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e18890ee-ba6f-43ff-a518-fce468bdc091.png</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8241,50 +8137,54 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>850056933285</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>KARS-APSAUGA-APSAUGA-PRD-NA</t>
+          <t>OLAP-NO-5FINE-BOND-CON-NA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Karščio apsauga plaukams | Apsauga nuo karščio</t>
+          <t>OLAPLEX No.5FINE Bond Maintenance Conditioner</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Karščio</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>OLAPLEX</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/karscio-apsauga-plaukams</t>
+          <t>https://plaukuosena.lt/no5fine-bond-maintenance-conditioner</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ccafd5f1-87db-45ae-af6b-3dad5b5af329.png</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8295,34 +8195,34 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>850056933612</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>LEAV-IN-FLOWER-CON-NA</t>
+          <t>OLAP-NO-5P-BLOND-CON-NA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LEAVE IN CONDITIONER FLOWER FRAGRANCE nenuskalaujamas kondicionierius</t>
+          <t>OLAPLEX No.5P BLOND ENHANCER TONING CONDITIONER</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8332,12 +8232,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/leave-in-conditioner-flower-fragrance-nenuskalaujamas-kondicionierius</t>
+          <t>https://plaukuosena.lt/olaplex-no5p-blond-enhancer-toning-conditioner</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8c38e360-1aa4-40f3-80d1-63fd05fadb48.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/35185d43-ba29-4be4-bd01-153f53e9628a.jpg</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8353,7 +8253,7 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>850045076290</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8365,22 +8265,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MILK-NO-FRIZZ-PRD-NA</t>
+          <t>OLAP-NO-7-BONDING-OIL-NA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING LIGHT MILK blizgesio ir glotnumo suteikiantis pienelis ploniems plaukams</t>
+          <t>OLAPLEX No.7 BONDING OIL</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MILK SHAKE</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>21.60</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8390,17 +8290,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-light-milk-blizgesio-ir-glotnumo-suteikiantis-pienelis-ploniems-plaukams</t>
+          <t>https://plaukuosena.lt/olaplex-no7-bonding-oil</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/05f9a283-0d68-4cbc-8b2b-a9319726c645.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8f444685-5686-42dd-b4a9-73afbcfb889f.png</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8411,7 +8311,7 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>896364002695</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8423,22 +8323,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MILK-NO-FRIZZ-SER-NA</t>
+          <t>OLAP-NO-8-BOND-MSK-NA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING RICH SERUM blizgesio ir glotnumo suteikiantis serumas storiems plaukams</t>
+          <t>OLAPLEX No.8 BOND INTENSE MOISTURE MASK</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MILK SHAKE</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8448,17 +8348,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-rich-serum-blizgesio-ir-glotnumo-suteikiantis-serumas-storiems-plaukams</t>
+          <t>https://plaukuosena.lt/olaplex-no8-bond-intense-moisture-mask</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ffc04fa-0925-48a2-86df-62a08a127ee1.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/552d57ab-d055-4c8c-9603-b292e1a25e64.png</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8469,7 +8369,7 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8481,22 +8381,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MILK-NO-FRIZZ-SPR-NA</t>
+          <t>OLAP-NO-9-BOND-SER-NA</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MILK SHAKE NO FRIZZ AMAZING ANTI-HUMIDITY SPRAY apsauginis purškiklis garbanotiems plaukams</t>
+          <t>OLAPLEX No.9 BOND PROTECTOR NOURISHING HAIR SERUM</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MILK SHAKE</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8506,17 +8406,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/amazing-anti-humidity-spray-apsauginis-purskiklis-garbanotiems-plaukams</t>
+          <t>https://plaukuosena.lt/olaplex-no9-bond-protector-nourishing-hair-serum</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ce022c83-2021-4842-9c57-7e44d680edec.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e7ab9fdc-43dc-45c3-914c-fa13f791dc3d.png</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8527,7 +8427,7 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>850018802826</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8539,38 +8439,42 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MILK-PRIEMONE-KOSMETIK-PRD-NA</t>
+          <t>OLAP-RICH-HYDRATIO-MSK-200ML</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Milk Shake plaukų priežiūros priemonės | Milk Shake kosmetika</t>
+          <t>OLAPLEX Rich Hydration Mask 200ML</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MILK SHAKE</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>OLAPLEX</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>47.00</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/milk-shake-plauku-prieziuros-priemones</t>
+          <t>https://plaukuosena.lt/rich-hydration-mask</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2d89d52d-0761-42dc-a4d6-d3ebe5da60b7.png</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8578,37 +8482,41 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>850056933919</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MOIS-MORE-DREKINAM-CON-NA</t>
+          <t>OLAP-VOLUMIZI-BLOW-PRD-NA</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MOISTURE &amp; MORE CONDITIONER drėkinamasis kondicionierius sausiems plaukams</t>
+          <t>OLAPLEX Volumizing Blow Dry Mist</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MOISTURE</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8618,17 +8526,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moisture-and-more-conditioner-drekinamasis-kondicionierius-sausiems-plaukams</t>
+          <t>https://plaukuosena.lt/olaplex-volumizing-blow-dry-mist</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9fd3e0cd-3cd4-4c27-9475-b1bd26bb4e46.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/87bf6622-3275-425b-8a73-1bb008b61716.jpg</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8639,7 +8547,7 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>850045076221</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8651,22 +8559,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MOIS-PLUS-WHIPPED-CRM-NA</t>
+          <t>OLAP-WEIGHTLE-NOURISHI-MSK-200ML</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MOISTURE PLUS WHIPPED CREAM drėkinamosios putos sausiems plaukams</t>
+          <t>OLAPLEX Weightless Nourishing Mask 200ML</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MOISTURE</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>47.00</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8676,17 +8584,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moisture-plus-whipped-cream-drekinamosios-putos-sausiems-plaukams</t>
+          <t>https://plaukuosena.lt/weightless-nourishing-mask</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8af7f7bd-70ae-43f3-b8a7-ca5fa1c0bbc8.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/da078417-7753-4c31-95e9-19242f1b1aff.png</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8694,10 +8602,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>850056933889</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8709,37 +8621,33 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MOIS-HYDRATIN-LOTION-PRD-NA</t>
+          <t>OLAP-PRIEMONE-PRODUKTA-PRD-NA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE HYDRATING LOTION drėkinamasis losjonas sausiems plaukams</t>
+          <t>Olaplex plaukų priežiūros priemonės | Olaplex produktai</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>29.00</t>
-        </is>
-      </c>
+          <t>OLAPLEX</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moistureandmore-hydrating-lotion-drekinamasis-losjonas-sausiems-plaukams</t>
+          <t>https://plaukuosena.lt/olaplex-plauku-prieziuros-priemones</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/34e3c3da-7fa7-4bb4-a951-8ff1150e33ac.webp</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8755,54 +8663,50 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MOIS-DREKINAM-SAUSIEMS-SHA-NA</t>
+          <t>PINI-GRAZINIM-POLITIKA-PRD-NA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE SHAMPOO drėkinamasis šampūnas sausiems plaukams</t>
+          <t>Pinigų grąžinimo politika – grąžinimo sąlygos</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
+          <t>Pinigų</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moistureandmore-shampoo-drekinamasis-sampunas-sausiems-plaukams</t>
+          <t>https://plaukuosena.lt/pinigu-grazinimo-politika</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3e5f63cf-df47-45e5-88af-e3561a3c7134.webp</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8813,49 +8717,45 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MOIS-SIERO-ILLUMINA-SER-NA</t>
+          <t>PLAU-GELIAI-SERUMAI-SER-NA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE SIERO ILLUMINANTE drėkinamasis spindesio suteikiantis serumas</t>
+          <t>Plaukų geliai ir serumai | Profesionalios formavimo priemonės</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>32.00</t>
-        </is>
-      </c>
+          <t>Plaukų</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moistureandmore-siero-illuminante-drekinamasis-spindesio-suteikiantis-serumas</t>
+          <t>https://plaukuosena.lt/plauku-geliai-ir-serumai</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/07c4138c-6a51-4ae1-b02a-24cdfad63075.webp</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8871,54 +8771,50 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NO-FRIZZ-ALLOWED-CON-NA</t>
+          <t>PLAU-KAUKES-PROFESIO-MSK-NA</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NO FRIZZ ALLOWED PERFECTING CONDITIONER kondicionierius šiauštis linkusiems plaukams</t>
+          <t>Plaukų kaukės | Profesionalios plaukų kaukės internetu</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
+          <t>Plaukų</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no-frizz-allowed-perfecting-conditioner-kondicionierius-siaustis-linkusiems-plaukams</t>
+          <t>https://plaukuosena.lt/plauku-kaukes</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/74260607-8186-41a3-aab0-fa7b9d33cdfa.png</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8929,34 +8825,34 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NO-FRIZZ-ALLOWED-SHA-NA</t>
+          <t>QIQI-BARE-REPAIR-OIL-NA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NO FRIZZ ALLOWED PERFECTING SHAMPOO šampūnas šiauštis linkusiems plaukams</t>
+          <t>QIQI Bare Repair Oil Plaukų aliejus</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>QIQI</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8966,17 +8862,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no-frizz-allowed-perfecting-shampoo-sampunas-siaustis-linkusiems-plaukams</t>
+          <t>https://plaukuosena.lt/qiqi-bare-repair-oil-plauku-aliejus</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1b73df2a-a171-4121-a186-d4279faaf31c.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/85f599b6-1ab5-4fe0-9330-8b393efc56d2.png</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8987,7 +8883,7 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>7290019116882</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8999,22 +8895,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NO-4-BOND-ENHANCER-SHA-NA</t>
+          <t>QIQI-GLOTNINA-SHA-NA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>No.4P BOND ENHANCER TONING SHAMPOO</t>
+          <t>QIQI Glotninantis šampūnas</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>No.4P</t>
+          <t>QIQI</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9024,12 +8920,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no4p-bond-enhancer-toning-shampoo</t>
+          <t>https://plaukuosena.lt/qiqi-glotninantis-sampunas</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/edb6f281-e6cd-4872-bec1-b7478940b7ed.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9ad34b38-7896-457c-8d2e-598db9e7336d.png</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9045,7 +8941,7 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>7290019116042</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9057,22 +8953,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>OLAP-NO-3-PRD-NA</t>
+          <t>QIQI-POROSITY-PLAY-SPR-NA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 3 HAIR PERFECTOR</t>
+          <t>QIQI Porosity Play Spray Plaukų purškiklis</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>QIQI</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9082,17 +8978,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-3-hair-perfector</t>
+          <t>https://plaukuosena.lt/qiqi-porosity-play-spray-plauku-purskiklis</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1832e17d-37c2-4f27-9dbf-03c1c80d368a.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c272a239-cd7a-422f-a950-d80d709d9259.png</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9103,7 +8999,7 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>850018802840</t>
+          <t>7290019116455</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9115,22 +9011,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>OLAP-NO-4-SHA-NA</t>
+          <t>QIQI-POROSITY-VOLUME-PRD-NA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 4 BOND MAINTENANCE SHAMPOO</t>
+          <t>QIQI Porosity Volume Code Mist Gausos apimties suteikianti dulksna</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>QIQI</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9140,17 +9036,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-4-bond-maintenance-shampoo</t>
+          <t>https://plaukuosena.lt/qiqi-porosity-volume-code-mist-gausos-apimties-suteikianti-dulksna</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2f17f7df-64a9-44b0-8d0d-7beb0d421ee2.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40938472-383c-4c92-9b8b-040403000e9d.png</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9161,7 +9057,7 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>896364002756</t>
+          <t>7290019116899</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9173,22 +9069,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>OLAP-NO-4D-SHA-NA</t>
+          <t>QIQI-SUPER-SOAKER-MSK-NA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 4D Dry Shampoo</t>
+          <t>QIQI Super Soaker Smoothing Masque Glotninanti plaukų kaukė</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>QIQI</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9198,17 +9094,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-4d-dry-shampoo</t>
+          <t>https://plaukuosena.lt/qiqi-super-soaker-smoothing-masque-glotninanti-plauku-kauke</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4b16b116-5392-4248-beaf-e788b5b65f8c.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c207ccff-61fd-499a-9db4-0ed63a8c34c7.png</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9219,7 +9115,7 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>850018802567</t>
+          <t>7290019116448</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9231,22 +9127,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>OLAP-NO-5-CON-NA</t>
+          <t>QIQI-DREKINAM-CON-NA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 5 BOND MAINTENANCE CONDITIONER</t>
+          <t>QIQI drėkinamasis kondicionierius</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>QIQI</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9256,12 +9152,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-5-bond-maintenance-conditioner</t>
+          <t>https://plaukuosena.lt/qiqi-drekinamasis-kondicionierius</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/17784e89-7411-4bd4-8b97-58350ae502d8.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e9113e8b-f95c-4cb6-ab03-9977a03ffcd1.png</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9277,7 +9173,7 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>896364002763</t>
+          <t>7290019116240</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9289,22 +9185,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>OLAP-NO-6-PRD-NA</t>
+          <t>QIQI-ALL-OUT-CRM-NA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 6 BOND SMOOTHER</t>
+          <t>Qiqi All Out Blowout užbaigimo kremas</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>QIQI</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9314,12 +9210,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-6-bond-smoother</t>
+          <t>https://plaukuosena.lt/qiqi-all-out-blowout-uzbaigimo-kremas</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39301ecc-75fd-4fca-9e6a-0af9debc2e46.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ed4db76-21f3-4ce0-a884-2230c7418f53.png</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9335,7 +9231,7 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>896364002961</t>
+          <t>7290019116264</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9347,37 +9243,33 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>OLAP-NO-0-INTENSIV-PRD-NA</t>
+          <t>QIQI-PRIEMONE-KOSMETIK-PRD-NA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>OLAPLEX No.0 INTENSIVE BOND BUILDING HAIR TREATMENT</t>
+          <t>Qiqi plaukų priežiūros priemonės | Qiqi kosmetika</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
-      </c>
+          <t>QIQI</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no0-intensive-bond-building-hair-treatment</t>
+          <t>https://plaukuosena.lt/qiqi-plauku-prieziuros-priemones</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d72c34ad-0dbf-4c23-af6a-9e6dbc63c38e.png</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9393,34 +9285,34 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>850018802833</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>OLAP-NO-10-BOND-GEL-NA</t>
+          <t>SILV-SHINE-ZILIEMS-CON-NA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>OLAPLEX No.10 BOND SHAPER™ CURL DEFINING GEL</t>
+          <t>SILVER SHINE CONDITIONER kondicionierius žiliems / šviesintiems plaukams</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>SILVER</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9430,17 +9322,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no10-bond-shapertm-curl-defining-gel</t>
+          <t>https://plaukuosena.lt/silver-shine-conditioner-kondicionierius-ziliems-sviesintiems-plaukams</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6e3ed035-956b-465b-a424-b8b30e2641de.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/78ae2b87-aede-4bf6-a3fc-ede2a0e31735.webp</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Plaukų geliai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9451,7 +9343,7 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>850056933155</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9463,22 +9355,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OLAP-NO-3-PLUS-PRD-NA</t>
+          <t>SILV-SHINE-LIGHT-SHA-NA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>OLAPLEX No.3 PLUS Ultimate Repair Treatment</t>
+          <t>SILVER SHINE LIGHT SHAMPOO šampūnas žiliems / šviesintiems plaukams</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>SILVER</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9488,17 +9380,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no3-plus-ultimate-repair-treatment</t>
+          <t>https://plaukuosena.lt/silver-shine-shampoo-sampunas-ziliems-sviesintiems-plaukams</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39908a67-c29d-4092-ad0e-d3b12c4c285f.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/33a6ba33-a228-4fc9-8fe9-6b66a129541b.webp</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9509,7 +9401,7 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>810177860273</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9521,22 +9413,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>OLAP-NO-4C-BOND-SHA-NA</t>
+          <t>SMOO-MIRACLE-SHIELD-SPR-NA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>OLAPLEX No.4C BOND MAINTENANCE CLARIFYING SHAMPOO</t>
+          <t>SMOOTHING MIRACLE SHIELD nuo karščio ir drėgmės apsaugantis purškiklis</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>SMOOTHING</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9546,17 +9438,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no4c-bond-maintenance-clarifying-shampoo</t>
+          <t>https://plaukuosena.lt/smoothing-miracle-shield-nuo-karscio-ir-dregmes-apsaugantis-purskiklis</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/15aa41ad-b5ee-455b-82fe-67dd4515079d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4f9a2abf-0979-4209-b9ac-a2365f16cfd9.webp</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9567,7 +9459,7 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>850018802581</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9579,42 +9471,38 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OLAP-NO-4FINE-BOND-SHA-NA</t>
+          <t>SAUL-APSAUGA-APSAUGA-PRD-NA</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>OLAPLEX No.4FINE Bond Maintenance Shampoo</t>
+          <t>Saulės apsauga plaukams | Apsauga nuo UV</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
-      </c>
+          <t>Saulės</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no4fine-bond-maintenance-shampoo</t>
+          <t>https://plaukuosena.lt/saules-apsauga-plaukams</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c99d5b13-2995-490c-b568-67b721c151a7.png</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9625,34 +9513,34 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>850056933575</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>OLAP-NO-5-LEAVE-IN-PRD-NA</t>
+          <t>ULTI-REPAIR-INTENSYV-MSK-NA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>OLAPLEX No.5 LEAVE-IN Moisturize</t>
+          <t>ULTIMATE REPAIR intensyvaus poveikio kaukė pažeistiems plaukams STEP 2</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>ULTIMATE</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9662,17 +9550,17 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no5-leave-in-moisturize</t>
+          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-kauke-pazeistiems-plaukams-step-2</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e18890ee-ba6f-43ff-a518-fce468bdc091.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40b6a8c2-185a-422b-9154-64aa5d5b8555.png</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9683,7 +9571,7 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>850056933285</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9695,22 +9583,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OLAP-NO-5FINE-BOND-CON-NA</t>
+          <t>ULTI-REPAIR-INTENSYV-CON-NA</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>OLAPLEX No.5FINE Bond Maintenance Conditioner</t>
+          <t>ULTIMATE REPAIR intensyvaus poveikio kondicionierius pažeistiems plaukams STEP 2</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>ULTIMATE</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9720,12 +9608,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no5fine-bond-maintenance-conditioner</t>
+          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-kondicionierius-pazeistiems-plaukams-step-2-</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ccafd5f1-87db-45ae-af6b-3dad5b5af329.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3634c6f3-03f0-47ee-800b-94c7e7402d89.jpg</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9741,7 +9629,7 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>850056933612</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -9753,22 +9641,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>OLAP-NO-5P-BLOND-CON-NA</t>
+          <t>ULTI-REPAIR-INTENSYV-SHA-NA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>OLAPLEX No.5P BLOND ENHANCER TONING CONDITIONER</t>
+          <t>ULTIMATE REPAIR intensyvaus poveikio šampūnas pažeistiems plaukams STEP 1</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>ULTIMATE</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>27.00</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9778,17 +9666,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no5p-blond-enhancer-toning-conditioner</t>
+          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-sampunas-pazeistiems-plaukams-step-1</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/35185d43-ba29-4be4-bd01-153f53e9628a.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/10b51403-3d69-4efa-8f65-c0c2bf55fa06.jpg</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9799,7 +9687,7 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>850045076290</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9811,22 +9699,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OLAP-NO-7-BONDING-OIL-NA</t>
+          <t>ULTI-REPAIR-NAKTINIS-SER-NA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>OLAPLEX No.7 BONDING OIL</t>
+          <t>ULTIMATE REPAIR naktinis plaukų serumas STEP 5</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>ULTIMATE</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9836,17 +9724,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no7-bonding-oil</t>
+          <t>https://plaukuosena.lt/ultimate-repair-naktinis-plauku-serumas-step-5</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8f444685-5686-42dd-b4a9-73afbcfb889f.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0cda5ab2-52cf-4f06-8b6c-0f7b5b4bc2cf.jpg</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Plaukų aliejai</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9857,7 +9745,7 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>896364002695</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -9869,22 +9757,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OLAP-NO-8-BOND-MSK-NA</t>
+          <t>ULTI-SMOOTH-MAITINAN-MSK-NA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>OLAPLEX No.8 BOND INTENSE MOISTURE MASK</t>
+          <t>ULTIMATE SMOOTH maitinanti kaukė su skvalanu ir omega-9</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>ULTIMATE</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9894,12 +9782,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no8-bond-intense-moisture-mask</t>
+          <t>https://plaukuosena.lt/ultimate-smooth-maitinanti-kauke-su-skvalanu-ir-omega-9</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/552d57ab-d055-4c8c-9603-b292e1a25e64.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f7774306-1953-481b-9f15-746af2bac04c.jpg</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -9915,7 +9803,7 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9927,22 +9815,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OLAP-NO-9-BOND-SER-NA</t>
+          <t>WELL-EIMI-ABSOLUTE-PRD-300ML</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>OLAPLEX No.9 BOND PROTECTOR NOURISHING HAIR SERUM</t>
+          <t>WELLA PROFESSIONALS EIMI Absolute Set lakas # 4+ | 300ML</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9952,17 +9840,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no9-bond-protector-nourishing-hair-serum</t>
+          <t>https://plaukuosena.lt/eimi-absolute-set-lakas-4-300-ml</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e7ab9fdc-43dc-45c3-914c-fa13f791dc3d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4609936e-f051-43d0-bf28-23a210169d95.jpg</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9970,10 +9858,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr"/>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>850018802826</t>
+          <t>8005610563244</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9985,22 +9877,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OLAP-RICH-HYDRATIO-MSK-200ML</t>
+          <t>WELL-EIMI-DRY-SHA-180ML</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>OLAPLEX Rich Hydration Mask 200ML</t>
+          <t>WELLA PROFESSIONALS EIMI Dry Me Dry sausas šampūnas #1 | 180ML</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>47.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10010,17 +9902,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/rich-hydration-mask</t>
+          <t>https://plaukuosena.lt/eimi-dry-me-dry-sausas-sampunas-1-180-ml</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2d89d52d-0761-42dc-a4d6-d3ebe5da60b7.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/685481b5-65b1-4e9e-a0d1-967851f46e02.jpg</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10030,12 +9922,12 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>180ml</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>850056933919</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10047,22 +9939,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>OLAP-VOLUMIZI-BLOW-PRD-NA</t>
+          <t>WELL-EIMI-EXTRA-FOA-300ML</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>OLAPLEX Volumizing Blow Dry Mist</t>
+          <t>WELLA PROFESSIONALS EIMI Extra Volume putos #3 | 300ML</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10072,12 +9964,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-volumizing-blow-dry-mist</t>
+          <t>https://plaukuosena.lt/eimi-extra-volume-putos-3-300-ml</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/87bf6622-3275-425b-8a73-1bb008b61716.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4ce5d05e-e0eb-4588-9266-14c75d59b5b2.jpg</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10090,10 +9982,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr"/>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>850045076221</t>
+          <t>4064666211916</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10105,22 +10001,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>OLAP-WEIGHTLE-NOURISHI-MSK-200ML</t>
+          <t>WELL-EIMI-FLEXIBLE-PRD-250ML</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>OLAPLEX Weightless Nourishing Mask 200ML</t>
+          <t>WELLA PROFESSIONALS EIMI Flexible Finish lakas #2 | 250ML</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>47.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10130,17 +10026,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/weightless-nourishing-mask</t>
+          <t>https://plaukuosena.lt/eimi-flexible-finish-lakas-2-250-ml</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/da078417-7753-4c31-95e9-19242f1b1aff.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/690edb16-bb3f-41bc-a6d0-6e1c32ae98d2.jpg</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10150,12 +10046,12 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>850056933889</t>
+          <t>4064666213958</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10167,33 +10063,37 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>OLAP-PRIEMONE-PRODUKTA-PRD-NA</t>
+          <t>WELL-EIMI-FLOWING-PRD-100ML</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Olaplex plaukų priežiūros priemonės | Olaplex produktai</t>
+          <t>WELLA PROFESSIONALS EIMI Flowing Form balzamas #2 | 100ML</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>WELLA PROFESSIONALS</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-plauku-prieziuros-priemones</t>
+          <t>https://plaukuosena.lt/eimi-flowing-form-balzamas-2-100-ml</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1544dbd7-35f9-42b5-92ec-d0cd6f9943ab.jpg</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10206,48 +10106,56 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr"/>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>8005610575025</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PINI-GRAZINIM-POLITIKA-PRD-NA</t>
+          <t>WELL-EIMI-GLAM-PRD-200ML</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Pinigų grąžinimo politika – grąžinimo sąlygos</t>
+          <t>WELLA PROFESSIONALS EIMI Glam Mist lakas / blizgis #1 | 200ML</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Pinigų</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>WELLA PROFESSIONALS</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>27.00</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/pinigu-grazinimo-politika</t>
+          <t>https://plaukuosena.lt/eimi-glam-mist-lakas-blizgis-1-200-ml</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/47a0bc9e-6340-462e-a327-ccd1efe76dda.jpg</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10260,53 +10168,61 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr"/>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666314532</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PLAU-GELIAI-SERUMAI-SER-NA</t>
+          <t>WELL-EIMI-MISTIFY-PRD-300ML</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Plaukų geliai ir serumai | Profesionalios formavimo priemonės</t>
+          <t>WELLA PROFESSIONALS EIMI Mistify Me Light lakas #2 | 300ML</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Plaukų</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>WELLA PROFESSIONALS</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/plauku-geliai-ir-serumai</t>
+          <t>https://plaukuosena.lt/eimi-mistify-me-light-lakas-2-300-ml</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f44de339-ff78-47c5-bef9-4840e03045b9.jpg</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10314,53 +10230,61 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr"/>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666214238</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PLAU-KAUKES-PROFESIO-MSK-NA</t>
+          <t>WELL-EIMI-MISTIFY-PRD-300ML-4AE5</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Plaukų kaukės | Profesionalios plaukų kaukės internetu</t>
+          <t>WELLA PROFESSIONALS EIMI Mistify Me Strong lakas #3 | 300ML</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Plaukų</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
+          <t>WELLA PROFESSIONALS</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/plauku-kaukes</t>
+          <t>https://plaukuosena.lt/eimi-mistify-me-strong-lakas-3-300-ml</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/25a65e8a-b11d-4d44-9b95-7db4a88549e5.jpg</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10368,37 +10292,41 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr"/>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666214252</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>QIQI-BARE-REPAIR-OIL-NA</t>
+          <t>WELL-EIMI-NUTRICUR-FOA-300ML</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>QIQI Bare Repair Oil Plaukų aliejus</t>
+          <t>WELLA PROFESSIONALS EIMI NUTRICURLS BOOST BOUNCE 72h švelnios putos garbanoms #2 | 300ML</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>QIQI</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>23.50</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10408,17 +10336,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-bare-repair-oil-plauku-aliejus</t>
+          <t>https://plaukuosena.lt/eimi-nutricurls-boost-bounce-72h-svelnios-putos-garbanoms-2-300-ml</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/85f599b6-1ab5-4fe0-9330-8b393efc56d2.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e1731c4e-394c-435e-b753-e948d7cfbf89.jpg</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Plaukų aliejai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10426,10 +10354,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr"/>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>7290019116882</t>
+          <t>4064666213392</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10441,22 +10373,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>QIQI-GLOTNINA-SHA-NA</t>
+          <t>WELL-EIMI-NATURAL-FOA-300ML</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>QIQI Glotninantis šampūnas</t>
+          <t>WELLA PROFESSIONALS EIMI Natural Volume putos #2 | 300ML</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>QIQI</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10466,17 +10398,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-glotninantis-sampunas</t>
+          <t>https://plaukuosena.lt/eimi-natural-volume-putos-2-300-ml</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9ad34b38-7896-457c-8d2e-598db9e7336d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9473f762-aafe-44c0-9acb-7e105a4f8d11.jpg</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10484,10 +10416,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr"/>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>7290019116042</t>
+          <t>4064666211893</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10499,22 +10435,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>QIQI-POROSITY-PLAY-SPR-NA</t>
+          <t>WELL-EIMI-NUTRICUR-CRM-150ML</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>QIQI Porosity Play Spray Plaukų purškiklis</t>
+          <t>WELLA PROFESSIONALS EIMI Nutricurls Curl Shaper kremas #2 | 150ML</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>QIQI</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10524,17 +10460,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-porosity-play-spray-plauku-purskiklis</t>
+          <t>https://plaukuosena.lt/eimi-nutricurls-curl-shaper-kremas-2-150-ml</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c272a239-cd7a-422f-a950-d80d709d9259.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/05eb6823-d484-4232-a92a-05a825b67fc3.jpg</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10542,10 +10478,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr"/>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>7290019116455</t>
+          <t>4064666213415</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10557,22 +10497,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>QIQI-POROSITY-VOLUME-PRD-NA</t>
+          <t>WELL-EIMI-NUTRICUR-PRD-150ML</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>QIQI Porosity Volume Code Mist Gausos apimties suteikianti dulksna</t>
+          <t>WELLA PROFESSIONALS EIMI Nutricurls Fresh Up purškalas #1 | 150ML</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>QIQI</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10582,17 +10522,17 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-porosity-volume-code-mist-gausos-apimties-suteikianti-dulksna</t>
+          <t>https://plaukuosena.lt/eimi-nutricurls-fresh-up-purskalas-1-150-ml</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40938472-383c-4c92-9b8b-040403000e9d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c849de07-4e68-4b6b-b4ed-a59ac843799e.jpg</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10600,10 +10540,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>7290019116899</t>
+          <t>4064666213439</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -10615,22 +10559,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>QIQI-SUPER-SOAKER-MSK-NA</t>
+          <t>WELL-EIMI-NUTRICUR-FOA-200ML</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>QIQI Super Soaker Smoothing Masque Glotninanti plaukų kaukė</t>
+          <t>WELLA PROFESSIONALS EIMI Nutricurls Soft Twirl putos #2 | 200ML</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>QIQI</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>26.50</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10640,17 +10584,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-super-soaker-smoothing-masque-glotninanti-plauku-kauke</t>
+          <t>https://plaukuosena.lt/eimi-nutricurls-soft-twirl-putos-2-200-ml</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c207ccff-61fd-499a-9db4-0ed63a8c34c7.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/01c8bbb3-0429-4f4c-9d1e-508b94ae4ba9.jpg</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10658,10 +10602,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr"/>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>7290019116448</t>
+          <t>4064666212869</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10673,22 +10621,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>QIQI-DREKINAM-CON-NA</t>
+          <t>WELL-EIMI-OCEAN-PRD-150ML</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>QIQI drėkinamasis kondicionierius</t>
+          <t>WELLA PROFESSIONALS EIMI Ocean Spritz purškalas su druska #2 | 150ML</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>QIQI</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10698,17 +10646,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-drekinamasis-kondicionierius</t>
+          <t>https://plaukuosena.lt/eimi-ocean-spritz-purskalas-su-druska-2-150-ml</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e9113e8b-f95c-4cb6-ab03-9977a03ffcd1.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ad6f5336-91da-4ba8-8a8d-12468afe45c7.jpg</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10716,10 +10664,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr"/>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>7290019116240</t>
+          <t>8005610534558</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10731,22 +10683,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>QIQI-ALL-OUT-CRM-NA</t>
+          <t>WELL-EIMI-PEARL-GEL-100ML</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Qiqi All Out Blowout užbaigimo kremas</t>
+          <t>WELLA PROFESSIONALS EIMI Pearl Styler gelis #3 | 100ML</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>QIQI</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10756,17 +10708,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-all-out-blowout-uzbaigimo-kremas</t>
+          <t>https://plaukuosena.lt/eimi-pearl-styler-gelis-3-100-ml</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ed4db76-21f3-4ce0-a884-2230c7418f53.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/144e8417-a5e5-4fb1-a96d-9ea6632bffa9.jpg</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų geliai</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10774,10 +10726,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr"/>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>7290019116264</t>
+          <t>8005610587745</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10789,33 +10745,37 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>QIQI-PRIEMONE-KOSMETIK-PRD-NA</t>
+          <t>WELL-EIMI-PERFECT-PRD-100ML</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Qiqi plaukų priežiūros priemonės | Qiqi kosmetika</t>
+          <t>WELLA PROFESSIONALS EIMI Perfect Me losjonas #1 | 100ML</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>QIQI</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>WELLA PROFESSIONALS</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-plauku-prieziuros-priemones</t>
+          <t>https://plaukuosena.lt/eimi-perfect-me-losjonas-1-100-ml</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c2858f89-5b77-4ca7-9214-22d5758e79fd.jpg</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10828,37 +10788,41 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr"/>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>8005610587509</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SILV-SHINE-ZILIEMS-CON-NA</t>
+          <t>WELL-EIMI-PERFECT-PRD-150ML</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SILVER SHINE CONDITIONER kondicionierius žiliems / šviesintiems plaukams</t>
+          <t>WELLA PROFESSIONALS EIMI Perfect Setting purškiamas plaukų losjonas #2 |150ML</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SILVER</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10868,17 +10832,17 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/silver-shine-conditioner-kondicionierius-ziliems-sviesintiems-plaukams</t>
+          <t>https://plaukuosena.lt/eimi-perfect-setting-purskiamas-plauku-losjonas-2-150-ml</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/78ae2b87-aede-4bf6-a3fc-ede2a0e31735.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/831cbe0a-7ea7-4da3-9d64-a7da293455c7.jpg</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10886,10 +10850,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr"/>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>8005610586052</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -10901,22 +10869,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SILV-SHINE-LIGHT-SHA-NA</t>
+          <t>WELL-EIMI-ROOT-FOA-200ML</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SILVER SHINE LIGHT SHAMPOO šampūnas žiliems / šviesintiems plaukams</t>
+          <t>WELLA PROFESSIONALS EIMI Root Shoot purškiamos putos #2 | 200ML</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SILVER</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>23.50</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10926,17 +10894,17 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/silver-shine-shampoo-sampunas-ziliems-sviesintiems-plaukams</t>
+          <t>https://plaukuosena.lt/eimi-root-shoot-purskiamos-putos-2-200-ml</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/33a6ba33-a228-4fc9-8fe9-6b66a129541b.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/20d544d5-a43b-420a-8011-c64e7eae68ee.jpg</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10944,10 +10912,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr"/>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666211978</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10959,22 +10931,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SMOO-MIRACLE-SHIELD-SPR-NA</t>
+          <t>WELL-EIMI-SHAPE-GEL-150ML</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SMOOTHING MIRACLE SHIELD nuo karščio ir drėgmės apsaugantis purškiklis</t>
+          <t>WELLA PROFESSIONALS EIMI SHAPE ME 48 val plaukų formą išlaikantis gelis #2 | 150ML</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SMOOTHING</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10984,17 +10956,17 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/smoothing-miracle-shield-nuo-karscio-ir-dregmes-apsaugantis-purskiklis</t>
+          <t>https://plaukuosena.lt/eimi-shape-me-48-val-plauku-forma-islaikantis-gelis-2-150-ml</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4f9a2abf-0979-4209-b9ac-a2365f16cfd9.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cf24ed41-364c-4e1f-8323-ab8095dae01b.jpg</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų geliai</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11002,10 +10974,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr"/>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666228976</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11017,33 +10993,37 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SAUL-APSAUGA-APSAUGA-PRD-NA</t>
+          <t>WELL-EIMI-SHAPE-FOA-300ML</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Saulės apsauga plaukams | Apsauga nuo UV</t>
+          <t>WELLA PROFESSIONALS EIMI Shape Control putos #4 | 300ML</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Saulės</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>WELLA PROFESSIONALS</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/saules-apsauga-plaukams</t>
+          <t>https://plaukuosena.lt/eimi-shape-control-putos-4-300-ml</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bbbd8914-6602-4103-878b-c10b2612242f.jpg</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11056,37 +11036,41 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr"/>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666211930</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ULTI-COLOR-MIRACLE-MSK-NA</t>
+          <t>WELL-EIMI-SUGAR-PRD-150ML</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ULTIMATE COLOR Miracle Leave–in Mask – Miracle nenuplaunama kaukė STEP 2</t>
+          <t>WELLA PROFESSIONALS EIMI Sugar Lift purškalas apimčiai #3 | 150ML</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11096,17 +11080,17 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-color-miracle-leave-in-mask-miracle-nenuplaunama-kauke-step-2</t>
+          <t>https://plaukuosena.lt/eimi-sugar-lift-purskalas-apimciai-3-150-ml</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6f764996-cf18-4ba3-a94a-1d565d3722ba.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0e33562e-8331-4101-a44a-730c2fbfb1af.jpg</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11114,10 +11098,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr"/>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>8005610587776</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11129,22 +11117,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ULTI-COLOR-SHINE-SPR-95ML</t>
+          <t>WELL-EIMI-SUPER-PRD-300ML</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ULTIMATE COLOR Shine Spray – Blizgesio suteikiantis purškiklis STEP 3, 95 ml</t>
+          <t>WELLA PROFESSIONALS EIMI Super Set lakas #4 | 300ML</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11154,17 +11142,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-color-shine-spray-blizgesio-suteikiantis-purskiklis-step-3-95-ml</t>
+          <t>https://plaukuosena.lt/eimi-super-set-lakas-4-300-ml</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/dde4d1d2-891e-49a2-8f98-89265d9ed025.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a4229f5f-7428-44ab-b006-da4faa1587a9.jpg</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11174,12 +11162,12 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>95ml</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666214153</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11191,22 +11179,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ULTI-REPAIR-INTENSYV-MSK-NA</t>
+          <t>WELL-EIMI-THERMAL-PRD-150ML</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR intensyvaus poveikio kaukė pažeistiems plaukams STEP 2</t>
+          <t>WELLA PROFESSIONALS EIMI Thermal Image purškalas nuo karščio #2 | 150ML</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11216,17 +11204,17 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-kauke-pazeistiems-plaukams-step-2</t>
+          <t>https://plaukuosena.lt/eimi-thermal-image-purskalas-nuo-karscio-2-150-ml</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40b6a8c2-185a-422b-9154-64aa5d5b8555.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/27f63de3-6f4d-4932-9873-48b4fbc2f296.jpg</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11234,10 +11222,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr"/>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>8005610587417</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11249,22 +11241,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ULTI-REPAIR-INTENSYV-CON-NA</t>
+          <t>WELL-FUSION-INTENSE-MSK-NA</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR intensyvaus poveikio kondicionierius pažeistiems plaukams STEP 2</t>
+          <t>WELLA PROFESSIONALS FUSION Intense Repair atkurianti kaukė</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11274,17 +11266,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-kondicionierius-pazeistiems-plaukams-step-2-</t>
+          <t>https://plaukuosena.lt/fusion-intense-repair-atkurianti-kauke</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3634c6f3-03f0-47ee-800b-94c7e7402d89.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/49ba0f2c-4336-4e46-8e4e-5997a332dd4b.jpg</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11295,7 +11287,7 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11307,22 +11299,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ULTI-REPAIR-INTENSYV-SHA-NA</t>
+          <t>WELL-INVIGO-BLONDE-SHA-300ML</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR intensyvaus poveikio šampūnas pažeistiems plaukams STEP 1</t>
+          <t>WELLA PROFESSIONALS INVIGO BLONDE RECHARGE geltoną atspalvį neutralizuojantis šampūnas 300ML | 500ML | 1000ML</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>27.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11332,12 +11324,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-sampunas-pazeistiems-plaukams-step-1</t>
+          <t>https://plaukuosena.lt/invigo-blonde-recharge-geltona-atspalvi-neutralizuojantis-sampunas</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/10b51403-3d69-4efa-8f65-c0c2bf55fa06.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/61e0e49f-b917-4955-b58c-1a2dc44b9b47.jpg</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11350,10 +11342,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr"/>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666338873</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11365,22 +11361,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ULTI-REPAIR-NAKTINIS-SER-NA</t>
+          <t>WELL-INVIGO-BLONDE-CON-200ML</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR naktinis plaukų serumas STEP 5</t>
+          <t>WELLA PROFESSIONALS INVIGO BLONDE RECHARGE šaltą atspalvį suteikiantis kondicionierius, 200 ml</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11390,17 +11386,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-repair-naktinis-plauku-serumas-step-5</t>
+          <t>https://plaukuosena.lt/invigo-blonde-recharge-salta-atspalvi-suteikiantis-kondicionierius-200-ml</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0cda5ab2-52cf-4f06-8b6c-0f7b5b4bc2cf.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3dc901e9-409d-4ffd-808f-292e3328f27b.jpg</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11408,10 +11404,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J183" t="inlineStr"/>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666339016</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11423,22 +11423,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ULTI-SMOOTH-MAITINAN-MSK-NA</t>
+          <t>WELL-INVIGO-SCALP-MSK-150ML</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ULTIMATE SMOOTH maitinanti kaukė su skvalanu ir omega-9</t>
+          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminanti bekvapė kaukė jautriai galvos odai, 150 ml</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11448,12 +11448,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-smooth-maitinanti-kauke-su-skvalanu-ir-omega-9</t>
+          <t>https://plaukuosena.lt/invigo-scalp-balance-raminanti-bekvape-kauke-jautriai-galvos-odai-150-ml</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f7774306-1953-481b-9f15-746af2bac04c.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2afb2854-6bd1-40cf-8cdc-974055d4e6d7.jpg</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11466,10 +11466,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr"/>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666585314</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11481,12 +11485,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>WELL-FUSION-INTENSE-MSK-NA</t>
+          <t>WELL-INVIGO-SCALP-SHA-300ML</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS FUSION Intense Repair atkurianti kaukė</t>
+          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminantis bekvapis šampūnas jautriai galvos odai, 300 ml |1000 ml</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11496,7 +11500,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11506,17 +11510,17 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/fusion-intense-repair-atkurianti-kauke</t>
+          <t>https://plaukuosena.lt/invigo-scalp-balance-raminantis-bekvapis-sampunas-jautriai-galvos-odai-300-ml</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/49ba0f2c-4336-4e46-8e4e-5997a332dd4b.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d760b01d-97b7-44c5-a495-8a1f29726f57.jpg</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11524,10 +11528,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666585284</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11539,12 +11547,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>WELL-INVIGO-SCALP-MSK-150ML</t>
+          <t>WELL-INVIGO-SCALP-SER-6ML</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminanti bekvapė kaukė jautriai galvos odai, 150 ml</t>
+          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE serumas nuo plaukų slinkimo, 8x6ml</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11554,7 +11562,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>44.00</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11564,17 +11572,17 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-scalp-balance-raminanti-bekvape-kauke-jautriai-galvos-odai-150-ml</t>
+          <t>https://plaukuosena.lt/invigo-scalp-balance-serumas-nuo-plauku-slinkimo-8x6ml</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2afb2854-6bd1-40cf-8cdc-974055d4e6d7.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0ac06d9c-42c4-4ede-b4e6-ff007d17f540.jpg</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11584,12 +11592,12 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>6ml</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666585369</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11601,12 +11609,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>WELL-INVIGO-SCALP-SHA-300ML</t>
+          <t>WELL-INVIGO-SCALP-SHA-300ML-496F</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminantis bekvapis šampūnas jautriai galvos odai, 300 ml |1000 ml</t>
+          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE šampūnas nuo pleiskanų, 300 ml</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11626,12 +11634,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-scalp-balance-raminantis-bekvapis-sampunas-jautriai-galvos-odai-300-ml</t>
+          <t>https://plaukuosena.lt/invigo-scalp-balance-sampunas-nuo-pleiskanu-300-ml</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d760b01d-97b7-44c5-a495-8a1f29726f57.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8da87958-5134-4d18-936e-4df20ffc120b.jpg</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11651,7 +11659,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666585246</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11663,12 +11671,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>WELL-INVIGO-SCALP-SHA-300ML-496F</t>
+          <t>WELL-INVIGO-SUN-PRD-150ML</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE šampūnas nuo pleiskanų, 300 ml</t>
+          <t>WELLA PROFESSIONALS INVIGO SUN CARE UV purškalas apsaugantis nuo UV spindulių su provitaminu B5 | 150ML</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11678,7 +11686,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11688,17 +11696,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-scalp-balance-sampunas-nuo-pleiskanu-300-ml</t>
+          <t>https://plaukuosena.lt/invigo-sun-care-uv-purskalas-apsaugantis-nuo-uv-spinduliu-su-provitaminu-b5-150-ml</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8da87958-5134-4d18-936e-4df20ffc120b.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bea4f015-42e6-4f80-b369-3c74778fa577.jpg</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11708,12 +11716,12 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4064666338996</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11725,12 +11733,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>WELL-ULTIMATE-COLOR-CON-NA</t>
+          <t>WELL-ULTIMATE-COLOR-CON-200ML</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE COLOR Conditioner – Drėkinantis dažytų plaukų kondicionierius STEP 2</t>
+          <t>WELLA PROFESSIONALS ULTIMATE COLOR Conditioner – Drėkinantis dažytų plaukų kondicionierius STEP 2 | 200ML | 1000ML</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11755,7 +11763,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bfeffc09-2cb6-4be4-aeec-026917a81c39.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/88cc20f0-3fde-46a7-8e0c-cb6bdf1b9c19.jpg</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11768,10 +11776,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J189" t="inlineStr"/>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4068359196528</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -11783,12 +11795,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>WELL-ULTIMATE-COLOR-SHA-NA</t>
+          <t>WELL-ULTIMATE-COLOR-MSK-30ML</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE COLOR Shampoo – Dažytų plaukų šampūnas be sulfatų STEP 1</t>
+          <t>WELLA PROFESSIONALS ULTIMATE COLOR Miracle Leave–in Mask – Miracle nenuplaunama kaukė STEP 2 | 30ML | 95ML</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11798,7 +11810,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11808,17 +11820,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-color-shampoo-dazytu-plauku-sampunas-be-sulfatu-step-1</t>
+          <t>https://plaukuosena.lt/ultimate-color-miracle-leave-in-mask-miracle-nenuplaunama-kauke-step-2</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/09df21fa-1581-431d-aba4-e172187f1cff.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6f764996-cf18-4ba3-a94a-1d565d3722ba.jpg</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -11826,10 +11838,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J190" t="inlineStr"/>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>30ml</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4068359196573</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11841,12 +11857,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>WELL-ULTIMATE-SMOOTH-CON-NA</t>
+          <t>WELL-ULTIMATE-COLOR-SHA-250ML</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE SMOOTH maitinantis kondicionierius su skvalanu ir omega-9</t>
+          <t>WELLA PROFESSIONALS ULTIMATE COLOR Shampoo – Dažytų plaukų šampūnas be sulfatų STEP 1 | 250ML | 1000ML</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11856,7 +11872,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11866,17 +11882,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-smooth-maitinantis-kondicionierius-su-skvalanu-ir-omega-9</t>
+          <t>https://plaukuosena.lt/ultimate-color-shampoo-dazytu-plauku-sampunas-be-sulfatu-step-1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/485269d4-f20c-4f8d-a9be-437f4b0aa81e.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9bcd73a1-e8a8-481d-9331-41e2eaf98c2b.jpg</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -11884,10 +11900,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J191" t="inlineStr"/>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4068359196474</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11899,12 +11919,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>WELL-ULTIMATE-SMOOTH-SER-NA</t>
+          <t>WELL-ULTIMATE-COLOR-SPR-95ML</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE SMOOTH miracle aliejinis serumas skvalanu ir omega-9</t>
+          <t>WELLA PROFESSIONALS ULTIMATE COLOR Shine Spray – Blizgesio suteikiantis purškiklis STEP 3 | 95ML</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11914,7 +11934,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11924,17 +11944,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-smooth-miracle-aliejinis-serumas-skvalanu-ir-omega-9</t>
+          <t>https://plaukuosena.lt/ultimate-color-shine-spray-blizgesio-suteikiantis-purskiklis-step-3-95-ml</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/518f9af2-8fc1-4590-932e-eaa87cdb3ac6.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/dde4d1d2-891e-49a2-8f98-89265d9ed025.jpg</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Plaukų aliejai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -11942,10 +11962,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J192" t="inlineStr"/>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>95ml</t>
+        </is>
+      </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>4068359196610</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11957,12 +11981,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>WELL-FUSION-ATSTATOM-SHA-NA</t>
+          <t>WELL-ULTIMATE-SMOOTH-CON-NA</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Wella Professionals FUSION atstatomasis šampūnas</t>
+          <t>WELLA PROFESSIONALS ULTIMATE SMOOTH maitinantis kondicionierius su skvalanu ir omega-9</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11972,7 +11996,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11982,17 +12006,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/loreal-professionnel-metal-detox-sampunas</t>
+          <t>https://plaukuosena.lt/ultimate-smooth-maitinantis-kondicionierius-su-skvalanu-ir-omega-9</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ed6894bd-b132-4cb6-9a8a-0a4f96b07eac.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/485269d4-f20c-4f8d-a9be-437f4b0aa81e.jpg</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12003,7 +12027,7 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12015,12 +12039,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>WELL-ULTIMATE-SMOOTH-SHA-NA</t>
+          <t>WELL-ULTIMATE-SMOOTH-SER-NA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Wella Professionals Ultimate Smooth intensyviai maitinantis šampūnas</t>
+          <t>WELLA PROFESSIONALS ULTIMATE SMOOTH miracle aliejinis serumas skvalanu ir omega-9</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12030,7 +12054,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>27.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12040,17 +12064,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/wella-professionals-ultimate-smooth-intensyviai-maitinantis-sampunas</t>
+          <t>https://plaukuosena.lt/ultimate-smooth-miracle-aliejinis-serumas-skvalanu-ir-omega-9</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/90552437-c3c8-46c1-ad07-2d1cbaa18300.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/518f9af2-8fc1-4590-932e-eaa87cdb3ac6.jpg</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12061,7 +12085,7 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12073,12 +12097,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>WELL-PRIEMONE-PRD-NA</t>
+          <t>WELL-FUSION-ATSTATOM-SHA-NA</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Wella Professionals plaukų priežiūros priemonės</t>
+          <t>Wella Professionals FUSION atstatomasis šampūnas</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12086,25 +12110,29 @@
           <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/wella-professionals-plauku-prieziuros-priemones</t>
+          <t>https://plaukuosena.lt/loreal-professionnel-metal-detox-sampunas</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ed6894bd-b132-4cb6-9a8a-0a4f96b07eac.jpg</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12115,10 +12143,122 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>1780380247042</t>
+          <t>1780508058948</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>WELL-ULTIMATE-SMOOTH-SHA-NA</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Wella Professionals Ultimate Smooth intensyviai maitinantis šampūnas</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>WELLA PROFESSIONALS</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>27.00</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/wella-professionals-ultimate-smooth-intensyviai-maitinantis-sampunas</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/90552437-c3c8-46c1-ad07-2d1cbaa18300.jpg</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Plaukų šampūnai</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>1780508058948</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>WELL-PRIEMONE-PRD-NA</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Wella Professionals plaukų priežiūros priemonės</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>WELLA PROFESSIONALS</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/wella-professionals-plauku-prieziuros-priemones</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Plaukų priežiūros priemonės</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>1780508058948</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
         <is>
           <t>CHECK_PRICE</t>
         </is>

--- a/products_snapshot.xlsx
+++ b/products_snapshot.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:L199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -3269,7 +3269,7 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3281,22 +3281,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>COLO-FRESH-DAZANTI-MSK-150ML</t>
+          <t>COLO-MAINTAIN-FLOWER-CON-NA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COLOR FRESH dažanti kaukė, 150 ml</t>
+          <t>COLOUR MAINTAINER FLOWER FRAGRANCE CONDITIONER kondicionierius dažytiems plaukams</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>COLOR</t>
+          <t>COLOUR</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3306,17 +3306,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/color-fresh-dazanti-kauke-150-ml</t>
+          <t>https://plaukuosena.lt/colour-maintainer-flower-fragrance-conditioner-kondicionierius-dazytiems-plaukams</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b46862ae-d30b-4244-a405-7edb625d60ad.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f12f4ee8-316b-41a7-8d3b-30ea414d5751.png</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3324,14 +3324,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>150ml</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3343,12 +3339,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>COLO-MAINTAIN-FLOWER-CON-NA</t>
+          <t>COLO-MAINTAIN-FLOWER-SHA-NA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>COLOUR MAINTAINER FLOWER FRAGRANCE CONDITIONER kondicionierius dažytiems plaukams</t>
+          <t>COLOUR MAINTAINER FLOWER FRAGRANCE SHAMPOO šampūnas dažytiems plaukams</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3354,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3368,17 +3364,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/colour-maintainer-flower-fragrance-conditioner-kondicionierius-dazytiems-plaukams</t>
+          <t>https://plaukuosena.lt/colour-maintainer-flower-fragrance-shampoo-sampunas-dazytiems-plaukams</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f12f4ee8-316b-41a7-8d3b-30ea414d5751.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e2ba385c-cd82-46d8-a674-c29c565d4b36.png</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3389,7 +3385,7 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3401,22 +3397,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>COLO-MAINTAIN-FLOWER-SHA-NA</t>
+          <t>CURL-PASSION-GARBANOT-CON-NA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COLOUR MAINTAINER FLOWER FRAGRANCE SHAMPOO šampūnas dažytiems plaukams</t>
+          <t>CURL PASSION CONDITIONER kondicionierius garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>COLOUR</t>
+          <t>CURL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3426,17 +3422,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/colour-maintainer-flower-fragrance-shampoo-sampunas-dazytiems-plaukams</t>
+          <t>https://plaukuosena.lt/curl-passion-conditioner-kondicionierius-garbanotiems-plaukams</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e2ba385c-cd82-46d8-a674-c29c565d4b36.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a9008a8a-9ca2-40f4-af88-644753de306f.webp</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3447,7 +3443,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3459,12 +3455,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CURL-PASSION-GARBANOT-CON-NA</t>
+          <t>CURL-PASSION-LEAVE-CON-NA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CURL PASSION CONDITIONER kondicionierius garbanotiems plaukams</t>
+          <t>CURL PASSION LEAVE IN nenuskalaujamas kondicionierius</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3474,7 +3470,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>22.30</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3484,12 +3480,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/curl-passion-conditioner-kondicionierius-garbanotiems-plaukams</t>
+          <t>https://plaukuosena.lt/curl-passion-leave-in-nenuskalaujamas-kondicionierius</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a9008a8a-9ca2-40f4-af88-644753de306f.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/03bbe43d-1d1e-40a3-b7eb-95a6c413e398.png</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3505,7 +3501,7 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3517,12 +3513,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CURL-PASSION-LEAVE-CON-NA</t>
+          <t>CURL-PASSION-GARBANOT-MSK-NA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CURL PASSION LEAVE IN nenuskalaujamas kondicionierius</t>
+          <t>CURL PASSION MASK kaukė garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3532,7 +3528,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>22.30</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3542,17 +3538,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/curl-passion-leave-in-nenuskalaujamas-kondicionierius</t>
+          <t>https://plaukuosena.lt/curl-passion-mask-kauke-garbanotiems-plaukams</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/03bbe43d-1d1e-40a3-b7eb-95a6c413e398.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/fd2c5cb6-c6fa-4919-b1b8-4581b2ab8a84.png</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3563,7 +3559,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3575,12 +3571,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CURL-PASSION-GARBANOT-MSK-NA</t>
+          <t>CURL-PASSION-PERFECTI-CRM-NA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CURL PASSION MASK kaukė garbanotiems plaukams</t>
+          <t>CURL PASSION PERFECTIONIST garbanų formavimo kremas</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3590,7 +3586,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>22.30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3600,17 +3596,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/curl-passion-mask-kauke-garbanotiems-plaukams</t>
+          <t>https://plaukuosena.lt/curl-passion-perfectionist-garbanu-formavimo-kremas</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/fd2c5cb6-c6fa-4919-b1b8-4581b2ab8a84.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/92fc1d2f-8e70-43aa-9649-4bf29c9685eb.png</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3621,7 +3617,7 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3633,12 +3629,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CURL-PASSION-PERFECTI-CRM-NA</t>
+          <t>CURL-PASSION-GARBANOT-SHA-NA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CURL PASSION PERFECTIONIST garbanų formavimo kremas</t>
+          <t>CURL PASSION SHAMPOO šampūnas garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3648,7 +3644,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>22.30</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3658,17 +3654,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/curl-passion-perfectionist-garbanu-formavimo-kremas</t>
+          <t>https://plaukuosena.lt/curl-passion-shampoo-sampunas-garbanotiems-plaukams</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/92fc1d2f-8e70-43aa-9649-4bf29c9685eb.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9abc0fee-56a1-407b-b57b-cc3b8f2b64d8.webp</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3679,7 +3675,7 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3691,12 +3687,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CURL-PASSION-GARBANOT-SHA-NA</t>
+          <t>CURL-PASSION-SHAPER-PRD-NA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CURL PASSION SHAMPOO šampūnas garbanotiems plaukams</t>
+          <t>CURL PASSION SHAPER garbanotų plaukų formavimo priemonė</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3706,7 +3702,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>29.30</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3716,17 +3712,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/curl-passion-shampoo-sampunas-garbanotiems-plaukams</t>
+          <t>https://plaukuosena.lt/curl-passion-shaper-garbanotu-plauku-formavimo-priemone</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9abc0fee-56a1-407b-b57b-cc3b8f2b64d8.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c0e31067-f847-411e-8829-46d992b004de.png</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3737,7 +3733,7 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3749,22 +3745,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CURL-PASSION-SHAPER-PRD-NA</t>
+          <t>DAVI-APSAUGIN-SKYSTIS-PRD-250ML</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CURL PASSION SHAPER garbanotų plaukų formavimo priemonė</t>
+          <t>DAVINES APSAUGINIS SKYSTIS PLAUKAMS PH: 4 | MELU | 250ML</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CURL</t>
+          <t>DAVINES</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>29.30</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3774,12 +3770,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/curl-passion-shaper-garbanotu-plauku-formavimo-priemone</t>
+          <t>https://plaukuosena.lt/apsauginis-skystis-plaukams-ph-4-or-melu</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c0e31067-f847-411e-8829-46d992b004de.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/958d66cb-6795-4885-88d2-e4748c0b2e4f.webp</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3792,10 +3788,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>8004608242505</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3807,12 +3807,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DAVI-APSAUGIN-SKYSTIS-PRD-250ML</t>
+          <t>DAVI-BLIZGESY-APSAUGA-PRD-150ML</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DAVINES APSAUGINIS SKYSTIS PLAUKAMS PH: 4 | MELU | 250ML</t>
+          <t>DAVINES Blizgesys ir apsauga šviesiems plaukams | Heart of Glass | 150ML</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>31.00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/apsauginis-skystis-plaukams-ph-4-or-melu</t>
+          <t>https://plaukuosena.lt/blizgesys-ir-apsauga-sviesiems-plaukams-or-heart-of-glass</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/958d66cb-6795-4885-88d2-e4748c0b2e4f.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/75106ebc-f23c-459b-aebd-1f78c58b78e0.png</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>250ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8004608242505</t>
+          <t>8004608294702</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3869,12 +3869,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DAVI-BLIZGESY-APSAUGA-PRD-150ML</t>
+          <t>DAVI-GEROS-SAVIJAUT-SHA-250ML</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DAVINES Blizgesys ir apsauga šviesiems plaukams | Heart of Glass | 150ML</t>
+          <t>DAVINES GEROS SAVIJAUTOS ŠAMPŪNAS PH: 5.5 | WELL–BEING | 250ML</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>31.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,17 +3894,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/blizgesys-ir-apsauga-sviesiems-plaukams-or-heart-of-glass</t>
+          <t>https://plaukuosena.lt/geros-savijautos-sampunas-ph-55-or-well-being</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/75106ebc-f23c-459b-aebd-1f78c58b78e0.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7510575f-99a2-4412-9ed4-4950f2f034fc.webp</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3914,12 +3914,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>8004608294702</t>
+          <t>8004608256502</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3931,12 +3931,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DAVI-GEROS-SAVIJAUT-SHA-250ML</t>
+          <t>DAVI-GREITAI-PLAUKUS-MSK-50ML</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DAVINES GEROS SAVIJAUTOS ŠAMPŪNAS PH: 5.5 | WELL–BEING | 250ML</t>
+          <t>DAVINES GREITAI PLAUKUS ATKURIANTI KAUKĖ | THE QUICK FIX CIRCLE | 50ML</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3956,17 +3956,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/geros-savijautos-sampunas-ph-55-or-well-being</t>
+          <t>https://plaukuosena.lt/greitai-plaukus-atkurianti-kauke-or-the-quick-fix-circle</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7510575f-99a2-4412-9ed4-4950f2f034fc.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/333ee115-9451-4bf1-b2b6-62c9b9b773df.png</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>250ml</t>
+          <t>50ml</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>8004608256502</t>
+          <t>58688808</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3993,12 +3993,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DAVI-GREITAI-PLAUKUS-MSK-50ML</t>
+          <t>DAVI-DAZYTIEM-PH-CON-250ML</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DAVINES GREITAI PLAUKUS ATKURIANTI KAUKĖ | THE QUICK FIX CIRCLE | 50ML</t>
+          <t>DAVINES KONDICIONIERIUS DAŽYTIEMS PLAUKAMS PH: 4 | MINU | 250ML</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4018,17 +4018,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/greitai-plaukus-atkurianti-kauke-or-the-quick-fix-circle</t>
+          <t>https://plaukuosena.lt/kondicionierius-dazytiems-plaukams-ph-4-or-minu</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/333ee115-9451-4bf1-b2b6-62c9b9b773df.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7ec299ab-4d5e-4428-8acb-1d7b2e351dc6.webp</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>50ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>58688808</t>
+          <t>8004608275879</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4055,12 +4055,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DAVI-DAZYTIEM-PH-CON-250ML</t>
+          <t>DAVI-PAZEISTI-PH-CON-250ML</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DAVINES KONDICIONIERIUS DAŽYTIEMS PLAUKAMS PH: 4 | MINU | 250ML</t>
+          <t>DAVINES KONDICIONIERIUS PAŽEISTIEMS PLAUKAMS PH: 4 | MELU | 250ML</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/kondicionierius-dazytiems-plaukams-ph-4-or-minu</t>
+          <t>https://plaukuosena.lt/kondicionierius-pazeistiems-plaukams-ph-4-or-melu</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7ec299ab-4d5e-4428-8acb-1d7b2e351dc6.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/27c868d9-4d9f-41dd-b2d1-57259b7ee377.webp</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>8004608275879</t>
+          <t>8004608276722</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4117,12 +4117,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DAVI-PAZEISTI-PH-CON-250ML</t>
+          <t>DAVI-REFIL-GARBANUO-SHA-500ML</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DAVINES KONDICIONIERIUS PAŽEISTIEMS PLAUKAMS PH: 4 | MELU | 250ML</t>
+          <t>DAVINES REFIL ŠAMPŪNAS GARBANUOTIEMS PLAUKAMS PH: 5.3 | LOVE CURL | 500ML</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>42.00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4142,17 +4142,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/kondicionierius-pazeistiems-plaukams-ph-4-or-melu</t>
+          <t>https://plaukuosena.lt/davines-sampunas-garbanuotiems-plaukams-ph-53-or-love-curl</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/27c868d9-4d9f-41dd-b2d1-57259b7ee377.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/abd9f475-8e18-4122-854e-e9807ba878f6.webp</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>250ml</t>
+          <t>500ml</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8004608276722</t>
+          <t>8004608280654</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4179,12 +4179,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DAVI-REFIL-GARBANUO-SHA-500ML</t>
+          <t>DAVI-TIESINAN-PH-SHA-250ML</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DAVINES REFIL ŠAMPŪNAS GARBANUOTIEMS PLAUKAMS PH: 5.3 | LOVE CURL | 500ML</t>
+          <t>DAVINES TIESINANTIS ŠAMPŪNAS PH: 5.3 | LOVE | 250ML</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>42.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/davines-sampunas-garbanuotiems-plaukams-ph-53-or-love-curl</t>
+          <t>https://plaukuosena.lt/tiesinantis-sampunas-ph-53-or-love</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/abd9f475-8e18-4122-854e-e9807ba878f6.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7691e5f8-be0d-4245-88b7-bade815e0174.webp</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>8004608280654</t>
+          <t>8004608274865</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4241,12 +4241,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DAVI-TIESINAN-PH-SHA-250ML</t>
+          <t>DAVI-VALANTIS-NUO-SHA-250ML</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DAVINES TIESINANTIS ŠAMPŪNAS PH: 5.3 | LOVE | 250ML</t>
+          <t>DAVINES VALANTIS ŠAMPŪNAS NUO PLEISKANŲ PH: 4.9 | PURIFYING | 250ML</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/tiesinantis-sampunas-ph-53-or-love</t>
+          <t>https://plaukuosena.lt/valantis-sampunas-nuo-pleiskanu-ph-49-or-purifying</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7691e5f8-be0d-4245-88b7-bade815e0174.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d4d74325-9146-4a5a-9026-794f20ec97be.webp</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>8004608274865</t>
+          <t>8004608236580</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4303,12 +4303,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DAVI-VALANTIS-NUO-SHA-250ML</t>
+          <t>DAVI-DAZYTIEM-PH-SHA-250ML</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DAVINES VALANTIS ŠAMPŪNAS NUO PLEISKANŲ PH: 4.9 | PURIFYING | 250ML</t>
+          <t>DAVINES ŠAMPŪNAS DAŽYTIEMS PLAUKAMS PH: 5.3 | MINU | 250ML</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/valantis-sampunas-nuo-pleiskanu-ph-49-or-purifying</t>
+          <t>https://plaukuosena.lt/sampunas-dazytiems-plaukams-ph-53-or-minu</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d4d74325-9146-4a5a-9026-794f20ec97be.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6a542969-9c0b-4be9-8aba-c7a8bd9ade42.webp</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>8004608236580</t>
+          <t>8004608242550</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4365,12 +4365,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DAVI-DAZYTIEM-PH-SHA-250ML</t>
+          <t>DAVI-PAZEISTI-PH-SHA-250ML</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DAVINES ŠAMPŪNAS DAŽYTIEMS PLAUKAMS PH: 5.3 | MINU | 250ML</t>
+          <t>DAVINES ŠAMPŪNAS PAŽEISTIEMS PLAUKAMS PH: 5.3 | MELU | 250ML</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/sampunas-dazytiems-plaukams-ph-53-or-minu</t>
+          <t>https://plaukuosena.lt/sampunas-pazeistiems-plaukams-ph-53-or-melu</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6a542969-9c0b-4be9-8aba-c7a8bd9ade42.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9e665e1f-46f0-43ad-a545-d89ee5dbd7d5.webp</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>8004608242550</t>
+          <t>8004608242444</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4427,12 +4427,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DAVI-PAZEISTI-PH-SHA-250ML</t>
+          <t>DAVI-GAUSINIM-PH-SHA-250ML</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DAVINES ŠAMPŪNAS PAŽEISTIEMS PLAUKAMS PH: 5.3 | MELU | 250ML</t>
+          <t>DAVINES ŠAMPŪNAS PLAUKŲ GAUSINIMUI PH: 5.3 | VOLU | 250ML</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/sampunas-pazeistiems-plaukams-ph-53-or-melu</t>
+          <t>https://plaukuosena.lt/sampunas-plauku-gausinimui-ph-53-or-volu</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9e665e1f-46f0-43ad-a545-d89ee5dbd7d5.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a13b2f02-8b1b-4288-9602-b6b3af8b7c0a.webp</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>8004608242444</t>
+          <t>8004608242512</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4489,12 +4489,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DAVI-GAUSINIM-PH-SHA-250ML</t>
+          <t>DAVI-SVIESIUS-PLAUKUS-CON-250ML</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DAVINES ŠAMPŪNAS PLAUKŲ GAUSINIMUI PH: 5.3 | VOLU | 250ML</t>
+          <t>DAVINES Šviesius plaukus maitinantis kondicionierius | Heart of Glass | 250ML</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>31.00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4514,17 +4514,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/sampunas-plauku-gausinimui-ph-53-or-volu</t>
+          <t>https://plaukuosena.lt/hand-soap-giguos</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a13b2f02-8b1b-4288-9602-b6b3af8b7c0a.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/729b8d37-dea5-416e-a920-52cc0231c3bb.png</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>8004608242512</t>
+          <t>8004608271697</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4551,12 +4551,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DAVI-SVIESIUS-PLAUKUS-CON-250ML</t>
+          <t>DAVI-SVIESIUS-PLAUKUS-MSK-150ML</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DAVINES Šviesius plaukus maitinantis kondicionierius | Heart of Glass | 250ML</t>
+          <t>DAVINES Šviesius plaukus stiprinanti kaukė | Heart of Glass | 150ml</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>31.00</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4576,17 +4576,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/hand-soap-giguos</t>
+          <t>https://plaukuosena.lt/sviesius-plaukus-stiprinanti-kauke-or-heart-of-glass</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/729b8d37-dea5-416e-a920-52cc0231c3bb.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7062fec7-9648-4348-95e4-b6109a41426c.webp</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>250ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>8004608271697</t>
+          <t>8004608272526</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4613,22 +4613,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DAVI-SVIESIUS-PLAUKUS-MSK-150ML</t>
+          <t>DEEP-CONDITIO-INTENSYV-MSK-NA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DAVINES Šviesius plaukus stiprinanti kaukė | Heart of Glass | 150ml</t>
+          <t>DEEP CONDITIONING MASK intensyvaus poveikio kaukė dažytiems plaukams</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DAVINES</t>
+          <t>DEEP</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/sviesius-plaukus-stiprinanti-kauke-or-heart-of-glass</t>
+          <t>https://plaukuosena.lt/deep-conditioning-mask-intensyvaus-poveikio-kauke-dazytiems-plaukams</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/7062fec7-9648-4348-95e4-b6109a41426c.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e6b9db3b-a6bb-4912-b17a-c6d3e9600555.webp</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,14 +4656,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>150ml</t>
-        </is>
-      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>8004608272526</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4675,22 +4671,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DEEP-CONDITIO-INTENSYV-MSK-NA</t>
+          <t>GLIS-ARGAN-ARGANU-OIL-NA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DEEP CONDITIONING MASK intensyvaus poveikio kaukė dažytiems plaukams</t>
+          <t>GLISTENING ARGAN OIL arganų aliejus</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DEEP</t>
+          <t>GLISTENING</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4700,17 +4696,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-conditioning-mask-intensyvaus-poveikio-kauke-dazytiems-plaukams</t>
+          <t>https://plaukuosena.lt/glistening-argan-oil-arganu-aliejus</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e6b9db3b-a6bb-4912-b17a-c6d3e9600555.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e8ec0139-6902-4e09-8f7e-92dbc42a0048.png</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4721,7 +4717,7 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4733,42 +4729,38 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FUSI-INTENSYV-PLAUKUS-CON-NA</t>
+          <t>GARB-PLAUKAI-PRIEMONE-PRD-NA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FUSION intensyviai plaukus atkuriantis kondicionierius</t>
+          <t>Garbanoti plaukai | Priežiūros priemonės garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FUSION</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>26.00</t>
-        </is>
-      </c>
+          <t>Garbanoti</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/fusion-intensyviai-plaukus-atkuriantis-kondicionierius</t>
+          <t>https://plaukuosena.lt/garbanoti-plaukai</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9f9fdb95-485e-476c-b6b2-486e49f19cfe.jpg</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4779,34 +4771,34 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GLIS-ARGAN-ARGANU-OIL-NA</t>
+          <t>ICY-BLOND-SVIESIEM-CON-NA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GLISTENING ARGAN OIL arganų aliejus</t>
+          <t>ICY BLOND CONDITIONER kondicionierius šviesiems plaukams</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GLISTENING</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4816,17 +4808,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/glistening-argan-oil-arganu-aliejus</t>
+          <t>https://plaukuosena.lt/icy-blond-conditioner-kondicionierius-sviesiems-plaukams</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e8ec0139-6902-4e09-8f7e-92dbc42a0048.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/43ff1e78-0eaf-481b-8b24-b56b697a19c0.png</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Plaukų aliejai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4837,7 +4829,7 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4849,38 +4841,42 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GARB-PLAUKAI-PRIEMONE-PRD-NA</t>
+          <t>ICY-BLOND-SVIESIEM-SHA-NA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Garbanoti plaukai | Priežiūros priemonės garbanotiems plaukams</t>
+          <t>ICY BLOND SHAMPOO šampūnas šviesiems plaukams</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Garbanoti</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>ICY</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/garbanoti-plaukai</t>
+          <t>https://plaukuosena.lt/icy-blond-shampoo-sampunas-sviesiems-plaukams</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cac84108-877e-4753-baa2-36d67665c464.png</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4891,34 +4887,34 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ICY-BLOND-SVIESIEM-CON-NA</t>
+          <t>INST-STIPRINA-SHA-NA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ICY BLOND CONDITIONER kondicionierius šviesiems plaukams</t>
+          <t>INSTALIGHT SHAMPOO stiprinamasis šampūnas plaukams</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>INSTALIGHT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4928,17 +4924,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/icy-blond-conditioner-kondicionierius-sviesiems-plaukams</t>
+          <t>https://plaukuosena.lt/instalight-shampoo-stiprinamasis-sampunas-plaukams</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/43ff1e78-0eaf-481b-8b24-b56b697a19c0.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40bb94ca-92af-4d11-9f97-87579e8d0d24.png</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4949,7 +4945,7 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4961,22 +4957,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ICY-BLOND-SVIESIEM-SHA-NA</t>
+          <t>INST-SKYSTA-MSK-NA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ICY BLOND SHAMPOO šampūnas šviesiems plaukams</t>
+          <t>INSTALOTION skysta kaukė plaukams</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>INSTALOTION</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4986,17 +4982,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/icy-blond-shampoo-sampunas-sviesiems-plaukams</t>
+          <t>https://plaukuosena.lt/instalotion-skysta-kauke-plaukams</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cac84108-877e-4753-baa2-36d67665c464.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b00458f3-53bf-48dc-a159-d98ece3d546d.webp</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5007,7 +5003,7 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5019,22 +5015,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>INCR-MILK-FLOWER-PRD-NA</t>
+          <t>INTE-INCREDIB-APSAUGIN-OIL-NA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>INCREDIBLE MILK FLOWER FRAGRANCE plaukus kondicionuojantis pienelis</t>
+          <t>INTEGRITY INCREDIBLE OIL apsauginis atkuriamasis aliejus</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>INCREDIBLE</t>
+          <t>INTEGRITY</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>18.90</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5044,17 +5040,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/incredible-milk-flower-fragrance-plaukus-kondicionuojantis-pienelis</t>
+          <t>https://plaukuosena.lt/integrity-incredible-oil-apsauginis-atkuriamasis-aliejus</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/728171ea-b913-4828-bd2e-5816d611a9a2.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/80d0d251-f362-4ff0-aa1f-23a517459152.png</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5065,7 +5061,7 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5077,22 +5073,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>INST-STIPRINA-SHA-NA</t>
+          <t>INTE-LEAVE-IN-SPR-NA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>INSTALIGHT SHAMPOO stiprinamasis šampūnas plaukams</t>
+          <t>INTEGRITY LEAVE IN purškiklis pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>INSTALIGHT</t>
+          <t>INTEGRITY</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5102,17 +5098,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/instalight-shampoo-stiprinamasis-sampunas-plaukams</t>
+          <t>https://plaukuosena.lt/integrity-leave-in-purskiklis-pazeistiems-plaukams</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40bb94ca-92af-4d11-9f97-87579e8d0d24.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f74f788d-213a-40fc-8be9-75aa8e85a177.webp</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5123,7 +5119,7 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5135,22 +5131,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>INST-SKYSTA-MSK-NA</t>
+          <t>INTE-INTENSIV-TREATMEN-MSK-NA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>INSTALOTION skysta kaukė plaukams</t>
+          <t>INTEGRITY&amp;STRENGTH INTENSIVE TREATMENT stipriai maitinanti kaukė pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>INSTALOTION</t>
+          <t>INTEGRITY&amp;STRENGTH</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5160,12 +5156,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/instalotion-skysta-kauke-plaukams</t>
+          <t>https://plaukuosena.lt/integrityandstrength-intensive-treatment-stipriai-maitinanti-kauke-pazeistiems-plaukams</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b00458f3-53bf-48dc-a159-d98ece3d546d.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9d17895a-b0dc-4293-9fb5-25d4e81c7172.png</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5181,7 +5177,7 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5193,22 +5189,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>INTE-INCREDIB-APSAUGIN-OIL-NA</t>
+          <t>INTE-NOURISHI-MAITINAN-CON-NA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>INTEGRITY INCREDIBLE OIL apsauginis atkuriamasis aliejus</t>
+          <t>INTEGRITY&amp;STRENGTH NOURISHING CONDITIONER maitinantis kondicionierius</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>INTEGRITY</t>
+          <t>INTEGRITY&amp;STRENGTH</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>56.00</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5218,17 +5214,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrity-incredible-oil-apsauginis-atkuriamasis-aliejus</t>
+          <t>https://plaukuosena.lt/integrityandstrength-nourishing-conditioner-maitinantis-kondicionierius</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/80d0d251-f362-4ff0-aa1f-23a517459152.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d7eb8303-1738-41b2-8aad-585928205249.png</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Plaukų aliejai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5239,7 +5235,7 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5251,22 +5247,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>INTE-LEAVE-IN-SPR-NA</t>
+          <t>INTE-NOURISHI-MAITINAN-SHA-NA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>INTEGRITY LEAVE IN purškiklis pažeistiems plaukams</t>
+          <t>INTEGRITY&amp;STRENGTH NOURISHING SHAMPOO maitinantis šampūnas pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>INTEGRITY</t>
+          <t>INTEGRITY&amp;STRENGTH</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5276,17 +5272,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrity-leave-in-purskiklis-pazeistiems-plaukams</t>
+          <t>https://plaukuosena.lt/integrityandstrength-nourishing-shampoo-maitinantis-sampunas-pazeistiems-plaukams</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f74f788d-213a-40fc-8be9-75aa8e85a177.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cf1f1398-28da-45f8-9ea9-a3c1e85c7ff6.png</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5297,7 +5293,7 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5309,12 +5305,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>INTE-INTENSIV-TREATMEN-MSK-NA</t>
+          <t>INTE-REPAIRIN-HAIR-PRD-NA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH INTENSIVE TREATMENT stipriai maitinanti kaukė pažeistiems plaukams</t>
+          <t>INTEGRITY&amp;STRENGTH REPAIRING HAIR LOTION stiprus proteinų koncentratas plaukams</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5334,17 +5330,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-intensive-treatment-stipriai-maitinanti-kauke-pazeistiems-plaukams</t>
+          <t>https://plaukuosena.lt/integrityandstrength-repairing-hair-lotion-stiprus-proteinu-koncentratas-plaukams</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9d17895a-b0dc-4293-9fb5-25d4e81c7172.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b1caa947-5c47-4e89-8b01-59096365bd8d.webp</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5355,7 +5351,7 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5367,12 +5363,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>INTE-NOURISHI-MAITINAN-CON-NA</t>
+          <t>INTE-SPLIT-ENDS-SPR-NA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH NOURISHING CONDITIONER maitinantis kondicionierius</t>
+          <t>INTEGRITY&amp;STRENGTH SPLIT ENDS SAVIOR purškiklis pažeistiems plaukams</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5382,7 +5378,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5392,17 +5388,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-nourishing-conditioner-maitinantis-kondicionierius</t>
+          <t>https://plaukuosena.lt/integrityandstrength-split-ends-savior-purskiklis-pazeistiems-plaukams</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d7eb8303-1738-41b2-8aad-585928205249.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/aeb4d580-8f81-4cc3-bdeb-0b966ad13c7e.png</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5413,7 +5409,7 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5425,22 +5421,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>INTE-NOURISHI-MAITINAN-SHA-NA</t>
+          <t>KADU-COLOR-RADIANCE-CON-250ML</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH NOURISHING SHAMPOO maitinantis šampūnas pažeistiems plaukams</t>
+          <t>KADUS PROFESSIONAL COLOR RADIANCE LEAVE-IN SPRAY purškiamas kondicionierius | 250 ml</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5450,17 +5446,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-nourishing-shampoo-maitinantis-sampunas-pazeistiems-plaukams</t>
+          <t>https://plaukuosena.lt/color-radiance-leave-in-spray-purskiamas-kondicionierius-250-ml</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cf1f1398-28da-45f8-9ea9-a3c1e85c7ff6.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1496fbcb-5032-476b-bcd5-ff6a423b360e.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5468,10 +5464,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>4064666318448</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5483,22 +5483,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>INTE-REPAIRIN-HAIR-PRD-NA</t>
+          <t>KADU-COLOR-RADIANCE-MSK-200ML</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH REPAIRING HAIR LOTION stiprus proteinų koncentratas plaukams</t>
+          <t>KADUS PROFESSIONAL COLOR RADIANCE kaukė | 200ML</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5508,17 +5508,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-repairing-hair-lotion-stiprus-proteinu-koncentratas-plaukams</t>
+          <t>https://plaukuosena.lt/color-radiance-kauke1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b1caa947-5c47-4e89-8b01-59096365bd8d.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/188953a6-01e0-4821-b09a-418707b8ae5a.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5526,10 +5526,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>4064666318509</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5541,22 +5545,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>INTE-SPLIT-ENDS-SPR-NA</t>
+          <t>KADU-COLOR-RADIANCE-CON-250ML-1EC4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH SPLIT ENDS SAVIOR purškiklis pažeistiems plaukams</t>
+          <t>KADUS PROFESSIONAL COLOR RADIANCE kondicionierius | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>INTEGRITY&amp;STRENGTH</t>
+          <t>Kadus Professional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5566,17 +5570,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/integrityandstrength-split-ends-savior-purskiklis-pazeistiems-plaukams</t>
+          <t>https://plaukuosena.lt/color-radiance-kauke</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/aeb4d580-8f81-4cc3-bdeb-0b966ad13c7e.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b5200496-819e-44d4-9eeb-cfa65fbe0213.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5584,10 +5588,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>4064666318387</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5599,12 +5607,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>KADU-COLOR-RADIANCE-CON-250ML</t>
+          <t>KADU-COLOR-RADIANCE-SHA-250ML</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL COLOR RADIANCE LEAVE-IN SPRAY purškiamas kondicionierius | 250 ml</t>
+          <t>KADUS PROFESSIONAL COLOR RADIANCE šampūnas | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5614,7 +5622,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5624,17 +5632,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/color-radiance-leave-in-spray-purskiamas-kondicionierius-250-ml</t>
+          <t>https://plaukuosena.lt/color-radiance-sampunas</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1496fbcb-5032-476b-bcd5-ff6a423b360e.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/70c7fad4-d7d0-4326-8b82-3955f89277d7.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5649,7 +5657,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>4064666318448</t>
+          <t>4064666318325</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5661,12 +5669,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KADU-COLOR-RADIANCE-MSK-200ML</t>
+          <t>KADU-DEEP-MOISTURE-CON-250ML</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL COLOR RADIANCE kaukė | 200ML</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE LEAVE-IN purškiamas kondicionierius | 250 ml</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5676,7 +5684,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5686,17 +5694,17 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/color-radiance-kauke1</t>
+          <t>https://plaukuosena.lt/deep-moisture-leave-in-purskiamas-kondicionierius-250-ml</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/188953a6-01e0-4821-b09a-418707b8ae5a.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/812ff0d8-83cf-4ae5-b03e-7ae58b54d4b3.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5706,12 +5714,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>4064666318509</t>
+          <t>8005610571560</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5723,12 +5731,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>KADU-COLOR-RADIANCE-CON-250ML-1EC4</t>
+          <t>KADU-DEEP-MOISTURE-MSK-200ML</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL COLOR RADIANCE kondicionierius | 250ML/1000ML</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE kaukė | 200ML</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5738,7 +5746,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5748,17 +5756,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/color-radiance-kauke</t>
+          <t>https://plaukuosena.lt/deep-moisture-kauke</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b5200496-819e-44d4-9eeb-cfa65fbe0213.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/02191c64-c0d0-435c-acfd-4abe70c7d286.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5768,12 +5776,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>250ml</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>4064666318387</t>
+          <t>8005610604022</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5785,12 +5793,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>KADU-COLOR-RADIANCE-SHA-250ML</t>
+          <t>KADU-DEEP-MOISTURE-CON-250ML-BB59</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL COLOR RADIANCE šampūnas | 250ML/1000ML</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE kondicionierius | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5800,7 +5808,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5810,17 +5818,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/color-radiance-sampunas</t>
+          <t>https://plaukuosena.lt/deep-moisture-kondicionierius</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/70c7fad4-d7d0-4326-8b82-3955f89277d7.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/11e9244b-f1b4-4fd1-a829-d04264f37221.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5835,7 +5843,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>4064666318325</t>
+          <t>8005610555089</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5847,12 +5855,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>KADU-DEEP-MOISTURE-CON-250ML</t>
+          <t>KADU-DEEP-MOISTURE-SHA-250ML</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE LEAVE-IN purškiamas kondicionierius | 250 ml</t>
+          <t>KADUS PROFESSIONAL DEEP MOISTURE šampūnas | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5862,7 +5870,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5872,17 +5880,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-moisture-leave-in-purskiamas-kondicionierius-250-ml</t>
+          <t>https://plaukuosena.lt/deep-moisture-sampunas</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/812ff0d8-83cf-4ae5-b03e-7ae58b54d4b3.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0f57fac1-e330-41e0-aa79-c1ef82ad3610.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5897,7 +5905,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>8005610571560</t>
+          <t>8005610602509</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5909,12 +5917,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>KADU-DEEP-MOISTURE-MSK-200ML</t>
+          <t>KADU-SUN-SPARK-PRD-250ML</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE kaukė | 200ML</t>
+          <t>KADUS PROFESSIONAL SUN SPARK LEAVE-IN losjonas | 250 ml</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5924,7 +5932,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5934,17 +5942,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-moisture-kauke</t>
+          <t>https://plaukuosena.lt/sun-spark-leave-in-losjonas-250-ml</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/02191c64-c0d0-435c-acfd-4abe70c7d286.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ed98f39-97be-49f3-9ff0-0d72b6b30996.png</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5954,12 +5962,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>8005610604022</t>
+          <t>8005610573397</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5971,12 +5979,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>KADU-DEEP-MOISTURE-CON-250ML-BB59</t>
+          <t>KADU-TONEPLEX-PEARL-SHA-250ML</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE kondicionierius | 250ML/1000ML</t>
+          <t>KADUS PROFESSIONAL TONEPLEX Pearl Blonde atspalvį suteikiantis šampūnas | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5986,7 +5994,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5996,17 +6004,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-moisture-kondicionierius</t>
+          <t>https://plaukuosena.lt/toneplex-pearl-blonde-atspalvi-suteikiantis-sampunas</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/11e9244b-f1b4-4fd1-a829-d04264f37221.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/078c44d1-6f55-4d97-9171-76689b1e9e61.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6021,7 +6029,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>8005610555089</t>
+          <t>4064666244150</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6033,12 +6041,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KADU-DEEP-MOISTURE-SHA-250ML</t>
+          <t>KADU-TONEPLEX-DAZANTI-MSK-200ML</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL DEEP MOISTURE šampūnas | 250ML/1000ML</t>
+          <t>KADUS PROFESSIONAL TONEPLEX dažanti kaukė | 200 ml</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6048,7 +6056,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6058,17 +6066,17 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/deep-moisture-sampunas</t>
+          <t>https://plaukuosena.lt/toneplex-dazanti-kauke-200-ml</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0f57fac1-e330-41e0-aa79-c1ef82ad3610.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/72f4806d-8501-4247-b92b-946b795f3452.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6078,12 +6086,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>250ml</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>8005610602509</t>
+          <t>4064666244396</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6095,12 +6103,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>KADU-SUN-SPARK-PRD-250ML</t>
+          <t>KADU-VISIBLE-REPAIR-PRD-250ML</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL SUN SPARK LEAVE-IN losjonas | 250 ml</t>
+          <t>KADUS PROFESSIONAL VISIBLE REPAIR LEAVE-IN balzamas | 250 ml</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6110,7 +6118,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6120,12 +6128,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/sun-spark-leave-in-losjonas-250-ml</t>
+          <t>https://plaukuosena.lt/visible-repair-leave-in-balzamas-250-ml</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ed98f39-97be-49f3-9ff0-0d72b6b30996.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f58db6be-f708-4260-b0ea-414e86e49877.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6145,7 +6153,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>8005610573397</t>
+          <t>4064666318035</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6157,12 +6165,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>KADU-TONEPLEX-PEARL-SHA-250ML</t>
+          <t>KADU-VISIBLE-REPAIR-MSK-200ML</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL TONEPLEX Pearl Blonde atspalvį suteikiantis šampūnas | 250ML/1000ML</t>
+          <t>KADUS PROFESSIONAL VISIBLE REPAIR kaukė | 200ML/750ML</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6172,7 +6180,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6182,17 +6190,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/toneplex-pearl-blonde-atspalvi-suteikiantis-sampunas</t>
+          <t>https://plaukuosena.lt/visible-repair-kauke</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/078c44d1-6f55-4d97-9171-76689b1e9e61.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bb4a55d4-fca2-4714-9e27-863c4396c8c5.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6202,12 +6210,12 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>250ml</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>4064666244150</t>
+          <t>4064666318967</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6219,12 +6227,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>KADU-TONEPLEX-DAZANTI-MSK-200ML</t>
+          <t>KADU-VISIBLE-REPAIR-CON-250ML</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL TONEPLEX dažanti kaukė | 200 ml</t>
+          <t>KADUS PROFESSIONAL VISIBLE REPAIR kondicionierius | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6234,7 +6242,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6244,17 +6252,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/toneplex-dazanti-kauke-200-ml</t>
+          <t>https://plaukuosena.lt/visible-repair-kondicionierius</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/72f4806d-8501-4247-b92b-946b795f3452.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/01643d0f-9cbd-4081-8652-c7463c2b4580.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6264,12 +6272,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>4064666244396</t>
+          <t>4064666317977</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6281,12 +6289,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>KADU-VISIBLE-REPAIR-PRD-250ML</t>
+          <t>KADU-VISIBLE-REPAIR-SHA-250ML</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL VISIBLE REPAIR LEAVE-IN balzamas | 250 ml</t>
+          <t>KADUS PROFESSIONAL VISIBLE REPAIR šampūnas | 250ML/1000ML</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6296,7 +6304,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6306,17 +6314,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/visible-repair-leave-in-balzamas-250-ml</t>
+          <t>https://plaukuosena.lt/visible-repair-sampunas</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f58db6be-f708-4260-b0ea-414e86e49877.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bc18386f-a0b4-4385-aa76-4494ebab2985.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6331,7 +6339,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>4064666318035</t>
+          <t>4064666317915</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6343,12 +6351,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>KADU-VISIBLE-REPAIR-MSK-200ML</t>
+          <t>KADU-PRIEMONE-KADUS-PRD-NA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL VISIBLE REPAIR kaukė | 200ML/750ML</t>
+          <t>Kadus Professional plaukų priemonės | Kadus kosmetika</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6356,29 +6364,25 @@
           <t>Kadus Professional</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/visible-repair-kauke</t>
+          <t>https://plaukuosena.lt/kadus-professional-plauku-priemones</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bb4a55d4-fca2-4714-9e27-863c4396c8c5.jpg</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6386,61 +6390,53 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>4064666318967</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>KADU-VISIBLE-REPAIR-CON-250ML</t>
+          <t>KARS-APSAUGA-APSAUGA-PRD-NA</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL VISIBLE REPAIR kondicionierius | 250ML/1000ML</t>
+          <t>Karščio apsauga plaukams | Apsauga nuo karščio</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>16.00</t>
-        </is>
-      </c>
+          <t>Karščio</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/visible-repair-kondicionierius</t>
+          <t>https://plaukuosena.lt/karscio-apsauga-plaukams</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/01643d0f-9cbd-4081-8652-c7463c2b4580.jpg</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6448,41 +6444,37 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>4064666317977</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>KADU-VISIBLE-REPAIR-SHA-250ML</t>
+          <t>MILK-NO-FRIZZ-PRD-NA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>KADUS PROFESSIONAL VISIBLE REPAIR šampūnas | 250ML/1000ML</t>
+          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING LIGHT MILK blizgesio ir glotnumo suteikiantis pienelis ploniems plaukams</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
+          <t>MILK SHAKE</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>21.60</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6492,17 +6484,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/visible-repair-sampunas</t>
+          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-light-milk-blizgesio-ir-glotnumo-suteikiantis-pienelis-ploniems-plaukams</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bc18386f-a0b4-4385-aa76-4494ebab2985.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/05f9a283-0d68-4cbc-8b2b-a9319726c645.png</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6510,14 +6502,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>4064666317915</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6529,38 +6517,42 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>KADU-PRIEMONE-KADUS-PRD-NA</t>
+          <t>MILK-NO-FRIZZ-SER-NA</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kadus Professional plaukų priemonės | Kadus kosmetika</t>
+          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING RICH SERUM blizgesio ir glotnumo suteikiantis serumas storiems plaukams</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kadus Professional</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>MILK SHAKE</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/kadus-professional-plauku-priemones</t>
+          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-rich-serum-blizgesio-ir-glotnumo-suteikiantis-serumas-storiems-plaukams</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ffc04fa-0925-48a2-86df-62a08a127ee1.png</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6571,50 +6563,54 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>KARS-APSAUGA-APSAUGA-PRD-NA</t>
+          <t>MILK-NO-FRIZZ-SPR-NA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Karščio apsauga plaukams | Apsauga nuo karščio</t>
+          <t>MILK SHAKE NO FRIZZ AMAZING ANTI-HUMIDITY SPRAY apsauginis purškiklis garbanotiems plaukams</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Karščio</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>MILK SHAKE</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>24.00</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/karscio-apsauga-plaukams</t>
+          <t>https://plaukuosena.lt/amazing-anti-humidity-spray-apsauginis-purskiklis-garbanotiems-plaukams</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ce022c83-2021-4842-9c57-7e44d680edec.png</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6625,54 +6621,50 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LEAV-IN-FLOWER-CON-NA</t>
+          <t>MILK-PRIEMONE-KOSMETIK-PRD-NA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LEAVE IN CONDITIONER FLOWER FRAGRANCE nenuskalaujamas kondicionierius</t>
+          <t>Milk Shake plaukų priežiūros priemonės | Milk Shake kosmetika</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LEAVE</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
+          <t>MILK SHAKE</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/leave-in-conditioner-flower-fragrance-nenuskalaujamas-kondicionierius</t>
+          <t>https://plaukuosena.lt/milk-shake-plauku-prieziuros-priemones</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8c38e360-1aa4-40f3-80d1-63fd05fadb48.png</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6683,34 +6675,34 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MILK-NO-FRIZZ-PRD-NA</t>
+          <t>MILK-INCREDIB-MILK-PRD-150ML</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING LIGHT MILK blizgesio ir glotnumo suteikiantis pienelis ploniems plaukams</t>
+          <t>MILKSHAKE INCREDIBLE MILK FLOWER FRAGRANCE plaukus kondicionuojantis pienelis 150ML</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MILK SHAKE</t>
+          <t>MILKSHAKE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>21.60</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6720,12 +6712,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-light-milk-blizgesio-ir-glotnumo-suteikiantis-pienelis-ploniems-plaukams</t>
+          <t>https://plaukuosena.lt/incredible-milk-flower-fragrance-plaukus-kondicionuojantis-pienelis</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/05f9a283-0d68-4cbc-8b2b-a9319726c645.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/728171ea-b913-4828-bd2e-5816d611a9a2.png</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6738,10 +6730,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6753,22 +6749,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MILK-NO-FRIZZ-SER-NA</t>
+          <t>MILK-LEAVE-IN-CON-350ML</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MILK SHAKE NO FRIZZ ALLOWED GLISTENING RICH SERUM blizgesio ir glotnumo suteikiantis serumas storiems plaukams</t>
+          <t>MILK_SHAKE LEAVE IN CONDITIONER FLOWER FRAGRANCE nenuskalaujamas kondicionierius 350ML</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MILK SHAKE</t>
+          <t>MILK_SHAKE</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6778,17 +6774,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no-frizz-allowed-glistening-rich-serum-blizgesio-ir-glotnumo-suteikiantis-serumas-storiems-plaukams</t>
+          <t>https://plaukuosena.lt/leave-in-conditioner-flower-fragrance-nenuskalaujamas-kondicionierius</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ffc04fa-0925-48a2-86df-62a08a127ee1.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8c38e360-1aa4-40f3-80d1-63fd05fadb48.png</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6796,10 +6792,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>350ml</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6811,22 +6811,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MILK-NO-FRIZZ-SPR-NA</t>
+          <t>MOIS-MORE-DREKINAM-CON-NA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MILK SHAKE NO FRIZZ AMAZING ANTI-HUMIDITY SPRAY apsauginis purškiklis garbanotiems plaukams</t>
+          <t>MOISTURE &amp; MORE CONDITIONER drėkinamasis kondicionierius sausiems plaukams</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MILK SHAKE</t>
+          <t>MOISTURE</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6836,17 +6836,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/amazing-anti-humidity-spray-apsauginis-purskiklis-garbanotiems-plaukams</t>
+          <t>https://plaukuosena.lt/moisture-and-more-conditioner-drekinamasis-kondicionierius-sausiems-plaukams</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ce022c83-2021-4842-9c57-7e44d680edec.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9fd3e0cd-3cd4-4c27-9475-b1bd26bb4e46.png</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6857,7 +6857,7 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6869,33 +6869,37 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MILK-PRIEMONE-KOSMETIK-PRD-NA</t>
+          <t>MOIS-PLUS-WHIPPED-CRM-NA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Milk Shake plaukų priežiūros priemonės | Milk Shake kosmetika</t>
+          <t>MOISTURE PLUS WHIPPED CREAM drėkinamosios putos sausiems plaukams</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MILK SHAKE</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>MOISTURE</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/milk-shake-plauku-prieziuros-priemones</t>
+          <t>https://plaukuosena.lt/moisture-plus-whipped-cream-drekinamosios-putos-sausiems-plaukams</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8af7f7bd-70ae-43f3-b8a7-ca5fa1c0bbc8.webp</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6911,34 +6915,34 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MOIS-MORE-DREKINAM-CON-NA</t>
+          <t>MOIS-HYDRATIN-LOTION-PRD-NA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MOISTURE &amp; MORE CONDITIONER drėkinamasis kondicionierius sausiems plaukams</t>
+          <t>MOISTURE&amp;MORE HYDRATING LOTION drėkinamasis losjonas sausiems plaukams</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MOISTURE</t>
+          <t>MOISTURE&amp;MORE</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6948,17 +6952,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moisture-and-more-conditioner-drekinamasis-kondicionierius-sausiems-plaukams</t>
+          <t>https://plaukuosena.lt/moistureandmore-hydrating-lotion-drekinamasis-losjonas-sausiems-plaukams</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9fd3e0cd-3cd4-4c27-9475-b1bd26bb4e46.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/34e3c3da-7fa7-4bb4-a951-8ff1150e33ac.webp</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6969,7 +6973,7 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6981,22 +6985,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MOIS-PLUS-WHIPPED-CRM-NA</t>
+          <t>MOIS-DREKINAM-SAUSIEMS-SHA-NA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MOISTURE PLUS WHIPPED CREAM drėkinamosios putos sausiems plaukams</t>
+          <t>MOISTURE&amp;MORE SHAMPOO drėkinamasis šampūnas sausiems plaukams</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MOISTURE</t>
+          <t>MOISTURE&amp;MORE</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7006,17 +7010,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moisture-plus-whipped-cream-drekinamosios-putos-sausiems-plaukams</t>
+          <t>https://plaukuosena.lt/moistureandmore-shampoo-drekinamasis-sampunas-sausiems-plaukams</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8af7f7bd-70ae-43f3-b8a7-ca5fa1c0bbc8.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3e5f63cf-df47-45e5-88af-e3561a3c7134.webp</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7027,7 +7031,7 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7039,12 +7043,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MOIS-HYDRATIN-LOTION-PRD-NA</t>
+          <t>MOIS-SIERO-ILLUMINA-SER-NA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE HYDRATING LOTION drėkinamasis losjonas sausiems plaukams</t>
+          <t>MOISTURE&amp;MORE SIERO ILLUMINANTE drėkinamasis spindesio suteikiantis serumas</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7054,7 +7058,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7064,17 +7068,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moistureandmore-hydrating-lotion-drekinamasis-losjonas-sausiems-plaukams</t>
+          <t>https://plaukuosena.lt/moistureandmore-siero-illuminante-drekinamasis-spindesio-suteikiantis-serumas</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/34e3c3da-7fa7-4bb4-a951-8ff1150e33ac.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/07c4138c-6a51-4ae1-b02a-24cdfad63075.webp</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7085,7 +7089,7 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7097,22 +7101,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MOIS-DREKINAM-SAUSIEMS-SHA-NA</t>
+          <t>NO-FRIZZ-ALLOWED-CON-NA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE SHAMPOO drėkinamasis šampūnas sausiems plaukams</t>
+          <t>NO FRIZZ ALLOWED PERFECTING CONDITIONER kondicionierius šiauštis linkusiems plaukams</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7122,17 +7126,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moistureandmore-shampoo-drekinamasis-sampunas-sausiems-plaukams</t>
+          <t>https://plaukuosena.lt/no-frizz-allowed-perfecting-conditioner-kondicionierius-siaustis-linkusiems-plaukams</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3e5f63cf-df47-45e5-88af-e3561a3c7134.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/74260607-8186-41a3-aab0-fa7b9d33cdfa.png</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7143,7 +7147,7 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7155,22 +7159,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MOIS-SIERO-ILLUMINA-SER-NA</t>
+          <t>NO-FRIZZ-ALLOWED-SHA-NA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE SIERO ILLUMINANTE drėkinamasis spindesio suteikiantis serumas</t>
+          <t>NO FRIZZ ALLOWED PERFECTING SHAMPOO šampūnas šiauštis linkusiems plaukams</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MOISTURE&amp;MORE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7180,17 +7184,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/moistureandmore-siero-illuminante-drekinamasis-spindesio-suteikiantis-serumas</t>
+          <t>https://plaukuosena.lt/no-frizz-allowed-perfecting-shampoo-sampunas-siaustis-linkusiems-plaukams</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/07c4138c-6a51-4ae1-b02a-24cdfad63075.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1b73df2a-a171-4121-a186-d4279faaf31c.png</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7201,7 +7205,7 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7213,22 +7217,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NO-FRIZZ-ALLOWED-CON-NA</t>
+          <t>NO-4-BOND-ENHANCER-SHA-NA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NO FRIZZ ALLOWED PERFECTING CONDITIONER kondicionierius šiauštis linkusiems plaukams</t>
+          <t>No.4P BOND ENHANCER TONING SHAMPOO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>No.4P</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7238,17 +7242,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no-frizz-allowed-perfecting-conditioner-kondicionierius-siaustis-linkusiems-plaukams</t>
+          <t>https://plaukuosena.lt/no4p-bond-enhancer-toning-shampoo</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/74260607-8186-41a3-aab0-fa7b9d33cdfa.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/edb6f281-e6cd-4872-bec1-b7478940b7ed.png</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7259,7 +7263,7 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7271,22 +7275,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>NO-FRIZZ-ALLOWED-SHA-NA</t>
+          <t>OLAP-NO-3-PRD-NA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NO FRIZZ ALLOWED PERFECTING SHAMPOO šampūnas šiauštis linkusiems plaukams</t>
+          <t>OLAPLEX No. 3 HAIR PERFECTOR</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7296,17 +7300,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no-frizz-allowed-perfecting-shampoo-sampunas-siaustis-linkusiems-plaukams</t>
+          <t>https://plaukuosena.lt/olaplex-no-3-hair-perfector</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1b73df2a-a171-4121-a186-d4279faaf31c.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1832e17d-37c2-4f27-9dbf-03c1c80d368a.png</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7317,7 +7321,7 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>850018802840</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7329,22 +7333,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NO-4-BOND-ENHANCER-SHA-NA</t>
+          <t>OLAP-NO-4-SHA-NA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>No.4P BOND ENHANCER TONING SHAMPOO</t>
+          <t>OLAPLEX No. 4 BOND MAINTENANCE SHAMPOO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>No.4P</t>
+          <t>OLAPLEX</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7354,12 +7358,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no4p-bond-enhancer-toning-shampoo</t>
+          <t>https://plaukuosena.lt/olaplex-no-4-bond-maintenance-shampoo</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/edb6f281-e6cd-4872-bec1-b7478940b7ed.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2f17f7df-64a9-44b0-8d0d-7beb0d421ee2.png</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7375,7 +7379,7 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>896364002756</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7387,12 +7391,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>OLAP-NO-3-PRD-NA</t>
+          <t>OLAP-NO-4D-SHA-NA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 3 HAIR PERFECTOR</t>
+          <t>OLAPLEX No. 4D Dry Shampoo</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7402,7 +7406,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7412,17 +7416,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-3-hair-perfector</t>
+          <t>https://plaukuosena.lt/olaplex-no-4d-dry-shampoo</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1832e17d-37c2-4f27-9dbf-03c1c80d368a.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4b16b116-5392-4248-beaf-e788b5b65f8c.png</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7433,7 +7437,7 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>850018802840</t>
+          <t>850018802567</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7445,12 +7449,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>OLAP-NO-4-SHA-NA</t>
+          <t>OLAP-NO-5-CON-NA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 4 BOND MAINTENANCE SHAMPOO</t>
+          <t>OLAPLEX No. 5 BOND MAINTENANCE CONDITIONER</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7470,17 +7474,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-4-bond-maintenance-shampoo</t>
+          <t>https://plaukuosena.lt/olaplex-no-5-bond-maintenance-conditioner</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2f17f7df-64a9-44b0-8d0d-7beb0d421ee2.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/17784e89-7411-4bd4-8b97-58350ae502d8.png</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7491,7 +7495,7 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>896364002756</t>
+          <t>896364002763</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7503,12 +7507,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>OLAP-NO-4D-SHA-NA</t>
+          <t>OLAP-NO-6-PRD-NA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 4D Dry Shampoo</t>
+          <t>OLAPLEX No. 6 BOND SMOOTHER</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7518,7 +7522,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7528,17 +7532,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-4d-dry-shampoo</t>
+          <t>https://plaukuosena.lt/olaplex-no-6-bond-smoother</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4b16b116-5392-4248-beaf-e788b5b65f8c.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39301ecc-75fd-4fca-9e6a-0af9debc2e46.png</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7549,7 +7553,7 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>850018802567</t>
+          <t>896364002961</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7561,12 +7565,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>OLAP-NO-5-CON-NA</t>
+          <t>OLAP-NO-0-INTENSIV-PRD-NA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 5 BOND MAINTENANCE CONDITIONER</t>
+          <t>OLAPLEX No.0 INTENSIVE BOND BUILDING HAIR TREATMENT</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7576,7 +7580,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7586,17 +7590,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-5-bond-maintenance-conditioner</t>
+          <t>https://plaukuosena.lt/olaplex-no0-intensive-bond-building-hair-treatment</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/17784e89-7411-4bd4-8b97-58350ae502d8.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d72c34ad-0dbf-4c23-af6a-9e6dbc63c38e.png</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7607,7 +7611,7 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>896364002763</t>
+          <t>850018802833</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7619,12 +7623,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>OLAP-NO-6-PRD-NA</t>
+          <t>OLAP-NO-10-BOND-GEL-NA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>OLAPLEX No. 6 BOND SMOOTHER</t>
+          <t>OLAPLEX No.10 BOND SHAPER™ CURL DEFINING GEL</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7644,17 +7648,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no-6-bond-smoother</t>
+          <t>https://plaukuosena.lt/no10-bond-shapertm-curl-defining-gel</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39301ecc-75fd-4fca-9e6a-0af9debc2e46.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6e3ed035-956b-465b-a424-b8b30e2641de.png</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų geliai</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7665,7 +7669,7 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>896364002961</t>
+          <t>850056933155</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7677,12 +7681,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>OLAP-NO-0-INTENSIV-PRD-NA</t>
+          <t>OLAP-NO-3-PLUS-PRD-NA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>OLAPLEX No.0 INTENSIVE BOND BUILDING HAIR TREATMENT</t>
+          <t>OLAPLEX No.3 PLUS Ultimate Repair Treatment</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7692,7 +7696,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7702,12 +7706,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no0-intensive-bond-building-hair-treatment</t>
+          <t>https://plaukuosena.lt/olaplex-no3-plus-ultimate-repair-treatment</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d72c34ad-0dbf-4c23-af6a-9e6dbc63c38e.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39908a67-c29d-4092-ad0e-d3b12c4c285f.png</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7723,7 +7727,7 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>850018802833</t>
+          <t>810177860273</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7735,12 +7739,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>OLAP-NO-10-BOND-GEL-NA</t>
+          <t>OLAP-NO-4-CURL-SHA-250ML</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>OLAPLEX No.10 BOND SHAPER™ CURL DEFINING GEL</t>
+          <t>OLAPLEX No.4 Curl Hydrating Shampoo | 250ML</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7750,7 +7754,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7760,17 +7764,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no10-bond-shapertm-curl-defining-gel</t>
+          <t>https://plaukuosena.lt/olaplex-no4-curl-hydrating-shampoo-or-250ml</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6e3ed035-956b-465b-a424-b8b30e2641de.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/96c834cd-3879-4555-8051-670ffa93e48b.png</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Plaukų geliai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7778,10 +7782,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>850056933155</t>
+          <t>810177861041</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7793,12 +7801,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>OLAP-NO-3-PLUS-PRD-NA</t>
+          <t>OLAP-NO-4C-BOND-SHA-NA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>OLAPLEX No.3 PLUS Ultimate Repair Treatment</t>
+          <t>OLAPLEX No.4C BOND MAINTENANCE CLARIFYING SHAMPOO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7808,7 +7816,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7818,17 +7826,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no3-plus-ultimate-repair-treatment</t>
+          <t>https://plaukuosena.lt/olaplex-no4c-bond-maintenance-clarifying-shampoo</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/39908a67-c29d-4092-ad0e-d3b12c4c285f.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/15aa41ad-b5ee-455b-82fe-67dd4515079d.png</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7839,7 +7847,7 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>810177860273</t>
+          <t>850018802581</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7851,12 +7859,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>OLAP-NO-4-CURL-SHA-250ML</t>
+          <t>OLAP-NO-4FINE-BOND-SHA-NA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>OLAPLEX No.4 Curl Hydrating Shampoo | 250ML</t>
+          <t>OLAPLEX No.4FINE Bond Maintenance Shampoo</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7866,7 +7874,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7876,12 +7884,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no4-curl-hydrating-shampoo-or-250ml</t>
+          <t>https://plaukuosena.lt/no4fine-bond-maintenance-shampoo</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/96c834cd-3879-4555-8051-670ffa93e48b.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c99d5b13-2995-490c-b568-67b721c151a7.png</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7894,14 +7902,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>810177861041</t>
+          <t>850056933575</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7913,12 +7917,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>OLAP-NO-4C-BOND-SHA-NA</t>
+          <t>OLAP-NO-5-CURL-CON-250ML</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>OLAPLEX No.4C BOND MAINTENANCE CLARIFYING SHAMPOO</t>
+          <t>OLAPLEX No.5 Curl Hydrating Conditioner | 250ml</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7928,7 +7932,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7938,17 +7942,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no4c-bond-maintenance-clarifying-shampoo</t>
+          <t>https://plaukuosena.lt/olaplex-no5-curl-hydrating-conditioner-or-250ml</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/15aa41ad-b5ee-455b-82fe-67dd4515079d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/57ab765d-6fa6-4d6b-83c0-03fee32aa033.png</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7956,10 +7960,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>850018802581</t>
+          <t>810177861010</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -7971,12 +7979,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>OLAP-NO-4FINE-BOND-SHA-NA</t>
+          <t>OLAP-NO-5-LEAVE-IN-PRD-NA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>OLAPLEX No.4FINE Bond Maintenance Shampoo</t>
+          <t>OLAPLEX No.5 LEAVE-IN Moisturize</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7986,7 +7994,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7996,17 +8004,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no4fine-bond-maintenance-shampoo</t>
+          <t>https://plaukuosena.lt/olaplex-no5-leave-in-moisturize</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c99d5b13-2995-490c-b568-67b721c151a7.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e18890ee-ba6f-43ff-a518-fce468bdc091.png</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8017,7 +8025,7 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>850056933575</t>
+          <t>850056933285</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8029,12 +8037,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>OLAP-NO-5-CURL-CON-250ML</t>
+          <t>OLAP-NO-5FINE-BOND-CON-NA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>OLAPLEX No.5 Curl Hydrating Conditioner | 250ml</t>
+          <t>OLAPLEX No.5FINE Bond Maintenance Conditioner</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8044,7 +8052,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8054,12 +8062,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no5-curl-hydrating-conditioner-or-250ml</t>
+          <t>https://plaukuosena.lt/no5fine-bond-maintenance-conditioner</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/73d73934-cc28-4c05-aa81-056ef03db222.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ccafd5f1-87db-45ae-af6b-3dad5b5af329.png</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8072,14 +8080,10 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>250ml</t>
-        </is>
-      </c>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>810177861010</t>
+          <t>850056933612</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8091,12 +8095,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>OLAP-NO-5-LEAVE-IN-PRD-NA</t>
+          <t>OLAP-NO-5P-BLOND-CON-NA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>OLAPLEX No.5 LEAVE-IN Moisturize</t>
+          <t>OLAPLEX No.5P BLOND ENHANCER TONING CONDITIONER</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8116,17 +8120,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no5-leave-in-moisturize</t>
+          <t>https://plaukuosena.lt/olaplex-no5p-blond-enhancer-toning-conditioner</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e18890ee-ba6f-43ff-a518-fce468bdc091.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/35185d43-ba29-4be4-bd01-153f53e9628a.jpg</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8137,7 +8141,7 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>850056933285</t>
+          <t>850045076290</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8149,12 +8153,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>OLAP-NO-5FINE-BOND-CON-NA</t>
+          <t>OLAP-NO-7-BONDING-OIL-NA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>OLAPLEX No.5FINE Bond Maintenance Conditioner</t>
+          <t>OLAPLEX No.7 BONDING OIL</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8164,7 +8168,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8174,17 +8178,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/no5fine-bond-maintenance-conditioner</t>
+          <t>https://plaukuosena.lt/olaplex-no7-bonding-oil</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ccafd5f1-87db-45ae-af6b-3dad5b5af329.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8f444685-5686-42dd-b4a9-73afbcfb889f.png</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8195,7 +8199,7 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>850056933612</t>
+          <t>896364002695</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8207,12 +8211,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OLAP-NO-5P-BLOND-CON-NA</t>
+          <t>OLAP-NO-8-BOND-MSK-NA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>OLAPLEX No.5P BLOND ENHANCER TONING CONDITIONER</t>
+          <t>OLAPLEX No.8 BOND INTENSE MOISTURE MASK</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8232,17 +8236,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no5p-blond-enhancer-toning-conditioner</t>
+          <t>https://plaukuosena.lt/olaplex-no8-bond-intense-moisture-mask</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/35185d43-ba29-4be4-bd01-153f53e9628a.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/552d57ab-d055-4c8c-9603-b292e1a25e64.png</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8253,7 +8257,7 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>850045076290</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8265,12 +8269,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>OLAP-NO-7-BONDING-OIL-NA</t>
+          <t>OLAP-NO-9-BOND-SER-NA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>OLAPLEX No.7 BONDING OIL</t>
+          <t>OLAPLEX No.9 BOND PROTECTOR NOURISHING HAIR SERUM</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8290,17 +8294,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no7-bonding-oil</t>
+          <t>https://plaukuosena.lt/olaplex-no9-bond-protector-nourishing-hair-serum</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8f444685-5686-42dd-b4a9-73afbcfb889f.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e7ab9fdc-43dc-45c3-914c-fa13f791dc3d.png</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Plaukų aliejai</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8311,7 +8315,7 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>896364002695</t>
+          <t>850018802826</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8323,12 +8327,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>OLAP-NO-8-BOND-MSK-NA</t>
+          <t>OLAP-RICH-HYDRATIO-MSK-200ML</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>OLAPLEX No.8 BOND INTENSE MOISTURE MASK</t>
+          <t>OLAPLEX Rich Hydration Mask 200ML</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8338,7 +8342,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>47.00</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8348,12 +8352,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no8-bond-intense-moisture-mask</t>
+          <t>https://plaukuosena.lt/rich-hydration-mask</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/552d57ab-d055-4c8c-9603-b292e1a25e64.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2d89d52d-0761-42dc-a4d6-d3ebe5da60b7.png</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8366,10 +8370,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>850056933919</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8381,12 +8389,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>OLAP-NO-9-BOND-SER-NA</t>
+          <t>OLAP-VOLUMIZI-BLOW-PRD-NA</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>OLAPLEX No.9 BOND PROTECTOR NOURISHING HAIR SERUM</t>
+          <t>OLAPLEX Volumizing Blow Dry Mist</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8406,17 +8414,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-no9-bond-protector-nourishing-hair-serum</t>
+          <t>https://plaukuosena.lt/olaplex-volumizing-blow-dry-mist</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e7ab9fdc-43dc-45c3-914c-fa13f791dc3d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/87bf6622-3275-425b-8a73-1bb008b61716.jpg</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8427,7 +8435,7 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>850018802826</t>
+          <t>850045076221</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8439,12 +8447,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>OLAP-RICH-HYDRATIO-MSK-200ML</t>
+          <t>OLAP-WEIGHTLE-NOURISHI-MSK-200ML</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>OLAPLEX Rich Hydration Mask 200ML</t>
+          <t>OLAPLEX Weightless Nourishing Mask 200ML</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8464,12 +8472,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/rich-hydration-mask</t>
+          <t>https://plaukuosena.lt/weightless-nourishing-mask</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2d89d52d-0761-42dc-a4d6-d3ebe5da60b7.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/da078417-7753-4c31-95e9-19242f1b1aff.png</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8489,7 +8497,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>850056933919</t>
+          <t>850056933889</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8501,12 +8509,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>OLAP-VOLUMIZI-BLOW-PRD-NA</t>
+          <t>OLAP-PRIEMONE-PRODUKTA-PRD-NA</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>OLAPLEX Volumizing Blow Dry Mist</t>
+          <t>Olaplex plaukų priežiūros priemonės | Olaplex produktai</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8514,24 +8522,20 @@
           <t>OLAPLEX</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
-      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-volumizing-blow-dry-mist</t>
+          <t>https://plaukuosena.lt/olaplex-plauku-prieziuros-priemones</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/87bf6622-3275-425b-8a73-1bb008b61716.jpg</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8547,54 +8551,50 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>850045076221</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>OLAP-WEIGHTLE-NOURISHI-MSK-200ML</t>
+          <t>PINI-GRAZINIM-POLITIKA-PRD-NA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>OLAPLEX Weightless Nourishing Mask 200ML</t>
+          <t>Pinigų grąžinimo politika – grąžinimo sąlygos</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>47.00</t>
-        </is>
-      </c>
+          <t>Pinigų</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/weightless-nourishing-mask</t>
+          <t>https://plaukuosena.lt/pinigu-grazinimo-politika</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/da078417-7753-4c31-95e9-19242f1b1aff.png</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8602,36 +8602,32 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>850056933889</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>OLAP-PRIEMONE-PRODUKTA-PRD-NA</t>
+          <t>PLAU-GELIAI-SERUMAI-SER-NA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Olaplex plaukų priežiūros priemonės | Olaplex produktai</t>
+          <t>Plaukų geliai ir serumai | Profesionalios formavimo priemonės</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>OLAPLEX</t>
+          <t>Plaukų</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -8642,7 +8638,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/olaplex-plauku-prieziuros-priemones</t>
+          <t>https://plaukuosena.lt/plauku-geliai-ir-serumai</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8652,7 +8648,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8663,7 +8659,7 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8675,17 +8671,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PINI-GRAZINIM-POLITIKA-PRD-NA</t>
+          <t>PLAU-KAUKES-PROFESIO-MSK-NA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Pinigų grąžinimo politika – grąžinimo sąlygos</t>
+          <t>Plaukų kaukės | Profesionalios plaukų kaukės internetu</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Pinigų</t>
+          <t>Plaukų</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -8696,7 +8692,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/pinigu-grazinimo-politika</t>
+          <t>https://plaukuosena.lt/plauku-kaukes</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8706,7 +8702,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8717,7 +8713,7 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8729,38 +8725,42 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PLAU-GELIAI-SERUMAI-SER-NA</t>
+          <t>QIQI-BARE-REPAIR-OIL-NA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Plaukų geliai ir serumai | Profesionalios formavimo priemonės</t>
+          <t>QIQI Bare Repair Oil Plaukų aliejus</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Plaukų</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
+          <t>QIQI</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/plauku-geliai-ir-serumai</t>
+          <t>https://plaukuosena.lt/qiqi-bare-repair-oil-plauku-aliejus</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/85f599b6-1ab5-4fe0-9330-8b393efc56d2.png</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų aliejai</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8771,50 +8771,54 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>7290019116882</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PLAU-KAUKES-PROFESIO-MSK-NA</t>
+          <t>QIQI-GLOTNINA-SHA-NA</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Plaukų kaukės | Profesionalios plaukų kaukės internetu</t>
+          <t>QIQI Glotninantis šampūnas</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Plaukų</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
+          <t>QIQI</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>14.00</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/plauku-kaukes</t>
+          <t>https://plaukuosena.lt/qiqi-glotninantis-sampunas</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9ad34b38-7896-457c-8d2e-598db9e7336d.png</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8825,24 +8829,24 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>7290019116042</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>QIQI-BARE-REPAIR-OIL-NA</t>
+          <t>QIQI-POROSITY-PLAY-SPR-NA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>QIQI Bare Repair Oil Plaukų aliejus</t>
+          <t>QIQI Porosity Play Spray Plaukų purškiklis</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8862,17 +8866,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-bare-repair-oil-plauku-aliejus</t>
+          <t>https://plaukuosena.lt/qiqi-porosity-play-spray-plauku-purskiklis</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/85f599b6-1ab5-4fe0-9330-8b393efc56d2.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c272a239-cd7a-422f-a950-d80d709d9259.png</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Plaukų aliejai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8883,7 +8887,7 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>7290019116882</t>
+          <t>7290019116455</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8895,12 +8899,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>QIQI-GLOTNINA-SHA-NA</t>
+          <t>QIQI-POROSITY-VOLUME-PRD-NA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>QIQI Glotninantis šampūnas</t>
+          <t>QIQI Porosity Volume Code Mist Gausos apimties suteikianti dulksna</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8910,7 +8914,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8920,17 +8924,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-glotninantis-sampunas</t>
+          <t>https://plaukuosena.lt/qiqi-porosity-volume-code-mist-gausos-apimties-suteikianti-dulksna</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9ad34b38-7896-457c-8d2e-598db9e7336d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40938472-383c-4c92-9b8b-040403000e9d.png</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8941,7 +8945,7 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>7290019116042</t>
+          <t>7290019116899</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -8953,12 +8957,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>QIQI-POROSITY-PLAY-SPR-NA</t>
+          <t>QIQI-SUPER-SOAKER-MSK-NA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>QIQI Porosity Play Spray Plaukų purškiklis</t>
+          <t>QIQI Super Soaker Smoothing Masque Glotninanti plaukų kaukė</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8968,7 +8972,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8978,17 +8982,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-porosity-play-spray-plauku-purskiklis</t>
+          <t>https://plaukuosena.lt/qiqi-super-soaker-smoothing-masque-glotninanti-plauku-kauke</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c272a239-cd7a-422f-a950-d80d709d9259.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c207ccff-61fd-499a-9db4-0ed63a8c34c7.png</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8999,7 +9003,7 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>7290019116455</t>
+          <t>7290019116448</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9011,12 +9015,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>QIQI-POROSITY-VOLUME-PRD-NA</t>
+          <t>QIQI-DREKINAM-CON-NA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>QIQI Porosity Volume Code Mist Gausos apimties suteikianti dulksna</t>
+          <t>QIQI drėkinamasis kondicionierius</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9026,7 +9030,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9036,17 +9040,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-porosity-volume-code-mist-gausos-apimties-suteikianti-dulksna</t>
+          <t>https://plaukuosena.lt/qiqi-drekinamasis-kondicionierius</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40938472-383c-4c92-9b8b-040403000e9d.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e9113e8b-f95c-4cb6-ab03-9977a03ffcd1.png</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9057,7 +9061,7 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>7290019116899</t>
+          <t>7290019116240</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9069,12 +9073,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>QIQI-SUPER-SOAKER-MSK-NA</t>
+          <t>QIQI-ALL-OUT-CRM-NA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>QIQI Super Soaker Smoothing Masque Glotninanti plaukų kaukė</t>
+          <t>Qiqi All Out Blowout užbaigimo kremas</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9084,7 +9088,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9094,17 +9098,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-super-soaker-smoothing-masque-glotninanti-plauku-kauke</t>
+          <t>https://plaukuosena.lt/qiqi-all-out-blowout-uzbaigimo-kremas</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c207ccff-61fd-499a-9db4-0ed63a8c34c7.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ed4db76-21f3-4ce0-a884-2230c7418f53.png</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9115,7 +9119,7 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>7290019116448</t>
+          <t>7290019116264</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9127,12 +9131,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>QIQI-DREKINAM-CON-NA</t>
+          <t>QIQI-PRIEMONE-KOSMETIK-PRD-NA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>QIQI drėkinamasis kondicionierius</t>
+          <t>Qiqi plaukų priežiūros priemonės | Qiqi kosmetika</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9140,29 +9144,25 @@
           <t>QIQI</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>14.00</t>
-        </is>
-      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-drekinamasis-kondicionierius</t>
+          <t>https://plaukuosena.lt/qiqi-plauku-prieziuros-priemones</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e9113e8b-f95c-4cb6-ab03-9977a03ffcd1.png</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9173,34 +9173,34 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>7290019116240</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>QIQI-ALL-OUT-CRM-NA</t>
+          <t>SILV-SHINE-ZILIEMS-CON-NA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Qiqi All Out Blowout užbaigimo kremas</t>
+          <t>SILVER SHINE CONDITIONER kondicionierius žiliems / šviesintiems plaukams</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>QIQI</t>
+          <t>SILVER</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9210,17 +9210,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-all-out-blowout-uzbaigimo-kremas</t>
+          <t>https://plaukuosena.lt/silver-shine-conditioner-kondicionierius-ziliems-sviesintiems-plaukams</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2ed4db76-21f3-4ce0-a884-2230c7418f53.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/78ae2b87-aede-4bf6-a3fc-ede2a0e31735.webp</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9231,7 +9231,7 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>7290019116264</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9243,38 +9243,42 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>QIQI-PRIEMONE-KOSMETIK-PRD-NA</t>
+          <t>SILV-SHINE-LIGHT-SHA-NA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Qiqi plaukų priežiūros priemonės | Qiqi kosmetika</t>
+          <t>SILVER SHINE LIGHT SHAMPOO šampūnas žiliems / šviesintiems plaukams</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>QIQI</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
+          <t>SILVER</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>17.50</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/qiqi-plauku-prieziuros-priemones</t>
+          <t>https://plaukuosena.lt/silver-shine-shampoo-sampunas-ziliems-sviesintiems-plaukams</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/33a6ba33-a228-4fc9-8fe9-6b66a129541b.webp</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9285,34 +9289,34 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SILV-SHINE-ZILIEMS-CON-NA</t>
+          <t>SMOO-MIRACLE-SHIELD-SPR-NA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SILVER SHINE CONDITIONER kondicionierius žiliems / šviesintiems plaukams</t>
+          <t>SMOOTHING MIRACLE SHIELD nuo karščio ir drėgmės apsaugantis purškiklis</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SILVER</t>
+          <t>SMOOTHING</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9322,17 +9326,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/silver-shine-conditioner-kondicionierius-ziliems-sviesintiems-plaukams</t>
+          <t>https://plaukuosena.lt/smoothing-miracle-shield-nuo-karscio-ir-dregmes-apsaugantis-purskiklis</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/78ae2b87-aede-4bf6-a3fc-ede2a0e31735.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4f9a2abf-0979-4209-b9ac-a2365f16cfd9.webp</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9343,7 +9347,7 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9355,42 +9359,38 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SILV-SHINE-LIGHT-SHA-NA</t>
+          <t>SAUL-APSAUGA-APSAUGA-PRD-NA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SILVER SHINE LIGHT SHAMPOO šampūnas žiliems / šviesintiems plaukams</t>
+          <t>Saulės apsauga plaukams | Apsauga nuo UV</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SILVER</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>17.50</t>
-        </is>
-      </c>
+          <t>Saulės</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/silver-shine-shampoo-sampunas-ziliems-sviesintiems-plaukams</t>
+          <t>https://plaukuosena.lt/saules-apsauga-plaukams</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/33a6ba33-a228-4fc9-8fe9-6b66a129541b.webp</t>
+          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9401,29 +9401,29 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CHECK_PRICE</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SMOO-MIRACLE-SHIELD-SPR-NA</t>
+          <t>WELL-COLOR-FRESH-MSK-150ML</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SMOOTHING MIRACLE SHIELD nuo karščio ir drėgmės apsaugantis purškiklis</t>
+          <t>WELLA PROFESSIONALS COLOR FRESH dažanti kaukė, 150 ml</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SMOOTHING</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9438,17 +9438,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/smoothing-miracle-shield-nuo-karscio-ir-dregmes-apsaugantis-purskiklis</t>
+          <t>https://plaukuosena.lt/color-fresh-dazanti-kauke-150-ml</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4f9a2abf-0979-4209-b9ac-a2365f16cfd9.webp</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/b46862ae-d30b-4244-a405-7edb625d60ad.jpg</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9456,10 +9456,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>4064666210902</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9471,33 +9475,37 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SAUL-APSAUGA-APSAUGA-PRD-NA</t>
+          <t>WELL-EIMI-ABSOLUTE-PRD-300ML</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Saulės apsauga plaukams | Apsauga nuo UV</t>
+          <t>WELLA PROFESSIONALS EIMI Absolute Set lakas # 4+ | 300ML</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Saulės</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>WELLA PROFESSIONALS</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/saules-apsauga-plaukams</t>
+          <t>https://plaukuosena.lt/eimi-absolute-set-lakas-4-300-ml</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4609936e-f051-43d0-bf28-23a210169d95.jpg</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9510,37 +9518,41 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>8005610563244</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>CHECK_PRICE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ULTI-REPAIR-INTENSYV-MSK-NA</t>
+          <t>WELL-EIMI-DRY-SHA-180ML</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR intensyvaus poveikio kaukė pažeistiems plaukams STEP 2</t>
+          <t>WELLA PROFESSIONALS EIMI Dry Me Dry sausas šampūnas #1 | 180ML</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9550,17 +9562,17 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-kauke-pazeistiems-plaukams-step-2</t>
+          <t>https://plaukuosena.lt/eimi-dry-me-dry-sausas-sampunas-1-180-ml</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40b6a8c2-185a-422b-9154-64aa5d5b8555.png</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/685481b5-65b1-4e9e-a0d1-967851f46e02.jpg</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9568,10 +9580,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>180ml</t>
+        </is>
+      </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>1780932909943</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9583,22 +9599,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ULTI-REPAIR-INTENSYV-CON-NA</t>
+          <t>WELL-EIMI-EXTRA-FOA-300ML</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR intensyvaus poveikio kondicionierius pažeistiems plaukams STEP 2</t>
+          <t>WELLA PROFESSIONALS EIMI Extra Volume putos #3 | 300ML</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9608,17 +9624,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-kondicionierius-pazeistiems-plaukams-step-2-</t>
+          <t>https://plaukuosena.lt/eimi-extra-volume-putos-3-300-ml</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3634c6f3-03f0-47ee-800b-94c7e7402d89.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4ce5d05e-e0eb-4588-9266-14c75d59b5b2.jpg</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9626,10 +9642,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>4064666211916</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -9641,22 +9661,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ULTI-REPAIR-INTENSYV-SHA-NA</t>
+          <t>WELL-EIMI-FLEXIBLE-PRD-250ML</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR intensyvaus poveikio šampūnas pažeistiems plaukams STEP 1</t>
+          <t>WELLA PROFESSIONALS EIMI Flexible Finish lakas #2 | 250ML</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>27.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9666,17 +9686,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-sampunas-pazeistiems-plaukams-step-1</t>
+          <t>https://plaukuosena.lt/eimi-flexible-finish-lakas-2-250-ml</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/10b51403-3d69-4efa-8f65-c0c2bf55fa06.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/690edb16-bb3f-41bc-a6d0-6e1c32ae98d2.jpg</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9684,10 +9704,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr"/>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>4064666213958</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9699,22 +9723,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ULTI-REPAIR-NAKTINIS-SER-NA</t>
+          <t>WELL-EIMI-FLOWING-PRD-100ML</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ULTIMATE REPAIR naktinis plaukų serumas STEP 5</t>
+          <t>WELLA PROFESSIONALS EIMI Flowing Form balzamas #2 | 100ML</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9724,17 +9748,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-repair-naktinis-plauku-serumas-step-5</t>
+          <t>https://plaukuosena.lt/eimi-flowing-form-balzamas-2-100-ml</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0cda5ab2-52cf-4f06-8b6c-0f7b5b4bc2cf.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1544dbd7-35f9-42b5-92ec-d0cd6f9943ab.jpg</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9742,10 +9766,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>8005610575025</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -9757,22 +9785,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ULTI-SMOOTH-MAITINAN-MSK-NA</t>
+          <t>WELL-EIMI-GLAM-PRD-200ML</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ULTIMATE SMOOTH maitinanti kaukė su skvalanu ir omega-9</t>
+          <t>WELLA PROFESSIONALS EIMI Glam Mist lakas / blizgis #1 | 200ML</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ULTIMATE</t>
+          <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>27.00</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9782,17 +9810,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-smooth-maitinanti-kauke-su-skvalanu-ir-omega-9</t>
+          <t>https://plaukuosena.lt/eimi-glam-mist-lakas-blizgis-1-200-ml</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f7774306-1953-481b-9f15-746af2bac04c.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/47a0bc9e-6340-462e-a327-ccd1efe76dda.jpg</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9800,10 +9828,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr"/>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>4064666314532</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9815,12 +9847,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>WELL-EIMI-ABSOLUTE-PRD-300ML</t>
+          <t>WELL-EIMI-MISTIFY-PRD-300ML</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Absolute Set lakas # 4+ | 300ML</t>
+          <t>WELLA PROFESSIONALS EIMI Mistify Me Light lakas #2 | 300ML</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9830,7 +9862,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9840,12 +9872,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-absolute-set-lakas-4-300-ml</t>
+          <t>https://plaukuosena.lt/eimi-mistify-me-light-lakas-2-300-ml</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4609936e-f051-43d0-bf28-23a210169d95.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f44de339-ff78-47c5-bef9-4840e03045b9.jpg</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -9865,7 +9897,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>8005610563244</t>
+          <t>4064666214238</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9877,12 +9909,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>WELL-EIMI-DRY-SHA-180ML</t>
+          <t>WELL-EIMI-MISTIFY-PRD-300ML-4AE5</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Dry Me Dry sausas šampūnas #1 | 180ML</t>
+          <t>WELLA PROFESSIONALS EIMI Mistify Me Strong lakas #3 | 300ML</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9902,17 +9934,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-dry-me-dry-sausas-sampunas-1-180-ml</t>
+          <t>https://plaukuosena.lt/eimi-mistify-me-strong-lakas-3-300-ml</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/685481b5-65b1-4e9e-a0d1-967851f46e02.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/25a65e8a-b11d-4d44-9b95-7db4a88549e5.jpg</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9922,12 +9954,12 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>180ml</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>4064666214252</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -9939,12 +9971,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>WELL-EIMI-EXTRA-FOA-300ML</t>
+          <t>WELL-EIMI-NUTRICUR-FOA-300ML</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Extra Volume putos #3 | 300ML</t>
+          <t>WELLA PROFESSIONALS EIMI NUTRICURLS BOOST BOUNCE 72h švelnios putos garbanoms #2 | 300ML</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9954,7 +9986,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>23.50</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9964,12 +9996,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-extra-volume-putos-3-300-ml</t>
+          <t>https://plaukuosena.lt/eimi-nutricurls-boost-bounce-72h-svelnios-putos-garbanoms-2-300-ml</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/4ce5d05e-e0eb-4588-9266-14c75d59b5b2.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e1731c4e-394c-435e-b753-e948d7cfbf89.jpg</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -9989,7 +10021,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>4064666211916</t>
+          <t>4064666213392</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10001,12 +10033,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>WELL-EIMI-FLEXIBLE-PRD-250ML</t>
+          <t>WELL-EIMI-NATURAL-FOA-300ML</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Flexible Finish lakas #2 | 250ML</t>
+          <t>WELLA PROFESSIONALS EIMI Natural Volume putos #2 | 300ML</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10016,7 +10048,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10026,12 +10058,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-flexible-finish-lakas-2-250-ml</t>
+          <t>https://plaukuosena.lt/eimi-natural-volume-putos-2-300-ml</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/690edb16-bb3f-41bc-a6d0-6e1c32ae98d2.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9473f762-aafe-44c0-9acb-7e105a4f8d11.jpg</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10046,12 +10078,12 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>250ml</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>4064666213958</t>
+          <t>4064666211893</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10063,12 +10095,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>WELL-EIMI-FLOWING-PRD-100ML</t>
+          <t>WELL-EIMI-NUTRICUR-CRM-150ML</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Flowing Form balzamas #2 | 100ML</t>
+          <t>WELLA PROFESSIONALS EIMI Nutricurls Curl Shaper kremas #2 | 150ML</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10078,7 +10110,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10088,12 +10120,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-flowing-form-balzamas-2-100-ml</t>
+          <t>https://plaukuosena.lt/eimi-nutricurls-curl-shaper-kremas-2-150-ml</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/1544dbd7-35f9-42b5-92ec-d0cd6f9943ab.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/05eb6823-d484-4232-a92a-05a825b67fc3.jpg</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10108,12 +10140,12 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>8005610575025</t>
+          <t>4064666213415</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10125,12 +10157,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>WELL-EIMI-GLAM-PRD-200ML</t>
+          <t>WELL-EIMI-NUTRICUR-PRD-150ML</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Glam Mist lakas / blizgis #1 | 200ML</t>
+          <t>WELLA PROFESSIONALS EIMI Nutricurls Fresh Up purškalas #1 | 150ML</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10140,7 +10172,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>27.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10150,17 +10182,17 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-glam-mist-lakas-blizgis-1-200-ml</t>
+          <t>https://plaukuosena.lt/eimi-nutricurls-fresh-up-purskalas-1-150-ml</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/47a0bc9e-6340-462e-a327-ccd1efe76dda.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c849de07-4e68-4b6b-b4ed-a59ac843799e.jpg</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10170,12 +10202,12 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>4064666314532</t>
+          <t>4064666213439</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10187,12 +10219,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>WELL-EIMI-MISTIFY-PRD-300ML</t>
+          <t>WELL-EIMI-NUTRICUR-FOA-200ML</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Mistify Me Light lakas #2 | 300ML</t>
+          <t>WELLA PROFESSIONALS EIMI Nutricurls Soft Twirl putos #2 | 200ML</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10202,7 +10234,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>26.50</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10212,12 +10244,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-mistify-me-light-lakas-2-300-ml</t>
+          <t>https://plaukuosena.lt/eimi-nutricurls-soft-twirl-putos-2-200-ml</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f44de339-ff78-47c5-bef9-4840e03045b9.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/01c8bbb3-0429-4f4c-9d1e-508b94ae4ba9.jpg</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10232,12 +10264,12 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>4064666214238</t>
+          <t>4064666212869</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10249,12 +10281,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>WELL-EIMI-MISTIFY-PRD-300ML-4AE5</t>
+          <t>WELL-EIMI-OCEAN-PRD-150ML</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Mistify Me Strong lakas #3 | 300ML</t>
+          <t>WELLA PROFESSIONALS EIMI Ocean Spritz purškalas su druska #2 | 150ML</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10264,7 +10296,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10274,17 +10306,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-mistify-me-strong-lakas-3-300-ml</t>
+          <t>https://plaukuosena.lt/eimi-ocean-spritz-purskalas-su-druska-2-150-ml</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/25a65e8a-b11d-4d44-9b95-7db4a88549e5.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ad6f5336-91da-4ba8-8a8d-12468afe45c7.jpg</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10294,12 +10326,12 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>4064666214252</t>
+          <t>8005610534558</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10311,12 +10343,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>WELL-EIMI-NUTRICUR-FOA-300ML</t>
+          <t>WELL-EIMI-PEARL-GEL-100ML</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI NUTRICURLS BOOST BOUNCE 72h švelnios putos garbanoms #2 | 300ML</t>
+          <t>WELLA PROFESSIONALS EIMI Pearl Styler gelis #3 | 100ML</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10326,7 +10358,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>23.50</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10336,17 +10368,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-nutricurls-boost-bounce-72h-svelnios-putos-garbanoms-2-300-ml</t>
+          <t>https://plaukuosena.lt/eimi-pearl-styler-gelis-3-100-ml</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/e1731c4e-394c-435e-b753-e948d7cfbf89.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/144e8417-a5e5-4fb1-a96d-9ea6632bffa9.jpg</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų geliai</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10356,12 +10388,12 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>4064666213392</t>
+          <t>8005610587745</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10373,12 +10405,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>WELL-EIMI-NATURAL-FOA-300ML</t>
+          <t>WELL-EIMI-PERFECT-PRD-100ML</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Natural Volume putos #2 | 300ML</t>
+          <t>WELLA PROFESSIONALS EIMI Perfect Me losjonas #1 | 100ML</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10398,12 +10430,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-natural-volume-putos-2-300-ml</t>
+          <t>https://plaukuosena.lt/eimi-perfect-me-losjonas-1-100-ml</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9473f762-aafe-44c0-9acb-7e105a4f8d11.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c2858f89-5b77-4ca7-9214-22d5758e79fd.jpg</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10418,12 +10450,12 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>4064666211893</t>
+          <t>8005610587509</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10435,12 +10467,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>WELL-EIMI-NUTRICUR-CRM-150ML</t>
+          <t>WELL-EIMI-PERFECT-PRD-150ML</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Nutricurls Curl Shaper kremas #2 | 150ML</t>
+          <t>WELLA PROFESSIONALS EIMI Perfect Setting purškiamas plaukų losjonas #2 |150ML</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10450,7 +10482,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10460,17 +10492,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-nutricurls-curl-shaper-kremas-2-150-ml</t>
+          <t>https://plaukuosena.lt/eimi-perfect-setting-purskiamas-plauku-losjonas-2-150-ml</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/05eb6823-d484-4232-a92a-05a825b67fc3.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/831cbe0a-7ea7-4da3-9d64-a7da293455c7.jpg</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10485,7 +10517,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>4064666213415</t>
+          <t>8005610586052</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10497,12 +10529,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>WELL-EIMI-NUTRICUR-PRD-150ML</t>
+          <t>WELL-EIMI-ROOT-FOA-200ML</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Nutricurls Fresh Up purškalas #1 | 150ML</t>
+          <t>WELLA PROFESSIONALS EIMI Root Shoot purškiamos putos #2 | 200ML</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10512,7 +10544,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>23.50</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10522,12 +10554,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-nutricurls-fresh-up-purskalas-1-150-ml</t>
+          <t>https://plaukuosena.lt/eimi-root-shoot-purskiamos-putos-2-200-ml</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c849de07-4e68-4b6b-b4ed-a59ac843799e.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/20d544d5-a43b-420a-8011-c64e7eae68ee.jpg</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10542,12 +10574,12 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>4064666213439</t>
+          <t>4064666211978</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -10559,12 +10591,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>WELL-EIMI-NUTRICUR-FOA-200ML</t>
+          <t>WELL-EIMI-SHAPE-GEL-150ML</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Nutricurls Soft Twirl putos #2 | 200ML</t>
+          <t>WELLA PROFESSIONALS EIMI SHAPE ME 48 val plaukų formą išlaikantis gelis #2 | 150ML</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10574,7 +10606,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10584,17 +10616,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-nutricurls-soft-twirl-putos-2-200-ml</t>
+          <t>https://plaukuosena.lt/eimi-shape-me-48-val-plauku-forma-islaikantis-gelis-2-150-ml</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/01c8bbb3-0429-4f4c-9d1e-508b94ae4ba9.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cf24ed41-364c-4e1f-8323-ab8095dae01b.jpg</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų geliai</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10604,12 +10636,12 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>4064666212869</t>
+          <t>4064666228976</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10621,12 +10653,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>WELL-EIMI-OCEAN-PRD-150ML</t>
+          <t>WELL-EIMI-SHAPE-FOA-300ML</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Ocean Spritz purškalas su druska #2 | 150ML</t>
+          <t>WELLA PROFESSIONALS EIMI Shape Control putos #4 | 300ML</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10636,7 +10668,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10646,17 +10678,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-ocean-spritz-purskalas-su-druska-2-150-ml</t>
+          <t>https://plaukuosena.lt/eimi-shape-control-putos-4-300-ml</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ad6f5336-91da-4ba8-8a8d-12468afe45c7.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bbbd8914-6602-4103-878b-c10b2612242f.jpg</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10666,12 +10698,12 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>8005610534558</t>
+          <t>4064666211930</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10683,12 +10715,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>WELL-EIMI-PEARL-GEL-100ML</t>
+          <t>WELL-EIMI-SUGAR-PRD-150ML</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Pearl Styler gelis #3 | 100ML</t>
+          <t>WELLA PROFESSIONALS EIMI Sugar Lift purškalas apimčiai #3 | 150ML</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10708,17 +10740,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-pearl-styler-gelis-3-100-ml</t>
+          <t>https://plaukuosena.lt/eimi-sugar-lift-purskalas-apimciai-3-150-ml</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/144e8417-a5e5-4fb1-a96d-9ea6632bffa9.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0e33562e-8331-4101-a44a-730c2fbfb1af.jpg</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Plaukų geliai</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10728,12 +10760,12 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>8005610587745</t>
+          <t>8005610587776</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10745,12 +10777,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>WELL-EIMI-PERFECT-PRD-100ML</t>
+          <t>WELL-EIMI-SUPER-PRD-300ML</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Perfect Me losjonas #1 | 100ML</t>
+          <t>WELLA PROFESSIONALS EIMI Super Set lakas #4 | 300ML</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10760,7 +10792,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10770,12 +10802,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-perfect-me-losjonas-1-100-ml</t>
+          <t>https://plaukuosena.lt/eimi-super-set-lakas-4-300-ml</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/c2858f89-5b77-4ca7-9214-22d5758e79fd.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a4229f5f-7428-44ab-b006-da4faa1587a9.jpg</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10790,12 +10822,12 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>8005610587509</t>
+          <t>4064666214153</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -10807,12 +10839,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>WELL-EIMI-PERFECT-PRD-150ML</t>
+          <t>WELL-EIMI-THERMAL-PRD-150ML</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Perfect Setting purškiamas plaukų losjonas #2 |150ML</t>
+          <t>WELLA PROFESSIONALS EIMI Thermal Image purškalas nuo karščio #2 | 150ML</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10832,12 +10864,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-perfect-setting-purskiamas-plauku-losjonas-2-150-ml</t>
+          <t>https://plaukuosena.lt/eimi-thermal-image-purskalas-nuo-karscio-2-150-ml</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/831cbe0a-7ea7-4da3-9d64-a7da293455c7.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/27f63de3-6f4d-4932-9873-48b4fbc2f296.jpg</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -10857,7 +10889,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>8005610586052</t>
+          <t>8005610587417</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -10869,12 +10901,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>WELL-EIMI-ROOT-FOA-200ML</t>
+          <t>WELL-FUSION-INTENSE-MSK-150ML</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Root Shoot purškiamos putos #2 | 200ML</t>
+          <t>WELLA PROFESSIONALS FUSION Intense Repair atkurianti kaukė 150ML | 500ML</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10884,7 +10916,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>23.50</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10894,17 +10926,17 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-root-shoot-purskiamos-putos-2-200-ml</t>
+          <t>https://plaukuosena.lt/fusion-intense-repair-atkurianti-kauke</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/20d544d5-a43b-420a-8011-c64e7eae68ee.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/805619f3-b3f3-4e8b-ab3f-10a58c9866ba.jpg</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10914,12 +10946,12 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>4064666211978</t>
+          <t>4064666316208</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10931,12 +10963,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>WELL-EIMI-SHAPE-GEL-150ML</t>
+          <t>WELL-FUSION-ATSTATOM-SHA-250ML</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI SHAPE ME 48 val plaukų formą išlaikantis gelis #2 | 150ML</t>
+          <t>WELLA PROFESSIONALS FUSION atstatomasis šampūnas 250ML | 500ML | 1000ML</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10946,7 +10978,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10956,17 +10988,17 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-shape-me-48-val-plauku-forma-islaikantis-gelis-2-150-ml</t>
+          <t>https://plaukuosena.lt/loreal-professionnel-metal-detox-sampunas</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/cf24ed41-364c-4e1f-8323-ab8095dae01b.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ed6894bd-b132-4cb6-9a8a-0a4f96b07eac.jpg</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Plaukų geliai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10976,12 +11008,12 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>4064666228976</t>
+          <t>4064666582931</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10993,12 +11025,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>WELL-EIMI-SHAPE-FOA-300ML</t>
+          <t>WELL-FUSION-INTENSYV-CON-200ML</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Shape Control putos #4 | 300ML</t>
+          <t>WELLA PROFESSIONALS FUSION intensyviai plaukus atkuriantis kondicionierius 200ML | 1000ML</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11008,7 +11040,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11018,17 +11050,17 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-shape-control-putos-4-300-ml</t>
+          <t>https://plaukuosena.lt/fusion-intensyviai-plaukus-atkuriantis-kondicionierius</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bbbd8914-6602-4103-878b-c10b2612242f.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9f9fdb95-485e-476c-b6b2-486e49f19cfe.jpg</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11038,12 +11070,12 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>4064666211930</t>
+          <t>4064666315713</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11055,12 +11087,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>WELL-EIMI-SUGAR-PRD-150ML</t>
+          <t>WELL-INVIGO-BLONDE-SHA-300ML</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Sugar Lift purškalas apimčiai #3 | 150ML</t>
+          <t>WELLA PROFESSIONALS INVIGO BLONDE RECHARGE geltoną atspalvį neutralizuojantis šampūnas 300ML | 500ML | 1000ML</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11080,17 +11112,17 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-sugar-lift-purskalas-apimciai-3-150-ml</t>
+          <t>https://plaukuosena.lt/invigo-blonde-recharge-geltona-atspalvi-neutralizuojantis-sampunas</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0e33562e-8331-4101-a44a-730c2fbfb1af.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/61e0e49f-b917-4955-b58c-1a2dc44b9b47.jpg</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11100,12 +11132,12 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>8005610587776</t>
+          <t>4064666338873</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11117,12 +11149,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>WELL-EIMI-SUPER-PRD-300ML</t>
+          <t>WELL-INVIGO-BLONDE-CON-200ML</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Super Set lakas #4 | 300ML</t>
+          <t>WELLA PROFESSIONALS INVIGO BLONDE RECHARGE šaltą atspalvį suteikiantis kondicionierius, 200 ml</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11132,7 +11164,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11142,17 +11174,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-super-set-lakas-4-300-ml</t>
+          <t>https://plaukuosena.lt/invigo-blonde-recharge-salta-atspalvi-suteikiantis-kondicionierius-200-ml</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/a4229f5f-7428-44ab-b006-da4faa1587a9.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3dc901e9-409d-4ffd-808f-292e3328f27b.jpg</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Plaukų priežiūros priemonės</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11162,12 +11194,12 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>4064666214153</t>
+          <t>4064666339016</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11179,12 +11211,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>WELL-EIMI-THERMAL-PRD-150ML</t>
+          <t>WELL-INVIGO-SCALP-MSK-150ML</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS EIMI Thermal Image purškalas nuo karščio #2 | 150ML</t>
+          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminanti bekvapė kaukė jautriai galvos odai, 150 ml</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11194,7 +11226,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11204,17 +11236,17 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/eimi-thermal-image-purskalas-nuo-karscio-2-150-ml</t>
+          <t>https://plaukuosena.lt/invigo-scalp-balance-raminanti-bekvape-kauke-jautriai-galvos-odai-150-ml</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/27f63de3-6f4d-4932-9873-48b4fbc2f296.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2afb2854-6bd1-40cf-8cdc-974055d4e6d7.jpg</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11229,7 +11261,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>8005610587417</t>
+          <t>4064666585314</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11241,12 +11273,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>WELL-FUSION-INTENSE-MSK-NA</t>
+          <t>WELL-INVIGO-SCALP-SHA-300ML</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS FUSION Intense Repair atkurianti kaukė</t>
+          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminantis bekvapis šampūnas jautriai galvos odai, 300 ml |1000 ml</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11256,7 +11288,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11266,17 +11298,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/fusion-intense-repair-atkurianti-kauke</t>
+          <t>https://plaukuosena.lt/invigo-scalp-balance-raminantis-bekvapis-sampunas-jautriai-galvos-odai-300-ml</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/49ba0f2c-4336-4e46-8e4e-5997a332dd4b.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d760b01d-97b7-44c5-a495-8a1f29726f57.jpg</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11284,10 +11316,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr"/>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>4064666585284</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11299,12 +11335,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>WELL-INVIGO-BLONDE-SHA-300ML</t>
+          <t>WELL-INVIGO-SCALP-SER-6ML</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO BLONDE RECHARGE geltoną atspalvį neutralizuojantis šampūnas 300ML | 500ML | 1000ML</t>
+          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE serumas nuo plaukų slinkimo, 8x6ml</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11314,7 +11350,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>44.00</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11324,17 +11360,17 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-blonde-recharge-geltona-atspalvi-neutralizuojantis-sampunas</t>
+          <t>https://plaukuosena.lt/invigo-scalp-balance-serumas-nuo-plauku-slinkimo-8x6ml</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/61e0e49f-b917-4955-b58c-1a2dc44b9b47.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0ac06d9c-42c4-4ede-b4e6-ff007d17f540.jpg</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11344,12 +11380,12 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>6ml</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>4064666338873</t>
+          <t>4064666585369</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11361,12 +11397,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>WELL-INVIGO-BLONDE-CON-200ML</t>
+          <t>WELL-INVIGO-SCALP-SHA-300ML-496F</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO BLONDE RECHARGE šaltą atspalvį suteikiantis kondicionierius, 200 ml</t>
+          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE šampūnas nuo pleiskanų, 300 ml</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11376,7 +11412,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11386,17 +11422,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-blonde-recharge-salta-atspalvi-suteikiantis-kondicionierius-200-ml</t>
+          <t>https://plaukuosena.lt/invigo-scalp-balance-sampunas-nuo-pleiskanu-300-ml</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3dc901e9-409d-4ffd-808f-292e3328f27b.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8da87958-5134-4d18-936e-4df20ffc120b.jpg</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11406,12 +11442,12 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>4064666339016</t>
+          <t>4064666585246</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11423,12 +11459,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>WELL-INVIGO-SCALP-MSK-150ML</t>
+          <t>WELL-INVIGO-SUN-PRD-150ML</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminanti bekvapė kaukė jautriai galvos odai, 150 ml</t>
+          <t>WELLA PROFESSIONALS INVIGO SUN CARE UV purškalas apsaugantis nuo UV spindulių su provitaminu B5 | 150ML</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11438,7 +11474,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11448,17 +11484,17 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-scalp-balance-raminanti-bekvape-kauke-jautriai-galvos-odai-150-ml</t>
+          <t>https://plaukuosena.lt/invigo-sun-care-uv-purskalas-apsaugantis-nuo-uv-spinduliu-su-provitaminu-b5-150-ml</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/2afb2854-6bd1-40cf-8cdc-974055d4e6d7.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bea4f015-42e6-4f80-b369-3c74778fa577.jpg</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Plaukų kaukės</t>
+          <t>Plaukų purškikliai</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11473,7 +11509,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>4064666585314</t>
+          <t>4064666338996</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11485,12 +11521,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>WELL-INVIGO-SCALP-SHA-300ML</t>
+          <t>WELL-ULTIMATE-COLOR-CON-200ML</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE raminantis bekvapis šampūnas jautriai galvos odai, 300 ml |1000 ml</t>
+          <t>WELLA PROFESSIONALS ULTIMATE COLOR Conditioner – Drėkinantis dažytų plaukų kondicionierius STEP 2 | 200ML | 1000ML</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11500,7 +11536,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11510,17 +11546,17 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-scalp-balance-raminantis-bekvapis-sampunas-jautriai-galvos-odai-300-ml</t>
+          <t>https://plaukuosena.lt/ultimate-color-conditioner-drekinantis-dazytu-plauku-kondicionierius-step-2</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/d760b01d-97b7-44c5-a495-8a1f29726f57.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/88cc20f0-3fde-46a7-8e0c-cb6bdf1b9c19.jpg</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11530,12 +11566,12 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>4064666585284</t>
+          <t>4068359196528</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11547,12 +11583,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>WELL-INVIGO-SCALP-SER-6ML</t>
+          <t>WELL-ULTIMATE-COLOR-MSK-30ML</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE serumas nuo plaukų slinkimo, 8x6ml</t>
+          <t>WELLA PROFESSIONALS ULTIMATE COLOR Miracle Leave–in Mask – Miracle nenuplaunama kaukė STEP 2 | 30ML | 95ML</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11562,7 +11598,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>44.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11572,17 +11608,17 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-scalp-balance-serumas-nuo-plauku-slinkimo-8x6ml</t>
+          <t>https://plaukuosena.lt/ultimate-color-miracle-leave-in-mask-miracle-nenuplaunama-kauke-step-2</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0ac06d9c-42c4-4ede-b4e6-ff007d17f540.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6f764996-cf18-4ba3-a94a-1d565d3722ba.jpg</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Plaukų serumai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11592,12 +11628,12 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>6ml</t>
+          <t>30ml</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>4064666585369</t>
+          <t>4068359196573</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11609,12 +11645,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>WELL-INVIGO-SCALP-SHA-300ML-496F</t>
+          <t>WELL-ULTIMATE-COLOR-SHA-250ML</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO SCALP BALANCE šampūnas nuo pleiskanų, 300 ml</t>
+          <t>WELLA PROFESSIONALS ULTIMATE COLOR Shampoo – Dažytų plaukų šampūnas be sulfatų STEP 1 | 250ML | 1000ML</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11624,7 +11660,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11634,12 +11670,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-scalp-balance-sampunas-nuo-pleiskanu-300-ml</t>
+          <t>https://plaukuosena.lt/ultimate-color-shampoo-dazytu-plauku-sampunas-be-sulfatu-step-1</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/8da87958-5134-4d18-936e-4df20ffc120b.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9bcd73a1-e8a8-481d-9331-41e2eaf98c2b.jpg</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11654,12 +11690,12 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>4064666585246</t>
+          <t>4068359196474</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11671,12 +11707,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>WELL-INVIGO-SUN-PRD-150ML</t>
+          <t>WELL-ULTIMATE-COLOR-SPR-95ML</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS INVIGO SUN CARE UV purškalas apsaugantis nuo UV spindulių su provitaminu B5 | 150ML</t>
+          <t>WELLA PROFESSIONALS ULTIMATE COLOR Shine Spray – Blizgesio suteikiantis purškiklis STEP 3 | 95ML</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11686,7 +11722,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11696,12 +11732,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/invigo-sun-care-uv-purskalas-apsaugantis-nuo-uv-spinduliu-su-provitaminu-b5-150-ml</t>
+          <t>https://plaukuosena.lt/ultimate-color-shine-spray-blizgesio-suteikiantis-purskiklis-step-3-95-ml</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/bea4f015-42e6-4f80-b369-3c74778fa577.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/dde4d1d2-891e-49a2-8f98-89265d9ed025.jpg</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11716,12 +11752,12 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>150ml</t>
+          <t>95ml</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>4064666338996</t>
+          <t>4068359196610</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11733,12 +11769,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>WELL-ULTIMATE-COLOR-CON-200ML</t>
+          <t>WELL-ULTIMATE-REPAIR-SER-95ML</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE COLOR Conditioner – Drėkinantis dažytų plaukų kondicionierius STEP 2 | 200ML | 1000ML</t>
+          <t>WELLA PROFESSIONALS ULTIMATE REPAIR apsauginis 5in1 nenuplaunamas serumas pažeistiems plaukams STEP 4, 95 ml</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11748,7 +11784,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11758,17 +11794,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-color-conditioner-drekinantis-dazytu-plauku-kondicionierius-step-2</t>
+          <t>https://plaukuosena.lt/wella-professionals-ultimate-repair-apsauginis-5in1-nenuplaunamas-serumas-pazeistiems-plaukams-step-4-95-ml</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/88cc20f0-3fde-46a7-8e0c-cb6bdf1b9c19.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3da42b69-58b6-42c5-8649-840c08abae4e.png</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -11778,12 +11814,12 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>200ml</t>
+          <t>95ml</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>4068359196528</t>
+          <t>4068359081183</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -11795,12 +11831,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>WELL-ULTIMATE-COLOR-MSK-30ML</t>
+          <t>WELL-ULTIMATE-REPAIR-MSK-150ML</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE COLOR Miracle Leave–in Mask – Miracle nenuplaunama kaukė STEP 2 | 30ML | 95ML</t>
+          <t>WELLA PROFESSIONALS ULTIMATE REPAIR intensyvaus poveikio kaukė pažeistiems plaukams STEP 2 | 150ML | 500ML</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11810,7 +11846,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11820,12 +11856,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-color-miracle-leave-in-mask-miracle-nenuplaunama-kauke-step-2</t>
+          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-kauke-pazeistiems-plaukams-step-2</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/6f764996-cf18-4ba3-a94a-1d565d3722ba.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/40b6a8c2-185a-422b-9154-64aa5d5b8555.png</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -11840,12 +11876,12 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>30ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>4068359196573</t>
+          <t>4064666599533</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11857,12 +11893,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>WELL-ULTIMATE-COLOR-SHA-250ML</t>
+          <t>WELL-ULTIMATE-REPAIR-CON-200ML</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE COLOR Shampoo – Dažytų plaukų šampūnas be sulfatų STEP 1 | 250ML | 1000ML</t>
+          <t>WELLA PROFESSIONALS ULTIMATE REPAIR intensyvaus poveikio kondicionierius pažeistiems plaukams STEP 2 | 200ML | 500ML</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11872,7 +11908,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11882,17 +11918,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-color-shampoo-dazytu-plauku-sampunas-be-sulfatu-step-1</t>
+          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-kondicionierius-pazeistiems-plaukams-step-2-</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/9bcd73a1-e8a8-481d-9331-41e2eaf98c2b.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/3634c6f3-03f0-47ee-800b-94c7e7402d89.jpg</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -11902,12 +11938,12 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>250ml</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>4068359196474</t>
+          <t>4064666336169</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11919,12 +11955,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>WELL-ULTIMATE-COLOR-SPR-95ML</t>
+          <t>WELL-ULTIMATE-REPAIR-SHA-250ML</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE COLOR Shine Spray – Blizgesio suteikiantis purškiklis STEP 3 | 95ML</t>
+          <t>WELLA PROFESSIONALS ULTIMATE REPAIR intensyvaus poveikio šampūnas pažeistiems plaukams STEP 1 | 250ML | 1000ML</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11934,7 +11970,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>27.00</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11944,17 +11980,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-color-shine-spray-blizgesio-suteikiantis-purskiklis-step-3-95-ml</t>
+          <t>https://plaukuosena.lt/ultimate-repair-intensyvaus-poveikio-sampunas-pazeistiems-plaukams-step-1</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/dde4d1d2-891e-49a2-8f98-89265d9ed025.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/10b51403-3d69-4efa-8f65-c0c2bf55fa06.jpg</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Plaukų purškikliai</t>
+          <t>Plaukų šampūnai</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -11964,12 +12000,12 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>95ml</t>
+          <t>250ml</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>4068359196610</t>
+          <t>4064666579917</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11981,12 +12017,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>WELL-ULTIMATE-SMOOTH-CON-NA</t>
+          <t>WELL-ULTIMATE-REPAIR-SER-30ML</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE SMOOTH maitinantis kondicionierius su skvalanu ir omega-9</t>
+          <t>WELLA PROFESSIONALS ULTIMATE REPAIR naktinis plaukų serumas STEP 5 | 30ML | 95ML</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11996,7 +12032,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12006,17 +12042,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-smooth-maitinantis-kondicionierius-su-skvalanu-ir-omega-9</t>
+          <t>https://plaukuosena.lt/ultimate-repair-naktinis-plauku-serumas-step-5</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/485269d4-f20c-4f8d-a9be-437f4b0aa81e.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/0cda5ab2-52cf-4f06-8b6c-0f7b5b4bc2cf.jpg</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Plaukų kondicionieriai</t>
+          <t>Plaukų serumai</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12024,10 +12060,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr"/>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>30ml</t>
+        </is>
+      </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>4064666939780</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12039,12 +12079,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>WELL-ULTIMATE-SMOOTH-SER-NA</t>
+          <t>WELL-ULTIMATE-SMOOTH-PRD-30ML</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS ULTIMATE SMOOTH miracle aliejinis serumas skvalanu ir omega-9</t>
+          <t>WELLA PROFESSIONALS ULTIMATE SMOOTH glotninantis pienelis su skvalanu ir omega-9, 30ML | 100ML</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12054,7 +12094,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12064,17 +12104,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/ultimate-smooth-miracle-aliejinis-serumas-skvalanu-ir-omega-9</t>
+          <t>https://plaukuosena.lt/wella-professionals-ultimate-smooth-glotninantis-pienelis-su-skvalanu-ir-omega-9-30ml-or-100ml</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/518f9af2-8fc1-4590-932e-eaa87cdb3ac6.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/5d5179ff-c763-456e-b966-7f63d506d9e0.png</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Plaukų aliejai</t>
+          <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12082,10 +12122,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J194" t="inlineStr"/>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>30ml</t>
+        </is>
+      </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>4068359275797</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12097,12 +12141,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>WELL-FUSION-ATSTATOM-SHA-NA</t>
+          <t>WELL-ULTIMATE-SMOOTH-MSK-150ML</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Wella Professionals FUSION atstatomasis šampūnas</t>
+          <t>WELLA PROFESSIONALS ULTIMATE SMOOTH maitinanti kaukė su skvalanu ir omega-9 150ML | 500ML</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12112,7 +12156,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12122,17 +12166,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/loreal-professionnel-metal-detox-sampunas</t>
+          <t>https://plaukuosena.lt/ultimate-smooth-maitinanti-kauke-su-skvalanu-ir-omega-9</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/ed6894bd-b132-4cb6-9a8a-0a4f96b07eac.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f7774306-1953-481b-9f15-746af2bac04c.jpg</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kaukės</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12140,10 +12184,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J195" t="inlineStr"/>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>4064666906935</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -12155,12 +12203,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>WELL-ULTIMATE-SMOOTH-SHA-NA</t>
+          <t>WELL-ULTIMATE-SMOOTH-CON-200ML</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Wella Professionals Ultimate Smooth intensyviai maitinantis šampūnas</t>
+          <t>WELLA PROFESSIONALS ULTIMATE SMOOTH maitinantis kondicionierius su skvalanu ir omega-9 200ML | 1000ML</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12170,7 +12218,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>27.00</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12180,17 +12228,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://plaukuosena.lt/wella-professionals-ultimate-smooth-intensyviai-maitinantis-sampunas</t>
+          <t>https://plaukuosena.lt/ultimate-smooth-maitinantis-kondicionierius-su-skvalanu-ir-omega-9</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/90552437-c3c8-46c1-ad07-2d1cbaa18300.jpg</t>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/f46bce62-74c6-4e3a-a9d4-330837eaaafa.jpg</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Plaukų šampūnai</t>
+          <t>Plaukų kondicionieriai</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12198,10 +12246,14 @@
           <t>in_stock</t>
         </is>
       </c>
-      <c r="J196" t="inlineStr"/>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>1780508058948</t>
+          <t>4064666945286</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12213,52 +12265,176 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
+          <t>WELL-ULTIMATE-SMOOTH-SER-30ML</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>WELLA PROFESSIONALS ULTIMATE SMOOTH miracle aliejinis serumas skvalanu ir omega-9 30ML | 100ML</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>WELLA PROFESSIONALS</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>29.00</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/ultimate-smooth-miracle-aliejinis-serumas-skvalanu-ir-omega-9</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/14e39a40-f132-4b3f-a627-590f51ad1624.jpg</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Plaukų aliejai</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>30ml</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>4064666906096</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>WELL-ULTIMATE-SMOOTH-SHA-250ML</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>WELLA PROFESSIONALS Ultimate Smooth intensyviai maitinantis šampūnas 250ML | 1000ML</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>WELLA PROFESSIONALS</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://plaukuosena.lt/wella-professionals-ultimate-smooth-intensyviai-maitinantis-sampunas</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://cdn.zyrosite.com/cdn-ecommerce/store_01K8TJ7Z5JW7HSEJN7SFYG20CX/assets/90552437-c3c8-46c1-ad07-2d1cbaa18300.jpg</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Plaukų šampūnai</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>250ml</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>4064666906102</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
           <t>WELL-PRIEMONE-PRD-NA</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>Wella Professionals plaukų priežiūros priemonės</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C199" t="inlineStr">
         <is>
           <t>WELLA PROFESSIONALS</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr">
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>https://plaukuosena.lt/wella-professionals-plauku-prieziuros-priemones</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
+      <c r="G199" t="inlineStr">
         <is>
           <t>https://assets.zyrosite.com/cdn-cgi/image/format=auto,w=1440,h=756,fit=crop,f=jpeg/YCBIxgFD4BQDpKte/hf_20260119_182333_2c51bc08-8293-40f0-ab56-621de252197c-d6KqDxeTBHEvXb2r.png</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
+      <c r="H199" t="inlineStr">
         <is>
           <t>Plaukų priežiūros priemonės</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>in_stock</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>1780508058948</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>1780932909943</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
         <is>
           <t>CHECK_PRICE</t>
         </is>

--- a/products_snapshot.xlsx
+++ b/products_snapshot.xlsx
@@ -437,8 +437,8 @@
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
